--- a/Results_isofys/Numex_preliminar_base.xlsx
+++ b/Results_isofys/Numex_preliminar_base.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X88"/>
+  <dimension ref="A1:X89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,24 +466,24 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>[C]_bulk</t>
+          <t>[C_b]%</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>bulk_δ13C (‰ v.s.V-PDB)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>[N]</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>δ15N (‰ v.s.AIR)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>bulk_δ13C (‰ v.s.V-PDB)</t>
-        </is>
-      </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
           <t>[O]</t>
@@ -496,7 +496,7 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>[C]_cellulose</t>
+          <t>[C]%</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -580,10 +580,18 @@
           <t xml:space="preserve">CaNu </t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0.4480191586670095</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-29.44540300025425</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.01131803144642526</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-2.57685093780849</v>
+      </c>
       <c r="M2" t="n">
         <v>0.4561099936161824</v>
       </c>
@@ -658,18 +666,10 @@
           <t>BoN</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>0.4747990247551567</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.01856225432287257</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.013305785123967</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-35.49405837387074</v>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
         <v>0.4624420611028641</v>
       </c>
@@ -748,13 +748,13 @@
         <v>0.4535642729123336</v>
       </c>
       <c r="J4" t="n">
+        <v>-29.50438870250449</v>
+      </c>
+      <c r="K4" t="n">
         <v>0.01067420660361178</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>-5.350568638713384</v>
-      </c>
-      <c r="L4" t="n">
-        <v>-29.50438870250449</v>
       </c>
       <c r="M4" t="n">
         <v>0.4503179387003649</v>
@@ -830,10 +830,18 @@
           <t>BoN</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>0.4703588943604595</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-33.27795830155097</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.01595792251766325</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.951796643632774</v>
+      </c>
       <c r="M5" t="n">
         <v>0.4788720298243632</v>
       </c>
@@ -908,10 +916,18 @@
           <t>BoN</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>0.4791089801909185</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-35.15302568014238</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.01625830149845377</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.64928923988154</v>
+      </c>
       <c r="M6" t="n">
         <v>0.5005616886364418</v>
       </c>
@@ -990,13 +1006,13 @@
         <v>0.4334987385507555</v>
       </c>
       <c r="J7" t="n">
+        <v>-28.19817039868924</v>
+      </c>
+      <c r="K7" t="n">
         <v>0.01634705431165279</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>0.9995749569213093</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-28.19817039868924</v>
       </c>
       <c r="M7" t="n">
         <v>0.4581197888643381</v>
@@ -1072,10 +1088,18 @@
           <t>BoN</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>0.4736238651283425</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-33.97853292651919</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.01592004904401406</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6477887462981242</v>
+      </c>
       <c r="M8" t="n">
         <v>0.4885362330699199</v>
       </c>
@@ -1154,13 +1178,13 @@
         <v>0.4889607519265933</v>
       </c>
       <c r="J9" t="n">
+        <v>-33.1257470465601</v>
+      </c>
+      <c r="K9" t="n">
         <v>0.0172873891247033</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>2.347098255280073</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-33.1257470465601</v>
       </c>
       <c r="M9" t="n">
         <v>0.4860272812175658</v>
@@ -1240,13 +1264,13 @@
         <v>0.4802616006587936</v>
       </c>
       <c r="J10" t="n">
+        <v>-34.93158443363446</v>
+      </c>
+      <c r="K10" t="n">
         <v>0.01714220413234367</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>0.5011294765840217</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-34.93158443363446</v>
       </c>
       <c r="M10" t="n">
         <v>0.4918763401339801</v>
@@ -1326,13 +1350,13 @@
         <v>0.4444393638213121</v>
       </c>
       <c r="J11" t="n">
+        <v>-29.19528360770851</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.01112756890862974</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>-3.611430212521539</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-29.19528360770851</v>
       </c>
       <c r="M11" t="n">
         <v>0.4714892948451986</v>
@@ -1412,13 +1436,13 @@
         <v>0.4569353654032219</v>
       </c>
       <c r="J12" t="n">
+        <v>-28.05857454942655</v>
+      </c>
+      <c r="K12" t="n">
         <v>0.01105471422361042</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>-2.684652498564044</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-28.05857454942655</v>
       </c>
       <c r="M12" t="n">
         <v>0.4499437143818137</v>
@@ -1446,11 +1470,15 @@
       <c r="T12" t="n">
         <v>1.02</v>
       </c>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="n">
+        <v>0.47</v>
+      </c>
       <c r="V12" t="n">
         <v>30.4822848</v>
       </c>
-      <c r="W12" t="inlineStr"/>
+      <c r="W12" t="n">
+        <v>64.85592510638298</v>
+      </c>
       <c r="X12" t="n">
         <v>0.009764266316897927</v>
       </c>
@@ -1490,10 +1518,18 @@
           <t xml:space="preserve">CaNu </t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>0.4494289496537361</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-28.13697686244596</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.01350868739106595</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-1.555883514313919</v>
+      </c>
       <c r="M13" t="n">
         <v>0.4300892484348987</v>
       </c>
@@ -1572,13 +1608,13 @@
         <v>0.4401683597416842</v>
       </c>
       <c r="J14" t="n">
+        <v>-28.69672700319888</v>
+      </c>
+      <c r="K14" t="n">
         <v>0.01795424306294941</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>0.3588397472716827</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-28.69672700319888</v>
       </c>
       <c r="M14" t="n">
         <v>0.4655422870601318</v>
@@ -1658,13 +1694,13 @@
         <v>0.4783481572267765</v>
       </c>
       <c r="J15" t="n">
+        <v>-31.5863446838082</v>
+      </c>
+      <c r="K15" t="n">
         <v>0.01606408665284519</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>3.371450872359963</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-31.5863446838082</v>
       </c>
       <c r="M15" t="n">
         <v>0.4746627870720003</v>
@@ -1740,10 +1776,18 @@
           <t>BoN</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0.4759531727963179</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-31.00109077040427</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.0147237797659312</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.912112537018756</v>
+      </c>
       <c r="M16" t="n">
         <v>0.4940621309511004</v>
       </c>
@@ -1822,13 +1866,13 @@
         <v>0.4817456805940388</v>
       </c>
       <c r="J17" t="n">
+        <v>-33.37244614315496</v>
+      </c>
+      <c r="K17" t="n">
         <v>0.01696616985233793</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>2.667208448117539</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-33.37244614315496</v>
       </c>
       <c r="M17" t="n">
         <v>0.5011136054952446</v>
@@ -1908,13 +1952,13 @@
         <v>0.4838664892473051</v>
       </c>
       <c r="J18" t="n">
+        <v>-33.40205003474635</v>
+      </c>
+      <c r="K18" t="n">
         <v>0.01658409509546208</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>1.888273645546372</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-33.40205003474635</v>
       </c>
       <c r="M18" t="n">
         <v>0.4963837698476942</v>
@@ -1994,13 +2038,13 @@
         <v>0.4669242938608412</v>
       </c>
       <c r="J19" t="n">
+        <v>-34.80330090340514</v>
+      </c>
+      <c r="K19" t="n">
         <v>0.01750894024675033</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>2.528494031221304</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-34.80330090340514</v>
       </c>
       <c r="M19" t="n">
         <v>0.5036375701736119</v>
@@ -2080,13 +2124,13 @@
         <v>0.4895749462803182</v>
       </c>
       <c r="J20" t="n">
+        <v>-32.60541078255443</v>
+      </c>
+      <c r="K20" t="n">
         <v>0.01591887792445199</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>2.65862148190695</v>
-      </c>
-      <c r="L20" t="n">
-        <v>-32.60541078255443</v>
       </c>
       <c r="M20" t="n">
         <v>0.4917688436859104</v>
@@ -2166,13 +2210,13 @@
         <v>0.4359943655999698</v>
       </c>
       <c r="J21" t="n">
+        <v>-25.62561831941953</v>
+      </c>
+      <c r="K21" t="n">
         <v>0.01899419416005163</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>-0.9226306720275705</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-25.62561831941953</v>
       </c>
       <c r="M21" t="n">
         <v>0.4449089288078428</v>
@@ -2200,11 +2244,15 @@
       <c r="T21" t="n">
         <v>13.68</v>
       </c>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" t="n">
+        <v>3.6</v>
+      </c>
       <c r="V21" t="n">
         <v>250.358</v>
       </c>
-      <c r="W21" t="inlineStr"/>
+      <c r="W21" t="n">
+        <v>69.54388888888889</v>
+      </c>
       <c r="X21" t="n">
         <v>0.00796432222195019</v>
       </c>
@@ -2248,13 +2296,13 @@
         <v>0.4324951192830386</v>
       </c>
       <c r="J22" t="n">
+        <v>-28.63690021065772</v>
+      </c>
+      <c r="K22" t="n">
         <v>0.008156316641451286</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>-6.757897759908099</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-28.63690021065772</v>
       </c>
       <c r="M22" t="n">
         <v>0.483480457534494</v>
@@ -2330,10 +2378,18 @@
           <t xml:space="preserve">CaNu </t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>0.4417281155212168</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-29.33207475209763</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.01150822081138797</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-5.781273445212241</v>
+      </c>
       <c r="M23" t="n">
         <v>0.4622168521839491</v>
       </c>
@@ -2412,13 +2468,13 @@
         <v>0.4380163521066905</v>
       </c>
       <c r="J24" t="n">
+        <v>-28.15828587032847</v>
+      </c>
+      <c r="K24" t="n">
         <v>0.01415120455101524</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>-4.664066628374497</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-28.15828587032847</v>
       </c>
       <c r="M24" t="n">
         <v>0.4847141205268352</v>
@@ -2498,13 +2554,13 @@
         <v>0.485515136040803</v>
       </c>
       <c r="J25" t="n">
+        <v>-34.20135510771368</v>
+      </c>
+      <c r="K25" t="n">
         <v>0.01578012578456391</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>1.35475665748393</v>
-      </c>
-      <c r="L25" t="n">
-        <v>-34.20135510771368</v>
       </c>
       <c r="M25" t="n">
         <v>0.4758214431139169</v>
@@ -2662,13 +2718,13 @@
         <v>0.4430764110993517</v>
       </c>
       <c r="J27" t="n">
+        <v>-31.62823983771553</v>
+      </c>
+      <c r="K27" t="n">
         <v>0.0228773313734308</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>1.113991958644457</v>
-      </c>
-      <c r="L27" t="n">
-        <v>-31.62823983771553</v>
       </c>
       <c r="M27" t="n">
         <v>0.4763608511567354</v>
@@ -2748,13 +2804,13 @@
         <v>0.4305786489225114</v>
       </c>
       <c r="J28" t="n">
+        <v>-29.7636381368495</v>
+      </c>
+      <c r="K28" t="n">
         <v>0.01352956924716987</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>-3.519896611143021</v>
-      </c>
-      <c r="L28" t="n">
-        <v>-29.7636381368495</v>
       </c>
       <c r="M28" t="n">
         <v>0.4707473922168177</v>
@@ -2834,13 +2890,13 @@
         <v>0.4517693832372563</v>
       </c>
       <c r="J29" t="n">
+        <v>-30.20236794881798</v>
+      </c>
+      <c r="K29" t="n">
         <v>0.02178024030778102</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>0.3359563469270532</v>
-      </c>
-      <c r="L29" t="n">
-        <v>-30.20236794881798</v>
       </c>
       <c r="M29" t="n">
         <v>0.4845936354593983</v>
@@ -2916,10 +2972,18 @@
           <t>BoN</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0.4739082686060644</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-32.72161962878209</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.01623424234232612</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.567670286278381</v>
+      </c>
       <c r="M30" t="n">
         <v>0.4778210123702108</v>
       </c>
@@ -2998,13 +3062,13 @@
         <v>0.429254675747858</v>
       </c>
       <c r="J31" t="n">
+        <v>-29.51435983459468</v>
+      </c>
+      <c r="K31" t="n">
         <v>0.009989040422315363</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>-5.934095347501437</v>
-      </c>
-      <c r="L31" t="n">
-        <v>-29.51435983459468</v>
       </c>
       <c r="M31" t="n">
         <v>0.4329627058776646</v>
@@ -3084,13 +3148,13 @@
         <v>0.4438056861824569</v>
       </c>
       <c r="J32" t="n">
+        <v>-32.0869119138644</v>
+      </c>
+      <c r="K32" t="n">
         <v>0.02152283244993847</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>0.9881332567489945</v>
-      </c>
-      <c r="L32" t="n">
-        <v>-32.0869119138644</v>
       </c>
       <c r="M32" t="n">
         <v>0.480919380240197</v>
@@ -3170,13 +3234,13 @@
         <v>0.421878647151706</v>
       </c>
       <c r="J33" t="n">
+        <v>-31.79774908324881</v>
+      </c>
+      <c r="K33" t="n">
         <v>0.01918401501862635</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>1.056783457782883</v>
-      </c>
-      <c r="L33" t="n">
-        <v>-31.79774908324881</v>
       </c>
       <c r="M33" t="n">
         <v>0.4785854777850417</v>
@@ -3256,13 +3320,13 @@
         <v>0.4417061893645464</v>
       </c>
       <c r="J34" t="n">
+        <v>-30.56132870406492</v>
+      </c>
+      <c r="K34" t="n">
         <v>0.01006809824950208</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>-4.686950028719128</v>
-      </c>
-      <c r="L34" t="n">
-        <v>-30.56132870406492</v>
       </c>
       <c r="M34" t="n">
         <v>0.4630762594655187</v>
@@ -3342,13 +3406,13 @@
         <v>0.4845667277474769</v>
       </c>
       <c r="J35" t="n">
+        <v>-33.74742876997914</v>
+      </c>
+      <c r="K35" t="n">
         <v>0.02004011868920577</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>1.6321854912764</v>
-      </c>
-      <c r="L35" t="n">
-        <v>-33.74742876997914</v>
       </c>
       <c r="M35" t="n">
         <v>0.5091676818938174</v>
@@ -3428,13 +3492,13 @@
         <v>0.4845667277474769</v>
       </c>
       <c r="J36" t="n">
+        <v>-33.74742876997914</v>
+      </c>
+      <c r="K36" t="n">
         <v>0.02004011868920577</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>1.6321854912764</v>
-      </c>
-      <c r="L36" t="n">
-        <v>-33.74742876997914</v>
       </c>
       <c r="M36" t="n">
         <v>0.5091676818938174</v>
@@ -3514,13 +3578,13 @@
         <v>0.4331052844000723</v>
       </c>
       <c r="J37" t="n">
+        <v>-29.24513926815948</v>
+      </c>
+      <c r="K37" t="n">
         <v>0.009472638433886908</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>-6.895198161975876</v>
-      </c>
-      <c r="L37" t="n">
-        <v>-29.24513926815948</v>
       </c>
       <c r="M37" t="n">
         <v>0.4592339528713787</v>
@@ -3600,13 +3664,13 @@
         <v>0.4507897625160574</v>
       </c>
       <c r="J38" t="n">
+        <v>-29.83343606148085</v>
+      </c>
+      <c r="K38" t="n">
         <v>0.01388067173237143</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>-2.307076392877657</v>
-      </c>
-      <c r="L38" t="n">
-        <v>-29.83343606148085</v>
       </c>
       <c r="M38" t="n">
         <v>0.4186918006982133</v>
@@ -3686,13 +3750,13 @@
         <v>0.4471624937868003</v>
       </c>
       <c r="J39" t="n">
+        <v>-28.93603417336351</v>
+      </c>
+      <c r="K39" t="n">
         <v>0.01431275840268917</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>-3.016461803561172</v>
-      </c>
-      <c r="L39" t="n">
-        <v>-28.93603417336351</v>
       </c>
       <c r="M39" t="n">
         <v>0.4558734002579018</v>
@@ -3772,13 +3836,13 @@
         <v>0.4471452818348329</v>
       </c>
       <c r="J40" t="n">
+        <v>-32.98431380198174</v>
+      </c>
+      <c r="K40" t="n">
         <v>0.02005968317918831</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>0.4732567489948303</v>
-      </c>
-      <c r="L40" t="n">
-        <v>-32.98431380198174</v>
       </c>
       <c r="M40" t="n">
         <v>0.4586127095697982</v>
@@ -3858,13 +3922,13 @@
         <v>0.4536458203718088</v>
       </c>
       <c r="J41" t="n">
+        <v>-29.7636381368495</v>
+      </c>
+      <c r="K41" t="n">
         <v>0.01107610916352798</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>-5.602286042504308</v>
-      </c>
-      <c r="L41" t="n">
-        <v>-29.7636381368495</v>
       </c>
       <c r="M41" t="n">
         <v>0.417374549909015</v>
@@ -3944,13 +4008,13 @@
         <v>0.4808260459001235</v>
       </c>
       <c r="J42" t="n">
+        <v>-34.12241139680333</v>
+      </c>
+      <c r="K42" t="n">
         <v>0.01472643691728776</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>1.493471074380165</v>
-      </c>
-      <c r="L42" t="n">
-        <v>-34.12241139680333</v>
       </c>
       <c r="M42" t="n">
         <v>0.4964781411103646</v>
@@ -4030,13 +4094,13 @@
         <v>0.4808260459001235</v>
       </c>
       <c r="J43" t="n">
+        <v>-34.12241139680333</v>
+      </c>
+      <c r="K43" t="n">
         <v>0.01472643691728776</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>1.493471074380165</v>
-      </c>
-      <c r="L43" t="n">
-        <v>-34.12241139680333</v>
       </c>
       <c r="M43" t="n">
         <v>0.4964781411103646</v>
@@ -4116,13 +4180,13 @@
         <v>0.4808260459001235</v>
       </c>
       <c r="J44" t="n">
+        <v>-34.12241139680333</v>
+      </c>
+      <c r="K44" t="n">
         <v>0.01472643691728776</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>1.493471074380165</v>
-      </c>
-      <c r="L44" t="n">
-        <v>-34.12241139680333</v>
       </c>
       <c r="M44" t="n">
         <v>0.4991718420926589</v>
@@ -4202,13 +4266,13 @@
         <v>0.4808260459001235</v>
       </c>
       <c r="J45" t="n">
+        <v>-34.12241139680333</v>
+      </c>
+      <c r="K45" t="n">
         <v>0.01472643691728776</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>1.493471074380165</v>
-      </c>
-      <c r="L45" t="n">
-        <v>-34.12241139680333</v>
       </c>
       <c r="M45" t="n">
         <v>0.4991718420926589</v>
@@ -4288,13 +4352,13 @@
         <v>0.5529691100407402</v>
       </c>
       <c r="J46" t="n">
+        <v>-32.73102849200833</v>
+      </c>
+      <c r="K46" t="n">
         <v>0.01582245621491315</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>0.8319100091827362</v>
-      </c>
-      <c r="L46" t="n">
-        <v>-32.73102849200833</v>
       </c>
       <c r="M46" t="n">
         <v>0.4982342568100142</v>
@@ -4374,13 +4438,13 @@
         <v>0.4048034045403733</v>
       </c>
       <c r="J47" t="n">
+        <v>-31.56841304517438</v>
+      </c>
+      <c r="K47" t="n">
         <v>0.01465648710577767</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>1.388592762780011</v>
-      </c>
-      <c r="L47" t="n">
-        <v>-31.56841304517438</v>
       </c>
       <c r="M47" t="n">
         <v>0.4196534345190529</v>
@@ -4460,13 +4524,13 @@
         <v>0.4797466266795016</v>
       </c>
       <c r="J48" t="n">
+        <v>-33.3132383599722</v>
+      </c>
+      <c r="K48" t="n">
         <v>0.01517650481243265</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>-0.8219926538108359</v>
-      </c>
-      <c r="L48" t="n">
-        <v>-33.3132383599722</v>
       </c>
       <c r="M48" t="n">
         <v>0.5289352711727004</v>
@@ -4546,13 +4610,13 @@
         <v>0.4729159635931</v>
       </c>
       <c r="J49" t="n">
+        <v>-33.11587908269631</v>
+      </c>
+      <c r="K49" t="n">
         <v>0.01451437505025755</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>0.7465472910927453</v>
-      </c>
-      <c r="L49" t="n">
-        <v>-33.11587908269631</v>
       </c>
       <c r="M49" t="n">
         <v>0.5139792544276368</v>
@@ -4632,13 +4696,13 @@
         <v>0.4536846932360223</v>
       </c>
       <c r="J50" t="n">
+        <v>-29.28502379652025</v>
+      </c>
+      <c r="K50" t="n">
         <v>0.01222813895115179</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>-2.982136703044228</v>
-      </c>
-      <c r="L50" t="n">
-        <v>-29.28502379652025</v>
       </c>
       <c r="M50" t="n">
         <v>0.4677412926709881</v>
@@ -4718,13 +4782,13 @@
         <v>0.4214334482112401</v>
       </c>
       <c r="J51" t="n">
+        <v>-30.13257002418663</v>
+      </c>
+      <c r="K51" t="n">
         <v>0.009039637607102099</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>-3.657197013210799</v>
-      </c>
-      <c r="L51" t="n">
-        <v>-30.13257002418663</v>
       </c>
       <c r="M51" t="n">
         <v>0.4788257204164694</v>
@@ -4804,13 +4868,13 @@
         <v>0.4321688821497172</v>
       </c>
       <c r="J52" t="n">
+        <v>-28.92606304127331</v>
+      </c>
+      <c r="K52" t="n">
         <v>0.01563420287363932</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
         <v>-2.066800689259047</v>
-      </c>
-      <c r="L52" t="n">
-        <v>-28.92606304127331</v>
       </c>
       <c r="M52" t="n">
         <v>0.4621982117777756</v>
@@ -4890,13 +4954,13 @@
         <v>0.4445023039071019</v>
       </c>
       <c r="J53" t="n">
+        <v>-27.87909417180308</v>
+      </c>
+      <c r="K53" t="n">
         <v>0.01413962817933663</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>-2.341401493394601</v>
-      </c>
-      <c r="L53" t="n">
-        <v>-27.87909417180308</v>
       </c>
       <c r="M53" t="n">
         <v>0.4708225103905904</v>
@@ -4976,13 +5040,13 @@
         <v>0.4179005456062779</v>
       </c>
       <c r="J54" t="n">
+        <v>-32.30627681984863</v>
+      </c>
+      <c r="K54" t="n">
         <v>0.0253654953216571</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
         <v>2.212395175186674</v>
-      </c>
-      <c r="L54" t="n">
-        <v>-32.30627681984863</v>
       </c>
       <c r="M54" t="n">
         <v>0.4824778018586999</v>
@@ -5062,13 +5126,13 @@
         <v>0.4187719245138669</v>
       </c>
       <c r="J55" t="n">
+        <v>-32.74500663181713</v>
+      </c>
+      <c r="K55" t="n">
         <v>0.02436191095400565</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>2.486995979322228</v>
-      </c>
-      <c r="L55" t="n">
-        <v>-32.74500663181713</v>
       </c>
       <c r="M55" t="n">
         <v>0.4223801490441385</v>
@@ -5148,13 +5212,13 @@
         <v>0.4434932712690353</v>
       </c>
       <c r="J56" t="n">
+        <v>-27.41045096356402</v>
+      </c>
+      <c r="K56" t="n">
         <v>0.01297934247566342</v>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" t="n">
         <v>-4.641183228029869</v>
-      </c>
-      <c r="L56" t="n">
-        <v>-27.41045096356402</v>
       </c>
       <c r="M56" t="n">
         <v>0.4352714140691329</v>
@@ -5234,13 +5298,13 @@
         <v>0.475435880291702</v>
       </c>
       <c r="J57" t="n">
+        <v>-34.05333564975677</v>
+      </c>
+      <c r="K57" t="n">
         <v>0.01527186857901122</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>0.7892286501377408</v>
-      </c>
-      <c r="L57" t="n">
-        <v>-34.05333564975677</v>
       </c>
       <c r="M57" t="n">
         <v>0.4432341526244388</v>
@@ -5320,13 +5384,13 @@
         <v>0.4445848501254013</v>
       </c>
       <c r="J58" t="n">
+        <v>-28.81638058828119</v>
+      </c>
+      <c r="K58" t="n">
         <v>0.01051460239352423</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>-1.769316484778863</v>
-      </c>
-      <c r="L58" t="n">
-        <v>-28.81638058828119</v>
       </c>
       <c r="M58" t="n">
         <v>0.46051385322432</v>
@@ -5406,13 +5470,13 @@
         <v>0.481014448560129</v>
       </c>
       <c r="J59" t="n">
+        <v>-33.16521890201528</v>
+      </c>
+      <c r="K59" t="n">
         <v>0.01581848657330364</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
         <v>0.1810192837465561</v>
-      </c>
-      <c r="L59" t="n">
-        <v>-33.16521890201528</v>
       </c>
       <c r="M59" t="n">
         <v>0.5731168598412615</v>
@@ -5492,13 +5556,13 @@
         <v>0.4665501089872499</v>
       </c>
       <c r="J60" t="n">
+        <v>-30.39181945853164</v>
+      </c>
+      <c r="K60" t="n">
         <v>0.01127099121776865</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>-3.451246410109133</v>
-      </c>
-      <c r="L60" t="n">
-        <v>-30.39181945853164</v>
       </c>
       <c r="M60" t="n">
         <v>0.4542331205187284</v>
@@ -5574,18 +5638,10 @@
           <t xml:space="preserve">CaNu </t>
         </is>
       </c>
-      <c r="I61" t="n">
-        <v>0.4322698024851607</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0.01534990713384907</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0.1528891441700169</v>
-      </c>
-      <c r="L61" t="n">
-        <v>-30.63112662869626</v>
-      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="n">
         <v>0.4466815926655569</v>
       </c>
@@ -5664,13 +5720,13 @@
         <v>0.4492421090010831</v>
       </c>
       <c r="J62" t="n">
+        <v>-27.85915190762269</v>
+      </c>
+      <c r="K62" t="n">
         <v>0.01584648292225062</v>
       </c>
-      <c r="K62" t="n">
+      <c r="L62" t="n">
         <v>-1.311648477886272</v>
-      </c>
-      <c r="L62" t="n">
-        <v>-27.85915190762269</v>
       </c>
       <c r="M62" t="n">
         <v>0.4468653827732803</v>
@@ -5750,13 +5806,13 @@
         <v>0.4908873569293199</v>
       </c>
       <c r="J63" t="n">
+        <v>-31.99093120222376</v>
+      </c>
+      <c r="K63" t="n">
         <v>0.0137309032598377</v>
       </c>
-      <c r="K63" t="n">
+      <c r="L63" t="n">
         <v>-0.1284205693296606</v>
-      </c>
-      <c r="L63" t="n">
-        <v>-31.99093120222376</v>
       </c>
       <c r="M63" t="n">
         <v>0.4734673022808513</v>
@@ -5832,10 +5888,18 @@
           <t>BoN</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
+      <c r="I64" t="n">
+        <v>0.4743131565541081</v>
+      </c>
+      <c r="J64" t="n">
+        <v>-33.55612763793541</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.01494123471994327</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1.597996051332675</v>
+      </c>
       <c r="M64" t="n">
         <v>0.4698293457032828</v>
       </c>
@@ -5880,85 +5944,85 @@
         <v>63</v>
       </c>
       <c r="B65" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C65" t="n">
-        <v>1313</v>
+        <v>5785</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Weinmania  loxensis</t>
+          <t>Pouteria torta</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weinmania </t>
+          <t>Pouteria</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>loxensis</t>
+          <t>torta</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">CaNu </t>
+          <t>BoN</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.4576038674208016</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0.01211240017104252</v>
-      </c>
+        <v>0.4786645153959252</v>
+      </c>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="n">
-        <v>-4.629741527857554</v>
-      </c>
-      <c r="L65" t="n">
-        <v>-29.25511040024967</v>
+        <v>0.01461355893199637</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>p11-5785</t>
+        </is>
       </c>
       <c r="M65" t="n">
-        <v>0.4055645127451206</v>
+        <v>0.4698293457032828</v>
       </c>
       <c r="N65" t="n">
-        <v>26.35363820829188</v>
+        <v>28.70949264114439</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>43.59%</t>
+          <t>41.42%</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>-28.27</v>
+        <v>-30.74</v>
       </c>
       <c r="Q65" t="n">
-        <v>6</v>
+        <v>10.12</v>
       </c>
       <c r="R65" t="n">
-        <v>37.22</v>
+        <v>29.13</v>
       </c>
       <c r="S65" t="n">
-        <v>1.638</v>
+        <v>1.206</v>
       </c>
       <c r="T65" t="n">
-        <v>1.17</v>
+        <v>25.15</v>
       </c>
       <c r="U65" t="n">
-        <v>0.53</v>
+        <v>18.2</v>
       </c>
       <c r="V65" t="n">
-        <v>37.5134951</v>
+        <v>1296.304</v>
       </c>
       <c r="W65" t="n">
-        <v>70.78017943396226</v>
+        <v>71.22549450549451</v>
       </c>
       <c r="X65" t="n">
-        <v>0.00890818231879471</v>
+        <v>0.01583676856674615</v>
       </c>
     </row>
     <row r="66">
@@ -5969,7 +6033,7 @@
         <v>12</v>
       </c>
       <c r="C66" t="n">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5997,54 +6061,54 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4321746849999652</v>
+        <v>0.4576038674208016</v>
       </c>
       <c r="J66" t="n">
-        <v>0.00923649413828698</v>
+        <v>-29.25511040024967</v>
       </c>
       <c r="K66" t="n">
-        <v>-6.620597357840322</v>
+        <v>0.01211240017104252</v>
       </c>
       <c r="L66" t="n">
-        <v>-30.12259889209644</v>
+        <v>-4.629741527857554</v>
       </c>
       <c r="M66" t="n">
-        <v>0.4173060299235028</v>
+        <v>0.4055645127451206</v>
       </c>
       <c r="N66" t="n">
-        <v>24.93032382702751</v>
+        <v>26.35363820829188</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>42.13%</t>
+          <t>43.59%</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>-29.59</v>
+        <v>-28.27</v>
       </c>
       <c r="Q66" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R66" t="n">
-        <v>29.73</v>
+        <v>37.22</v>
       </c>
       <c r="S66" t="n">
-        <v>1.488</v>
+        <v>1.638</v>
       </c>
       <c r="T66" t="n">
-        <v>0.96</v>
+        <v>1.17</v>
       </c>
       <c r="U66" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="V66" t="n">
-        <v>32.1353494</v>
+        <v>37.5134951</v>
       </c>
       <c r="W66" t="n">
-        <v>73.034885</v>
+        <v>70.78017943396226</v>
       </c>
       <c r="X66" t="n">
-        <v>0.01399756241761017</v>
+        <v>0.00890818231879471</v>
       </c>
     </row>
     <row r="67">
@@ -6055,7 +6119,7 @@
         <v>12</v>
       </c>
       <c r="C67" t="n">
-        <v>19013</v>
+        <v>1318</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6064,17 +6128,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hedyosmun  purpurascens</t>
+          <t>Weinmania  loxensis</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedyosmun </t>
+          <t xml:space="preserve">Weinmania </t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>purpurascens</t>
+          <t>loxensis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6083,54 +6147,54 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.4363440656798133</v>
+        <v>0.4321746849999652</v>
       </c>
       <c r="J67" t="n">
-        <v>0.01476206022289017</v>
+        <v>-30.12259889209644</v>
       </c>
       <c r="K67" t="n">
-        <v>-1.586249282021827</v>
+        <v>0.00923649413828698</v>
       </c>
       <c r="L67" t="n">
-        <v>-30.54138643988453</v>
+        <v>-6.620597357840322</v>
       </c>
       <c r="M67" t="n">
-        <v>0.4537285991426437</v>
+        <v>0.4173060299235028</v>
       </c>
       <c r="N67" t="n">
-        <v>27.22369617956494</v>
+        <v>24.93032382702751</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>43.36%</t>
+          <t>42.13%</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>-28.78</v>
+        <v>-29.59</v>
       </c>
       <c r="Q67" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R67" t="n">
-        <v>25.65</v>
+        <v>29.73</v>
       </c>
       <c r="S67" t="n">
-        <v>2.62</v>
+        <v>1.488</v>
       </c>
       <c r="T67" t="n">
-        <v>22.56</v>
+        <v>0.96</v>
       </c>
       <c r="U67" t="n">
-        <v>5.28</v>
+        <v>0.44</v>
       </c>
       <c r="V67" t="n">
-        <v>449.0825564</v>
+        <v>32.1353494</v>
       </c>
       <c r="W67" t="n">
-        <v>85.05351446969696</v>
+        <v>73.034885</v>
       </c>
       <c r="X67" t="n">
-        <v>0.001963495408493621</v>
+        <v>0.01399756241761017</v>
       </c>
     </row>
     <row r="68">
@@ -6141,7 +6205,7 @@
         <v>12</v>
       </c>
       <c r="C68" t="n">
-        <v>19014</v>
+        <v>19013</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6169,48 +6233,54 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.4423523651821347</v>
+        <v>0.4363440656798133</v>
       </c>
       <c r="J68" t="n">
-        <v>0.01582594724194683</v>
+        <v>-30.54138643988453</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.494715680643309</v>
+        <v>0.01476206022289017</v>
       </c>
       <c r="L68" t="n">
-        <v>-30.70092455332761</v>
+        <v>-1.586249282021827</v>
       </c>
       <c r="M68" t="n">
-        <v>0.4516529314857435</v>
+        <v>0.4537285991426437</v>
       </c>
       <c r="N68" t="n">
-        <v>27.38533973085717</v>
-      </c>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
+        <v>27.22369617956494</v>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>43.36%</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>-28.78</v>
+      </c>
       <c r="Q68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R68" t="n">
-        <v>25.44</v>
+        <v>25.65</v>
       </c>
       <c r="S68" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="T68" t="n">
-        <v>14.31</v>
+        <v>22.56</v>
       </c>
       <c r="U68" t="n">
-        <v>3.33</v>
+        <v>5.28</v>
       </c>
       <c r="V68" t="n">
-        <v>319.0305596</v>
+        <v>449.0825564</v>
       </c>
       <c r="W68" t="n">
-        <v>95.80497285285286</v>
+        <v>85.05351446969696</v>
       </c>
       <c r="X68" t="n">
-        <v>0.002922466566001904</v>
+        <v>0.001963495408493621</v>
       </c>
     </row>
     <row r="69">
@@ -6221,82 +6291,76 @@
         <v>12</v>
       </c>
       <c r="C69" t="n">
-        <v>2176</v>
+        <v>19014</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Clarisia  racemosa</t>
+          <t>Hedyosmun  purpurascens</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clarisia </t>
+          <t xml:space="preserve">Hedyosmun </t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>racemosa</t>
+          <t>purpurascens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>BoN</t>
+          <t xml:space="preserve">CaNu </t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.4291508403147593</v>
+        <v>0.4423523651821347</v>
       </c>
       <c r="J69" t="n">
-        <v>0.01780456902283986</v>
+        <v>-30.70092455332761</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.2475703618609997</v>
+        <v>0.01582594724194683</v>
       </c>
       <c r="L69" t="n">
-        <v>-32.61538191464461</v>
+        <v>-1.494715680643309</v>
       </c>
       <c r="M69" t="n">
-        <v>0.3900741436042789</v>
+        <v>0.4516529314857435</v>
       </c>
       <c r="N69" t="n">
-        <v>26.75093380147758</v>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>39.84%</t>
-        </is>
-      </c>
-      <c r="P69" t="n">
-        <v>-31.09</v>
-      </c>
+        <v>27.38533973085717</v>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="n">
-        <v>10.5</v>
+        <v>6</v>
       </c>
       <c r="R69" t="n">
-        <v>32.14</v>
+        <v>25.44</v>
       </c>
       <c r="S69" t="n">
-        <v>1.136</v>
+        <v>2.41</v>
       </c>
       <c r="T69" t="n">
-        <v>15.52</v>
+        <v>14.31</v>
       </c>
       <c r="U69" t="n">
-        <v>6.82</v>
+        <v>3.33</v>
       </c>
       <c r="V69" t="n">
-        <v>701.997</v>
+        <v>319.0305596</v>
       </c>
       <c r="W69" t="n">
-        <v>102.9321114369501</v>
+        <v>95.80497285285286</v>
       </c>
       <c r="X69" t="n">
-        <v>0.09820065714814662</v>
+        <v>0.002922466566001904</v>
       </c>
     </row>
     <row r="70">
@@ -6307,7 +6371,7 @@
         <v>12</v>
       </c>
       <c r="C70" t="n">
-        <v>6007</v>
+        <v>2176</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6316,17 +6380,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Pouteria torta</t>
+          <t>Clarisia  racemosa</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pouteria</t>
+          <t xml:space="preserve">Clarisia </t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>torta</t>
+          <t>racemosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6334,47 +6398,55 @@
           <t>BoN</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
+      <c r="I70" t="n">
+        <v>0.4291508403147593</v>
+      </c>
+      <c r="J70" t="n">
+        <v>-32.61538191464461</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.01780456902283986</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-0.2475703618609997</v>
+      </c>
       <c r="M70" t="n">
-        <v>0.4862382280731273</v>
+        <v>0.3900741436042789</v>
       </c>
       <c r="N70" t="n">
-        <v>32.48040521908751</v>
+        <v>26.75093380147758</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>43.43%</t>
+          <t>39.84%</t>
         </is>
       </c>
       <c r="P70" t="n">
-        <v>-31.62</v>
+        <v>-31.09</v>
       </c>
       <c r="Q70" t="n">
-        <v>13.4</v>
+        <v>10.5</v>
       </c>
       <c r="R70" t="n">
-        <v>24.84</v>
+        <v>32.14</v>
       </c>
       <c r="S70" t="n">
-        <v>1.068</v>
+        <v>1.136</v>
       </c>
       <c r="T70" t="n">
-        <v>61.26</v>
+        <v>15.52</v>
       </c>
       <c r="U70" t="n">
-        <v>28.89</v>
+        <v>6.82</v>
       </c>
       <c r="V70" t="n">
-        <v>2273.071</v>
+        <v>701.997</v>
       </c>
       <c r="W70" t="n">
-        <v>78.68020076150917</v>
+        <v>102.9321114369501</v>
       </c>
       <c r="X70" t="n">
-        <v>0.04776128753733373</v>
+        <v>0.09820065714814662</v>
       </c>
     </row>
     <row r="71">
@@ -6385,7 +6457,7 @@
         <v>12</v>
       </c>
       <c r="C71" t="n">
-        <v>7626</v>
+        <v>6007</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6412,47 +6484,55 @@
           <t>BoN</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+      <c r="I71" t="n">
+        <v>0.4302949477821517</v>
+      </c>
+      <c r="J71" t="n">
+        <v>-34.5142664632596</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.01300822023579649</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1.193652517275419</v>
+      </c>
       <c r="M71" t="n">
-        <v>0.4713228058972143</v>
+        <v>0.4862382280731273</v>
       </c>
       <c r="N71" t="n">
-        <v>27.08545670900341</v>
+        <v>32.48040521908751</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>43.72%</t>
+          <t>43.43%</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-31.19</v>
+        <v>-31.62</v>
       </c>
       <c r="Q71" t="n">
-        <v>10.4</v>
+        <v>13.4</v>
       </c>
       <c r="R71" t="n">
-        <v>28.7</v>
+        <v>24.84</v>
       </c>
       <c r="S71" t="n">
-        <v>1.146</v>
+        <v>1.068</v>
       </c>
       <c r="T71" t="n">
-        <v>34.26</v>
+        <v>61.26</v>
       </c>
       <c r="U71" t="n">
-        <v>16.66</v>
+        <v>28.89</v>
       </c>
       <c r="V71" t="n">
-        <v>1240.024</v>
+        <v>2273.071</v>
       </c>
       <c r="W71" t="n">
-        <v>74.43121248499399</v>
+        <v>78.68020076150917</v>
       </c>
       <c r="X71" t="n">
-        <v>0.02613000840067389</v>
+        <v>0.04776128753733373</v>
       </c>
     </row>
     <row r="72">
@@ -6460,29 +6540,29 @@
         <v>70</v>
       </c>
       <c r="B72" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C72" t="n">
-        <v>1840</v>
+        <v>7626</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Clarisia  racemosa</t>
+          <t>Pouteria torta</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clarisia </t>
+          <t>Pouteria</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>racemosa</t>
+          <t>torta</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6491,54 +6571,54 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.4359243347156534</v>
+        <v>0.4752627246598828</v>
       </c>
       <c r="J72" t="n">
-        <v>0.01599162114519767</v>
+        <v>-33.76217899822018</v>
       </c>
       <c r="K72" t="n">
-        <v>0.01558874210223982</v>
+        <v>0.01671240334170168</v>
       </c>
       <c r="L72" t="n">
-        <v>-32.12679644222517</v>
+        <v>1.77995064165844</v>
       </c>
       <c r="M72" t="n">
-        <v>0.4797153685801971</v>
+        <v>0.4713228058972143</v>
       </c>
       <c r="N72" t="n">
-        <v>26.99009445970414</v>
+        <v>27.08545670900341</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>35.73%</t>
+          <t>43.72%</t>
         </is>
       </c>
       <c r="P72" t="n">
-        <v>-29.19</v>
+        <v>-31.19</v>
       </c>
       <c r="Q72" t="n">
-        <v>13</v>
+        <v>10.4</v>
       </c>
       <c r="R72" t="n">
-        <v>41.7</v>
+        <v>28.7</v>
       </c>
       <c r="S72" t="n">
-        <v>1.449</v>
+        <v>1.146</v>
       </c>
       <c r="T72" t="n">
-        <v>18.52</v>
+        <v>34.26</v>
       </c>
       <c r="U72" t="n">
-        <v>8.31</v>
+        <v>16.66</v>
       </c>
       <c r="V72" t="n">
-        <v>779.79</v>
+        <v>1240.024</v>
       </c>
       <c r="W72" t="n">
-        <v>93.83754512635377</v>
+        <v>74.43121248499399</v>
       </c>
       <c r="X72" t="n">
-        <v>0.02474495088554085</v>
+        <v>0.02613000840067389</v>
       </c>
     </row>
     <row r="73">
@@ -6549,7 +6629,7 @@
         <v>13</v>
       </c>
       <c r="C73" t="n">
-        <v>19015</v>
+        <v>1840</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6558,73 +6638,73 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Hedyosmun  purpurascens</t>
+          <t>Clarisia  racemosa</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedyosmun </t>
+          <t xml:space="preserve">Clarisia </t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>purpurascens</t>
+          <t>racemosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">CaNu </t>
+          <t>BoN</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.4291297171025792</v>
+        <v>0.4359243347156534</v>
       </c>
       <c r="J73" t="n">
-        <v>0.01429440337088152</v>
+        <v>-32.12679644222517</v>
       </c>
       <c r="K73" t="n">
-        <v>-2.707535898908673</v>
+        <v>0.01599162114519767</v>
       </c>
       <c r="L73" t="n">
-        <v>-29.71378247639853</v>
+        <v>0.01558874210223982</v>
       </c>
       <c r="M73" t="n">
-        <v>0.4331422109545765</v>
+        <v>0.4797153685801971</v>
       </c>
       <c r="N73" t="n">
-        <v>27.83276225125201</v>
+        <v>26.99009445970414</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>45.00%</t>
+          <t>35.73%</t>
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-28.06</v>
+        <v>-29.19</v>
       </c>
       <c r="Q73" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="R73" t="n">
-        <v>26.91</v>
+        <v>41.7</v>
       </c>
       <c r="S73" t="n">
-        <v>2.75</v>
+        <v>1.449</v>
       </c>
       <c r="T73" t="n">
-        <v>27.55</v>
+        <v>18.52</v>
       </c>
       <c r="U73" t="n">
-        <v>7.06</v>
+        <v>8.31</v>
       </c>
       <c r="V73" t="n">
-        <v>569.7283394</v>
+        <v>779.79</v>
       </c>
       <c r="W73" t="n">
-        <v>80.69806507082153</v>
+        <v>93.83754512635377</v>
       </c>
       <c r="X73" t="n">
-        <v>0.003117245310524472</v>
+        <v>0.02474495088554085</v>
       </c>
     </row>
     <row r="74">
@@ -6635,7 +6715,7 @@
         <v>13</v>
       </c>
       <c r="C74" t="n">
-        <v>19016</v>
+        <v>19015</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6663,54 +6743,54 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.4448181824792202</v>
+        <v>0.4291297171025792</v>
       </c>
       <c r="J74" t="n">
-        <v>0.01680647189877027</v>
+        <v>-29.71378247639853</v>
       </c>
       <c r="K74" t="n">
-        <v>-1.986708788052843</v>
+        <v>0.01429440337088152</v>
       </c>
       <c r="L74" t="n">
-        <v>-26.93183662323477</v>
+        <v>-2.707535898908673</v>
       </c>
       <c r="M74" t="n">
-        <v>0.4451892832493313</v>
+        <v>0.4331422109545765</v>
       </c>
       <c r="N74" t="n">
-        <v>27.19654611636838</v>
+        <v>27.83276225125201</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>44.46%</t>
+          <t>45.00%</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>-24.53</v>
+        <v>-28.06</v>
       </c>
       <c r="Q74" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R74" t="n">
-        <v>28</v>
+        <v>26.91</v>
       </c>
       <c r="S74" t="n">
-        <v>3.34</v>
+        <v>2.75</v>
       </c>
       <c r="T74" t="n">
-        <v>20.5</v>
+        <v>27.55</v>
       </c>
       <c r="U74" t="n">
-        <v>5.26</v>
+        <v>7.06</v>
       </c>
       <c r="V74" t="n">
-        <v>305.8202715</v>
+        <v>569.7283394</v>
       </c>
       <c r="W74" t="n">
-        <v>58.14073602661597</v>
+        <v>80.69806507082153</v>
       </c>
       <c r="X74" t="n">
-        <v>0.002733971006786517</v>
+        <v>0.003117245310524472</v>
       </c>
     </row>
     <row r="75">
@@ -6721,7 +6801,7 @@
         <v>13</v>
       </c>
       <c r="C75" t="n">
-        <v>7540</v>
+        <v>19016</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6730,65 +6810,73 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Pouteria torta</t>
+          <t>Hedyosmun  purpurascens</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pouteria</t>
+          <t xml:space="preserve">Hedyosmun </t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>torta</t>
+          <t>purpurascens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>BoN</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
+          <t xml:space="preserve">CaNu </t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>0.4448181824792202</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-26.93183662323477</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.01680647189877027</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-1.986708788052843</v>
+      </c>
       <c r="M75" t="n">
-        <v>0.4526713223191351</v>
+        <v>0.4451892832493313</v>
       </c>
       <c r="N75" t="n">
-        <v>28.30911682693158</v>
+        <v>27.19654611636838</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>43.19%</t>
+          <t>44.46%</t>
         </is>
       </c>
       <c r="P75" t="n">
-        <v>-30.13</v>
+        <v>-24.53</v>
       </c>
       <c r="Q75" t="n">
-        <v>16.7</v>
+        <v>3</v>
       </c>
       <c r="R75" t="n">
-        <v>36.26</v>
+        <v>28</v>
       </c>
       <c r="S75" t="n">
-        <v>1.58</v>
+        <v>3.34</v>
       </c>
       <c r="T75" t="n">
-        <v>35.12</v>
+        <v>20.5</v>
       </c>
       <c r="U75" t="n">
-        <v>19.32</v>
+        <v>5.26</v>
       </c>
       <c r="V75" t="n">
-        <v>1135.959</v>
+        <v>305.8202715</v>
       </c>
       <c r="W75" t="n">
-        <v>58.797049689441</v>
+        <v>58.14073602661597</v>
       </c>
       <c r="X75" t="n">
-        <v>0.1121021103925018</v>
+        <v>0.002733971006786517</v>
       </c>
     </row>
     <row r="76">
@@ -6796,85 +6884,85 @@
         <v>74</v>
       </c>
       <c r="B76" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C76" t="n">
-        <v>19017</v>
+        <v>7540</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>P</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hedyosmun  purpurascens</t>
+          <t>Pouteria torta</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedyosmun </t>
+          <t>Pouteria</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>purpurascens</t>
+          <t>torta</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">CaNu </t>
+          <t>BoN</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.4447771418133701</v>
+        <v>0.4759264914628947</v>
       </c>
       <c r="J76" t="n">
-        <v>0.01358788463589055</v>
+        <v>-32.81434274091024</v>
       </c>
       <c r="K76" t="n">
-        <v>-4.160631820792648</v>
+        <v>0.01574807849417584</v>
       </c>
       <c r="L76" t="n">
-        <v>-29.11551455098698</v>
+        <v>0.3748568608094767</v>
       </c>
       <c r="M76" t="n">
-        <v>0.4342487557007104</v>
+        <v>0.4526713223191351</v>
       </c>
       <c r="N76" t="n">
-        <v>26.27287016153906</v>
+        <v>28.30911682693158</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>45.46%</t>
+          <t>43.19%</t>
         </is>
       </c>
       <c r="P76" t="n">
-        <v>-27.23</v>
+        <v>-30.13</v>
       </c>
       <c r="Q76" t="n">
-        <v>3</v>
+        <v>16.7</v>
       </c>
       <c r="R76" t="n">
-        <v>29.06</v>
+        <v>36.26</v>
       </c>
       <c r="S76" t="n">
-        <v>2.732</v>
+        <v>1.58</v>
       </c>
       <c r="T76" t="n">
-        <v>17.85</v>
+        <v>35.12</v>
       </c>
       <c r="U76" t="n">
-        <v>5.1</v>
+        <v>19.32</v>
       </c>
       <c r="V76" t="n">
-        <v>342.9727765</v>
+        <v>1135.959</v>
       </c>
       <c r="W76" t="n">
-        <v>67.24956401960785</v>
+        <v>58.797049689441</v>
       </c>
       <c r="X76" t="n">
-        <v>0.000855298599939821</v>
+        <v>0.1121021103925018</v>
       </c>
     </row>
     <row r="77">
@@ -6885,7 +6973,7 @@
         <v>14</v>
       </c>
       <c r="C77" t="n">
-        <v>19018</v>
+        <v>19017</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6913,54 +7001,54 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.4315268248536531</v>
+        <v>0.4447771418133701</v>
       </c>
       <c r="J77" t="n">
-        <v>0.01548934902767845</v>
+        <v>-29.11551455098698</v>
       </c>
       <c r="K77" t="n">
-        <v>0.393164847788627</v>
+        <v>0.01358788463589055</v>
       </c>
       <c r="L77" t="n">
-        <v>-28.09845907778731</v>
+        <v>-4.160631820792648</v>
       </c>
       <c r="M77" t="n">
-        <v>0.4635036843292526</v>
+        <v>0.4342487557007104</v>
       </c>
       <c r="N77" t="n">
-        <v>27.20401300674918</v>
+        <v>26.27287016153906</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>43.72%</t>
+          <t>45.46%</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>-25.7</v>
+        <v>-27.23</v>
       </c>
       <c r="Q77" t="n">
         <v>3</v>
       </c>
       <c r="R77" t="n">
-        <v>45.3</v>
+        <v>29.06</v>
       </c>
       <c r="S77" t="n">
-        <v>2.817</v>
+        <v>2.732</v>
       </c>
       <c r="T77" t="n">
-        <v>18.45</v>
+        <v>17.85</v>
       </c>
       <c r="U77" t="n">
-        <v>4.96</v>
+        <v>5.1</v>
       </c>
       <c r="V77" t="n">
-        <v>335.4892103</v>
+        <v>342.9727765</v>
       </c>
       <c r="W77" t="n">
-        <v>67.63895368951613</v>
+        <v>67.24956401960785</v>
       </c>
       <c r="X77" t="n">
-        <v>0.00090792027688745</v>
+        <v>0.000855298599939821</v>
       </c>
     </row>
     <row r="78">
@@ -6971,7 +7059,7 @@
         <v>14</v>
       </c>
       <c r="C78" t="n">
-        <v>3011</v>
+        <v>19018</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6980,73 +7068,73 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Clarisia  racemosa</t>
+          <t>Hedyosmun  purpurascens</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clarisia </t>
+          <t xml:space="preserve">Hedyosmun </t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>racemosa</t>
+          <t>purpurascens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>BoN</t>
+          <t xml:space="preserve">CaNu </t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4301614784194553</v>
+        <v>0.4315268248536531</v>
       </c>
       <c r="J78" t="n">
-        <v>0.01971751674268555</v>
+        <v>-28.09845907778731</v>
       </c>
       <c r="K78" t="n">
-        <v>0.7020907524411255</v>
+        <v>0.01548934902767845</v>
       </c>
       <c r="L78" t="n">
-        <v>-32.48575719747211</v>
+        <v>0.393164847788627</v>
       </c>
       <c r="M78" t="n">
-        <v>0.3913576039397094</v>
+        <v>0.4635036843292526</v>
       </c>
       <c r="N78" t="n">
-        <v>26.88215374083289</v>
+        <v>27.20401300674918</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>38.08%</t>
+          <t>43.72%</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>-30.54</v>
+        <v>-25.7</v>
       </c>
       <c r="Q78" t="n">
-        <v>17.5</v>
+        <v>3</v>
       </c>
       <c r="R78" t="n">
-        <v>37.76</v>
+        <v>45.3</v>
       </c>
       <c r="S78" t="n">
-        <v>1.395</v>
+        <v>2.817</v>
       </c>
       <c r="T78" t="n">
-        <v>25.52</v>
+        <v>18.45</v>
       </c>
       <c r="U78" t="n">
-        <v>11.67</v>
+        <v>4.96</v>
       </c>
       <c r="V78" t="n">
-        <v>1073.276</v>
+        <v>335.4892103</v>
       </c>
       <c r="W78" t="n">
-        <v>91.96880891173952</v>
+        <v>67.63895368951613</v>
       </c>
       <c r="X78" t="n">
-        <v>0.02328928607551839</v>
+        <v>0.00090792027688745</v>
       </c>
     </row>
     <row r="79">
@@ -7054,85 +7142,85 @@
         <v>77</v>
       </c>
       <c r="B79" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C79" t="n">
-        <v>1538</v>
+        <v>3011</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hedyosmun  purpurascens</t>
+          <t>Clarisia  racemosa</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedyosmun </t>
+          <t xml:space="preserve">Clarisia </t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>purpurascens</t>
+          <t>racemosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">CaNu </t>
+          <t>BoN</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.4337511242156616</v>
+        <v>0.4301614784194553</v>
       </c>
       <c r="J79" t="n">
-        <v>0.02372196824247066</v>
+        <v>-32.48575719747211</v>
       </c>
       <c r="K79" t="n">
-        <v>-0.4306375646180359</v>
+        <v>0.01971751674268555</v>
       </c>
       <c r="L79" t="n">
-        <v>-27.07143247249747</v>
+        <v>0.7020907524411255</v>
       </c>
       <c r="M79" t="n">
-        <v>0.4585504489693114</v>
+        <v>0.3913576039397094</v>
       </c>
       <c r="N79" t="n">
-        <v>31.26679412002084</v>
+        <v>26.88215374083289</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>45.97%</t>
+          <t>38.08%</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>-24.88</v>
+        <v>-30.54</v>
       </c>
       <c r="Q79" t="n">
-        <v>5</v>
+        <v>17.5</v>
       </c>
       <c r="R79" t="n">
-        <v>36.78</v>
+        <v>37.76</v>
       </c>
       <c r="S79" t="n">
-        <v>2.622</v>
+        <v>1.395</v>
       </c>
       <c r="T79" t="n">
-        <v>8.630000000000001</v>
+        <v>25.52</v>
       </c>
       <c r="U79" t="n">
-        <v>2.42</v>
+        <v>11.67</v>
       </c>
       <c r="V79" t="n">
-        <v>176.6137053</v>
+        <v>1073.276</v>
       </c>
       <c r="W79" t="n">
-        <v>72.98086995867769</v>
+        <v>91.96880891173952</v>
       </c>
       <c r="X79" t="n">
-        <v>0.01020703453151324</v>
+        <v>0.02328928607551839</v>
       </c>
     </row>
     <row r="80">
@@ -7143,7 +7231,7 @@
         <v>15</v>
       </c>
       <c r="C80" t="n">
-        <v>1547</v>
+        <v>1538</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7171,54 +7259,54 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.4189742261891197</v>
+        <v>0.4337511242156616</v>
       </c>
       <c r="J80" t="n">
-        <v>0.01893318860454643</v>
+        <v>-27.07143247249747</v>
       </c>
       <c r="K80" t="n">
-        <v>-0.06450315910396345</v>
+        <v>0.02372196824247066</v>
       </c>
       <c r="L80" t="n">
-        <v>-28.09845907778731</v>
+        <v>-0.4306375646180359</v>
       </c>
       <c r="M80" t="n">
-        <v>0.4228831025901615</v>
+        <v>0.4585504489693114</v>
       </c>
       <c r="N80" t="n">
-        <v>27.4581572901716</v>
+        <v>31.26679412002084</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>40.08%</t>
+          <t>45.97%</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>-29.76</v>
+        <v>-24.88</v>
       </c>
       <c r="Q80" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R80" t="n">
-        <v>36.3</v>
+        <v>36.78</v>
       </c>
       <c r="S80" t="n">
-        <v>2.68</v>
+        <v>2.622</v>
       </c>
       <c r="T80" t="n">
-        <v>10.22</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="U80" t="n">
-        <v>2.97</v>
+        <v>2.42</v>
       </c>
       <c r="V80" t="n">
-        <v>187.5230679</v>
+        <v>176.6137053</v>
       </c>
       <c r="W80" t="n">
-        <v>63.13908010101009</v>
+        <v>72.98086995867769</v>
       </c>
       <c r="X80" t="n">
-        <v>0.03617006728264883</v>
+        <v>0.01020703453151324</v>
       </c>
     </row>
     <row r="81">
@@ -7229,7 +7317,7 @@
         <v>15</v>
       </c>
       <c r="C81" t="n">
-        <v>1557</v>
+        <v>1547</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7257,54 +7345,54 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.4325338338266033</v>
+        <v>0.4189742261891197</v>
       </c>
       <c r="J81" t="n">
-        <v>0.01810694629783977</v>
+        <v>-28.09845907778731</v>
       </c>
       <c r="K81" t="n">
-        <v>1.148317059161401</v>
+        <v>0.01893318860454643</v>
       </c>
       <c r="L81" t="n">
-        <v>-25.74527190450183</v>
+        <v>-0.06450315910396345</v>
       </c>
       <c r="M81" t="n">
-        <v>0.4327573190881843</v>
+        <v>0.4228831025901615</v>
       </c>
       <c r="N81" t="n">
-        <v>27.98857065959375</v>
+        <v>27.4581572901716</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>45.00%</t>
+          <t>40.08%</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>-23.86</v>
+        <v>-29.76</v>
       </c>
       <c r="Q81" t="n">
         <v>8</v>
       </c>
       <c r="R81" t="n">
-        <v>46.01000000000001</v>
+        <v>36.3</v>
       </c>
       <c r="S81" t="n">
-        <v>2.723</v>
+        <v>2.68</v>
       </c>
       <c r="T81" t="n">
-        <v>11.38</v>
+        <v>10.22</v>
       </c>
       <c r="U81" t="n">
-        <v>3.33</v>
+        <v>2.97</v>
       </c>
       <c r="V81" t="n">
-        <v>201.377356</v>
+        <v>187.5230679</v>
       </c>
       <c r="W81" t="n">
-        <v>60.47368048048047</v>
+        <v>63.13908010101009</v>
       </c>
       <c r="X81" t="n">
-        <v>0.05620014732960866</v>
+        <v>0.03617006728264883</v>
       </c>
     </row>
     <row r="82">
@@ -7315,7 +7403,7 @@
         <v>15</v>
       </c>
       <c r="C82" t="n">
-        <v>1860</v>
+        <v>1557</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7324,73 +7412,73 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pouteria torta</t>
+          <t>Hedyosmun  purpurascens</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pouteria</t>
+          <t xml:space="preserve">Hedyosmun </t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>torta</t>
+          <t>purpurascens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>BoN</t>
+          <t xml:space="preserve">CaNu </t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.4798797005234955</v>
+        <v>0.4325338338266033</v>
       </c>
       <c r="J82" t="n">
-        <v>0.01642218463524144</v>
+        <v>-25.74527190450183</v>
       </c>
       <c r="K82" t="n">
-        <v>1.16269054178145</v>
+        <v>0.01810694629783977</v>
       </c>
       <c r="L82" t="n">
-        <v>-33.49086170952049</v>
+        <v>1.148317059161401</v>
       </c>
       <c r="M82" t="n">
-        <v>0.4990409613911599</v>
+        <v>0.4327573190881843</v>
       </c>
       <c r="N82" t="n">
-        <v>28.80264579553639</v>
+        <v>27.98857065959375</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>41.56%</t>
+          <t>45.00%</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>-30.92</v>
+        <v>-23.86</v>
       </c>
       <c r="Q82" t="n">
-        <v>12.1</v>
+        <v>8</v>
       </c>
       <c r="R82" t="n">
-        <v>30.41</v>
+        <v>46.01000000000001</v>
       </c>
       <c r="S82" t="n">
-        <v>1.151</v>
+        <v>2.723</v>
       </c>
       <c r="T82" t="n">
-        <v>48.81</v>
+        <v>11.38</v>
       </c>
       <c r="U82" t="n">
-        <v>24.88</v>
+        <v>3.33</v>
       </c>
       <c r="V82" t="n">
-        <v>2057.218</v>
+        <v>201.377356</v>
       </c>
       <c r="W82" t="n">
-        <v>82.68561093247588</v>
+        <v>60.47368048048047</v>
       </c>
       <c r="X82" t="n">
-        <v>0.01459088360616714</v>
+        <v>0.05620014732960866</v>
       </c>
     </row>
     <row r="83">
@@ -7401,7 +7489,7 @@
         <v>15</v>
       </c>
       <c r="C83" t="n">
-        <v>1875</v>
+        <v>1860</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7428,47 +7516,55 @@
           <t>BoN</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
+      <c r="I83" t="n">
+        <v>0.4798797005234955</v>
+      </c>
+      <c r="J83" t="n">
+        <v>-33.49086170952049</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.01642218463524144</v>
+      </c>
+      <c r="L83" t="n">
+        <v>1.16269054178145</v>
+      </c>
       <c r="M83" t="n">
-        <v>0.4897063924561476</v>
+        <v>0.4990409613911599</v>
       </c>
       <c r="N83" t="n">
-        <v>31.25829991784251</v>
+        <v>28.80264579553639</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>42.23%</t>
+          <t>41.56%</t>
         </is>
       </c>
       <c r="P83" t="n">
-        <v>-32.67</v>
+        <v>-30.92</v>
       </c>
       <c r="Q83" t="n">
-        <v>8</v>
+        <v>12.1</v>
       </c>
       <c r="R83" t="n">
-        <v>29.06</v>
+        <v>30.41</v>
       </c>
       <c r="S83" t="n">
-        <v>1.035</v>
+        <v>1.151</v>
       </c>
       <c r="T83" t="n">
-        <v>29.47</v>
+        <v>48.81</v>
       </c>
       <c r="U83" t="n">
-        <v>12.98</v>
+        <v>24.88</v>
       </c>
       <c r="V83" t="n">
-        <v>1380.372</v>
+        <v>2057.218</v>
       </c>
       <c r="W83" t="n">
-        <v>106.3460708782743</v>
+        <v>82.68561093247588</v>
       </c>
       <c r="X83" t="n">
-        <v>0.00804360816654516</v>
+        <v>0.01459088360616714</v>
       </c>
     </row>
     <row r="84">
@@ -7479,7 +7575,7 @@
         <v>15</v>
       </c>
       <c r="C84" t="n">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7506,47 +7602,55 @@
           <t>BoN</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
+      <c r="I84" t="n">
+        <v>0.4407193460180195</v>
+      </c>
+      <c r="J84" t="n">
+        <v>-34.79243579964403</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.01674704199884629</v>
+      </c>
+      <c r="L84" t="n">
+        <v>-0.009269496544916246</v>
+      </c>
       <c r="M84" t="n">
-        <v>0.4957304623190273</v>
+        <v>0.4897063924561476</v>
       </c>
       <c r="N84" t="n">
-        <v>31.6081740993542</v>
+        <v>31.25829991784251</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>42.33%</t>
+          <t>42.23%</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>-31.98</v>
+        <v>-32.67</v>
       </c>
       <c r="Q84" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R84" t="n">
-        <v>24.8</v>
+        <v>29.06</v>
       </c>
       <c r="S84" t="n">
-        <v>0.9600000000000001</v>
+        <v>1.035</v>
       </c>
       <c r="T84" t="n">
-        <v>45.56</v>
+        <v>29.47</v>
       </c>
       <c r="U84" t="n">
-        <v>22.83</v>
+        <v>12.98</v>
       </c>
       <c r="V84" t="n">
-        <v>2199.616</v>
+        <v>1380.372</v>
       </c>
       <c r="W84" t="n">
-        <v>96.34761279018835</v>
+        <v>106.3460708782743</v>
       </c>
       <c r="X84" t="n">
-        <v>0.008413381475854314</v>
+        <v>0.00804360816654516</v>
       </c>
     </row>
     <row r="85">
@@ -7557,7 +7661,7 @@
         <v>15</v>
       </c>
       <c r="C85" t="n">
-        <v>1887</v>
+        <v>1877</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7584,47 +7688,55 @@
           <t>BoN</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
+      <c r="I85" t="n">
+        <v>0.4730944245450511</v>
+      </c>
+      <c r="J85" t="n">
+        <v>-34.1948868548182</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.01566321828736725</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.951046396841066</v>
+      </c>
       <c r="M85" t="n">
-        <v>0.4757597560161007</v>
+        <v>0.4957304623190273</v>
       </c>
       <c r="N85" t="n">
-        <v>29.25874627645676</v>
+        <v>31.6081740993542</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>42.17%</t>
+          <t>42.33%</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>-30.91</v>
+        <v>-31.98</v>
       </c>
       <c r="Q85" t="n">
-        <v>14.6</v>
+        <v>9</v>
       </c>
       <c r="R85" t="n">
-        <v>30.89</v>
+        <v>24.8</v>
       </c>
       <c r="S85" t="n">
-        <v>1.223</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="T85" t="n">
-        <v>42.02</v>
+        <v>45.56</v>
       </c>
       <c r="U85" t="n">
-        <v>22.92</v>
+        <v>22.83</v>
       </c>
       <c r="V85" t="n">
-        <v>1739.915</v>
+        <v>2199.616</v>
       </c>
       <c r="W85" t="n">
-        <v>75.91252181500872</v>
+        <v>96.34761279018835</v>
       </c>
       <c r="X85" t="n">
-        <v>0.07655184792447974</v>
+        <v>0.008413381475854314</v>
       </c>
     </row>
     <row r="86">
@@ -7632,14 +7744,14 @@
         <v>84</v>
       </c>
       <c r="B86" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C86" t="n">
-        <v>1894</v>
+        <v>1887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7663,54 +7775,54 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.482776617910343</v>
+        <v>0.480387755270591</v>
       </c>
       <c r="J86" t="n">
-        <v>0.01577773061086078</v>
+        <v>-33.76217899822018</v>
       </c>
       <c r="K86" t="n">
-        <v>0.906602387511478</v>
+        <v>0.01716693439128926</v>
       </c>
       <c r="L86" t="n">
-        <v>-33.42178596247393</v>
+        <v>1.668756169792695</v>
       </c>
       <c r="M86" t="n">
-        <v>0.4866900926202177</v>
+        <v>0.4757597560161007</v>
       </c>
       <c r="N86" t="n">
-        <v>27.51967488982305</v>
+        <v>29.25874627645676</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>43.21%</t>
+          <t>42.17%</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>-31.35</v>
+        <v>-30.91</v>
       </c>
       <c r="Q86" t="n">
-        <v>14.2</v>
+        <v>14.6</v>
       </c>
       <c r="R86" t="n">
-        <v>34.45</v>
+        <v>30.89</v>
       </c>
       <c r="S86" t="n">
-        <v>1.263</v>
+        <v>1.223</v>
       </c>
       <c r="T86" t="n">
-        <v>32.3</v>
+        <v>42.02</v>
       </c>
       <c r="U86" t="n">
-        <v>16.47</v>
+        <v>22.92</v>
       </c>
       <c r="V86" t="n">
-        <v>1219.036</v>
+        <v>1739.915</v>
       </c>
       <c r="W86" t="n">
-        <v>74.01554341226473</v>
+        <v>75.91252181500872</v>
       </c>
       <c r="X86" t="n">
-        <v>0.08434178033822919</v>
+        <v>0.07655184792447974</v>
       </c>
     </row>
     <row r="87">
@@ -7721,7 +7833,7 @@
         <v>16</v>
       </c>
       <c r="C87" t="n">
-        <v>19019</v>
+        <v>1894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7730,73 +7842,73 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Hedyosmun  purpurascens</t>
+          <t>Pouteria torta</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedyosmun </t>
+          <t>Pouteria</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>purpurascens</t>
+          <t>torta</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">CaNu </t>
+          <t>BoN</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.4428154728641102</v>
+        <v>0.482776617910343</v>
       </c>
       <c r="J87" t="n">
-        <v>0.01639638322576012</v>
+        <v>-33.42178596247393</v>
       </c>
       <c r="K87" t="n">
-        <v>-0.06450315910396345</v>
+        <v>0.01577773061086078</v>
       </c>
       <c r="L87" t="n">
-        <v>-27.48024888819537</v>
+        <v>0.906602387511478</v>
       </c>
       <c r="M87" t="n">
-        <v>0.4391742515380573</v>
+        <v>0.4866900926202177</v>
       </c>
       <c r="N87" t="n">
-        <v>25.52514993907187</v>
+        <v>27.51967488982305</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>43.60%</t>
+          <t>43.21%</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>-25.51</v>
+        <v>-31.35</v>
       </c>
       <c r="Q87" t="n">
-        <v>5</v>
+        <v>14.2</v>
       </c>
       <c r="R87" t="n">
-        <v>27.48</v>
+        <v>34.45</v>
       </c>
       <c r="S87" t="n">
-        <v>2.774</v>
+        <v>1.263</v>
       </c>
       <c r="T87" t="n">
-        <v>19.8</v>
+        <v>32.3</v>
       </c>
       <c r="U87" t="n">
-        <v>5.31</v>
+        <v>16.47</v>
       </c>
       <c r="V87" t="n">
-        <v>319.7217765</v>
+        <v>1219.036</v>
       </c>
       <c r="W87" t="n">
-        <v>60.21125734463277</v>
+        <v>74.01554341226473</v>
       </c>
       <c r="X87" t="n">
-        <v>0.002733971006786517</v>
+        <v>0.08434178033822919</v>
       </c>
     </row>
     <row r="88">
@@ -7807,81 +7919,167 @@
         <v>16</v>
       </c>
       <c r="C88" t="n">
+        <v>19019</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NP</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Hedyosmun  purpurascens</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hedyosmun </t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>purpurascens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CaNu </t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>0.4428154728641102</v>
+      </c>
+      <c r="J88" t="n">
+        <v>-27.48024888819537</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.01639638322576012</v>
+      </c>
+      <c r="L88" t="n">
+        <v>-0.06450315910396345</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.4391742515380573</v>
+      </c>
+      <c r="N88" t="n">
+        <v>25.52514993907187</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>43.60%</t>
+        </is>
+      </c>
+      <c r="P88" t="n">
+        <v>-25.51</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>5</v>
+      </c>
+      <c r="R88" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="S88" t="n">
+        <v>2.774</v>
+      </c>
+      <c r="T88" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="U88" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="V88" t="n">
+        <v>319.7217765</v>
+      </c>
+      <c r="W88" t="n">
+        <v>60.21125734463277</v>
+      </c>
+      <c r="X88" t="n">
+        <v>0.002733971006786517</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="n">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
         <v>7543</v>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>NP</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>Clarisia  racemosa</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t xml:space="preserve">Clarisia </t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>racemosa</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>BoN</t>
         </is>
       </c>
-      <c r="I88" t="n">
+      <c r="I89" t="n">
         <v>0.4422406146015264</v>
       </c>
-      <c r="J88" t="n">
+      <c r="J89" t="n">
+        <v>-31.79774908324881</v>
+      </c>
+      <c r="K89" t="n">
         <v>0.02200222194324181</v>
       </c>
-      <c r="K88" t="n">
+      <c r="L89" t="n">
         <v>2.326812176909822</v>
       </c>
-      <c r="L88" t="n">
-        <v>-31.79774908324881</v>
-      </c>
-      <c r="M88" t="n">
+      <c r="M89" t="n">
         <v>0.474514983493865</v>
       </c>
-      <c r="N88" t="n">
+      <c r="N89" t="n">
         <v>32.60054718808122</v>
       </c>
-      <c r="O88" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>43.85%</t>
         </is>
       </c>
-      <c r="P88" t="n">
+      <c r="P89" t="n">
         <v>-31.07</v>
       </c>
-      <c r="Q88" t="n">
+      <c r="Q89" t="n">
         <v>13</v>
       </c>
-      <c r="R88" t="n">
+      <c r="R89" t="n">
         <v>33.4</v>
       </c>
-      <c r="S88" t="n">
+      <c r="S89" t="n">
         <v>1.446</v>
       </c>
-      <c r="T88" t="n">
+      <c r="T89" t="n">
         <v>17.53</v>
       </c>
-      <c r="U88" t="n">
+      <c r="U89" t="n">
         <v>7.08</v>
       </c>
-      <c r="V88" t="n">
+      <c r="V89" t="n">
         <v>719.373</v>
       </c>
-      <c r="W88" t="n">
+      <c r="W89" t="n">
         <v>101.6063559322034</v>
       </c>
-      <c r="X88" t="n">
+      <c r="X89" t="n">
         <v>0.04169220176949628</v>
       </c>
     </row>

--- a/Results_isofys/Numex_preliminar_base.xlsx
+++ b/Results_isofys/Numex_preliminar_base.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -511,12 +511,12 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_toughness_(kN/m)</t>
+          <t>mean toughness (kN/m)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>mean_thickness_(mm)</t>
+          <t>mean thickness (mm)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SLA (cm²/g)</t>
+          <t>Specific leaf area (g/cm²)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
@@ -556,12 +556,12 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SLA </t>
+          <t>code</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>C:N</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,9 @@
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>39.58454796558406</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -743,7 +745,9 @@
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
+      <c r="AB3" t="n">
+        <v>25.57873717795717</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -833,7 +837,9 @@
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>42.49161457666214</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -923,7 +929,9 @@
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>29.47494536584171</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1013,7 +1021,9 @@
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>29.46857519135586</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1103,7 +1113,9 @@
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
+      <c r="AB7" t="n">
+        <v>26.51846199848627</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1193,7 +1205,9 @@
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
+      <c r="AB8" t="n">
+        <v>29.75015113451708</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1283,7 +1297,9 @@
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
+      <c r="AB9" t="n">
+        <v>28.28424514537473</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1373,7 +1389,9 @@
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
+      <c r="AB10" t="n">
+        <v>28.01632724421026</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1463,7 +1481,9 @@
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
+      <c r="AB11" t="n">
+        <v>39.94038297769038</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1553,7 +1573,9 @@
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
+      <c r="AB12" t="n">
+        <v>41.33398260330502</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1643,7 +1665,9 @@
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
+      <c r="AB13" t="n">
+        <v>33.26962395702254</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1733,7 +1757,9 @@
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
+      <c r="AB14" t="n">
+        <v>24.51611901423017</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1823,7 +1849,9 @@
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
+      <c r="AB15" t="n">
+        <v>29.77748860325364</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1913,7 +1941,9 @@
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
+      <c r="AB16" t="n">
+        <v>32.32547486872957</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -2003,7 +2033,9 @@
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
+      <c r="AB17" t="n">
+        <v>28.39448648615612</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -2093,7 +2125,9 @@
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
+      <c r="AB18" t="n">
+        <v>29.17653851247548</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -2183,7 +2217,9 @@
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
+      <c r="AB19" t="n">
+        <v>26.66776442666212</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -2273,7 +2309,9 @@
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
+      <c r="AB20" t="n">
+        <v>30.75436275117814</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -2363,7 +2401,9 @@
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
+      <c r="AB21" t="n">
+        <v>22.9540859657499</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -2453,7 +2493,9 @@
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
+      <c r="AB22" t="n">
+        <v>53.02578826881873</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -2543,7 +2585,9 @@
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
+      <c r="AB23" t="n">
+        <v>38.38370176944333</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -2633,7 +2677,9 @@
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
+      <c r="AB24" t="n">
+        <v>30.95258432083551</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -2723,7 +2769,9 @@
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
+      <c r="AB25" t="n">
+        <v>30.76750734875213</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -2813,7 +2861,9 @@
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
+      <c r="AB26" t="n">
+        <v>29.19160870007697</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2903,7 +2953,9 @@
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
+      <c r="AB27" t="n">
+        <v>19.36748669969131</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2993,7 +3045,9 @@
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
+      <c r="AB28" t="n">
+        <v>31.82500795526659</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -3083,7 +3137,9 @@
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
+      <c r="AB29" t="n">
+        <v>20.74216706763612</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -3173,7 +3229,9 @@
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
+      <c r="AB30" t="n">
+        <v>29.19189319790335</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -3263,7 +3321,9 @@
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
       <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
+      <c r="AB31" t="n">
+        <v>42.97256368979243</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -3353,7 +3413,9 @@
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
+      <c r="AB32" t="n">
+        <v>20.62022678542598</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -3443,7 +3505,9 @@
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
       <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
+      <c r="AB33" t="n">
+        <v>21.99115496636606</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -3533,7 +3597,9 @@
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
       <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
+      <c r="AB34" t="n">
+        <v>43.87185925469005</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -3623,7 +3689,9 @@
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
+      <c r="AB35" t="n">
+        <v>24.17983322666046</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -3713,7 +3781,9 @@
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
       <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
+      <c r="AB36" t="n">
+        <v>45.72171601638512</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -3803,7 +3873,9 @@
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
+      <c r="AB37" t="n">
+        <v>32.47607689365352</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -3893,7 +3965,9 @@
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr"/>
+      <c r="AB38" t="n">
+        <v>31.24223026798138</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -3983,7 +4057,9 @@
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
       <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
+      <c r="AB39" t="n">
+        <v>22.29074496544098</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -4073,7 +4149,9 @@
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
-      <c r="AB40" t="inlineStr"/>
+      <c r="AB40" t="n">
+        <v>40.95714602250389</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -4163,7 +4241,9 @@
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
       <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
+      <c r="AB41" t="n">
+        <v>32.65053512949007</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -4253,7 +4333,9 @@
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
       <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
+      <c r="AB42" t="n">
+        <v>32.65053512949007</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -4343,7 +4425,9 @@
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
       <c r="AA43" t="inlineStr"/>
-      <c r="AB43" t="inlineStr"/>
+      <c r="AB43" t="n">
+        <v>32.65053512949007</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -4433,7 +4517,9 @@
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="inlineStr"/>
+      <c r="AB44" t="n">
+        <v>32.65053512949007</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -4523,7 +4609,9 @@
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
       <c r="AA45" t="inlineStr"/>
-      <c r="AB45" t="inlineStr"/>
+      <c r="AB45" t="n">
+        <v>34.94837353504887</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -4613,7 +4701,9 @@
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr"/>
-      <c r="AB46" t="inlineStr"/>
+      <c r="AB46" t="n">
+        <v>27.61940167646294</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -4703,7 +4793,9 @@
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="inlineStr"/>
-      <c r="AB47" t="inlineStr"/>
+      <c r="AB47" t="n">
+        <v>31.61114054973259</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -4793,7 +4885,9 @@
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr"/>
-      <c r="AB48" t="inlineStr"/>
+      <c r="AB48" t="n">
+        <v>32.58259222016648</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -4883,7 +4977,9 @@
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
       <c r="AA49" t="inlineStr"/>
-      <c r="AB49" t="inlineStr"/>
+      <c r="AB49" t="n">
+        <v>37.10169593659131</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -4973,7 +5069,9 @@
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
       <c r="AA50" t="inlineStr"/>
-      <c r="AB50" t="inlineStr"/>
+      <c r="AB50" t="n">
+        <v>46.62061318477367</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -5063,7 +5161,9 @@
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
       <c r="AA51" t="inlineStr"/>
-      <c r="AB51" t="inlineStr"/>
+      <c r="AB51" t="n">
+        <v>27.64252745359939</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -5153,7 +5253,9 @@
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
       <c r="AA52" t="inlineStr"/>
-      <c r="AB52" t="inlineStr"/>
+      <c r="AB52" t="n">
+        <v>31.43663314688067</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -5243,7 +5345,9 @@
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
       <c r="AA53" t="inlineStr"/>
-      <c r="AB53" t="inlineStr"/>
+      <c r="AB53" t="n">
+        <v>16.47515809594595</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -5333,7 +5437,9 @@
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
       <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
+      <c r="AB54" t="n">
+        <v>17.18961723916043</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -5423,7 +5529,9 @@
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
       <c r="AA55" t="inlineStr"/>
-      <c r="AB55" t="inlineStr"/>
+      <c r="AB55" t="n">
+        <v>34.16916319918331</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -5513,7 +5621,9 @@
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
       <c r="AA56" t="inlineStr"/>
-      <c r="AB56" t="inlineStr"/>
+      <c r="AB56" t="n">
+        <v>31.13148059335148</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -5603,7 +5713,9 @@
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
       <c r="AA57" t="inlineStr"/>
-      <c r="AB57" t="inlineStr"/>
+      <c r="AB57" t="n">
+        <v>42.28261169430561</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -5693,7 +5805,9 @@
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
       <c r="AA58" t="inlineStr"/>
-      <c r="AB58" t="inlineStr"/>
+      <c r="AB58" t="n">
+        <v>30.4083735401035</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -5783,7 +5897,9 @@
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
       <c r="AA59" t="inlineStr"/>
-      <c r="AB59" t="inlineStr"/>
+      <c r="AB59" t="n">
+        <v>41.39388452825128</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -5873,7 +5989,9 @@
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
       <c r="AA60" t="inlineStr"/>
-      <c r="AB60" t="inlineStr"/>
+      <c r="AB60" t="n">
+        <v>28.16106955669685</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -5963,7 +6081,9 @@
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
       <c r="AA61" t="inlineStr"/>
-      <c r="AB61" t="inlineStr"/>
+      <c r="AB61" t="n">
+        <v>28.34964144442967</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -6053,7 +6173,9 @@
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
-      <c r="AB62" t="inlineStr"/>
+      <c r="AB62" t="n">
+        <v>35.750550975415</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -6143,7 +6265,9 @@
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="inlineStr"/>
-      <c r="AB63" t="inlineStr"/>
+      <c r="AB63" t="n">
+        <v>31.74524498440573</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -6233,7 +6357,9 @@
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="inlineStr"/>
-      <c r="AB64" t="inlineStr"/>
+      <c r="AB64" t="n">
+        <v>32.75482157518042</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -6323,7 +6449,9 @@
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
       <c r="AA65" t="inlineStr"/>
-      <c r="AB65" t="inlineStr"/>
+      <c r="AB65" t="n">
+        <v>37.77978443238764</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -6413,7 +6541,9 @@
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
       <c r="AA66" t="inlineStr"/>
-      <c r="AB66" t="inlineStr"/>
+      <c r="AB66" t="n">
+        <v>46.78990518799996</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -6503,7 +6633,9 @@
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
       <c r="AA67" t="inlineStr"/>
-      <c r="AB67" t="inlineStr"/>
+      <c r="AB67" t="n">
+        <v>29.55848025895564</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -6593,7 +6725,9 @@
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr"/>
-      <c r="AB68" t="inlineStr"/>
+      <c r="AB68" t="n">
+        <v>27.95108301698842</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -6683,7 +6817,9 @@
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr"/>
       <c r="AA69" t="inlineStr"/>
-      <c r="AB69" t="inlineStr"/>
+      <c r="AB69" t="n">
+        <v>24.10341074609785</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -6773,7 +6909,9 @@
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
       <c r="AA70" t="inlineStr"/>
-      <c r="AB70" t="inlineStr"/>
+      <c r="AB70" t="n">
+        <v>33.07869485466203</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -6863,7 +7001,9 @@
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
       <c r="AA71" t="inlineStr"/>
-      <c r="AB71" t="inlineStr"/>
+      <c r="AB71" t="n">
+        <v>28.43772466129882</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -6953,7 +7093,9 @@
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
       <c r="AA72" t="inlineStr"/>
-      <c r="AB72" t="inlineStr"/>
+      <c r="AB72" t="n">
+        <v>27.25954615592946</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -7043,7 +7185,9 @@
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
       <c r="AA73" t="inlineStr"/>
-      <c r="AB73" t="inlineStr"/>
+      <c r="AB73" t="n">
+        <v>30.02082045458015</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -7133,7 +7277,9 @@
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr"/>
       <c r="AA74" t="inlineStr"/>
-      <c r="AB74" t="inlineStr"/>
+      <c r="AB74" t="n">
+        <v>26.46707679984683</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -7223,7 +7369,9 @@
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr"/>
       <c r="AA75" t="inlineStr"/>
-      <c r="AB75" t="inlineStr"/>
+      <c r="AB75" t="n">
+        <v>30.22124201621856</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -7313,7 +7461,9 @@
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr"/>
-      <c r="AB76" t="inlineStr"/>
+      <c r="AB76" t="n">
+        <v>32.73336164766602</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -7403,7 +7553,9 @@
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="inlineStr"/>
       <c r="AA77" t="inlineStr"/>
-      <c r="AB77" t="inlineStr"/>
+      <c r="AB77" t="n">
+        <v>27.85958429127932</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -7493,7 +7645,9 @@
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr"/>
-      <c r="AB78" t="inlineStr"/>
+      <c r="AB78" t="n">
+        <v>21.8162096187406</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -7583,7 +7737,9 @@
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
       <c r="AA79" t="inlineStr"/>
-      <c r="AB79" t="inlineStr"/>
+      <c r="AB79" t="n">
+        <v>18.28478648070588</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -7673,7 +7829,9 @@
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr"/>
-      <c r="AB80" t="inlineStr"/>
+      <c r="AB80" t="n">
+        <v>22.12908955486301</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -7763,7 +7921,9 @@
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="inlineStr"/>
       <c r="AA81" t="inlineStr"/>
-      <c r="AB81" t="inlineStr"/>
+      <c r="AB81" t="n">
+        <v>23.88772942228289</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -7853,7 +8013,9 @@
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="inlineStr"/>
       <c r="AA82" t="inlineStr"/>
-      <c r="AB82" t="inlineStr"/>
+      <c r="AB82" t="n">
+        <v>29.22142888916803</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -7943,7 +8105,9 @@
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="inlineStr"/>
       <c r="AA83" t="inlineStr"/>
-      <c r="AB83" t="inlineStr"/>
+      <c r="AB83" t="n">
+        <v>26.31625012037236</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -8033,7 +8197,9 @@
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="inlineStr"/>
       <c r="AA84" t="inlineStr"/>
-      <c r="AB84" t="inlineStr"/>
+      <c r="AB84" t="n">
+        <v>30.20416467837983</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -8123,7 +8289,9 @@
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr"/>
       <c r="AA85" t="inlineStr"/>
-      <c r="AB85" t="inlineStr"/>
+      <c r="AB85" t="n">
+        <v>27.98331631734705</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -8213,7 +8381,9 @@
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="inlineStr"/>
       <c r="AA86" t="inlineStr"/>
-      <c r="AB86" t="inlineStr"/>
+      <c r="AB86" t="n">
+        <v>30.59860950966031</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -8303,7 +8473,9 @@
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="inlineStr"/>
       <c r="AA87" t="inlineStr"/>
-      <c r="AB87" t="inlineStr"/>
+      <c r="AB87" t="n">
+        <v>27.00689943428555</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -8393,7 +8565,9 @@
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="inlineStr"/>
       <c r="AA88" t="inlineStr"/>
-      <c r="AB88" t="inlineStr"/>
+      <c r="AB88" t="n">
+        <v>20.09981608868212</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -8472,11 +8646,13 @@
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="inlineStr"/>
-      <c r="AA89" t="inlineStr"/>
-      <c r="AB89" t="inlineStr">
+      <c r="AA89" t="inlineStr">
         <is>
           <t>592012</t>
         </is>
+      </c>
+      <c r="AB89" t="n">
+        <v>59.38716473519461</v>
       </c>
     </row>
     <row r="90">
@@ -8556,11 +8732,13 @@
       <c r="X90" t="inlineStr"/>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="inlineStr"/>
-      <c r="AA90" t="inlineStr"/>
-      <c r="AB90" t="inlineStr">
+      <c r="AA90" t="inlineStr">
         <is>
           <t>592033</t>
         </is>
+      </c>
+      <c r="AB90" t="n">
+        <v>55.07549417735655</v>
       </c>
     </row>
     <row r="91">
@@ -8640,11 +8818,13 @@
       <c r="X91" t="inlineStr"/>
       <c r="Y91" t="inlineStr"/>
       <c r="Z91" t="inlineStr"/>
-      <c r="AA91" t="inlineStr"/>
-      <c r="AB91" t="inlineStr">
+      <c r="AA91" t="inlineStr">
         <is>
           <t>592031</t>
         </is>
+      </c>
+      <c r="AB91" t="n">
+        <v>45.17757835768303</v>
       </c>
     </row>
     <row r="92">
@@ -8724,11 +8904,13 @@
       <c r="X92" t="inlineStr"/>
       <c r="Y92" t="inlineStr"/>
       <c r="Z92" t="inlineStr"/>
-      <c r="AA92" t="inlineStr"/>
-      <c r="AB92" t="inlineStr">
+      <c r="AA92" t="inlineStr">
         <is>
           <t>592251</t>
         </is>
+      </c>
+      <c r="AB92" t="n">
+        <v>43.38637434690112</v>
       </c>
     </row>
     <row r="93">
@@ -8808,11 +8990,13 @@
       <c r="X93" t="inlineStr"/>
       <c r="Y93" t="inlineStr"/>
       <c r="Z93" t="inlineStr"/>
-      <c r="AA93" t="inlineStr"/>
-      <c r="AB93" t="inlineStr">
+      <c r="AA93" t="inlineStr">
         <is>
           <t>592151</t>
         </is>
+      </c>
+      <c r="AB93" t="n">
+        <v>61.02294354014969</v>
       </c>
     </row>
     <row r="94">
@@ -8892,11 +9076,13 @@
       <c r="X94" t="inlineStr"/>
       <c r="Y94" t="inlineStr"/>
       <c r="Z94" t="inlineStr"/>
-      <c r="AA94" t="inlineStr"/>
-      <c r="AB94" t="inlineStr">
+      <c r="AA94" t="inlineStr">
         <is>
           <t>592379</t>
         </is>
+      </c>
+      <c r="AB94" t="n">
+        <v>50.18888849181604</v>
       </c>
     </row>
     <row r="95">
@@ -8976,11 +9162,13 @@
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr"/>
       <c r="Z95" t="inlineStr"/>
-      <c r="AA95" t="inlineStr"/>
-      <c r="AB95" t="inlineStr">
+      <c r="AA95" t="inlineStr">
         <is>
           <t>592333</t>
         </is>
+      </c>
+      <c r="AB95" t="n">
+        <v>44.53537356895627</v>
       </c>
     </row>
     <row r="96">
@@ -9060,11 +9248,13 @@
       <c r="X96" t="inlineStr"/>
       <c r="Y96" t="inlineStr"/>
       <c r="Z96" t="inlineStr"/>
-      <c r="AA96" t="inlineStr"/>
-      <c r="AB96" t="inlineStr">
+      <c r="AA96" t="inlineStr">
         <is>
           <t>592305</t>
         </is>
+      </c>
+      <c r="AB96" t="n">
+        <v>41.91201493351629</v>
       </c>
     </row>
     <row r="97">
@@ -9144,11 +9334,13 @@
       <c r="X97" t="inlineStr"/>
       <c r="Y97" t="inlineStr"/>
       <c r="Z97" t="inlineStr"/>
-      <c r="AA97" t="inlineStr"/>
-      <c r="AB97" t="inlineStr">
+      <c r="AA97" t="inlineStr">
         <is>
           <t>592315</t>
         </is>
+      </c>
+      <c r="AB97" t="n">
+        <v>70.70612613426273</v>
       </c>
     </row>
     <row r="98">
@@ -9228,11 +9420,13 @@
       <c r="X98" t="inlineStr"/>
       <c r="Y98" t="inlineStr"/>
       <c r="Z98" t="inlineStr"/>
-      <c r="AA98" t="inlineStr"/>
-      <c r="AB98" t="inlineStr">
+      <c r="AA98" t="inlineStr">
         <is>
           <t>592052</t>
         </is>
+      </c>
+      <c r="AB98" t="n">
+        <v>56.15700798713841</v>
       </c>
     </row>
     <row r="99">
@@ -9312,11 +9506,13 @@
       <c r="X99" t="inlineStr"/>
       <c r="Y99" t="inlineStr"/>
       <c r="Z99" t="inlineStr"/>
-      <c r="AA99" t="inlineStr"/>
-      <c r="AB99" t="inlineStr">
+      <c r="AA99" t="inlineStr">
         <is>
           <t>592353</t>
         </is>
+      </c>
+      <c r="AB99" t="n">
+        <v>55.79246449666994</v>
       </c>
     </row>
     <row r="100">
@@ -9396,11 +9592,13 @@
       <c r="X100" t="inlineStr"/>
       <c r="Y100" t="inlineStr"/>
       <c r="Z100" t="inlineStr"/>
-      <c r="AA100" t="inlineStr"/>
-      <c r="AB100" t="inlineStr">
+      <c r="AA100" t="inlineStr">
         <is>
           <t>592324</t>
         </is>
+      </c>
+      <c r="AB100" t="n">
+        <v>65.93475017680478</v>
       </c>
     </row>
     <row r="101">
@@ -9480,11 +9678,13 @@
       <c r="X101" t="inlineStr"/>
       <c r="Y101" t="inlineStr"/>
       <c r="Z101" t="inlineStr"/>
-      <c r="AA101" t="inlineStr"/>
-      <c r="AB101" t="inlineStr">
+      <c r="AA101" t="inlineStr">
         <is>
           <t>592378</t>
         </is>
+      </c>
+      <c r="AB101" t="n">
+        <v>35.49376434405512</v>
       </c>
     </row>
     <row r="102">
@@ -9564,11 +9764,13 @@
       <c r="X102" t="inlineStr"/>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr"/>
-      <c r="AA102" t="inlineStr"/>
-      <c r="AB102" t="inlineStr">
+      <c r="AA102" t="inlineStr">
         <is>
           <t>592339</t>
         </is>
+      </c>
+      <c r="AB102" t="n">
+        <v>62.55686848770559</v>
       </c>
     </row>
     <row r="103">
@@ -9648,11 +9850,13 @@
       <c r="X103" t="inlineStr"/>
       <c r="Y103" t="inlineStr"/>
       <c r="Z103" t="inlineStr"/>
-      <c r="AA103" t="inlineStr"/>
-      <c r="AB103" t="inlineStr">
+      <c r="AA103" t="inlineStr">
         <is>
           <t>592129</t>
         </is>
+      </c>
+      <c r="AB103" t="n">
+        <v>48.18483993222593</v>
       </c>
     </row>
     <row r="104">
@@ -9732,11 +9936,13 @@
       <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr"/>
       <c r="Z104" t="inlineStr"/>
-      <c r="AA104" t="inlineStr"/>
-      <c r="AB104" t="inlineStr">
+      <c r="AA104" t="inlineStr">
         <is>
           <t>592101</t>
         </is>
+      </c>
+      <c r="AB104" t="n">
+        <v>48.50036505453044</v>
       </c>
     </row>
     <row r="105">
@@ -9816,11 +10022,13 @@
       <c r="X105" t="inlineStr"/>
       <c r="Y105" t="inlineStr"/>
       <c r="Z105" t="inlineStr"/>
-      <c r="AA105" t="inlineStr"/>
-      <c r="AB105" t="inlineStr">
+      <c r="AA105" t="inlineStr">
         <is>
           <t>592222</t>
         </is>
+      </c>
+      <c r="AB105" t="n">
+        <v>48.82405714366423</v>
       </c>
     </row>
     <row r="106">
@@ -9900,11 +10108,13 @@
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr"/>
       <c r="Z106" t="inlineStr"/>
-      <c r="AA106" t="inlineStr"/>
-      <c r="AB106" t="inlineStr">
+      <c r="AA106" t="inlineStr">
         <is>
           <t>592115</t>
         </is>
+      </c>
+      <c r="AB106" t="n">
+        <v>42.08566962870098</v>
       </c>
     </row>
     <row r="107">
@@ -9984,11 +10194,13 @@
       <c r="X107" t="inlineStr"/>
       <c r="Y107" t="inlineStr"/>
       <c r="Z107" t="inlineStr"/>
-      <c r="AA107" t="inlineStr"/>
-      <c r="AB107" t="inlineStr">
+      <c r="AA107" t="inlineStr">
         <is>
           <t>592065</t>
         </is>
+      </c>
+      <c r="AB107" t="n">
+        <v>51.94526295590641</v>
       </c>
     </row>
     <row r="108">
@@ -10068,11 +10280,13 @@
       <c r="X108" t="inlineStr"/>
       <c r="Y108" t="inlineStr"/>
       <c r="Z108" t="inlineStr"/>
-      <c r="AA108" t="inlineStr"/>
-      <c r="AB108" t="inlineStr">
+      <c r="AA108" t="inlineStr">
         <is>
           <t>592180</t>
         </is>
+      </c>
+      <c r="AB108" t="n">
+        <v>55.62393534386633</v>
       </c>
     </row>
     <row r="109">
@@ -10152,11 +10366,13 @@
       <c r="X109" t="inlineStr"/>
       <c r="Y109" t="inlineStr"/>
       <c r="Z109" t="inlineStr"/>
-      <c r="AA109" t="inlineStr"/>
-      <c r="AB109" t="inlineStr">
+      <c r="AA109" t="inlineStr">
         <is>
           <t>592225</t>
         </is>
+      </c>
+      <c r="AB109" t="n">
+        <v>58.95157666997726</v>
       </c>
     </row>
     <row r="110">
@@ -10236,11 +10452,13 @@
       <c r="X110" t="inlineStr"/>
       <c r="Y110" t="inlineStr"/>
       <c r="Z110" t="inlineStr"/>
-      <c r="AA110" t="inlineStr"/>
-      <c r="AB110" t="inlineStr">
+      <c r="AA110" t="inlineStr">
         <is>
           <t>592156</t>
         </is>
+      </c>
+      <c r="AB110" t="n">
+        <v>61.68991897543837</v>
       </c>
     </row>
     <row r="111">
@@ -10320,11 +10538,13 @@
       <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr"/>
       <c r="Z111" t="inlineStr"/>
-      <c r="AA111" t="inlineStr"/>
-      <c r="AB111" t="inlineStr">
+      <c r="AA111" t="inlineStr">
         <is>
           <t>592293</t>
         </is>
+      </c>
+      <c r="AB111" t="n">
+        <v>42.51564615776595</v>
       </c>
     </row>
     <row r="112">
@@ -10404,11 +10624,13 @@
       <c r="X112" t="inlineStr"/>
       <c r="Y112" t="inlineStr"/>
       <c r="Z112" t="inlineStr"/>
-      <c r="AA112" t="inlineStr"/>
-      <c r="AB112" t="inlineStr">
+      <c r="AA112" t="inlineStr">
         <is>
           <t>592141</t>
         </is>
+      </c>
+      <c r="AB112" t="n">
+        <v>43.63977691743113</v>
       </c>
     </row>
     <row r="113">
@@ -10488,11 +10710,13 @@
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr"/>
       <c r="Z113" t="inlineStr"/>
-      <c r="AA113" t="inlineStr"/>
-      <c r="AB113" t="inlineStr">
+      <c r="AA113" t="inlineStr">
         <is>
           <t>592087</t>
         </is>
+      </c>
+      <c r="AB113" t="n">
+        <v>48.27107341587141</v>
       </c>
     </row>
     <row r="114">
@@ -10572,11 +10796,13 @@
       <c r="X114" t="inlineStr"/>
       <c r="Y114" t="inlineStr"/>
       <c r="Z114" t="inlineStr"/>
-      <c r="AA114" t="inlineStr"/>
-      <c r="AB114" t="inlineStr">
+      <c r="AA114" t="inlineStr">
         <is>
           <t>592041</t>
         </is>
+      </c>
+      <c r="AB114" t="n">
+        <v>55.68533253151493</v>
       </c>
     </row>
     <row r="115">
@@ -10656,11 +10882,13 @@
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr"/>
       <c r="Z115" t="inlineStr"/>
-      <c r="AA115" t="inlineStr"/>
-      <c r="AB115" t="inlineStr">
+      <c r="AA115" t="inlineStr">
         <is>
           <t>592043</t>
         </is>
+      </c>
+      <c r="AB115" t="n">
+        <v>46.55285938373989</v>
       </c>
     </row>
     <row r="116">
@@ -10740,11 +10968,13 @@
       <c r="X116" t="inlineStr"/>
       <c r="Y116" t="inlineStr"/>
       <c r="Z116" t="inlineStr"/>
-      <c r="AA116" t="inlineStr"/>
-      <c r="AB116" t="inlineStr">
+      <c r="AA116" t="inlineStr">
         <is>
           <t>592064</t>
         </is>
+      </c>
+      <c r="AB116" t="n">
+        <v>28.78285344011537</v>
       </c>
     </row>
     <row r="117">
@@ -10824,11 +11054,13 @@
       <c r="X117" t="inlineStr"/>
       <c r="Y117" t="inlineStr"/>
       <c r="Z117" t="inlineStr"/>
-      <c r="AA117" t="inlineStr"/>
-      <c r="AB117" t="inlineStr">
+      <c r="AA117" t="inlineStr">
         <is>
           <t>592046</t>
         </is>
+      </c>
+      <c r="AB117" t="n">
+        <v>40.26096003557048</v>
       </c>
     </row>
     <row r="118">
@@ -10908,11 +11140,13 @@
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr"/>
       <c r="Z118" t="inlineStr"/>
-      <c r="AA118" t="inlineStr"/>
-      <c r="AB118" t="inlineStr">
+      <c r="AA118" t="inlineStr">
         <is>
           <t>592046</t>
         </is>
+      </c>
+      <c r="AB118" t="n">
+        <v>40.26096003557048</v>
       </c>
     </row>
     <row r="119">
@@ -10992,11 +11226,13 @@
       <c r="X119" t="inlineStr"/>
       <c r="Y119" t="inlineStr"/>
       <c r="Z119" t="inlineStr"/>
-      <c r="AA119" t="inlineStr"/>
-      <c r="AB119" t="inlineStr">
+      <c r="AA119" t="inlineStr">
         <is>
           <t>592004</t>
         </is>
+      </c>
+      <c r="AB119" t="n">
+        <v>38.62830546324884</v>
       </c>
     </row>
     <row r="120">
@@ -11076,11 +11312,13 @@
       <c r="X120" t="inlineStr"/>
       <c r="Y120" t="inlineStr"/>
       <c r="Z120" t="inlineStr"/>
-      <c r="AA120" t="inlineStr"/>
-      <c r="AB120" t="inlineStr">
+      <c r="AA120" t="inlineStr">
         <is>
           <t>592037</t>
         </is>
+      </c>
+      <c r="AB120" t="n">
+        <v>47.60443554531614</v>
       </c>
     </row>
     <row r="121">
@@ -11160,11 +11398,13 @@
       <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr"/>
       <c r="Z121" t="inlineStr"/>
-      <c r="AA121" t="inlineStr"/>
-      <c r="AB121" t="inlineStr">
+      <c r="AA121" t="inlineStr">
         <is>
           <t>592037</t>
         </is>
+      </c>
+      <c r="AB121" t="n">
+        <v>47.60443554531614</v>
       </c>
     </row>
     <row r="122">
@@ -11244,11 +11484,13 @@
       <c r="X122" t="inlineStr"/>
       <c r="Y122" t="inlineStr"/>
       <c r="Z122" t="inlineStr"/>
-      <c r="AA122" t="inlineStr"/>
-      <c r="AB122" t="inlineStr">
+      <c r="AA122" t="inlineStr">
         <is>
           <t>592073</t>
         </is>
+      </c>
+      <c r="AB122" t="n">
+        <v>38.09610849251812</v>
       </c>
     </row>
     <row r="123">
@@ -11328,11 +11570,13 @@
       <c r="X123" t="inlineStr"/>
       <c r="Y123" t="inlineStr"/>
       <c r="Z123" t="inlineStr"/>
-      <c r="AA123" t="inlineStr"/>
-      <c r="AB123" t="inlineStr">
+      <c r="AA123" t="inlineStr">
         <is>
           <t>592227</t>
         </is>
+      </c>
+      <c r="AB123" t="n">
+        <v>35.84967061566433</v>
       </c>
     </row>
     <row r="124">
@@ -11412,11 +11656,13 @@
       <c r="X124" t="inlineStr"/>
       <c r="Y124" t="inlineStr"/>
       <c r="Z124" t="inlineStr"/>
-      <c r="AA124" t="inlineStr"/>
-      <c r="AB124" t="inlineStr">
+      <c r="AA124" t="inlineStr">
         <is>
           <t>592223</t>
         </is>
+      </c>
+      <c r="AB124" t="n">
+        <v>46.88581586268426</v>
       </c>
     </row>
     <row r="125">
@@ -11496,11 +11742,13 @@
       <c r="X125" t="inlineStr"/>
       <c r="Y125" t="inlineStr"/>
       <c r="Z125" t="inlineStr"/>
-      <c r="AA125" t="inlineStr"/>
-      <c r="AB125" t="inlineStr">
+      <c r="AA125" t="inlineStr">
         <is>
           <t>592231</t>
         </is>
+      </c>
+      <c r="AB125" t="n">
+        <v>51.2080861390158</v>
       </c>
     </row>
     <row r="126">
@@ -11580,11 +11828,13 @@
       <c r="X126" t="inlineStr"/>
       <c r="Y126" t="inlineStr"/>
       <c r="Z126" t="inlineStr"/>
-      <c r="AA126" t="inlineStr"/>
-      <c r="AB126" t="inlineStr">
+      <c r="AA126" t="inlineStr">
         <is>
           <t>592273</t>
         </is>
+      </c>
+      <c r="AB126" t="n">
+        <v>44.75623909743305</v>
       </c>
     </row>
     <row r="127">
@@ -11664,11 +11914,13 @@
       <c r="X127" t="inlineStr"/>
       <c r="Y127" t="inlineStr"/>
       <c r="Z127" t="inlineStr"/>
-      <c r="AA127" t="inlineStr"/>
-      <c r="AB127" t="inlineStr">
+      <c r="AA127" t="inlineStr">
         <is>
           <t>592269</t>
         </is>
+      </c>
+      <c r="AB127" t="n">
+        <v>38.4857211629195</v>
       </c>
     </row>
     <row r="128">
@@ -11748,11 +12000,13 @@
       <c r="X128" t="inlineStr"/>
       <c r="Y128" t="inlineStr"/>
       <c r="Z128" t="inlineStr"/>
-      <c r="AA128" t="inlineStr"/>
-      <c r="AB128" t="inlineStr">
+      <c r="AA128" t="inlineStr">
         <is>
           <t>592299</t>
         </is>
+      </c>
+      <c r="AB128" t="n">
+        <v>38.02881287743782</v>
       </c>
     </row>
     <row r="129">
@@ -11832,11 +12086,13 @@
       <c r="X129" t="inlineStr"/>
       <c r="Y129" t="inlineStr"/>
       <c r="Z129" t="inlineStr"/>
-      <c r="AA129" t="inlineStr"/>
-      <c r="AB129" t="inlineStr">
+      <c r="AA129" t="inlineStr">
         <is>
           <t>592105</t>
         </is>
+      </c>
+      <c r="AB129" t="n">
+        <v>42.69161633319679</v>
       </c>
     </row>
     <row r="130">
@@ -11916,11 +12172,13 @@
       <c r="X130" t="inlineStr"/>
       <c r="Y130" t="inlineStr"/>
       <c r="Z130" t="inlineStr"/>
-      <c r="AA130" t="inlineStr"/>
-      <c r="AB130" t="inlineStr">
+      <c r="AA130" t="inlineStr">
         <is>
           <t>592220</t>
         </is>
+      </c>
+      <c r="AB130" t="n">
+        <v>42.92451945516472</v>
       </c>
     </row>
     <row r="131">
@@ -12000,11 +12258,13 @@
       <c r="X131" t="inlineStr"/>
       <c r="Y131" t="inlineStr"/>
       <c r="Z131" t="inlineStr"/>
-      <c r="AA131" t="inlineStr"/>
-      <c r="AB131" t="inlineStr">
+      <c r="AA131" t="inlineStr">
         <is>
           <t>592198</t>
         </is>
+      </c>
+      <c r="AB131" t="n">
+        <v>40.16479905872414</v>
       </c>
     </row>
     <row r="132">
@@ -12084,11 +12344,13 @@
       <c r="X132" t="inlineStr"/>
       <c r="Y132" t="inlineStr"/>
       <c r="Z132" t="inlineStr"/>
-      <c r="AA132" t="inlineStr"/>
-      <c r="AB132" t="inlineStr">
+      <c r="AA132" t="inlineStr">
         <is>
           <t>592092</t>
         </is>
+      </c>
+      <c r="AB132" t="n">
+        <v>54.14554217891045</v>
       </c>
     </row>
     <row r="133">
@@ -12168,11 +12430,13 @@
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr"/>
       <c r="Z133" t="inlineStr"/>
-      <c r="AA133" t="inlineStr"/>
-      <c r="AB133" t="inlineStr">
+      <c r="AA133" t="inlineStr">
         <is>
           <t>592092</t>
         </is>
+      </c>
+      <c r="AB133" t="n">
+        <v>54.14554217891045</v>
       </c>
     </row>
     <row r="134">
@@ -12252,11 +12516,13 @@
       <c r="X134" t="inlineStr"/>
       <c r="Y134" t="inlineStr"/>
       <c r="Z134" t="inlineStr"/>
-      <c r="AA134" t="inlineStr"/>
-      <c r="AB134" t="inlineStr">
+      <c r="AA134" t="inlineStr">
         <is>
           <t>592206</t>
         </is>
+      </c>
+      <c r="AB134" t="n">
+        <v>34.63030631687734</v>
       </c>
     </row>
     <row r="135">
@@ -12336,11 +12602,13 @@
       <c r="X135" t="inlineStr"/>
       <c r="Y135" t="inlineStr"/>
       <c r="Z135" t="inlineStr"/>
-      <c r="AA135" t="inlineStr"/>
-      <c r="AB135" t="inlineStr">
+      <c r="AA135" t="inlineStr">
         <is>
           <t>592249</t>
         </is>
+      </c>
+      <c r="AB135" t="n">
+        <v>44.89996935838486</v>
       </c>
     </row>
     <row r="136">
@@ -12420,11 +12688,13 @@
       <c r="X136" t="inlineStr"/>
       <c r="Y136" t="inlineStr"/>
       <c r="Z136" t="inlineStr"/>
-      <c r="AA136" t="inlineStr"/>
-      <c r="AB136" t="inlineStr">
+      <c r="AA136" t="inlineStr">
         <is>
           <t>592162</t>
         </is>
+      </c>
+      <c r="AB136" t="n">
+        <v>43.93419906095097</v>
       </c>
     </row>
     <row r="137">
@@ -12504,11 +12774,13 @@
       <c r="X137" t="inlineStr"/>
       <c r="Y137" t="inlineStr"/>
       <c r="Z137" t="inlineStr"/>
-      <c r="AA137" t="inlineStr"/>
-      <c r="AB137" t="inlineStr">
+      <c r="AA137" t="inlineStr">
         <is>
           <t>592317</t>
         </is>
+      </c>
+      <c r="AB137" t="n">
+        <v>62.73974732172039</v>
       </c>
     </row>
     <row r="138">
@@ -12588,11 +12860,13 @@
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr"/>
       <c r="Z138" t="inlineStr"/>
-      <c r="AA138" t="inlineStr"/>
-      <c r="AB138" t="inlineStr">
+      <c r="AA138" t="inlineStr">
         <is>
           <t>592323</t>
         </is>
+      </c>
+      <c r="AB138" t="n">
+        <v>56.82593529734338</v>
       </c>
     </row>
     <row r="139">
@@ -12672,11 +12946,13 @@
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr"/>
       <c r="Z139" t="inlineStr"/>
-      <c r="AA139" t="inlineStr"/>
-      <c r="AB139" t="inlineStr">
+      <c r="AA139" t="inlineStr">
         <is>
           <t>592325</t>
         </is>
+      </c>
+      <c r="AB139" t="n">
+        <v>51.97156457320585</v>
       </c>
     </row>
     <row r="140">
@@ -12756,11 +13032,13 @@
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr"/>
       <c r="Z140" t="inlineStr"/>
-      <c r="AA140" t="inlineStr"/>
-      <c r="AB140" t="inlineStr">
+      <c r="AA140" t="inlineStr">
         <is>
           <t>592365</t>
         </is>
+      </c>
+      <c r="AB140" t="n">
+        <v>34.71279366258031</v>
       </c>
     </row>
     <row r="141">
@@ -12840,11 +13118,13 @@
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr"/>
       <c r="Z141" t="inlineStr"/>
-      <c r="AA141" t="inlineStr"/>
-      <c r="AB141" t="inlineStr">
+      <c r="AA141" t="inlineStr">
         <is>
           <t>592344</t>
         </is>
+      </c>
+      <c r="AB141" t="n">
+        <v>16.82978356315537</v>
       </c>
     </row>
     <row r="142">
@@ -12924,11 +13204,13 @@
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr"/>
       <c r="Z142" t="inlineStr"/>
-      <c r="AA142" t="inlineStr"/>
-      <c r="AB142" t="inlineStr">
+      <c r="AA142" t="inlineStr">
         <is>
           <t>592359</t>
         </is>
+      </c>
+      <c r="AB142" t="n">
+        <v>48.86662529556703</v>
       </c>
     </row>
     <row r="143">
@@ -13008,11 +13290,13 @@
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr"/>
       <c r="Z143" t="inlineStr"/>
-      <c r="AA143" t="inlineStr"/>
-      <c r="AB143" t="inlineStr">
+      <c r="AA143" t="inlineStr">
         <is>
           <t>592246</t>
         </is>
+      </c>
+      <c r="AB143" t="n">
+        <v>48.48989580379418</v>
       </c>
     </row>
     <row r="144">
@@ -13092,11 +13376,13 @@
       <c r="X144" t="inlineStr"/>
       <c r="Y144" t="inlineStr"/>
       <c r="Z144" t="inlineStr"/>
-      <c r="AA144" t="inlineStr"/>
-      <c r="AB144" t="inlineStr">
+      <c r="AA144" t="inlineStr">
         <is>
           <t>592005</t>
         </is>
+      </c>
+      <c r="AB144" t="n">
+        <v>52.45513538310598</v>
       </c>
     </row>
     <row r="145">
@@ -13176,11 +13462,13 @@
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="inlineStr"/>
       <c r="Z145" t="inlineStr"/>
-      <c r="AA145" t="inlineStr"/>
-      <c r="AB145" t="inlineStr">
+      <c r="AA145" t="inlineStr">
         <is>
           <t>592132</t>
         </is>
+      </c>
+      <c r="AB145" t="n">
+        <v>50.12173210626537</v>
       </c>
     </row>
     <row r="146">
@@ -13260,11 +13548,13 @@
       <c r="X146" t="inlineStr"/>
       <c r="Y146" t="inlineStr"/>
       <c r="Z146" t="inlineStr"/>
-      <c r="AA146" t="inlineStr"/>
-      <c r="AB146" t="inlineStr">
+      <c r="AA146" t="inlineStr">
         <is>
           <t>592361</t>
         </is>
+      </c>
+      <c r="AB146" t="n">
+        <v>51.64905585832408</v>
       </c>
     </row>
     <row r="147">
@@ -13344,11 +13634,13 @@
       <c r="X147" t="inlineStr"/>
       <c r="Y147" t="inlineStr"/>
       <c r="Z147" t="inlineStr"/>
-      <c r="AA147" t="inlineStr"/>
-      <c r="AB147" t="inlineStr">
+      <c r="AA147" t="inlineStr">
         <is>
           <t>592074</t>
         </is>
+      </c>
+      <c r="AB147" t="n">
+        <v>40.84573233660999</v>
       </c>
     </row>
     <row r="148">
@@ -13428,11 +13720,13 @@
       <c r="X148" t="inlineStr"/>
       <c r="Y148" t="inlineStr"/>
       <c r="Z148" t="inlineStr"/>
-      <c r="AA148" t="inlineStr"/>
-      <c r="AB148" t="inlineStr">
+      <c r="AA148" t="inlineStr">
         <is>
           <t>592334</t>
         </is>
+      </c>
+      <c r="AB148" t="n">
+        <v>37.41961875184389</v>
       </c>
     </row>
     <row r="149">
@@ -13512,11 +13806,13 @@
       <c r="X149" t="inlineStr"/>
       <c r="Y149" t="inlineStr"/>
       <c r="Z149" t="inlineStr"/>
-      <c r="AA149" t="inlineStr"/>
-      <c r="AB149" t="inlineStr">
+      <c r="AA149" t="inlineStr">
         <is>
           <t>592016</t>
         </is>
+      </c>
+      <c r="AB149" t="n">
+        <v>44.98594091218243</v>
       </c>
     </row>
     <row r="150">
@@ -13596,11 +13892,13 @@
       <c r="X150" t="inlineStr"/>
       <c r="Y150" t="inlineStr"/>
       <c r="Z150" t="inlineStr"/>
-      <c r="AA150" t="inlineStr"/>
-      <c r="AB150" t="inlineStr">
+      <c r="AA150" t="inlineStr">
         <is>
           <t>592253</t>
         </is>
+      </c>
+      <c r="AB150" t="n">
+        <v>62.3287590104805</v>
       </c>
     </row>
     <row r="151">
@@ -13680,11 +13978,13 @@
       <c r="X151" t="inlineStr"/>
       <c r="Y151" t="inlineStr"/>
       <c r="Z151" t="inlineStr"/>
-      <c r="AA151" t="inlineStr"/>
-      <c r="AB151" t="inlineStr">
+      <c r="AA151" t="inlineStr">
         <is>
           <t>592139</t>
         </is>
+      </c>
+      <c r="AB151" t="n">
+        <v>63.04106431069755</v>
       </c>
     </row>
     <row r="152">
@@ -13764,11 +14064,13 @@
       <c r="X152" t="inlineStr"/>
       <c r="Y152" t="inlineStr"/>
       <c r="Z152" t="inlineStr"/>
-      <c r="AA152" t="inlineStr"/>
-      <c r="AB152" t="inlineStr">
+      <c r="AA152" t="inlineStr">
         <is>
           <t>592014</t>
         </is>
+      </c>
+      <c r="AB152" t="n">
+        <v>55.56667726163774</v>
       </c>
     </row>
     <row r="153">
@@ -13848,11 +14150,13 @@
       <c r="X153" t="inlineStr"/>
       <c r="Y153" t="inlineStr"/>
       <c r="Z153" t="inlineStr"/>
-      <c r="AA153" t="inlineStr"/>
-      <c r="AB153" t="inlineStr">
+      <c r="AA153" t="inlineStr">
         <is>
           <t>592136</t>
         </is>
+      </c>
+      <c r="AB153" t="n">
+        <v>61.70799806962501</v>
       </c>
     </row>
     <row r="154">
@@ -13932,11 +14236,13 @@
       <c r="X154" t="inlineStr"/>
       <c r="Y154" t="inlineStr"/>
       <c r="Z154" t="inlineStr"/>
-      <c r="AA154" t="inlineStr"/>
-      <c r="AB154" t="inlineStr">
+      <c r="AA154" t="inlineStr">
         <is>
           <t>592377</t>
         </is>
+      </c>
+      <c r="AB154" t="n">
+        <v>47.27323855607655</v>
       </c>
     </row>
     <row r="155">
@@ -14016,11 +14322,13 @@
       <c r="X155" t="inlineStr"/>
       <c r="Y155" t="inlineStr"/>
       <c r="Z155" t="inlineStr"/>
-      <c r="AA155" t="inlineStr"/>
-      <c r="AB155" t="inlineStr">
+      <c r="AA155" t="inlineStr">
         <is>
           <t>592368</t>
         </is>
+      </c>
+      <c r="AB155" t="n">
+        <v>46.60021045219221</v>
       </c>
     </row>
     <row r="156">
@@ -14100,11 +14408,13 @@
       <c r="X156" t="inlineStr"/>
       <c r="Y156" t="inlineStr"/>
       <c r="Z156" t="inlineStr"/>
-      <c r="AA156" t="inlineStr"/>
-      <c r="AB156" t="inlineStr">
+      <c r="AA156" t="inlineStr">
         <is>
           <t>592320</t>
         </is>
+      </c>
+      <c r="AB156" t="n">
+        <v>36.4008599384631</v>
       </c>
     </row>
     <row r="157">
@@ -14184,11 +14494,13 @@
       <c r="X157" t="inlineStr"/>
       <c r="Y157" t="inlineStr"/>
       <c r="Z157" t="inlineStr"/>
-      <c r="AA157" t="inlineStr"/>
-      <c r="AB157" t="inlineStr">
+      <c r="AA157" t="inlineStr">
         <is>
           <t>592351</t>
         </is>
+      </c>
+      <c r="AB157" t="n">
+        <v>55.60819532627404</v>
       </c>
     </row>
     <row r="158">
@@ -14268,11 +14580,13 @@
       <c r="X158" t="inlineStr"/>
       <c r="Y158" t="inlineStr"/>
       <c r="Z158" t="inlineStr"/>
-      <c r="AA158" t="inlineStr"/>
-      <c r="AB158" t="inlineStr">
+      <c r="AA158" t="inlineStr">
         <is>
           <t>592172</t>
         </is>
+      </c>
+      <c r="AB158" t="n">
+        <v>43.12164298019695</v>
       </c>
     </row>
     <row r="159">
@@ -14352,11 +14666,13 @@
       <c r="X159" t="inlineStr"/>
       <c r="Y159" t="inlineStr"/>
       <c r="Z159" t="inlineStr"/>
-      <c r="AA159" t="inlineStr"/>
-      <c r="AB159" t="inlineStr">
+      <c r="AA159" t="inlineStr">
         <is>
           <t>592172</t>
         </is>
+      </c>
+      <c r="AB159" t="n">
+        <v>43.12164298019695</v>
       </c>
     </row>
     <row r="160">
@@ -14436,11 +14752,13 @@
       <c r="X160" t="inlineStr"/>
       <c r="Y160" t="inlineStr"/>
       <c r="Z160" t="inlineStr"/>
-      <c r="AA160" t="inlineStr"/>
-      <c r="AB160" t="inlineStr">
+      <c r="AA160" t="inlineStr">
         <is>
           <t>592124</t>
         </is>
+      </c>
+      <c r="AB160" t="n">
+        <v>40.64145553340282</v>
       </c>
     </row>
     <row r="161">
@@ -14518,11 +14836,13 @@
       <c r="X161" t="inlineStr"/>
       <c r="Y161" t="inlineStr"/>
       <c r="Z161" t="inlineStr"/>
-      <c r="AA161" t="inlineStr"/>
-      <c r="AB161" t="inlineStr">
+      <c r="AA161" t="inlineStr">
         <is>
           <t>592118</t>
         </is>
+      </c>
+      <c r="AB161" t="n">
+        <v>39.86388713858987</v>
       </c>
     </row>
     <row r="162">
@@ -14600,11 +14920,13 @@
       <c r="X162" t="inlineStr"/>
       <c r="Y162" t="inlineStr"/>
       <c r="Z162" t="inlineStr"/>
-      <c r="AA162" t="inlineStr"/>
-      <c r="AB162" t="inlineStr">
+      <c r="AA162" t="inlineStr">
         <is>
           <t>592097</t>
         </is>
+      </c>
+      <c r="AB162" t="n">
+        <v>50.48954256485062</v>
       </c>
     </row>
     <row r="163">
@@ -14684,11 +15006,13 @@
       <c r="X163" t="inlineStr"/>
       <c r="Y163" t="inlineStr"/>
       <c r="Z163" t="inlineStr"/>
-      <c r="AA163" t="inlineStr"/>
-      <c r="AB163" t="inlineStr">
+      <c r="AA163" t="inlineStr">
         <is>
           <t>592235</t>
         </is>
+      </c>
+      <c r="AB163" t="n">
+        <v>53.08725031617568</v>
       </c>
     </row>
     <row r="164">
@@ -14768,11 +15092,13 @@
       <c r="X164" t="inlineStr"/>
       <c r="Y164" t="inlineStr"/>
       <c r="Z164" t="inlineStr"/>
-      <c r="AA164" t="inlineStr"/>
-      <c r="AB164" t="inlineStr">
+      <c r="AA164" t="inlineStr">
         <is>
           <t>592123</t>
         </is>
+      </c>
+      <c r="AB164" t="n">
+        <v>45.2001414226272</v>
       </c>
     </row>
     <row r="165">
@@ -14852,11 +15178,13 @@
       <c r="X165" t="inlineStr"/>
       <c r="Y165" t="inlineStr"/>
       <c r="Z165" t="inlineStr"/>
-      <c r="AA165" t="inlineStr"/>
-      <c r="AB165" t="inlineStr">
+      <c r="AA165" t="inlineStr">
         <is>
           <t>592107</t>
         </is>
+      </c>
+      <c r="AB165" t="n">
+        <v>48.16685335643782</v>
       </c>
     </row>
     <row r="166">
@@ -14936,11 +15264,13 @@
       <c r="X166" t="inlineStr"/>
       <c r="Y166" t="inlineStr"/>
       <c r="Z166" t="inlineStr"/>
-      <c r="AA166" t="inlineStr"/>
-      <c r="AB166" t="inlineStr">
+      <c r="AA166" t="inlineStr">
         <is>
           <t>592108</t>
         </is>
+      </c>
+      <c r="AB166" t="n">
+        <v>42.61425540516829</v>
       </c>
     </row>
     <row r="167">
@@ -15020,11 +15350,13 @@
       <c r="X167" t="inlineStr"/>
       <c r="Y167" t="inlineStr"/>
       <c r="Z167" t="inlineStr"/>
-      <c r="AA167" t="inlineStr"/>
-      <c r="AB167" t="inlineStr">
+      <c r="AA167" t="inlineStr">
         <is>
           <t>592055</t>
         </is>
+      </c>
+      <c r="AB167" t="n">
+        <v>42.46993249100026</v>
       </c>
     </row>
     <row r="168">
@@ -15104,11 +15436,13 @@
       <c r="X168" t="inlineStr"/>
       <c r="Y168" t="inlineStr"/>
       <c r="Z168" t="inlineStr"/>
-      <c r="AA168" t="inlineStr"/>
-      <c r="AB168" t="inlineStr">
+      <c r="AA168" t="inlineStr">
         <is>
           <t>592277</t>
         </is>
+      </c>
+      <c r="AB168" t="n">
+        <v>38.40701417106357</v>
       </c>
     </row>
     <row r="169">
@@ -15188,11 +15522,13 @@
       <c r="X169" t="inlineStr"/>
       <c r="Y169" t="inlineStr"/>
       <c r="Z169" t="inlineStr"/>
-      <c r="AA169" t="inlineStr"/>
-      <c r="AB169" t="inlineStr">
+      <c r="AA169" t="inlineStr">
         <is>
           <t>592117</t>
         </is>
+      </c>
+      <c r="AB169" t="n">
+        <v>41.27967137504851</v>
       </c>
     </row>
     <row r="170">
@@ -15272,11 +15608,13 @@
       <c r="X170" t="inlineStr"/>
       <c r="Y170" t="inlineStr"/>
       <c r="Z170" t="inlineStr"/>
-      <c r="AA170" t="inlineStr"/>
-      <c r="AB170" t="inlineStr">
+      <c r="AA170" t="inlineStr">
         <is>
           <t>592250</t>
         </is>
+      </c>
+      <c r="AB170" t="n">
+        <v>40.6374878617617</v>
       </c>
     </row>
     <row r="171">
@@ -15356,11 +15694,13 @@
       <c r="X171" t="inlineStr"/>
       <c r="Y171" t="inlineStr"/>
       <c r="Z171" t="inlineStr"/>
-      <c r="AA171" t="inlineStr"/>
-      <c r="AB171" t="inlineStr">
+      <c r="AA171" t="inlineStr">
         <is>
           <t>592148</t>
         </is>
+      </c>
+      <c r="AB171" t="n">
+        <v>38.08684472600527</v>
       </c>
     </row>
     <row r="172">
@@ -15440,11 +15780,13 @@
       <c r="X172" t="inlineStr"/>
       <c r="Y172" t="inlineStr"/>
       <c r="Z172" t="inlineStr"/>
-      <c r="AA172" t="inlineStr"/>
-      <c r="AB172" t="inlineStr">
+      <c r="AA172" t="inlineStr">
         <is>
           <t>592015</t>
         </is>
+      </c>
+      <c r="AB172" t="n">
+        <v>43.33108356621307</v>
       </c>
     </row>
     <row r="173">
@@ -15524,11 +15866,13 @@
       <c r="X173" t="inlineStr"/>
       <c r="Y173" t="inlineStr"/>
       <c r="Z173" t="inlineStr"/>
-      <c r="AA173" t="inlineStr"/>
-      <c r="AB173" t="inlineStr">
+      <c r="AA173" t="inlineStr">
         <is>
           <t>592133</t>
         </is>
+      </c>
+      <c r="AB173" t="n">
+        <v>45.59782712484886</v>
       </c>
     </row>
     <row r="174">
@@ -15608,11 +15952,13 @@
       <c r="X174" t="inlineStr"/>
       <c r="Y174" t="inlineStr"/>
       <c r="Z174" t="inlineStr"/>
-      <c r="AA174" t="inlineStr"/>
-      <c r="AB174" t="inlineStr">
+      <c r="AA174" t="inlineStr">
         <is>
           <t>592286</t>
         </is>
+      </c>
+      <c r="AB174" t="n">
+        <v>46.08862851636469</v>
       </c>
     </row>
     <row r="175">
@@ -15692,11 +16038,13 @@
       <c r="X175" t="inlineStr"/>
       <c r="Y175" t="inlineStr"/>
       <c r="Z175" t="inlineStr"/>
-      <c r="AA175" t="inlineStr"/>
-      <c r="AB175" t="inlineStr">
+      <c r="AA175" t="inlineStr">
         <is>
           <t>592079</t>
         </is>
+      </c>
+      <c r="AB175" t="n">
+        <v>31.20218338168698</v>
       </c>
     </row>
     <row r="176">
@@ -15776,11 +16124,13 @@
       <c r="X176" t="inlineStr"/>
       <c r="Y176" t="inlineStr"/>
       <c r="Z176" t="inlineStr"/>
-      <c r="AA176" t="inlineStr"/>
-      <c r="AB176" t="inlineStr">
+      <c r="AA176" t="inlineStr">
         <is>
           <t>592019</t>
         </is>
+      </c>
+      <c r="AB176" t="n">
+        <v>37.47652040214079</v>
       </c>
     </row>
     <row r="177">
@@ -15860,11 +16210,13 @@
       <c r="X177" t="inlineStr"/>
       <c r="Y177" t="inlineStr"/>
       <c r="Z177" t="inlineStr"/>
-      <c r="AA177" t="inlineStr"/>
-      <c r="AB177" t="inlineStr">
+      <c r="AA177" t="inlineStr">
         <is>
           <t>592103</t>
         </is>
+      </c>
+      <c r="AB177" t="n">
+        <v>45.90057484261069</v>
       </c>
     </row>
     <row r="178">
@@ -15944,11 +16296,13 @@
       <c r="X178" t="inlineStr"/>
       <c r="Y178" t="inlineStr"/>
       <c r="Z178" t="inlineStr"/>
-      <c r="AA178" t="inlineStr"/>
-      <c r="AB178" t="inlineStr">
+      <c r="AA178" t="inlineStr">
         <is>
           <t>592294</t>
         </is>
+      </c>
+      <c r="AB178" t="n">
+        <v>47.40155652187085</v>
       </c>
     </row>
     <row r="179">
@@ -16028,11 +16382,13 @@
       <c r="X179" t="inlineStr"/>
       <c r="Y179" t="inlineStr"/>
       <c r="Z179" t="inlineStr"/>
-      <c r="AA179" t="inlineStr"/>
-      <c r="AB179" t="inlineStr">
+      <c r="AA179" t="inlineStr">
         <is>
           <t>592091</t>
         </is>
+      </c>
+      <c r="AB179" t="n">
+        <v>44.74207179927146</v>
       </c>
     </row>
     <row r="180">
@@ -16112,11 +16468,13 @@
       <c r="X180" t="inlineStr"/>
       <c r="Y180" t="inlineStr"/>
       <c r="Z180" t="inlineStr"/>
-      <c r="AA180" t="inlineStr"/>
-      <c r="AB180" t="inlineStr">
+      <c r="AA180" t="inlineStr">
         <is>
           <t>592302</t>
         </is>
+      </c>
+      <c r="AB180" t="n">
+        <v>44.0343228797727</v>
       </c>
     </row>
     <row r="181">
@@ -16196,11 +16554,13 @@
       <c r="X181" t="inlineStr"/>
       <c r="Y181" t="inlineStr"/>
       <c r="Z181" t="inlineStr"/>
-      <c r="AA181" t="inlineStr"/>
-      <c r="AB181" t="inlineStr">
+      <c r="AA181" t="inlineStr">
         <is>
           <t>592272</t>
         </is>
+      </c>
+      <c r="AB181" t="n">
+        <v>54.20072825178515</v>
       </c>
     </row>
     <row r="182">
@@ -16280,11 +16640,13 @@
       <c r="X182" t="inlineStr"/>
       <c r="Y182" t="inlineStr"/>
       <c r="Z182" t="inlineStr"/>
-      <c r="AA182" t="inlineStr"/>
-      <c r="AB182" t="inlineStr">
+      <c r="AA182" t="inlineStr">
         <is>
           <t>592029</t>
         </is>
+      </c>
+      <c r="AB182" t="n">
+        <v>39.38800376216415</v>
       </c>
     </row>
     <row r="183">
@@ -16364,11 +16726,13 @@
       <c r="X183" t="inlineStr"/>
       <c r="Y183" t="inlineStr"/>
       <c r="Z183" t="inlineStr"/>
-      <c r="AA183" t="inlineStr"/>
-      <c r="AB183" t="inlineStr">
+      <c r="AA183" t="inlineStr">
         <is>
           <t>592291</t>
         </is>
+      </c>
+      <c r="AB183" t="n">
+        <v>42.7829066706362</v>
       </c>
     </row>
     <row r="184">
@@ -16444,11 +16808,13 @@
       <c r="X184" t="inlineStr"/>
       <c r="Y184" t="inlineStr"/>
       <c r="Z184" t="inlineStr"/>
-      <c r="AA184" t="inlineStr"/>
-      <c r="AB184" t="inlineStr">
+      <c r="AA184" t="inlineStr">
         <is>
           <t>592158</t>
         </is>
+      </c>
+      <c r="AB184" t="n">
+        <v>45.5591915641724</v>
       </c>
     </row>
   </sheetData>

--- a/Results_isofys/Numex_preliminar_base.xlsx
+++ b/Results_isofys/Numex_preliminar_base.xlsx
@@ -6307,14 +6307,14 @@
       <c r="I64" t="n">
         <v>0.4786645153959252</v>
       </c>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="n">
+        <v>-33.6</v>
+      </c>
       <c r="K64" t="n">
         <v>0.01461355893199637</v>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>p11-5785</t>
-        </is>
+      <c r="L64" t="n">
+        <v>1.37</v>
       </c>
       <c r="M64" t="n">
         <v>0.4698293457032828</v>

--- a/Results_isofys/Numex_preliminar_base.xlsx
+++ b/Results_isofys/Numex_preliminar_base.xlsx
@@ -12955,7 +12955,11 @@
       <c r="A89" s="1" t="n">
         <v>87</v>
       </c>
-      <c r="B89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C89" t="n">
         <v>88</v>
       </c>
@@ -13116,7 +13120,11 @@
       <c r="A90" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="B90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="C90" t="n">
         <v>8386</v>
       </c>
@@ -13277,7 +13285,11 @@
       <c r="A91" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="B91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C91" t="n">
         <v>9096</v>
       </c>
@@ -13438,7 +13450,11 @@
       <c r="A92" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="C92" t="n">
         <v>721</v>
       </c>
@@ -13599,7 +13615,11 @@
       <c r="A93" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="B93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="C93" t="n">
         <v>7994</v>
       </c>
@@ -13760,7 +13780,11 @@
       <c r="A94" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="B94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="C94" t="n">
         <v>795</v>
       </c>
@@ -13921,7 +13945,11 @@
       <c r="A95" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="B95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="C95" t="n">
         <v>881</v>
       </c>
@@ -14082,7 +14110,11 @@
       <c r="A96" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="B96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="C96" t="n">
         <v>693</v>
       </c>
@@ -14243,7 +14275,11 @@
       <c r="A97" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="B97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="C97" t="n">
         <v>740</v>
       </c>
@@ -14404,7 +14440,11 @@
       <c r="A98" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="B98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="C98" t="n">
         <v>8384</v>
       </c>
@@ -14565,7 +14605,11 @@
       <c r="A99" s="1" t="n">
         <v>97</v>
       </c>
-      <c r="B99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="C99" t="n">
         <v>8954</v>
       </c>
@@ -14726,7 +14770,11 @@
       <c r="A100" s="1" t="n">
         <v>98</v>
       </c>
-      <c r="B100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="C100" t="n">
         <v>764</v>
       </c>
@@ -14887,7 +14935,11 @@
       <c r="A101" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="B101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="C101" t="n">
         <v>4955</v>
       </c>
@@ -15048,7 +15100,11 @@
       <c r="A102" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="B102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C102" t="n">
         <v>7645</v>
       </c>
@@ -15209,7 +15265,11 @@
       <c r="A103" s="1" t="n">
         <v>101</v>
       </c>
-      <c r="B103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C103" t="n">
         <v>6021</v>
       </c>
@@ -15370,7 +15430,11 @@
       <c r="A104" s="1" t="n">
         <v>102</v>
       </c>
-      <c r="B104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C104" t="n">
         <v>205</v>
       </c>
@@ -15531,7 +15595,11 @@
       <c r="A105" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="B105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C105" t="n">
         <v>4898</v>
       </c>
@@ -15692,7 +15760,11 @@
       <c r="A106" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="B106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="C106" t="n">
         <v>8381</v>
       </c>
@@ -15853,7 +15925,11 @@
       <c r="A107" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="B107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="C107" t="n">
         <v>9090</v>
       </c>
@@ -16014,7 +16090,11 @@
       <c r="A108" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="B108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="C108" t="n">
         <v>9080</v>
       </c>
@@ -16175,7 +16255,11 @@
       <c r="A109" s="1" t="n">
         <v>107</v>
       </c>
-      <c r="B109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="C109" t="n">
         <v>580</v>
       </c>
@@ -16336,7 +16420,11 @@
       <c r="A110" s="1" t="n">
         <v>108</v>
       </c>
-      <c r="B110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="C110" t="n">
         <v>378</v>
       </c>
@@ -16497,7 +16585,11 @@
       <c r="A111" s="1" t="n">
         <v>109</v>
       </c>
-      <c r="B111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C111" t="n">
         <v>9738</v>
       </c>
@@ -16658,7 +16750,11 @@
       <c r="A112" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="B112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="C112" t="n">
         <v>356</v>
       </c>
@@ -16819,7 +16915,11 @@
       <c r="A113" s="1" t="n">
         <v>111</v>
       </c>
-      <c r="B113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="C113" t="n">
         <v>172</v>
       </c>
@@ -16980,7 +17080,11 @@
       <c r="A114" s="1" t="n">
         <v>112</v>
       </c>
-      <c r="B114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C114" t="n">
         <v>9084</v>
       </c>
@@ -17141,7 +17245,11 @@
       <c r="A115" s="1" t="n">
         <v>113</v>
       </c>
-      <c r="B115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="C115" t="n">
         <v>254</v>
       </c>
@@ -17302,7 +17410,11 @@
       <c r="A116" s="1" t="n">
         <v>114</v>
       </c>
-      <c r="B116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="C116" t="n">
         <v>8396</v>
       </c>
@@ -17463,7 +17575,11 @@
       <c r="A117" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="B117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C117" t="n">
         <v>7924</v>
       </c>
@@ -17624,7 +17740,11 @@
       <c r="A118" s="1" t="n">
         <v>116</v>
       </c>
-      <c r="B118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="C118" t="n">
         <v>7924</v>
       </c>
@@ -17785,7 +17905,11 @@
       <c r="A119" s="1" t="n">
         <v>117</v>
       </c>
-      <c r="B119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="C119" t="n">
         <v>69</v>
       </c>
@@ -17946,7 +18070,11 @@
       <c r="A120" s="1" t="n">
         <v>118</v>
       </c>
-      <c r="B120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C120" t="n">
         <v>7922</v>
       </c>
@@ -18107,7 +18235,11 @@
       <c r="A121" s="1" t="n">
         <v>119</v>
       </c>
-      <c r="B121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="C121" t="n">
         <v>7922</v>
       </c>
@@ -18268,7 +18400,11 @@
       <c r="A122" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="B122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="C122" t="n">
         <v>141</v>
       </c>
@@ -18429,7 +18565,11 @@
       <c r="A123" s="1" t="n">
         <v>121</v>
       </c>
-      <c r="B123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="C123" t="n">
         <v>587</v>
       </c>
@@ -18590,7 +18730,11 @@
       <c r="A124" s="1" t="n">
         <v>122</v>
       </c>
-      <c r="B124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="C124" t="n">
         <v>575</v>
       </c>
@@ -18751,7 +18895,11 @@
       <c r="A125" s="1" t="n">
         <v>123</v>
       </c>
-      <c r="B125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="C125" t="n">
         <v>596</v>
       </c>
@@ -18912,7 +19060,11 @@
       <c r="A126" s="1" t="n">
         <v>124</v>
       </c>
-      <c r="B126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="C126" t="n">
         <v>631</v>
       </c>
@@ -19073,7 +19225,11 @@
       <c r="A127" s="1" t="n">
         <v>125</v>
       </c>
-      <c r="B127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C127" t="n">
         <v>4445</v>
       </c>
@@ -19234,7 +19390,11 @@
       <c r="A128" s="1" t="n">
         <v>126</v>
       </c>
-      <c r="B128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="C128" t="n">
         <v>6976</v>
       </c>
@@ -19395,7 +19555,11 @@
       <c r="A129" s="1" t="n">
         <v>127</v>
       </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="C129" t="n">
         <v>213</v>
       </c>
@@ -19556,7 +19720,11 @@
       <c r="A130" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="B130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C130" t="n">
         <v>569</v>
       </c>
@@ -19717,7 +19885,11 @@
       <c r="A131" s="1" t="n">
         <v>129</v>
       </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C131" t="n">
         <v>8361</v>
       </c>
@@ -19878,7 +20050,11 @@
       <c r="A132" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="B132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="C132" t="n">
         <v>191</v>
       </c>
@@ -20039,7 +20215,11 @@
       <c r="A133" s="1" t="n">
         <v>131</v>
       </c>
-      <c r="B133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="C133" t="n">
         <v>191</v>
       </c>
@@ -20200,7 +20380,11 @@
       <c r="A134" s="1" t="n">
         <v>132</v>
       </c>
-      <c r="B134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="C134" t="n">
         <v>4469</v>
       </c>
@@ -20361,7 +20545,11 @@
       <c r="A135" s="1" t="n">
         <v>133</v>
       </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="C135" t="n">
         <v>4894</v>
       </c>
@@ -20522,7 +20710,11 @@
       <c r="A136" s="1" t="n">
         <v>134</v>
       </c>
-      <c r="B136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="C136" t="n">
         <v>389</v>
       </c>
@@ -20683,7 +20875,11 @@
       <c r="A137" s="1" t="n">
         <v>135</v>
       </c>
-      <c r="B137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="C137" t="n">
         <v>746</v>
       </c>
@@ -20844,7 +21040,11 @@
       <c r="A138" s="1" t="n">
         <v>136</v>
       </c>
-      <c r="B138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="C138" t="n">
         <v>763</v>
       </c>
@@ -21005,7 +21205,11 @@
       <c r="A139" s="1" t="n">
         <v>137</v>
       </c>
-      <c r="B139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="C139" t="n">
         <v>768</v>
       </c>
@@ -21166,7 +21370,11 @@
       <c r="A140" s="1" t="n">
         <v>138</v>
       </c>
-      <c r="B140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="C140" t="n">
         <v>4940</v>
       </c>
@@ -21327,7 +21535,11 @@
       <c r="A141" s="1" t="n">
         <v>139</v>
       </c>
-      <c r="B141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="C141" t="n">
         <v>902</v>
       </c>
@@ -21488,7 +21700,11 @@
       <c r="A142" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="B142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C142" t="n">
         <v>5880</v>
       </c>
@@ -21649,7 +21865,11 @@
       <c r="A143" s="1" t="n">
         <v>141</v>
       </c>
-      <c r="B143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="C143" t="n">
         <v>708</v>
       </c>
@@ -21810,7 +22030,11 @@
       <c r="A144" s="1" t="n">
         <v>142</v>
       </c>
-      <c r="B144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="C144" t="n">
         <v>5812</v>
       </c>
@@ -21971,7 +22195,11 @@
       <c r="A145" s="1" t="n">
         <v>143</v>
       </c>
-      <c r="B145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C145" t="n">
         <v>333</v>
       </c>
@@ -22132,7 +22360,11 @@
       <c r="A146" s="1" t="n">
         <v>144</v>
       </c>
-      <c r="B146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="C146" t="n">
         <v>816</v>
       </c>
@@ -22293,7 +22525,11 @@
       <c r="A147" s="1" t="n">
         <v>145</v>
       </c>
-      <c r="B147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C147" t="n">
         <v>143</v>
       </c>
@@ -22454,7 +22690,11 @@
       <c r="A148" s="1" t="n">
         <v>146</v>
       </c>
-      <c r="B148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="C148" t="n">
         <v>4932</v>
       </c>
@@ -22615,7 +22855,11 @@
       <c r="A149" s="1" t="n">
         <v>147</v>
       </c>
-      <c r="B149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="C149" t="n">
         <v>96</v>
       </c>
@@ -22776,7 +23020,11 @@
       <c r="A150" s="1" t="n">
         <v>148</v>
       </c>
-      <c r="B150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C150" t="n">
         <v>729</v>
       </c>
@@ -22937,7 +23185,11 @@
       <c r="A151" s="1" t="n">
         <v>149</v>
       </c>
-      <c r="B151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="C151" t="n">
         <v>6992</v>
       </c>
@@ -23098,7 +23350,11 @@
       <c r="A152" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="B152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="C152" t="n">
         <v>90</v>
       </c>
@@ -23259,7 +23515,11 @@
       <c r="A153" s="1" t="n">
         <v>151</v>
       </c>
-      <c r="B153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="C153" t="n">
         <v>341</v>
       </c>
@@ -23420,7 +23680,11 @@
       <c r="A154" s="1" t="n">
         <v>152</v>
       </c>
-      <c r="B154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="C154" t="n">
         <v>4952</v>
       </c>
@@ -23581,7 +23845,11 @@
       <c r="A155" s="1" t="n">
         <v>153</v>
       </c>
-      <c r="B155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="C155" t="n">
         <v>7578</v>
       </c>
@@ -23742,7 +24010,11 @@
       <c r="A156" s="1" t="n">
         <v>154</v>
       </c>
-      <c r="B156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="C156" t="n">
         <v>755</v>
       </c>
@@ -23903,7 +24175,11 @@
       <c r="A157" s="1" t="n">
         <v>155</v>
       </c>
-      <c r="B157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="C157" t="n">
         <v>4933</v>
       </c>
@@ -24064,7 +24340,11 @@
       <c r="A158" s="1" t="n">
         <v>156</v>
       </c>
-      <c r="B158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C158" t="n">
         <v>410</v>
       </c>
@@ -24225,7 +24505,11 @@
       <c r="A159" s="1" t="n">
         <v>157</v>
       </c>
-      <c r="B159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C159" t="n">
         <v>410</v>
       </c>
@@ -24382,7 +24666,11 @@
       <c r="A160" s="1" t="n">
         <v>158</v>
       </c>
-      <c r="B160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C160" t="n">
         <v>310</v>
       </c>
@@ -24539,7 +24827,11 @@
       <c r="A161" s="1" t="n">
         <v>159</v>
       </c>
-      <c r="B161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="C161" t="n">
         <v>290</v>
       </c>
@@ -24700,7 +24992,11 @@
       <c r="A162" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="B162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C162" t="n">
         <v>200</v>
       </c>
@@ -24861,7 +25157,11 @@
       <c r="A163" s="1" t="n">
         <v>161</v>
       </c>
-      <c r="B163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C163" t="n">
         <v>915</v>
       </c>
@@ -25022,7 +25322,11 @@
       <c r="A164" s="1" t="n">
         <v>162</v>
       </c>
-      <c r="B164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C164" t="n">
         <v>4905</v>
       </c>
@@ -25183,7 +25487,11 @@
       <c r="A165" s="1" t="n">
         <v>163</v>
       </c>
-      <c r="B165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="C165" t="n">
         <v>5807</v>
       </c>
@@ -25344,7 +25652,11 @@
       <c r="A166" s="1" t="n">
         <v>164</v>
       </c>
-      <c r="B166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="C166" t="n">
         <v>219</v>
       </c>
@@ -25505,7 +25817,11 @@
       <c r="A167" s="1" t="n">
         <v>165</v>
       </c>
-      <c r="B167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C167" t="n">
         <v>267</v>
       </c>
@@ -25666,7 +25982,11 @@
       <c r="A168" s="1" t="n">
         <v>166</v>
       </c>
-      <c r="B168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="C168" t="n">
         <v>642</v>
       </c>
@@ -25827,7 +26147,11 @@
       <c r="A169" s="1" t="n">
         <v>167</v>
       </c>
-      <c r="B169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="C169" t="n">
         <v>286</v>
       </c>
@@ -25988,7 +26312,11 @@
       <c r="A170" s="1" t="n">
         <v>168</v>
       </c>
-      <c r="B170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C170" t="n">
         <v>7594</v>
       </c>
@@ -26149,7 +26477,11 @@
       <c r="A171" s="1" t="n">
         <v>169</v>
       </c>
-      <c r="B171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="C171" t="n">
         <v>6994</v>
       </c>
@@ -26310,7 +26642,11 @@
       <c r="A172" s="1" t="n">
         <v>170</v>
       </c>
-      <c r="B172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="C172" t="n">
         <v>92</v>
       </c>
@@ -26471,7 +26807,11 @@
       <c r="A173" s="1" t="n">
         <v>171</v>
       </c>
-      <c r="B173" t="inlineStr"/>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="C173" t="n">
         <v>335</v>
       </c>
@@ -26632,7 +26972,11 @@
       <c r="A174" s="1" t="n">
         <v>172</v>
       </c>
-      <c r="B174" t="inlineStr"/>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C174" t="n">
         <v>9742</v>
       </c>
@@ -26793,7 +27137,11 @@
       <c r="A175" s="1" t="n">
         <v>173</v>
       </c>
-      <c r="B175" t="inlineStr"/>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C175" t="n">
         <v>155</v>
       </c>
@@ -26954,7 +27302,11 @@
       <c r="A176" s="1" t="n">
         <v>174</v>
       </c>
-      <c r="B176" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="C176" t="n">
         <v>101</v>
       </c>
@@ -27115,7 +27467,11 @@
       <c r="A177" s="1" t="n">
         <v>175</v>
       </c>
-      <c r="B177" t="inlineStr"/>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="C177" t="n">
         <v>209</v>
       </c>
@@ -27276,7 +27632,11 @@
       <c r="A178" s="1" t="n">
         <v>176</v>
       </c>
-      <c r="B178" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="C178" t="n">
         <v>666</v>
       </c>
@@ -27437,7 +27797,11 @@
       <c r="A179" s="1" t="n">
         <v>177</v>
       </c>
-      <c r="B179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="C179" t="n">
         <v>188</v>
       </c>
@@ -27598,7 +27962,11 @@
       <c r="A180" s="1" t="n">
         <v>178</v>
       </c>
-      <c r="B180" t="inlineStr"/>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="C180" t="n">
         <v>685</v>
       </c>
@@ -27759,7 +28127,11 @@
       <c r="A181" s="1" t="n">
         <v>179</v>
       </c>
-      <c r="B181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="C181" t="n">
         <v>627</v>
       </c>

--- a/Results_isofys/Numex_preliminar_base.xlsx
+++ b/Results_isofys/Numex_preliminar_base.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY181"/>
+  <dimension ref="A1:BA181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -655,30 +655,40 @@
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>Specific leaf area (g/cm²)</t>
+          <t>Bloque</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
+          <t>Specific leaf area (cm²/g)</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>LMA g/m2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
           <t>leaf water content</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>C:N</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>13dC/18dO</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>Narea</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>Carea</t>
         </is>
@@ -807,21 +817,27 @@
         <v>0.536</v>
       </c>
       <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="n">
         <v>71.47877382352941</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AV2" t="n">
+        <v>13.99016724138068</v>
+      </c>
+      <c r="AW2" t="n">
         <v>0.5072463768115941</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AX2" t="n">
         <v>39.58454796558406</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="AY2" t="n">
         <v>-1.069204566063425</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="AZ2" t="n">
         <v>0.1583411527786951</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="BA2" t="n">
         <v>6.267862957094129</v>
       </c>
     </row>
@@ -948,21 +964,27 @@
         <v>0.788</v>
       </c>
       <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="n">
         <v>96.28079739625713</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="AV3" t="n">
+        <v>10.38628705872013</v>
+      </c>
+      <c r="AW3" t="n">
         <v>0.4815439780636996</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AX3" t="n">
         <v>25.57873717795717</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="AY3" t="n">
         <v>-1.162714378482783</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="AZ3" t="n">
         <v>0.1927929018543231</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="BA3" t="n">
         <v>4.931398966307422</v>
       </c>
     </row>
@@ -1089,21 +1111,27 @@
         <v>0.536</v>
       </c>
       <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
         <v>73.13888888888889</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="AV4" t="n">
+        <v>13.67261678693506</v>
+      </c>
+      <c r="AW4" t="n">
         <v>0.5263157894736842</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AX4" t="n">
         <v>42.49161457666214</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="AY4" t="n">
         <v>-1.083217188451016</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="AZ4" t="n">
         <v>0.1459443363957555</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="BA4" t="n">
         <v>6.201410491775166</v>
       </c>
     </row>
@@ -1230,21 +1258,27 @@
         <v>0.788</v>
       </c>
       <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
         <v>69.1300964630225</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AV5" t="n">
+        <v>14.46547959809223</v>
+      </c>
+      <c r="AW5" t="n">
         <v>0.4547685834502104</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AX5" t="n">
         <v>29.47494536584171</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="AY5" t="n">
         <v>-1.173469655199274</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="AZ5" t="n">
         <v>0.2308390026071944</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="BA5" t="n">
         <v>6.803966990152447</v>
       </c>
     </row>
@@ -1371,21 +1405,27 @@
         <v>0.788</v>
       </c>
       <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="n">
         <v>82.4059385665529</v>
       </c>
-      <c r="AU6" t="n">
+      <c r="AV6" t="n">
+        <v>12.13504775741832</v>
+      </c>
+      <c r="AW6" t="n">
         <v>0.4913194444444444</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AX6" t="n">
         <v>29.46857519135586</v>
       </c>
-      <c r="AW6" t="n">
+      <c r="AY6" t="n">
         <v>-1.152717050430573</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="AZ6" t="n">
         <v>0.1972952651382424</v>
       </c>
-      <c r="AY6" t="n">
+      <c r="BA6" t="n">
         <v>5.814010355624786</v>
       </c>
     </row>
@@ -1512,21 +1552,27 @@
         <v>0.585</v>
       </c>
       <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="n">
         <v>67.8012654945055</v>
       </c>
-      <c r="AU7" t="n">
+      <c r="AV7" t="n">
+        <v>14.7489872453935</v>
+      </c>
+      <c r="AW7" t="n">
         <v>0.736122618061309</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AX7" t="n">
         <v>26.51846199848627</v>
       </c>
-      <c r="AW7" t="n">
+      <c r="AY7" t="n">
         <v>-0.9757692279498354</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="AZ7" t="n">
         <v>0.2411024955423218</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="BA7" t="n">
         <v>6.393667365779264</v>
       </c>
     </row>
@@ -1653,21 +1699,27 @@
         <v>0.788</v>
       </c>
       <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="n">
         <v>71.94738415545589</v>
       </c>
-      <c r="AU8" t="n">
+      <c r="AV8" t="n">
+        <v>13.89904597280856</v>
+      </c>
+      <c r="AW8" t="n">
         <v>0.486963190184049</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AX8" t="n">
         <v>29.75015113451708</v>
       </c>
-      <c r="AW8" t="n">
+      <c r="AY8" t="n">
         <v>-1.066817746219274</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="AZ8" t="n">
         <v>0.2212734935521185</v>
       </c>
-      <c r="AY8" t="n">
+      <c r="BA8" t="n">
         <v>6.582919875238116</v>
       </c>
     </row>
@@ -1794,21 +1846,27 @@
         <v>0.788</v>
       </c>
       <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="n">
         <v>69.39019390581717</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="AV9" t="n">
+        <v>14.4112581866725</v>
+      </c>
+      <c r="AW9" t="n">
         <v>0.4296998420221169</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AX9" t="n">
         <v>28.28424514537473</v>
       </c>
-      <c r="AW9" t="n">
+      <c r="AY9" t="n">
         <v>-1.120257664680253</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="AZ9" t="n">
         <v>0.2491330280495736</v>
       </c>
-      <c r="AY9" t="n">
+      <c r="BA9" t="n">
         <v>7.04653963916366</v>
       </c>
     </row>
@@ -1935,21 +1993,27 @@
         <v>0.788</v>
       </c>
       <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="n">
         <v>89.16889483065954</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AV10" t="n">
+        <v>11.2146730303106</v>
+      </c>
+      <c r="AW10" t="n">
         <v>0.5689588935843257</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AX10" t="n">
         <v>28.01632724421026</v>
       </c>
-      <c r="AW10" t="n">
+      <c r="AY10" t="n">
         <v>-1.176763154946914</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="AZ10" t="n">
         <v>0.1922442143630735</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="BA10" t="n">
         <v>5.385976820401974</v>
       </c>
     </row>
@@ -2076,21 +2140,27 @@
         <v>0.536</v>
       </c>
       <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="n">
         <v>72.18481374999999</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AV11" t="n">
+        <v>13.85332936458536</v>
+      </c>
+      <c r="AW11" t="n">
         <v>0.5061728395061729</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AX11" t="n">
         <v>39.94038297769038</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="AY11" t="n">
         <v>-1.083133704760353</v>
       </c>
-      <c r="AX11" t="n">
+      <c r="AZ11" t="n">
         <v>0.1541538771183675</v>
       </c>
-      <c r="AY11" t="n">
+      <c r="BA11" t="n">
         <v>6.156964889603419</v>
       </c>
     </row>
@@ -2217,21 +2287,27 @@
         <v>0.536</v>
       </c>
       <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="n">
         <v>64.85592510638298</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="AV12" t="n">
+        <v>15.41879170422291</v>
+      </c>
+      <c r="AW12" t="n">
         <v>0.5392156862745099</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AX12" t="n">
         <v>41.33398260330502</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="AY12" t="n">
         <v>-0.9693632665794485</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="AZ12" t="n">
         <v>0.1704503359635594</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BA12" t="n">
         <v>7.04539122144526</v>
       </c>
     </row>
@@ -2358,21 +2434,27 @@
         <v>0.536</v>
       </c>
       <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="n">
         <v>71.358</v>
       </c>
-      <c r="AU13" t="n">
+      <c r="AV13" t="n">
+        <v>14.01384567953138</v>
+      </c>
+      <c r="AW13" t="n">
         <v>0.5726495726495726</v>
       </c>
-      <c r="AV13" t="n">
+      <c r="AX13" t="n">
         <v>33.26962395702254</v>
       </c>
-      <c r="AW13" t="n">
+      <c r="AY13" t="n">
         <v>-1.01178671221848</v>
       </c>
-      <c r="AX13" t="n">
+      <c r="AZ13" t="n">
         <v>0.1893086604314295</v>
       </c>
-      <c r="AY13" t="n">
+      <c r="BA13" t="n">
         <v>6.298227944361334</v>
       </c>
     </row>
@@ -2499,21 +2581,27 @@
         <v>0.585</v>
       </c>
       <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="n">
         <v>74.18300281914894</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="AV14" t="n">
+        <v>13.48017688685243</v>
+      </c>
+      <c r="AW14" t="n">
         <v>0.7566867989646247</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="AX14" t="n">
         <v>24.51611901423017</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="AY14" t="n">
         <v>-0.9086318732906992</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="AZ14" t="n">
         <v>0.2420263723581012</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BA14" t="n">
         <v>5.933547349313596</v>
       </c>
     </row>
@@ -2586,10 +2674,10 @@
         <v>0.1961666666666667</v>
       </c>
       <c r="T15" t="n">
-        <v>30.07</v>
+        <v>38.97</v>
       </c>
       <c r="U15" t="n">
-        <v>15.23</v>
+        <v>18.77</v>
       </c>
       <c r="V15" t="n">
         <v>1332.582</v>
@@ -2603,7 +2691,7 @@
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
-        <v>506.4848686398404</v>
+        <v>481.6525532460868</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
@@ -2640,22 +2728,28 @@
         <v>0.788</v>
       </c>
       <c r="AT15" t="n">
-        <v>87.49717662508208</v>
+        <v>1</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.4935151313601596</v>
+        <v>70.99531166755462</v>
       </c>
       <c r="AV15" t="n">
+        <v>14.08543714383055</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.5183474467539133</v>
+      </c>
+      <c r="AX15" t="n">
         <v>29.77748860325364</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="AY15" t="n">
         <v>-0.9710658232898745</v>
       </c>
-      <c r="AX15" t="n">
-        <v>0.1835954858483998</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>5.467012487459539</v>
+      <c r="AZ15" t="n">
+        <v>0.2262696828216982</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>6.737742901484933</v>
       </c>
     </row>
     <row r="16">
@@ -2727,10 +2821,10 @@
         <v>0.239</v>
       </c>
       <c r="T16" t="n">
-        <v>34.11</v>
+        <v>30</v>
       </c>
       <c r="U16" t="n">
-        <v>18.97</v>
+        <v>16.69</v>
       </c>
       <c r="V16" t="n">
         <v>1047.219</v>
@@ -2744,7 +2838,7 @@
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="n">
-        <v>556.1418938727646</v>
+        <v>556.3333333333334</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -2781,22 +2875,28 @@
         <v>0.788</v>
       </c>
       <c r="AT16" t="n">
-        <v>55.20395361096469</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.4438581061272354</v>
+        <v>62.74529658478131</v>
       </c>
       <c r="AV16" t="n">
+        <v>15.93744956881035</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.4436666666666666</v>
+      </c>
+      <c r="AX16" t="n">
         <v>32.32547486872957</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="AY16" t="n">
         <v>-0.9202190103021481</v>
       </c>
-      <c r="AX16" t="n">
-        <v>0.2667160375811695</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>8.621722569917226</v>
+      <c r="AZ16" t="n">
+        <v>0.2346594974817987</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>7.585479688556592</v>
       </c>
     </row>
     <row r="17">
@@ -2922,21 +3022,27 @@
         <v>0.788</v>
       </c>
       <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="n">
         <v>83.15552898983861</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="AV17" t="n">
+        <v>12.02565857192968</v>
+      </c>
+      <c r="AW17" t="n">
         <v>0.4855473554735548</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="AX17" t="n">
         <v>28.39448648615612</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="AY17" t="n">
         <v>-1.137930339273472</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="AZ17" t="n">
         <v>0.2040293659175826</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="BA17" t="n">
         <v>5.793309073325802</v>
       </c>
     </row>
@@ -3063,21 +3169,27 @@
         <v>0.788</v>
       </c>
       <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="n">
         <v>75.3908671973188</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="AV18" t="n">
+        <v>13.2642060925327</v>
+      </c>
+      <c r="AW18" t="n">
         <v>0.4816503800217155</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="AX18" t="n">
         <v>29.17653851247548</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="AY18" t="n">
         <v>-0.9983195512068304</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="AZ18" t="n">
         <v>0.2199748552043699</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BA18" t="n">
         <v>6.418104834646514</v>
       </c>
     </row>
@@ -3204,21 +3316,27 @@
         <v>0.788</v>
       </c>
       <c r="AT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="n">
         <v>97.0510460251046</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AV19" t="n">
+        <v>10.30385597020073</v>
+      </c>
+      <c r="AW19" t="n">
         <v>0.5304518664047152</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="AX19" t="n">
         <v>26.66776442666212</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="AY19" t="n">
         <v>-1.159881181147376</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="AZ19" t="n">
         <v>0.1804095984933663</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BA19" t="n">
         <v>4.811120672929789</v>
       </c>
     </row>
@@ -3291,10 +3409,10 @@
         <v>0.2016666666666667</v>
       </c>
       <c r="T20" t="n">
-        <v>38.97</v>
+        <v>34.11</v>
       </c>
       <c r="U20" t="n">
-        <v>18.77</v>
+        <v>18.97</v>
       </c>
       <c r="V20" t="n">
         <v>1362.462</v>
@@ -3308,7 +3426,7 @@
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="n">
-        <v>481.6525532460868</v>
+        <v>556.1418938727646</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
@@ -3345,22 +3463,28 @@
         <v>0.788</v>
       </c>
       <c r="AT20" t="n">
-        <v>72.5872136387853</v>
+        <v>1</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.5183474467539133</v>
+        <v>71.82192936215077</v>
       </c>
       <c r="AV20" t="n">
+        <v>13.92332410004829</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0.4438581061272354</v>
+      </c>
+      <c r="AX20" t="n">
         <v>30.75436275117814</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="AY20" t="n">
         <v>-0.9251081452731393</v>
       </c>
-      <c r="AX20" t="n">
-        <v>0.2193069154530283</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>6.744644431684386</v>
+      <c r="AZ20" t="n">
+        <v>0.2216436966512492</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>6.816510648324604</v>
       </c>
     </row>
     <row r="21">
@@ -3486,21 +3610,27 @@
         <v>0.585</v>
       </c>
       <c r="AT21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU21" t="n">
         <v>69.54388888888889</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="AV21" t="n">
+        <v>14.37940868676056</v>
+      </c>
+      <c r="AW21" t="n">
         <v>0.736842105263158</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="AX21" t="n">
         <v>22.9540859657499</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="AY21" t="n">
         <v>-0.8250529055541557</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="AZ21" t="n">
         <v>0.2731252805030631</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BA21" t="n">
         <v>6.269341168086865</v>
       </c>
     </row>
@@ -3627,21 +3757,27 @@
         <v>0.536</v>
       </c>
       <c r="AT22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU22" t="n">
         <v>59.98653846153847</v>
       </c>
-      <c r="AU22" t="n">
+      <c r="AV22" t="n">
+        <v>16.67040682204341</v>
+      </c>
+      <c r="AW22" t="n">
         <v>0.5555555555555555</v>
       </c>
-      <c r="AV22" t="n">
+      <c r="AX22" t="n">
         <v>53.02578826881873</v>
       </c>
-      <c r="AW22" t="n">
+      <c r="AY22" t="n">
         <v>-0.9307778716019919</v>
       </c>
-      <c r="AX22" t="n">
+      <c r="AZ22" t="n">
         <v>0.1359691165823957</v>
       </c>
-      <c r="AY22" t="n">
+      <c r="BA22" t="n">
         <v>7.209869586996444</v>
       </c>
     </row>
@@ -3768,21 +3904,27 @@
         <v>0.536</v>
       </c>
       <c r="AT23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU23" t="n">
         <v>75.1049597826087</v>
       </c>
-      <c r="AU23" t="n">
+      <c r="AV23" t="n">
+        <v>13.31469989324939</v>
+      </c>
+      <c r="AW23" t="n">
         <v>0.5533980582524273</v>
       </c>
-      <c r="AV23" t="n">
+      <c r="AX23" t="n">
         <v>38.38370176944333</v>
       </c>
-      <c r="AW23" t="n">
+      <c r="AY23" t="n">
         <v>-1.076624094600751</v>
       </c>
-      <c r="AX23" t="n">
+      <c r="AZ23" t="n">
         <v>0.1532285064088778</v>
       </c>
-      <c r="AY23" t="n">
+      <c r="BA23" t="n">
         <v>5.8814772925756</v>
       </c>
     </row>
@@ -3909,21 +4051,27 @@
         <v>0.585</v>
       </c>
       <c r="AT24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU24" t="n">
         <v>67.90667645714286</v>
       </c>
-      <c r="AU24" t="n">
+      <c r="AV24" t="n">
+        <v>14.72609251656011</v>
+      </c>
+      <c r="AW24" t="n">
         <v>0.751538097491718</v>
       </c>
-      <c r="AV24" t="n">
+      <c r="AX24" t="n">
         <v>30.95258432083551</v>
       </c>
-      <c r="AW24" t="n">
+      <c r="AY24" t="n">
         <v>-0.9531215121310557</v>
       </c>
-      <c r="AX24" t="n">
+      <c r="AZ24" t="n">
         <v>0.2083919474390169</v>
       </c>
-      <c r="AY24" t="n">
+      <c r="BA24" t="n">
         <v>6.450269324889292</v>
       </c>
     </row>
@@ -3996,10 +4144,10 @@
         <v>0.1948333333333333</v>
       </c>
       <c r="T25" t="n">
-        <v>14.55</v>
+        <v>30.07</v>
       </c>
       <c r="U25" t="n">
-        <v>5.69</v>
+        <v>15.23</v>
       </c>
       <c r="V25" t="n">
         <v>1248.499</v>
@@ -4013,7 +4161,7 @@
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="n">
-        <v>391.0652920962199</v>
+        <v>506.4848686398404</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
@@ -4050,22 +4198,28 @@
         <v>0.788</v>
       </c>
       <c r="AT25" t="n">
-        <v>219.4198594024604</v>
+        <v>2</v>
       </c>
       <c r="AU25" t="n">
-        <v>0.60893470790378</v>
+        <v>81.97629678266578</v>
       </c>
       <c r="AV25" t="n">
+        <v>12.19864813668253</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0.4935151313601596</v>
+      </c>
+      <c r="AX25" t="n">
         <v>30.76750734875213</v>
       </c>
-      <c r="AW25" t="n">
+      <c r="AY25" t="n">
         <v>-1.127672428671739</v>
       </c>
-      <c r="AX25" t="n">
-        <v>0.07191749109464135</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>2.212721935758194</v>
+      <c r="AZ25" t="n">
+        <v>0.1924962019984864</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>5.922628309595306</v>
       </c>
     </row>
     <row r="26">
@@ -4191,21 +4345,27 @@
         <v>0.788</v>
       </c>
       <c r="AT26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU26" t="n">
         <v>81.5699164345404</v>
       </c>
-      <c r="AU26" t="n">
+      <c r="AV26" t="n">
+        <v>12.25942165580735</v>
+      </c>
+      <c r="AW26" t="n">
         <v>0.491741387446909</v>
       </c>
-      <c r="AV26" t="n">
+      <c r="AX26" t="n">
         <v>29.19160870007697</v>
       </c>
-      <c r="AW26" t="n">
+      <c r="AY26" t="n">
         <v>-1.093730835683608</v>
       </c>
-      <c r="AX26" t="n">
+      <c r="AZ26" t="n">
         <v>0.1993680458705612</v>
       </c>
-      <c r="AY26" t="n">
+      <c r="BA26" t="n">
         <v>5.819873982352418</v>
       </c>
     </row>
@@ -4278,10 +4438,10 @@
         <v>0.2273333333333334</v>
       </c>
       <c r="T27" t="n">
-        <v>30</v>
+        <v>14.55</v>
       </c>
       <c r="U27" t="n">
-        <v>16.69</v>
+        <v>5.69</v>
       </c>
       <c r="V27" t="n">
         <v>579.081</v>
@@ -4295,7 +4455,7 @@
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="n">
-        <v>556.3333333333334</v>
+        <v>391.0652920962199</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
@@ -4332,22 +4492,28 @@
         <v>0.585</v>
       </c>
       <c r="AT27" t="n">
-        <v>34.69628520071899</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="n">
-        <v>0.4436666666666666</v>
+        <v>101.771704745167</v>
       </c>
       <c r="AV27" t="n">
+        <v>9.825913818619503</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0.60893470790378</v>
+      </c>
+      <c r="AX27" t="n">
         <v>19.36748669969131</v>
       </c>
-      <c r="AW27" t="n">
+      <c r="AY27" t="n">
         <v>-0.9251981278059437</v>
       </c>
-      <c r="AX27" t="n">
-        <v>0.6593596761464461</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>12.77013975807906</v>
+      <c r="AZ27" t="n">
+        <v>0.2247906864753312</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>4.353630630525455</v>
       </c>
     </row>
     <row r="28">
@@ -4473,21 +4639,27 @@
         <v>0.585</v>
       </c>
       <c r="AT28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU28" t="n">
         <v>69.6693247757256</v>
       </c>
-      <c r="AU28" t="n">
+      <c r="AV28" t="n">
+        <v>14.35351933177373</v>
+      </c>
+      <c r="AW28" t="n">
         <v>0.7484234981745768</v>
       </c>
-      <c r="AV28" t="n">
+      <c r="AX28" t="n">
         <v>31.82500795526659</v>
       </c>
-      <c r="AW28" t="n">
+      <c r="AY28" t="n">
         <v>-1.110646754176239</v>
       </c>
-      <c r="AX28" t="n">
+      <c r="AZ28" t="n">
         <v>0.1941969337398241</v>
       </c>
-      <c r="AY28" t="n">
+      <c r="BA28" t="n">
         <v>6.180318961158282</v>
       </c>
     </row>
@@ -4614,21 +4786,27 @@
         <v>0.585</v>
       </c>
       <c r="AT29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU29" t="n">
         <v>94.70271604938272</v>
       </c>
-      <c r="AU29" t="n">
+      <c r="AV29" t="n">
+        <v>10.55935924243767</v>
+      </c>
+      <c r="AW29" t="n">
         <v>0.5573770491803279</v>
       </c>
-      <c r="AV29" t="n">
+      <c r="AX29" t="n">
         <v>20.74216706763612</v>
       </c>
-      <c r="AW29" t="n">
+      <c r="AY29" t="n">
         <v>-0.8721981465115956</v>
       </c>
-      <c r="AX29" t="n">
+      <c r="AZ29" t="n">
         <v>0.2299853817964811</v>
       </c>
-      <c r="AY29" t="n">
+      <c r="BA29" t="n">
         <v>4.77039521233669</v>
       </c>
     </row>
@@ -4755,21 +4933,27 @@
         <v>0.788</v>
       </c>
       <c r="AT30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU30" t="n">
         <v>78.94186507936509</v>
       </c>
-      <c r="AU30" t="n">
+      <c r="AV30" t="n">
+        <v>12.66754970882229</v>
+      </c>
+      <c r="AW30" t="n">
         <v>0.5222748815165877</v>
       </c>
-      <c r="AV30" t="n">
+      <c r="AX30" t="n">
         <v>29.19189319790335</v>
       </c>
-      <c r="AW30" t="n">
+      <c r="AY30" t="n">
         <v>-1.026018023099852</v>
       </c>
-      <c r="AX30" t="n">
+      <c r="AZ30" t="n">
         <v>0.2056480718564838</v>
       </c>
-      <c r="AY30" t="n">
+      <c r="BA30" t="n">
         <v>6.003256549989229</v>
       </c>
     </row>
@@ -4896,21 +5080,27 @@
         <v>0.536</v>
       </c>
       <c r="AT31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU31" t="n">
         <v>73.10914565217391</v>
       </c>
-      <c r="AU31" t="n">
+      <c r="AV31" t="n">
+        <v>13.67817926306549</v>
+      </c>
+      <c r="AW31" t="n">
         <v>0.5533980582524273</v>
       </c>
-      <c r="AV31" t="n">
+      <c r="AX31" t="n">
         <v>42.97256368979243</v>
       </c>
-      <c r="AW31" t="n">
+      <c r="AY31" t="n">
         <v>-1.081725628636109</v>
       </c>
-      <c r="AX31" t="n">
+      <c r="AZ31" t="n">
         <v>0.136631885562437</v>
       </c>
-      <c r="AY31" t="n">
+      <c r="BA31" t="n">
         <v>5.871422404388254</v>
       </c>
     </row>
@@ -5037,21 +5227,27 @@
         <v>0.585</v>
       </c>
       <c r="AT32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU32" t="n">
         <v>104.4525773195876</v>
       </c>
-      <c r="AU32" t="n">
+      <c r="AV32" t="n">
+        <v>9.573722598920243</v>
+      </c>
+      <c r="AW32" t="n">
         <v>0.5579427083333334</v>
       </c>
-      <c r="AV32" t="n">
+      <c r="AX32" t="n">
         <v>20.62022678542598</v>
       </c>
-      <c r="AW32" t="n">
+      <c r="AY32" t="n">
         <v>-0.9757257325131097</v>
       </c>
-      <c r="AX32" t="n">
+      <c r="AZ32" t="n">
         <v>0.2060536274187499</v>
       </c>
-      <c r="AY32" t="n">
+      <c r="BA32" t="n">
         <v>4.248872527334292</v>
       </c>
     </row>
@@ -5178,21 +5374,27 @@
         <v>0.585</v>
       </c>
       <c r="AT33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU33" t="n">
         <v>89.62449856733524</v>
       </c>
-      <c r="AU33" t="n">
+      <c r="AV33" t="n">
+        <v>11.15766354049608</v>
+      </c>
+      <c r="AW33" t="n">
         <v>0.5238744884038199</v>
       </c>
-      <c r="AV33" t="n">
+      <c r="AX33" t="n">
         <v>21.99115496636606</v>
       </c>
-      <c r="AW33" t="n">
+      <c r="AY33" t="n">
         <v>-1.108000186694067</v>
       </c>
-      <c r="AX33" t="n">
+      <c r="AZ33" t="n">
         <v>0.2140487849336566</v>
       </c>
-      <c r="AY33" t="n">
+      <c r="BA33" t="n">
         <v>4.707179999838402</v>
       </c>
     </row>
@@ -5319,21 +5521,27 @@
         <v>0.536</v>
       </c>
       <c r="AT34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU34" t="n">
         <v>79.74831617021276</v>
       </c>
-      <c r="AU34" t="n">
+      <c r="AV34" t="n">
+        <v>12.53944970907756</v>
+      </c>
+      <c r="AW34" t="n">
         <v>0.584070796460177</v>
       </c>
-      <c r="AV34" t="n">
+      <c r="AX34" t="n">
         <v>43.87185925469005</v>
       </c>
-      <c r="AW34" t="n">
+      <c r="AY34" t="n">
         <v>-1.1317622997201</v>
       </c>
-      <c r="AX34" t="n">
+      <c r="AZ34" t="n">
         <v>0.1262484116656832</v>
       </c>
-      <c r="AY34" t="n">
+      <c r="BA34" t="n">
         <v>5.538752547725021</v>
       </c>
     </row>
@@ -5460,21 +5668,27 @@
         <v>0.788</v>
       </c>
       <c r="AT35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU35" t="n">
         <v>84.60972568578555</v>
       </c>
-      <c r="AU35" t="n">
+      <c r="AV35" t="n">
+        <v>11.81897225046789</v>
+      </c>
+      <c r="AW35" t="n">
         <v>0.4962311557788945</v>
       </c>
-      <c r="AV35" t="n">
+      <c r="AX35" t="n">
         <v>24.17983322666046</v>
       </c>
-      <c r="AW35" t="n">
+      <c r="AY35" t="n">
         <v>-1.097985206987246</v>
       </c>
-      <c r="AX35" t="n">
+      <c r="AZ35" t="n">
         <v>0.236853606683806</v>
       </c>
-      <c r="AY35" t="n">
+      <c r="BA35" t="n">
         <v>5.72708070874746</v>
       </c>
     </row>
@@ -5601,21 +5815,27 @@
         <v>0.536</v>
       </c>
       <c r="AT36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU36" t="n">
         <v>67.44528301886793</v>
       </c>
-      <c r="AU36" t="n">
+      <c r="AV36" t="n">
+        <v>14.82683377161081</v>
+      </c>
+      <c r="AW36" t="n">
         <v>0.5</v>
       </c>
-      <c r="AV36" t="n">
+      <c r="AX36" t="n">
         <v>45.72171601638512</v>
       </c>
-      <c r="AW36" t="n">
+      <c r="AY36" t="n">
         <v>-1.041003254864917</v>
       </c>
-      <c r="AX36" t="n">
+      <c r="AZ36" t="n">
         <v>0.1404492354378129</v>
       </c>
-      <c r="AY36" t="n">
+      <c r="BA36" t="n">
         <v>6.421580057406096</v>
       </c>
     </row>
@@ -5742,21 +5962,27 @@
         <v>0.536</v>
       </c>
       <c r="AT37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU37" t="n">
         <v>83.75136225806452</v>
       </c>
-      <c r="AU37" t="n">
+      <c r="AV37" t="n">
+        <v>11.94010429249715</v>
+      </c>
+      <c r="AW37" t="n">
         <v>0.5633802816901409</v>
       </c>
-      <c r="AV37" t="n">
+      <c r="AX37" t="n">
         <v>32.47607689365352</v>
       </c>
-      <c r="AW37" t="n">
+      <c r="AY37" t="n">
         <v>-1.128326182974303</v>
       </c>
-      <c r="AX37" t="n">
+      <c r="AZ37" t="n">
         <v>0.165736668134432</v>
       </c>
-      <c r="AY37" t="n">
+      <c r="BA37" t="n">
         <v>5.382476778431748</v>
       </c>
     </row>
@@ -5883,21 +6109,27 @@
         <v>0.585</v>
       </c>
       <c r="AT38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU38" t="n">
         <v>56.4139702</v>
       </c>
-      <c r="AU38" t="n">
+      <c r="AV38" t="n">
+        <v>17.72610572265662</v>
+      </c>
+      <c r="AW38" t="n">
         <v>0.66078697421981</v>
       </c>
-      <c r="AV38" t="n">
+      <c r="AX38" t="n">
         <v>31.24223026798138</v>
       </c>
-      <c r="AW38" t="n">
+      <c r="AY38" t="n">
         <v>-1.052221717593601</v>
       </c>
-      <c r="AX38" t="n">
+      <c r="AZ38" t="n">
         <v>0.25370946862891</v>
       </c>
-      <c r="AY38" t="n">
+      <c r="BA38" t="n">
         <v>7.926449640071605</v>
       </c>
     </row>
@@ -6024,21 +6256,27 @@
         <v>0.585</v>
       </c>
       <c r="AT39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU39" t="n">
         <v>112.059891598916</v>
       </c>
-      <c r="AU39" t="n">
+      <c r="AV39" t="n">
+        <v>8.923799458767936</v>
+      </c>
+      <c r="AW39" t="n">
         <v>0.555421686746988</v>
       </c>
-      <c r="AV39" t="n">
+      <c r="AX39" t="n">
         <v>22.29074496544098</v>
       </c>
-      <c r="AW39" t="n">
+      <c r="AY39" t="n">
         <v>-1.018263130425242</v>
       </c>
-      <c r="AX39" t="n">
+      <c r="AZ39" t="n">
         <v>0.1790085898974969</v>
       </c>
-      <c r="AY39" t="n">
+      <c r="BA39" t="n">
         <v>3.990234824028318</v>
       </c>
     </row>
@@ -6165,21 +6403,27 @@
         <v>0.536</v>
       </c>
       <c r="AT40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU40" t="n">
         <v>67.68852459016394</v>
       </c>
-      <c r="AU40" t="n">
+      <c r="AV40" t="n">
+        <v>14.77355291838217</v>
+      </c>
+      <c r="AW40" t="n">
         <v>0.5447761194029851</v>
       </c>
-      <c r="AV40" t="n">
+      <c r="AX40" t="n">
         <v>40.95714602250389</v>
       </c>
-      <c r="AW40" t="n">
+      <c r="AY40" t="n">
         <v>-1.134852638614013</v>
       </c>
-      <c r="AX40" t="n">
+      <c r="AZ40" t="n">
         <v>0.1636334848571583</v>
       </c>
-      <c r="AY40" t="n">
+      <c r="BA40" t="n">
         <v>6.701960533465813</v>
       </c>
     </row>
@@ -6306,21 +6550,27 @@
         <v>0.788</v>
       </c>
       <c r="AT41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU41" t="n">
         <v>75.04706336939722</v>
       </c>
-      <c r="AU41" t="n">
+      <c r="AV41" t="n">
+        <v>13.32497175909192</v>
+      </c>
+      <c r="AW41" t="n">
         <v>0.4500637484062899</v>
       </c>
-      <c r="AV41" t="n">
+      <c r="AX41" t="n">
         <v>32.65053512949007</v>
       </c>
-      <c r="AW41" t="n">
+      <c r="AY41" t="n">
         <v>-1.046794083447492</v>
       </c>
-      <c r="AX41" t="n">
+      <c r="AZ41" t="n">
         <v>0.1962293560349081</v>
       </c>
-      <c r="AY41" t="n">
+      <c r="BA41" t="n">
         <v>6.406993482654983</v>
       </c>
     </row>
@@ -6447,21 +6697,27 @@
         <v>0.788</v>
       </c>
       <c r="AT42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU42" t="n">
         <v>75.04706336939722</v>
       </c>
-      <c r="AU42" t="n">
+      <c r="AV42" t="n">
+        <v>13.32497175909192</v>
+      </c>
+      <c r="AW42" t="n">
         <v>0.4500637484062899</v>
       </c>
-      <c r="AV42" t="n">
+      <c r="AX42" t="n">
         <v>32.65053512949007</v>
       </c>
-      <c r="AW42" t="n">
+      <c r="AY42" t="n">
         <v>-1.055363556422817</v>
       </c>
-      <c r="AX42" t="n">
+      <c r="AZ42" t="n">
         <v>0.1962293560349081</v>
       </c>
-      <c r="AY42" t="n">
+      <c r="BA42" t="n">
         <v>6.406993482654983</v>
       </c>
     </row>
@@ -6588,21 +6844,27 @@
         <v>0.788</v>
       </c>
       <c r="AT43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU43" t="n">
         <v>75.04706336939722</v>
       </c>
-      <c r="AU43" t="n">
+      <c r="AV43" t="n">
+        <v>13.32497175909192</v>
+      </c>
+      <c r="AW43" t="n">
         <v>0.4500637484062899</v>
       </c>
-      <c r="AV43" t="n">
+      <c r="AX43" t="n">
         <v>32.65053512949007</v>
       </c>
-      <c r="AW43" t="n">
+      <c r="AY43" t="n">
         <v>-1.027478472194354</v>
       </c>
-      <c r="AX43" t="n">
+      <c r="AZ43" t="n">
         <v>0.1962293560349081</v>
       </c>
-      <c r="AY43" t="n">
+      <c r="BA43" t="n">
         <v>6.406993482654983</v>
       </c>
     </row>
@@ -6729,21 +6991,27 @@
         <v>0.788</v>
       </c>
       <c r="AT44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU44" t="n">
         <v>75.04706336939722</v>
       </c>
-      <c r="AU44" t="n">
+      <c r="AV44" t="n">
+        <v>13.32497175909192</v>
+      </c>
+      <c r="AW44" t="n">
         <v>0.4500637484062899</v>
       </c>
-      <c r="AV44" t="n">
+      <c r="AX44" t="n">
         <v>32.65053512949007</v>
       </c>
-      <c r="AW44" t="n">
+      <c r="AY44" t="n">
         <v>-1.035889819888641</v>
       </c>
-      <c r="AX44" t="n">
+      <c r="AZ44" t="n">
         <v>0.1962293560349081</v>
       </c>
-      <c r="AY44" t="n">
+      <c r="BA44" t="n">
         <v>6.406993482654983</v>
       </c>
     </row>
@@ -6870,21 +7138,27 @@
         <v>0.788</v>
       </c>
       <c r="AT45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU45" t="n">
         <v>76.05677919203099</v>
       </c>
-      <c r="AU45" t="n">
+      <c r="AV45" t="n">
+        <v>13.1480718829174</v>
+      </c>
+      <c r="AW45" t="n">
         <v>0.4354889097157138</v>
       </c>
-      <c r="AV45" t="n">
+      <c r="AX45" t="n">
         <v>34.94837353504887</v>
       </c>
-      <c r="AW45" t="n">
+      <c r="AY45" t="n">
         <v>-1.016944806660762</v>
       </c>
-      <c r="AX45" t="n">
+      <c r="AZ45" t="n">
         <v>0.2080347916779913</v>
       </c>
-      <c r="AY45" t="n">
+      <c r="BA45" t="n">
         <v>7.270477607848516</v>
       </c>
     </row>
@@ -7011,21 +7285,27 @@
         <v>0.585</v>
       </c>
       <c r="AT46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU46" t="n">
         <v>81.26364883401921</v>
       </c>
-      <c r="AU46" t="n">
+      <c r="AV46" t="n">
+        <v>12.30562513926119</v>
+      </c>
+      <c r="AW46" t="n">
         <v>0.5100806451612904</v>
       </c>
-      <c r="AV46" t="n">
+      <c r="AX46" t="n">
         <v>27.61940167646294</v>
       </c>
-      <c r="AW46" t="n">
+      <c r="AY46" t="n">
         <v>-1.168428613749502</v>
       </c>
-      <c r="AX46" t="n">
+      <c r="AZ46" t="n">
         <v>0.1803572361821152</v>
       </c>
-      <c r="AY46" t="n">
+      <c r="BA46" t="n">
         <v>4.981358951370535</v>
       </c>
     </row>
@@ -7152,21 +7432,27 @@
         <v>0.788</v>
       </c>
       <c r="AT47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU47" t="n">
         <v>97.08402533427164</v>
       </c>
-      <c r="AU47" t="n">
+      <c r="AV47" t="n">
+        <v>10.3003557645749</v>
+      </c>
+      <c r="AW47" t="n">
         <v>0.516502211636611</v>
       </c>
-      <c r="AV47" t="n">
+      <c r="AX47" t="n">
         <v>31.61114054973259</v>
       </c>
-      <c r="AW47" t="n">
+      <c r="AY47" t="n">
         <v>-1.006406074511895</v>
       </c>
-      <c r="AX47" t="n">
+      <c r="AZ47" t="n">
         <v>0.1563233988308393</v>
       </c>
-      <c r="AY47" t="n">
+      <c r="BA47" t="n">
         <v>4.941560931653564</v>
       </c>
     </row>
@@ -7293,21 +7579,27 @@
         <v>0.788</v>
       </c>
       <c r="AT48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU48" t="n">
         <v>84.03498467824311</v>
       </c>
-      <c r="AU48" t="n">
+      <c r="AV48" t="n">
+        <v>11.89980582288251</v>
+      </c>
+      <c r="AW48" t="n">
         <v>0.5043037974683545</v>
       </c>
-      <c r="AV48" t="n">
+      <c r="AX48" t="n">
         <v>32.58259222016648</v>
       </c>
-      <c r="AW48" t="n">
+      <c r="AY48" t="n">
         <v>-1.002974473340656</v>
       </c>
-      <c r="AX48" t="n">
+      <c r="AZ48" t="n">
         <v>0.1727182447385554</v>
       </c>
-      <c r="AY48" t="n">
+      <c r="BA48" t="n">
         <v>5.627608137299266</v>
       </c>
     </row>
@@ -7434,21 +7726,27 @@
         <v>0.536</v>
       </c>
       <c r="AT49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU49" t="n">
         <v>57.71341344827587</v>
       </c>
-      <c r="AU49" t="n">
+      <c r="AV49" t="n">
+        <v>17.32699454514545</v>
+      </c>
+      <c r="AW49" t="n">
         <v>0.4081632653061225</v>
       </c>
-      <c r="AV49" t="n">
+      <c r="AX49" t="n">
         <v>37.10169593659131</v>
       </c>
-      <c r="AW49" t="n">
+      <c r="AY49" t="n">
         <v>-1.033343565098957</v>
       </c>
-      <c r="AX49" t="n">
+      <c r="AZ49" t="n">
         <v>0.2118768969038876</v>
       </c>
-      <c r="AY49" t="n">
+      <c r="BA49" t="n">
         <v>7.860992204916545</v>
       </c>
     </row>
@@ -7575,21 +7873,27 @@
         <v>0.536</v>
       </c>
       <c r="AT50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU50" t="n">
         <v>69.24775590361446</v>
       </c>
-      <c r="AU50" t="n">
+      <c r="AV50" t="n">
+        <v>14.44090118085406</v>
+      </c>
+      <c r="AW50" t="n">
         <v>0.5585106382978723</v>
       </c>
-      <c r="AV50" t="n">
+      <c r="AX50" t="n">
         <v>46.62061318477367</v>
       </c>
-      <c r="AW50" t="n">
+      <c r="AY50" t="n">
         <v>-1.094831536193773</v>
       </c>
-      <c r="AX50" t="n">
+      <c r="AZ50" t="n">
         <v>0.1305405133948935</v>
       </c>
-      <c r="AY50" t="n">
+      <c r="BA50" t="n">
         <v>6.085878779925097</v>
       </c>
     </row>
@@ -7716,21 +8020,27 @@
         <v>0.585</v>
       </c>
       <c r="AT51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU51" t="n">
         <v>56.8577403125</v>
       </c>
-      <c r="AU51" t="n">
+      <c r="AV51" t="n">
+        <v>17.58775488620945</v>
+      </c>
+      <c r="AW51" t="n">
         <v>0.6854334226988382</v>
       </c>
-      <c r="AV51" t="n">
+      <c r="AX51" t="n">
         <v>27.64252745359939</v>
       </c>
-      <c r="AW51" t="n">
+      <c r="AY51" t="n">
         <v>-1.034130614924995</v>
       </c>
-      <c r="AX51" t="n">
+      <c r="AZ51" t="n">
         <v>0.2749705279828398</v>
       </c>
-      <c r="AY51" t="n">
+      <c r="BA51" t="n">
         <v>7.600880368696366</v>
       </c>
     </row>
@@ -7857,21 +8167,27 @@
         <v>0.585</v>
       </c>
       <c r="AT52" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU52" t="n">
         <v>55.35752960352423</v>
       </c>
-      <c r="AU52" t="n">
+      <c r="AV52" t="n">
+        <v>18.06438992422698</v>
+      </c>
+      <c r="AW52" t="n">
         <v>0.6959821428571429</v>
       </c>
-      <c r="AV52" t="n">
+      <c r="AX52" t="n">
         <v>31.43663314688067</v>
       </c>
-      <c r="AW52" t="n">
+      <c r="AY52" t="n">
         <v>-0.9330413776996519</v>
       </c>
-      <c r="AX52" t="n">
+      <c r="AZ52" t="n">
         <v>0.2554237568151246</v>
       </c>
-      <c r="AY52" t="n">
+      <c r="BA52" t="n">
         <v>8.029662939995131</v>
       </c>
     </row>
@@ -7998,21 +8314,27 @@
         <v>0.585</v>
       </c>
       <c r="AT53" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU53" t="n">
         <v>120.4613095238095</v>
       </c>
-      <c r="AU53" t="n">
+      <c r="AV53" t="n">
+        <v>8.301420630018528</v>
+      </c>
+      <c r="AW53" t="n">
         <v>0.5561426684280054</v>
       </c>
-      <c r="AV53" t="n">
+      <c r="AX53" t="n">
         <v>16.47515809594595</v>
       </c>
-      <c r="AW53" t="n">
+      <c r="AY53" t="n">
         <v>-1.059704205037399</v>
       </c>
-      <c r="AX53" t="n">
+      <c r="AZ53" t="n">
         <v>0.2105696461538427</v>
       </c>
-      <c r="AY53" t="n">
+      <c r="BA53" t="n">
         <v>3.469168210591955</v>
       </c>
     </row>
@@ -8139,21 +8461,27 @@
         <v>0.585</v>
       </c>
       <c r="AT54" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU54" t="n">
         <v>109.2225954198473</v>
       </c>
-      <c r="AU54" t="n">
+      <c r="AV54" t="n">
+        <v>9.155614698186209</v>
+      </c>
+      <c r="AW54" t="n">
         <v>0.5568335588633289</v>
       </c>
-      <c r="AV54" t="n">
+      <c r="AX54" t="n">
         <v>17.18961723916043</v>
       </c>
-      <c r="AW54" t="n">
+      <c r="AY54" t="n">
         <v>-1.09799079624996</v>
       </c>
-      <c r="AX54" t="n">
+      <c r="AZ54" t="n">
         <v>0.2230482700063978</v>
       </c>
-      <c r="AY54" t="n">
+      <c r="BA54" t="n">
         <v>3.834114387266885</v>
       </c>
     </row>
@@ -8280,21 +8608,27 @@
         <v>0.585</v>
       </c>
       <c r="AT55" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU55" t="n">
         <v>48.06573001322752</v>
       </c>
-      <c r="AU55" t="n">
+      <c r="AV55" t="n">
+        <v>20.80484369476556</v>
+      </c>
+      <c r="AW55" t="n">
         <v>0.6501619620546044</v>
       </c>
-      <c r="AV55" t="n">
+      <c r="AX55" t="n">
         <v>34.16916319918331</v>
       </c>
-      <c r="AW55" t="n">
+      <c r="AY55" t="n">
         <v>-1.013558134662488</v>
       </c>
-      <c r="AX55" t="n">
+      <c r="AZ55" t="n">
         <v>0.2700331914670088</v>
       </c>
-      <c r="AY55" t="n">
+      <c r="BA55" t="n">
         <v>9.226808188432537</v>
       </c>
     </row>
@@ -8421,21 +8755,27 @@
         <v>0.788</v>
       </c>
       <c r="AT56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU56" t="n">
         <v>84.28579136690648</v>
       </c>
-      <c r="AU56" t="n">
+      <c r="AV56" t="n">
+        <v>11.86439592940258</v>
+      </c>
+      <c r="AW56" t="n">
         <v>0.5164166123070233</v>
       </c>
-      <c r="AV56" t="n">
+      <c r="AX56" t="n">
         <v>31.13148059335148</v>
       </c>
-      <c r="AW56" t="n">
+      <c r="AY56" t="n">
         <v>-1.029758709416929</v>
       </c>
-      <c r="AX56" t="n">
+      <c r="AZ56" t="n">
         <v>0.1811914954031918</v>
       </c>
-      <c r="AY56" t="n">
+      <c r="BA56" t="n">
         <v>5.640759522824799</v>
       </c>
     </row>
@@ -8562,21 +8902,27 @@
         <v>0.536</v>
       </c>
       <c r="AT57" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU57" t="n">
         <v>70.80198674418605</v>
       </c>
-      <c r="AU57" t="n">
+      <c r="AV57" t="n">
+        <v>14.12389744956014</v>
+      </c>
+      <c r="AW57" t="n">
         <v>0.5656565656565657</v>
       </c>
-      <c r="AV57" t="n">
+      <c r="AX57" t="n">
         <v>42.28261169430561</v>
       </c>
-      <c r="AW57" t="n">
+      <c r="AY57" t="n">
         <v>-1.071407723597514</v>
       </c>
-      <c r="AX57" t="n">
+      <c r="AZ57" t="n">
         <v>0.1485071659290358</v>
       </c>
-      <c r="AY57" t="n">
+      <c r="BA57" t="n">
         <v>6.279270830799232</v>
       </c>
     </row>
@@ -8703,21 +9049,27 @@
         <v>0.788</v>
       </c>
       <c r="AT58" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU58" t="n">
         <v>87.00776041666667</v>
       </c>
-      <c r="AU58" t="n">
+      <c r="AV58" t="n">
+        <v>11.4932276754528</v>
+      </c>
+      <c r="AW58" t="n">
         <v>0.5489781536293165</v>
       </c>
-      <c r="AV58" t="n">
+      <c r="AX58" t="n">
         <v>30.4083735401035</v>
       </c>
-      <c r="AW58" t="n">
+      <c r="AY58" t="n">
         <v>-1.076020463092165</v>
       </c>
-      <c r="AX58" t="n">
+      <c r="AZ58" t="n">
         <v>0.181805467668072</v>
       </c>
-      <c r="AY58" t="n">
+      <c r="BA58" t="n">
         <v>5.528408572483942</v>
       </c>
     </row>
@@ -8844,21 +9196,27 @@
         <v>0.536</v>
       </c>
       <c r="AT59" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU59" t="n">
         <v>76.72765957446808</v>
       </c>
-      <c r="AU59" t="n">
+      <c r="AV59" t="n">
+        <v>13.03310964450114</v>
+      </c>
+      <c r="AW59" t="n">
         <v>0.5607476635514019</v>
       </c>
-      <c r="AV59" t="n">
+      <c r="AX59" t="n">
         <v>41.39388452825128</v>
       </c>
-      <c r="AW59" t="n">
+      <c r="AY59" t="n">
         <v>-1.131721301339614</v>
       </c>
-      <c r="AX59" t="n">
+      <c r="AZ59" t="n">
         <v>0.1468960643433882</v>
       </c>
-      <c r="AY59" t="n">
+      <c r="BA59" t="n">
         <v>6.080598725084783</v>
       </c>
     </row>
@@ -8985,21 +9343,27 @@
         <v>0.585</v>
       </c>
       <c r="AT60" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU60" t="n">
         <v>93.55598173611111</v>
       </c>
-      <c r="AU60" t="n">
+      <c r="AV60" t="n">
+        <v>10.68878741308762</v>
+      </c>
+      <c r="AW60" t="n">
         <v>0.7698454981353223</v>
       </c>
-      <c r="AV60" t="n">
+      <c r="AX60" t="n">
         <v>28.16106955669685</v>
       </c>
-      <c r="AW60" t="n">
+      <c r="AY60" t="n">
         <v>-1.148906986345209</v>
       </c>
-      <c r="AX60" t="n">
+      <c r="AZ60" t="n">
         <v>0.1640718941643498</v>
       </c>
-      <c r="AY60" t="n">
+      <c r="BA60" t="n">
         <v>4.620440023861259</v>
       </c>
     </row>
@@ -9126,21 +9490,27 @@
         <v>0.585</v>
       </c>
       <c r="AT61" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU61" t="n">
         <v>68.17344376893939</v>
       </c>
-      <c r="AU61" t="n">
+      <c r="AV61" t="n">
+        <v>14.66846831721315</v>
+      </c>
+      <c r="AW61" t="n">
         <v>0.7409224730127575</v>
       </c>
-      <c r="AV61" t="n">
+      <c r="AX61" t="n">
         <v>28.34964144442967</v>
       </c>
-      <c r="AW61" t="n">
+      <c r="AY61" t="n">
         <v>-0.9802187884414533</v>
       </c>
-      <c r="AX61" t="n">
+      <c r="AZ61" t="n">
         <v>0.2324436326842925</v>
       </c>
-      <c r="AY61" t="n">
+      <c r="BA61" t="n">
         <v>6.589693642640406</v>
       </c>
     </row>
@@ -9213,7 +9583,7 @@
         <v>0.2556666666666667</v>
       </c>
       <c r="T62" t="n">
-        <v>25.52</v>
+        <v>35.52</v>
       </c>
       <c r="U62" t="n">
         <v>17.36</v>
@@ -9230,7 +9600,7 @@
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="n">
-        <v>680.2507836990595</v>
+        <v>488.7387387387387</v>
       </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr"/>
@@ -9267,21 +9637,27 @@
         <v>0.788</v>
       </c>
       <c r="AT62" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU62" t="n">
         <v>60.43922811059907</v>
       </c>
-      <c r="AU62" t="n">
-        <v>0.3197492163009404</v>
-      </c>
       <c r="AV62" t="n">
+        <v>16.54554552169459</v>
+      </c>
+      <c r="AW62" t="n">
+        <v>0.5112612612612614</v>
+      </c>
+      <c r="AX62" t="n">
         <v>35.750550975415</v>
       </c>
-      <c r="AW62" t="n">
+      <c r="AY62" t="n">
         <v>-1.059967417806882</v>
       </c>
-      <c r="AX62" t="n">
+      <c r="AZ62" t="n">
         <v>0.2271852849396293</v>
       </c>
-      <c r="AY62" t="n">
+      <c r="BA62" t="n">
         <v>8.1219991100984</v>
       </c>
     </row>
@@ -9354,7 +9730,7 @@
         <v>0.201</v>
       </c>
       <c r="T63" t="n">
-        <v>25.15</v>
+        <v>35.15</v>
       </c>
       <c r="U63" t="n">
         <v>18.2</v>
@@ -9371,7 +9747,7 @@
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
       <c r="AA63" t="n">
-        <v>723.6580516898608</v>
+        <v>517.7809388335704</v>
       </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr"/>
@@ -9408,21 +9784,27 @@
         <v>0.788</v>
       </c>
       <c r="AT63" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU63" t="n">
         <v>71.22549450549451</v>
       </c>
-      <c r="AU63" t="n">
-        <v>0.2763419483101391</v>
-      </c>
       <c r="AV63" t="n">
+        <v>14.03991656278157</v>
+      </c>
+      <c r="AW63" t="n">
+        <v>0.4822190611664296</v>
+      </c>
+      <c r="AX63" t="n">
         <v>31.74524498440573</v>
       </c>
-      <c r="AW63" t="n">
+      <c r="AY63" t="n">
         <v>-1.07072599241777</v>
       </c>
-      <c r="AX63" t="n">
+      <c r="AZ63" t="n">
         <v>0.2097736888129386</v>
       </c>
-      <c r="AY63" t="n">
+      <c r="BA63" t="n">
         <v>6.659317142649229</v>
       </c>
     </row>
@@ -9495,7 +9877,7 @@
         <v>0.201</v>
       </c>
       <c r="T64" t="n">
-        <v>25.15</v>
+        <v>35.15</v>
       </c>
       <c r="U64" t="n">
         <v>18.2</v>
@@ -9512,7 +9894,7 @@
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
       <c r="AA64" t="n">
-        <v>723.6580516898608</v>
+        <v>517.7809388335704</v>
       </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr"/>
@@ -9549,21 +9931,27 @@
         <v>0.788</v>
       </c>
       <c r="AT64" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU64" t="n">
         <v>71.22549450549451</v>
       </c>
-      <c r="AU64" t="n">
-        <v>0.2763419483101391</v>
-      </c>
       <c r="AV64" t="n">
+        <v>14.03991656278157</v>
+      </c>
+      <c r="AW64" t="n">
+        <v>0.4822190611664296</v>
+      </c>
+      <c r="AX64" t="n">
         <v>32.75482157518042</v>
       </c>
-      <c r="AW64" t="n">
+      <c r="AY64" t="n">
         <v>-1.07072599241777</v>
       </c>
-      <c r="AX64" t="n">
+      <c r="AZ64" t="n">
         <v>0.2051731480905204</v>
       </c>
-      <c r="AY64" t="n">
+      <c r="BA64" t="n">
         <v>6.720409857723063</v>
       </c>
     </row>
@@ -9690,21 +10078,27 @@
         <v>0.536</v>
       </c>
       <c r="AT65" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU65" t="n">
         <v>70.78017943396226</v>
       </c>
-      <c r="AU65" t="n">
+      <c r="AV65" t="n">
+        <v>14.12824900978102</v>
+      </c>
+      <c r="AW65" t="n">
         <v>0.547008547008547</v>
       </c>
-      <c r="AV65" t="n">
+      <c r="AX65" t="n">
         <v>37.77978443238764</v>
       </c>
-      <c r="AW65" t="n">
+      <c r="AY65" t="n">
         <v>-1.072717162486702</v>
       </c>
-      <c r="AX65" t="n">
+      <c r="AZ65" t="n">
         <v>0.1711270057226029</v>
       </c>
-      <c r="AY65" t="n">
+      <c r="BA65" t="n">
         <v>6.465141386759904</v>
       </c>
     </row>
@@ -9831,21 +10225,27 @@
         <v>0.536</v>
       </c>
       <c r="AT66" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU66" t="n">
         <v>73.034885</v>
       </c>
-      <c r="AU66" t="n">
+      <c r="AV66" t="n">
+        <v>13.69208700746226</v>
+      </c>
+      <c r="AW66" t="n">
         <v>0.5416666666666667</v>
       </c>
-      <c r="AV66" t="n">
+      <c r="AX66" t="n">
         <v>46.78990518799996</v>
       </c>
-      <c r="AW66" t="n">
+      <c r="AY66" t="n">
         <v>-1.186907968195777</v>
       </c>
-      <c r="AX66" t="n">
+      <c r="AZ66" t="n">
         <v>0.1264668813853405</v>
       </c>
-      <c r="AY66" t="n">
+      <c r="BA66" t="n">
         <v>5.917373389442116</v>
       </c>
     </row>
@@ -9972,21 +10372,27 @@
         <v>0.585</v>
       </c>
       <c r="AT67" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU67" t="n">
         <v>85.05351446969696</v>
       </c>
-      <c r="AU67" t="n">
+      <c r="AV67" t="n">
+        <v>11.75730369561956</v>
+      </c>
+      <c r="AW67" t="n">
         <v>0.7659574468085105</v>
       </c>
-      <c r="AV67" t="n">
+      <c r="AX67" t="n">
         <v>29.55848025895564</v>
       </c>
-      <c r="AW67" t="n">
+      <c r="AY67" t="n">
         <v>-1.05716724908219</v>
       </c>
-      <c r="AX67" t="n">
+      <c r="AZ67" t="n">
         <v>0.1735620252135451</v>
       </c>
-      <c r="AY67" t="n">
+      <c r="BA67" t="n">
         <v>5.130229695978934</v>
       </c>
     </row>
@@ -10113,21 +10519,27 @@
         <v>0.585</v>
       </c>
       <c r="AT68" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU68" t="n">
         <v>95.80497285285286</v>
       </c>
-      <c r="AU68" t="n">
+      <c r="AV68" t="n">
+        <v>10.43787154489259</v>
+      </c>
+      <c r="AW68" t="n">
         <v>0.7672955974842768</v>
       </c>
-      <c r="AV68" t="n">
+      <c r="AX68" t="n">
         <v>27.95108301698842</v>
       </c>
-      <c r="AW68" t="n">
+      <c r="AY68" t="n">
         <v>-1.062612342442872</v>
       </c>
-      <c r="AX68" t="n">
+      <c r="AZ68" t="n">
         <v>0.1651892043876882</v>
       </c>
-      <c r="AY68" t="n">
+      <c r="BA68" t="n">
         <v>4.61721716535054</v>
       </c>
     </row>
@@ -10254,21 +10666,27 @@
         <v>0.585</v>
       </c>
       <c r="AT69" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU69" t="n">
         <v>102.9321114369501</v>
       </c>
-      <c r="AU69" t="n">
+      <c r="AV69" t="n">
+        <v>9.715141232797292</v>
+      </c>
+      <c r="AW69" t="n">
         <v>0.5605670103092784</v>
       </c>
-      <c r="AV69" t="n">
+      <c r="AX69" t="n">
         <v>24.10341074609785</v>
       </c>
-      <c r="AW69" t="n">
+      <c r="AY69" t="n">
         <v>-1.162202419950019</v>
       </c>
-      <c r="AX69" t="n">
+      <c r="AZ69" t="n">
         <v>0.1729739026459769</v>
       </c>
-      <c r="AY69" t="n">
+      <c r="BA69" t="n">
         <v>4.169261023831525</v>
       </c>
     </row>
@@ -10395,21 +10813,27 @@
         <v>0.788</v>
       </c>
       <c r="AT70" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU70" t="n">
         <v>78.68020076150917</v>
       </c>
-      <c r="AU70" t="n">
+      <c r="AV70" t="n">
+        <v>12.70967778833129</v>
+      </c>
+      <c r="AW70" t="n">
         <v>0.5284035259549461</v>
       </c>
-      <c r="AV70" t="n">
+      <c r="AX70" t="n">
         <v>33.07869485466203</v>
       </c>
-      <c r="AW70" t="n">
+      <c r="AY70" t="n">
         <v>-0.9735100220183867</v>
       </c>
-      <c r="AX70" t="n">
+      <c r="AZ70" t="n">
         <v>0.1653302877966243</v>
       </c>
-      <c r="AY70" t="n">
+      <c r="BA70" t="n">
         <v>5.468910140257988</v>
       </c>
     </row>
@@ -10536,21 +10960,27 @@
         <v>0.788</v>
       </c>
       <c r="AT71" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU71" t="n">
         <v>74.43121248499399</v>
       </c>
-      <c r="AU71" t="n">
+      <c r="AV71" t="n">
+        <v>13.4352238343774</v>
+      </c>
+      <c r="AW71" t="n">
         <v>0.5137186223000584</v>
       </c>
-      <c r="AV71" t="n">
+      <c r="AX71" t="n">
         <v>28.43772466129882</v>
       </c>
-      <c r="AW71" t="n">
+      <c r="AY71" t="n">
         <v>-1.151540486656524</v>
       </c>
-      <c r="AX71" t="n">
+      <c r="AZ71" t="n">
         <v>0.224534879706159</v>
       </c>
-      <c r="AY71" t="n">
+      <c r="BA71" t="n">
         <v>6.385261085941602</v>
       </c>
     </row>
@@ -10677,21 +11107,27 @@
         <v>0.585</v>
       </c>
       <c r="AT72" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU72" t="n">
         <v>93.83754512635377</v>
       </c>
-      <c r="AU72" t="n">
+      <c r="AV72" t="n">
+        <v>10.65671526949563</v>
+      </c>
+      <c r="AW72" t="n">
         <v>0.5512958963282937</v>
       </c>
-      <c r="AV72" t="n">
+      <c r="AX72" t="n">
         <v>27.25954615592946</v>
       </c>
-      <c r="AW72" t="n">
+      <c r="AY72" t="n">
         <v>-1.081507885923864</v>
       </c>
-      <c r="AX72" t="n">
+      <c r="AZ72" t="n">
         <v>0.1704181532420173</v>
       </c>
-      <c r="AY72" t="n">
+      <c r="BA72" t="n">
         <v>4.64552151410903</v>
       </c>
     </row>
@@ -10818,21 +11254,27 @@
         <v>0.585</v>
       </c>
       <c r="AT73" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU73" t="n">
         <v>80.69806507082153</v>
       </c>
-      <c r="AU73" t="n">
+      <c r="AV73" t="n">
+        <v>12.39187084749044</v>
+      </c>
+      <c r="AW73" t="n">
         <v>0.7437386569872959</v>
       </c>
-      <c r="AV73" t="n">
+      <c r="AX73" t="n">
         <v>30.02082045458015</v>
       </c>
-      <c r="AW73" t="n">
+      <c r="AY73" t="n">
         <v>-1.008164398010397</v>
       </c>
-      <c r="AX73" t="n">
+      <c r="AZ73" t="n">
         <v>0.1771344004138958</v>
       </c>
-      <c r="AY73" t="n">
+      <c r="BA73" t="n">
         <v>5.317720031155273</v>
       </c>
     </row>
@@ -10959,21 +11401,27 @@
         <v>0.585</v>
       </c>
       <c r="AT74" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU74" t="n">
         <v>58.14073602661597</v>
       </c>
-      <c r="AU74" t="n">
+      <c r="AV74" t="n">
+        <v>17.19964466122711</v>
+      </c>
+      <c r="AW74" t="n">
         <v>0.7434146341463415</v>
       </c>
-      <c r="AV74" t="n">
+      <c r="AX74" t="n">
         <v>26.46707679984683</v>
       </c>
-      <c r="AW74" t="n">
+      <c r="AY74" t="n">
         <v>-0.9019527661726316</v>
       </c>
-      <c r="AX74" t="n">
+      <c r="AZ74" t="n">
         <v>0.2890653446677475</v>
       </c>
-      <c r="AY74" t="n">
+      <c r="BA74" t="n">
         <v>7.650714677495467</v>
       </c>
     </row>
@@ -11100,21 +11548,27 @@
         <v>0.788</v>
       </c>
       <c r="AT75" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU75" t="n">
         <v>58.797049689441</v>
       </c>
-      <c r="AU75" t="n">
+      <c r="AV75" t="n">
+        <v>17.00765608617917</v>
+      </c>
+      <c r="AW75" t="n">
         <v>0.449886104783599</v>
       </c>
-      <c r="AV75" t="n">
+      <c r="AX75" t="n">
         <v>30.22124201621856</v>
       </c>
-      <c r="AW75" t="n">
+      <c r="AY75" t="n">
         <v>-1.064321440481539</v>
       </c>
-      <c r="AX75" t="n">
+      <c r="AZ75" t="n">
         <v>0.2678379030470969</v>
       </c>
-      <c r="AY75" t="n">
+      <c r="BA75" t="n">
         <v>8.094394089102797</v>
       </c>
     </row>
@@ -11241,21 +11695,27 @@
         <v>0.585</v>
       </c>
       <c r="AT76" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU76" t="n">
         <v>67.24956401960785</v>
       </c>
-      <c r="AU76" t="n">
+      <c r="AV76" t="n">
+        <v>14.86998487764815</v>
+      </c>
+      <c r="AW76" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="AV76" t="n">
+      <c r="AX76" t="n">
         <v>32.73336164766602</v>
       </c>
-      <c r="AW76" t="n">
+      <c r="AY76" t="n">
         <v>-1.036430349351861</v>
       </c>
-      <c r="AX76" t="n">
+      <c r="AZ76" t="n">
         <v>0.2020516390549202</v>
       </c>
-      <c r="AY76" t="n">
+      <c r="BA76" t="n">
         <v>6.613829372688381</v>
       </c>
     </row>
@@ -11382,21 +11842,27 @@
         <v>0.585</v>
       </c>
       <c r="AT77" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU77" t="n">
         <v>67.63895368951613</v>
       </c>
-      <c r="AU77" t="n">
+      <c r="AV77" t="n">
+        <v>14.78438008651511</v>
+      </c>
+      <c r="AW77" t="n">
         <v>0.7311653116531165</v>
       </c>
-      <c r="AV77" t="n">
+      <c r="AX77" t="n">
         <v>27.85958429127932</v>
       </c>
-      <c r="AW77" t="n">
+      <c r="AY77" t="n">
         <v>-0.9447135609596995</v>
       </c>
-      <c r="AX77" t="n">
+      <c r="AZ77" t="n">
         <v>0.2290004233178914</v>
       </c>
-      <c r="AY77" t="n">
+      <c r="BA77" t="n">
         <v>6.379856596163442</v>
       </c>
     </row>
@@ -11523,21 +11989,27 @@
         <v>0.585</v>
       </c>
       <c r="AT78" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU78" t="n">
         <v>91.96880891173952</v>
       </c>
-      <c r="AU78" t="n">
+      <c r="AV78" t="n">
+        <v>10.87325161468252</v>
+      </c>
+      <c r="AW78" t="n">
         <v>0.5427115987460815</v>
       </c>
-      <c r="AV78" t="n">
+      <c r="AX78" t="n">
         <v>21.8162096187406</v>
       </c>
-      <c r="AW78" t="n">
+      <c r="AY78" t="n">
         <v>-1.136069687512091</v>
       </c>
-      <c r="AX78" t="n">
+      <c r="AZ78" t="n">
         <v>0.2143935207599353</v>
       </c>
-      <c r="AY78" t="n">
+      <c r="BA78" t="n">
         <v>4.677253989798563</v>
       </c>
     </row>
@@ -11664,21 +12136,27 @@
         <v>0.585</v>
       </c>
       <c r="AT79" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU79" t="n">
         <v>72.98086995867769</v>
       </c>
-      <c r="AU79" t="n">
+      <c r="AV79" t="n">
+        <v>13.70222087741908</v>
+      </c>
+      <c r="AW79" t="n">
         <v>0.7195828505214369</v>
       </c>
-      <c r="AV79" t="n">
+      <c r="AX79" t="n">
         <v>18.28478648070588</v>
       </c>
-      <c r="AW79" t="n">
+      <c r="AY79" t="n">
         <v>-0.7957323640055816</v>
       </c>
-      <c r="AX79" t="n">
+      <c r="AZ79" t="n">
         <v>0.3250436485054538</v>
       </c>
-      <c r="AY79" t="n">
+      <c r="BA79" t="n">
         <v>5.943353709831833</v>
       </c>
     </row>
@@ -11805,21 +12283,27 @@
         <v>0.585</v>
       </c>
       <c r="AT80" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU80" t="n">
         <v>63.13908010101009</v>
       </c>
-      <c r="AU80" t="n">
+      <c r="AV80" t="n">
+        <v>15.83805146353411</v>
+      </c>
+      <c r="AW80" t="n">
         <v>0.7093933463796477</v>
       </c>
-      <c r="AV80" t="n">
+      <c r="AX80" t="n">
         <v>22.12908955486301</v>
       </c>
-      <c r="AW80" t="n">
+      <c r="AY80" t="n">
         <v>-1.083830924468203</v>
       </c>
-      <c r="AX80" t="n">
+      <c r="AZ80" t="n">
         <v>0.2998648154876037</v>
       </c>
-      <c r="AY80" t="n">
+      <c r="BA80" t="n">
         <v>6.635735356277657</v>
       </c>
     </row>
@@ -11946,21 +12430,27 @@
         <v>0.585</v>
       </c>
       <c r="AT81" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU81" t="n">
         <v>60.47368048048047</v>
       </c>
-      <c r="AU81" t="n">
+      <c r="AV81" t="n">
+        <v>16.53611938375038</v>
+      </c>
+      <c r="AW81" t="n">
         <v>0.7073813708260106</v>
       </c>
-      <c r="AV81" t="n">
+      <c r="AX81" t="n">
         <v>23.88772942228289</v>
       </c>
-      <c r="AW81" t="n">
+      <c r="AY81" t="n">
         <v>-0.852490835998494</v>
       </c>
-      <c r="AX81" t="n">
+      <c r="AZ81" t="n">
         <v>0.2994186256562353</v>
       </c>
-      <c r="AY81" t="n">
+      <c r="BA81" t="n">
         <v>7.152431113667959</v>
       </c>
     </row>
@@ -12087,21 +12577,27 @@
         <v>0.788</v>
       </c>
       <c r="AT82" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU82" t="n">
         <v>82.68561093247588</v>
       </c>
-      <c r="AU82" t="n">
+      <c r="AV82" t="n">
+        <v>12.0940026774022</v>
+      </c>
+      <c r="AW82" t="n">
         <v>0.4902683876254866</v>
       </c>
-      <c r="AV82" t="n">
+      <c r="AX82" t="n">
         <v>29.22142888916803</v>
       </c>
-      <c r="AW82" t="n">
+      <c r="AY82" t="n">
         <v>-1.073512489772441</v>
       </c>
-      <c r="AX82" t="n">
+      <c r="AZ82" t="n">
         <v>0.1986099449474032</v>
       </c>
-      <c r="AY82" t="n">
+      <c r="BA82" t="n">
         <v>5.80366638296212</v>
       </c>
     </row>
@@ -12228,21 +12724,27 @@
         <v>0.788</v>
       </c>
       <c r="AT83" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU83" t="n">
         <v>106.3460708782743</v>
       </c>
-      <c r="AU83" t="n">
+      <c r="AV83" t="n">
+        <v>9.403262309000761</v>
+      </c>
+      <c r="AW83" t="n">
         <v>0.5595520868680013</v>
       </c>
-      <c r="AV83" t="n">
+      <c r="AX83" t="n">
         <v>26.31625012037236</v>
       </c>
-      <c r="AW83" t="n">
+      <c r="AY83" t="n">
         <v>-1.045162407612312</v>
       </c>
-      <c r="AX83" t="n">
+      <c r="AZ83" t="n">
         <v>0.1574768288150041</v>
       </c>
-      <c r="AY83" t="n">
+      <c r="BA83" t="n">
         <v>4.144199615258708</v>
       </c>
     </row>
@@ -12369,21 +12871,27 @@
         <v>0.788</v>
       </c>
       <c r="AT84" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU84" t="n">
         <v>96.34761279018835</v>
       </c>
-      <c r="AU84" t="n">
+      <c r="AV84" t="n">
+        <v>10.37908434926823</v>
+      </c>
+      <c r="AW84" t="n">
         <v>0.4989025460930642</v>
       </c>
-      <c r="AV84" t="n">
+      <c r="AX84" t="n">
         <v>30.20416467837983</v>
       </c>
-      <c r="AW84" t="n">
+      <c r="AY84" t="n">
         <v>-1.011763599487811</v>
       </c>
-      <c r="AX84" t="n">
+      <c r="AZ84" t="n">
         <v>0.1625698637855855</v>
       </c>
-      <c r="AY84" t="n">
+      <c r="BA84" t="n">
         <v>4.910286937521602</v>
       </c>
     </row>
@@ -12510,21 +13018,27 @@
         <v>0.788</v>
       </c>
       <c r="AT85" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU85" t="n">
         <v>75.91252181500872</v>
       </c>
-      <c r="AU85" t="n">
+      <c r="AV85" t="n">
+        <v>13.1730573045235</v>
+      </c>
+      <c r="AW85" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="AV85" t="n">
+      <c r="AX85" t="n">
         <v>27.98331631734705</v>
       </c>
-      <c r="AW85" t="n">
+      <c r="AY85" t="n">
         <v>-1.056436243301099</v>
       </c>
-      <c r="AX85" t="n">
+      <c r="AZ85" t="n">
         <v>0.2261410104794487</v>
       </c>
-      <c r="AY85" t="n">
+      <c r="BA85" t="n">
         <v>6.328175428570905</v>
       </c>
     </row>
@@ -12651,21 +13165,27 @@
         <v>0.788</v>
       </c>
       <c r="AT86" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU86" t="n">
         <v>74.01554341226473</v>
       </c>
-      <c r="AU86" t="n">
+      <c r="AV86" t="n">
+        <v>13.51067564862728</v>
+      </c>
+      <c r="AW86" t="n">
         <v>0.4900928792569659</v>
       </c>
-      <c r="AV86" t="n">
+      <c r="AX86" t="n">
         <v>30.59860950966031</v>
       </c>
-      <c r="AW86" t="n">
+      <c r="AY86" t="n">
         <v>-1.139184969499528</v>
       </c>
-      <c r="AX86" t="n">
+      <c r="AZ86" t="n">
         <v>0.2131678007547578</v>
       </c>
-      <c r="AY86" t="n">
+      <c r="BA86" t="n">
         <v>6.522638295327906</v>
       </c>
     </row>
@@ -12792,21 +13312,27 @@
         <v>0.585</v>
       </c>
       <c r="AT87" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU87" t="n">
         <v>60.21125734463277</v>
       </c>
-      <c r="AU87" t="n">
+      <c r="AV87" t="n">
+        <v>16.60818996481461</v>
+      </c>
+      <c r="AW87" t="n">
         <v>0.7318181818181819</v>
       </c>
-      <c r="AV87" t="n">
+      <c r="AX87" t="n">
         <v>27.00689943428555</v>
       </c>
-      <c r="AW87" t="n">
+      <c r="AY87" t="n">
         <v>-0.9994064701242487</v>
       </c>
-      <c r="AX87" t="n">
+      <c r="AZ87" t="n">
         <v>0.2723142473493239</v>
       </c>
-      <c r="AY87" t="n">
+      <c r="BA87" t="n">
         <v>7.354363492686352</v>
       </c>
     </row>
@@ -12933,21 +13459,27 @@
         <v>0.585</v>
       </c>
       <c r="AT88" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU88" t="n">
         <v>101.6063559322034</v>
       </c>
-      <c r="AU88" t="n">
+      <c r="AV88" t="n">
+        <v>9.841903991392504</v>
+      </c>
+      <c r="AW88" t="n">
         <v>0.5961209355390759</v>
       </c>
-      <c r="AV88" t="n">
+      <c r="AX88" t="n">
         <v>20.09981608868212</v>
       </c>
-      <c r="AW88" t="n">
+      <c r="AY88" t="n">
         <v>-0.9530514877786842</v>
       </c>
-      <c r="AX88" t="n">
+      <c r="AZ88" t="n">
         <v>0.2165437559626953</v>
       </c>
-      <c r="AY88" t="n">
+      <c r="BA88" t="n">
         <v>4.352489670002637</v>
       </c>
     </row>
@@ -12955,10 +13487,8 @@
       <c r="A89" s="1" t="n">
         <v>87</v>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B89" t="n">
+        <v>1</v>
       </c>
       <c r="C89" t="n">
         <v>88</v>
@@ -13098,21 +13628,27 @@
         <v>0.717</v>
       </c>
       <c r="AT89" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU89" t="n">
         <v>34.15994277539342</v>
       </c>
-      <c r="AU89" t="n">
+      <c r="AV89" t="n">
+        <v>29.27405372354237</v>
+      </c>
+      <c r="AW89" t="n">
         <v>0.5212328767123288</v>
       </c>
-      <c r="AV89" t="n">
+      <c r="AX89" t="n">
         <v>59.38716473519461</v>
       </c>
-      <c r="AW89" t="n">
+      <c r="AY89" t="n">
         <v>-0.921325744894543</v>
       </c>
-      <c r="AX89" t="n">
+      <c r="AZ89" t="n">
         <v>0.2273110803333757</v>
       </c>
-      <c r="AY89" t="n">
+      <c r="BA89" t="n">
         <v>13.49936057389324</v>
       </c>
     </row>
@@ -13120,10 +13656,8 @@
       <c r="A90" s="1" t="n">
         <v>88</v>
       </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="B90" t="n">
+        <v>2</v>
       </c>
       <c r="C90" t="n">
         <v>8386</v>
@@ -13263,21 +13797,27 @@
         <v>0.717</v>
       </c>
       <c r="AT90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU90" t="n">
         <v>33.18294478527607</v>
       </c>
-      <c r="AU90" t="n">
+      <c r="AV90" t="n">
+        <v>30.13596311210209</v>
+      </c>
+      <c r="AW90" t="n">
         <v>0.5018337408312958</v>
       </c>
-      <c r="AV90" t="n">
+      <c r="AX90" t="n">
         <v>55.07549417735655</v>
       </c>
-      <c r="AW90" t="n">
+      <c r="AY90" t="n">
         <v>-0.9396264176117411</v>
       </c>
-      <c r="AX90" t="n">
+      <c r="AZ90" t="n">
         <v>0.2562349769016561</v>
       </c>
-      <c r="AY90" t="n">
+      <c r="BA90" t="n">
         <v>14.11226797838226</v>
       </c>
     </row>
@@ -13285,10 +13825,8 @@
       <c r="A91" s="1" t="n">
         <v>89</v>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B91" t="n">
+        <v>1</v>
       </c>
       <c r="C91" t="n">
         <v>9096</v>
@@ -13428,21 +13966,27 @@
         <v>0.717</v>
       </c>
       <c r="AT91" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU91" t="n">
         <v>37.93648208469055</v>
       </c>
-      <c r="AU91" t="n">
+      <c r="AV91" t="n">
+        <v>26.35985059889238</v>
+      </c>
+      <c r="AW91" t="n">
         <v>0.5147523709167544</v>
       </c>
-      <c r="AV91" t="n">
+      <c r="AX91" t="n">
         <v>45.17757835768303</v>
       </c>
-      <c r="AW91" t="n">
+      <c r="AY91" t="n">
         <v>-0.9000000000000001</v>
       </c>
-      <c r="AX91" t="n">
+      <c r="AZ91" t="n">
         <v>0.2747689268163115</v>
       </c>
-      <c r="AY91" t="n">
+      <c r="BA91" t="n">
         <v>12.41339472150039</v>
       </c>
     </row>
@@ -13450,10 +13994,8 @@
       <c r="A92" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="B92" t="n">
+        <v>12</v>
       </c>
       <c r="C92" t="n">
         <v>721</v>
@@ -13593,21 +14135,27 @@
         <v>0.717</v>
       </c>
       <c r="AT92" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU92" t="n">
         <v>40.56470588235294</v>
       </c>
-      <c r="AU92" t="n">
+      <c r="AV92" t="n">
+        <v>24.65197215777262</v>
+      </c>
+      <c r="AW92" t="n">
         <v>0.5620483820295319</v>
       </c>
-      <c r="AV92" t="n">
+      <c r="AX92" t="n">
         <v>43.38637434690112</v>
       </c>
-      <c r="AW92" t="n">
+      <c r="AY92" t="n">
         <v>-0.9772876892692561</v>
       </c>
-      <c r="AX92" t="n">
+      <c r="AZ92" t="n">
         <v>0.2638257036105743</v>
       </c>
-      <c r="AY92" t="n">
+      <c r="BA92" t="n">
         <v>11.44644073918296</v>
       </c>
     </row>
@@ -13615,10 +14163,8 @@
       <c r="A93" s="1" t="n">
         <v>91</v>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="B93" t="n">
+        <v>7</v>
       </c>
       <c r="C93" t="n">
         <v>7994</v>
@@ -13758,21 +14304,27 @@
         <v>0.717</v>
       </c>
       <c r="AT93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU93" t="n">
         <v>35.25954751131221</v>
       </c>
-      <c r="AU93" t="n">
+      <c r="AV93" t="n">
+        <v>28.36111267959899</v>
+      </c>
+      <c r="AW93" t="n">
         <v>0.4891354600092463</v>
       </c>
-      <c r="AV93" t="n">
+      <c r="AX93" t="n">
         <v>61.02294354014969</v>
       </c>
-      <c r="AW93" t="n">
+      <c r="AY93" t="n">
         <v>-0.8726919339164237</v>
       </c>
-      <c r="AX93" t="n">
+      <c r="AZ93" t="n">
         <v>0.2205905999210828</v>
       </c>
-      <c r="AY93" t="n">
+      <c r="BA93" t="n">
         <v>13.46108772447198</v>
       </c>
     </row>
@@ -13780,10 +14332,8 @@
       <c r="A94" s="1" t="n">
         <v>92</v>
       </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="B94" t="n">
+        <v>19</v>
       </c>
       <c r="C94" t="n">
         <v>795</v>
@@ -13923,21 +14473,27 @@
         <v>0.717</v>
       </c>
       <c r="AT94" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU94" t="n">
         <v>33.15173383317713</v>
       </c>
-      <c r="AU94" t="n">
+      <c r="AV94" t="n">
+        <v>30.16433484390593</v>
+      </c>
+      <c r="AW94" t="n">
         <v>0.4981185324553152</v>
       </c>
-      <c r="AV94" t="n">
+      <c r="AX94" t="n">
         <v>50.18888849181604</v>
       </c>
-      <c r="AW94" t="n">
+      <c r="AY94" t="n">
         <v>-0.8030209617755858</v>
       </c>
-      <c r="AX94" t="n">
+      <c r="AZ94" t="n">
         <v>0.2899244513121407</v>
       </c>
-      <c r="AY94" t="n">
+      <c r="BA94" t="n">
         <v>14.55098595795598</v>
       </c>
     </row>
@@ -13945,10 +14501,8 @@
       <c r="A95" s="1" t="n">
         <v>93</v>
       </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="B95" t="n">
+        <v>17</v>
       </c>
       <c r="C95" t="n">
         <v>881</v>
@@ -14088,21 +14642,27 @@
         <v>0.523</v>
       </c>
       <c r="AT95" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU95" t="n">
         <v>30.50483754512636</v>
       </c>
-      <c r="AU95" t="n">
+      <c r="AV95" t="n">
+        <v>32.78168580706853</v>
+      </c>
+      <c r="AW95" t="n">
         <v>0.5650125628140704</v>
       </c>
-      <c r="AV95" t="n">
+      <c r="AX95" t="n">
         <v>44.53537356895627</v>
       </c>
-      <c r="AW95" t="n">
+      <c r="AY95" t="n">
         <v>-0.9410150891632374</v>
       </c>
-      <c r="AX95" t="n">
+      <c r="AZ95" t="n">
         <v>0.3639814907180162</v>
       </c>
-      <c r="AY95" t="n">
+      <c r="BA95" t="n">
         <v>16.21005166131244</v>
       </c>
     </row>
@@ -14110,10 +14670,8 @@
       <c r="A96" s="1" t="n">
         <v>94</v>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="B96" t="n">
+        <v>14</v>
       </c>
       <c r="C96" t="n">
         <v>693</v>
@@ -14253,21 +14811,27 @@
         <v>0.717</v>
       </c>
       <c r="AT96" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU96" t="n">
         <v>40.07197898423818</v>
       </c>
-      <c r="AU96" t="n">
+      <c r="AV96" t="n">
+        <v>24.95509394216187</v>
+      </c>
+      <c r="AW96" t="n">
         <v>0.5391444713478613</v>
       </c>
-      <c r="AV96" t="n">
+      <c r="AX96" t="n">
         <v>41.91201493351629</v>
       </c>
-      <c r="AW96" t="n">
+      <c r="AY96" t="n">
         <v>-0.8697027197975964</v>
       </c>
-      <c r="AX96" t="n">
+      <c r="AZ96" t="n">
         <v>0.2754165199655664</v>
       </c>
-      <c r="AY96" t="n">
+      <c r="BA96" t="n">
         <v>11.5432612977339</v>
       </c>
     </row>
@@ -14275,10 +14839,8 @@
       <c r="A97" s="1" t="n">
         <v>95</v>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="B97" t="n">
+        <v>16</v>
       </c>
       <c r="C97" t="n">
         <v>740</v>
@@ -14418,21 +14980,27 @@
         <v>0.717</v>
       </c>
       <c r="AT97" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU97" t="n">
         <v>25.14212910532276</v>
       </c>
-      <c r="AU97" t="n">
+      <c r="AV97" t="n">
+        <v>39.77387896668994</v>
+      </c>
+      <c r="AW97" t="n">
         <v>0.5298189563365282</v>
       </c>
-      <c r="AV97" t="n">
+      <c r="AX97" t="n">
         <v>70.70612613426273</v>
       </c>
-      <c r="AW97" t="n">
+      <c r="AY97" t="n">
         <v>-0.8926196808510639</v>
       </c>
-      <c r="AX97" t="n">
+      <c r="AZ97" t="n">
         <v>0.2635851161810385</v>
       </c>
-      <c r="AY97" t="n">
+      <c r="BA97" t="n">
         <v>18.63708247181081</v>
       </c>
     </row>
@@ -14440,10 +15008,8 @@
       <c r="A98" s="1" t="n">
         <v>96</v>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="B98" t="n">
+        <v>2</v>
       </c>
       <c r="C98" t="n">
         <v>8384</v>
@@ -14583,21 +15149,27 @@
         <v>0.717</v>
       </c>
       <c r="AT98" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU98" t="n">
         <v>34.10823136818687</v>
       </c>
-      <c r="AU98" t="n">
+      <c r="AV98" t="n">
+        <v>29.31843604569632</v>
+      </c>
+      <c r="AW98" t="n">
         <v>0.5177038626609443</v>
       </c>
-      <c r="AV98" t="n">
+      <c r="AX98" t="n">
         <v>56.15700798713841</v>
       </c>
-      <c r="AW98" t="n">
+      <c r="AY98" t="n">
         <v>-0.9120214909335124</v>
       </c>
-      <c r="AX98" t="n">
+      <c r="AZ98" t="n">
         <v>0.2379812101557392</v>
       </c>
-      <c r="AY98" t="n">
+      <c r="BA98" t="n">
         <v>13.36431271950471</v>
       </c>
     </row>
@@ -14605,10 +15177,8 @@
       <c r="A99" s="1" t="n">
         <v>97</v>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="B99" t="n">
+        <v>17</v>
       </c>
       <c r="C99" t="n">
         <v>8954</v>
@@ -14748,21 +15318,27 @@
         <v>0.717</v>
       </c>
       <c r="AT99" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU99" t="n">
         <v>43.40028169014084</v>
       </c>
-      <c r="AU99" t="n">
+      <c r="AV99" t="n">
+        <v>23.04132510336143</v>
+      </c>
+      <c r="AW99" t="n">
         <v>0.5321560358460727</v>
       </c>
-      <c r="AV99" t="n">
+      <c r="AX99" t="n">
         <v>55.79246449666994</v>
       </c>
-      <c r="AW99" t="n">
+      <c r="AY99" t="n">
         <v>-0.9579330904272938</v>
       </c>
-      <c r="AX99" t="n">
+      <c r="AZ99" t="n">
         <v>0.1937192235493845</v>
       </c>
-      <c r="AY99" t="n">
+      <c r="BA99" t="n">
         <v>10.8080729022015</v>
       </c>
     </row>
@@ -14770,10 +15346,8 @@
       <c r="A100" s="1" t="n">
         <v>98</v>
       </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="B100" t="n">
+        <v>16</v>
       </c>
       <c r="C100" t="n">
         <v>764</v>
@@ -14913,21 +15487,27 @@
         <v>0.717</v>
       </c>
       <c r="AT100" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU100" t="n">
         <v>35.8758865248227</v>
       </c>
-      <c r="AU100" t="n">
+      <c r="AV100" t="n">
+        <v>27.87387565483839</v>
+      </c>
+      <c r="AW100" t="n">
         <v>0.535966149506347</v>
       </c>
-      <c r="AV100" t="n">
+      <c r="AX100" t="n">
         <v>65.93475017680478</v>
       </c>
-      <c r="AW100" t="n">
+      <c r="AY100" t="n">
         <v>-0.8845169545745361</v>
       </c>
-      <c r="AX100" t="n">
+      <c r="AZ100" t="n">
         <v>0.1937567807703534</v>
       </c>
-      <c r="AY100" t="n">
+      <c r="BA100" t="n">
         <v>12.77530493515518</v>
       </c>
     </row>
@@ -14935,10 +15515,8 @@
       <c r="A101" s="1" t="n">
         <v>99</v>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="B101" t="n">
+        <v>17</v>
       </c>
       <c r="C101" t="n">
         <v>4955</v>
@@ -15078,21 +15656,27 @@
         <v>0.523</v>
       </c>
       <c r="AT101" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU101" t="n">
         <v>31.9693215339233</v>
       </c>
-      <c r="AU101" t="n">
+      <c r="AV101" t="n">
+        <v>31.279988189267</v>
+      </c>
+      <c r="AW101" t="n">
         <v>0.5531634446397189</v>
       </c>
-      <c r="AV101" t="n">
+      <c r="AX101" t="n">
         <v>62.55686848770559</v>
       </c>
-      <c r="AW101" t="n">
+      <c r="AY101" t="n">
         <v>-0.8345370978332239</v>
       </c>
-      <c r="AX101" t="n">
+      <c r="AZ101" t="n">
         <v>0.2390186769233919</v>
       </c>
-      <c r="AY101" t="n">
+      <c r="BA101" t="n">
         <v>14.95225993840202</v>
       </c>
     </row>
@@ -15100,10 +15684,8 @@
       <c r="A102" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="B102" t="n">
+        <v>6</v>
       </c>
       <c r="C102" t="n">
         <v>7645</v>
@@ -15243,21 +15825,27 @@
         <v>0.717</v>
       </c>
       <c r="AT102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU102" t="n">
         <v>32.25160202360878</v>
       </c>
-      <c r="AU102" t="n">
+      <c r="AV102" t="n">
+        <v>31.00621169974693</v>
+      </c>
+      <c r="AW102" t="n">
         <v>0.5488779003423355</v>
       </c>
-      <c r="AV102" t="n">
+      <c r="AX102" t="n">
         <v>48.18483993222593</v>
       </c>
-      <c r="AW102" t="n">
+      <c r="AY102" t="n">
         <v>-0.8655913978494624</v>
       </c>
-      <c r="AX102" t="n">
+      <c r="AZ102" t="n">
         <v>0.3022826134073608</v>
       </c>
-      <c r="AY102" t="n">
+      <c r="BA102" t="n">
         <v>14.56543934132861</v>
       </c>
     </row>
@@ -15265,10 +15853,8 @@
       <c r="A103" s="1" t="n">
         <v>101</v>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B103" t="n">
+        <v>4</v>
       </c>
       <c r="C103" t="n">
         <v>6021</v>
@@ -15408,21 +15994,27 @@
         <v>0.717</v>
       </c>
       <c r="AT103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU103" t="n">
         <v>35.23089668615984</v>
       </c>
-      <c r="AU103" t="n">
+      <c r="AV103" t="n">
+        <v>28.38417678971087</v>
+      </c>
+      <c r="AW103" t="n">
         <v>0.4877683474787819</v>
       </c>
-      <c r="AV103" t="n">
+      <c r="AX103" t="n">
         <v>48.50036505453044</v>
       </c>
-      <c r="AW103" t="n">
+      <c r="AY103" t="n">
         <v>-0.8713188220230473</v>
       </c>
-      <c r="AX103" t="n">
+      <c r="AZ103" t="n">
         <v>0.2697981424651091</v>
       </c>
-      <c r="AY103" t="n">
+      <c r="BA103" t="n">
         <v>13.085308400592</v>
       </c>
     </row>
@@ -15430,10 +16022,8 @@
       <c r="A104" s="1" t="n">
         <v>102</v>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="B104" t="n">
+        <v>6</v>
       </c>
       <c r="C104" t="n">
         <v>205</v>
@@ -15573,21 +16163,27 @@
         <v>0.717</v>
       </c>
       <c r="AT104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU104" t="n">
         <v>34.03149664929263</v>
       </c>
-      <c r="AU104" t="n">
+      <c r="AV104" t="n">
+        <v>29.38454368626147</v>
+      </c>
+      <c r="AW104" t="n">
         <v>0.5196709585121603</v>
       </c>
-      <c r="AV104" t="n">
+      <c r="AX104" t="n">
         <v>42.08566962870098</v>
       </c>
-      <c r="AW104" t="n">
+      <c r="AY104" t="n">
         <v>-0.873405299313052</v>
       </c>
-      <c r="AX104" t="n">
+      <c r="AZ104" t="n">
         <v>0.3273385634947573</v>
       </c>
-      <c r="AY104" t="n">
+      <c r="BA104" t="n">
         <v>13.77626263997392</v>
       </c>
     </row>
@@ -15595,10 +16191,8 @@
       <c r="A105" s="1" t="n">
         <v>103</v>
       </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="B105" t="n">
+        <v>3</v>
       </c>
       <c r="C105" t="n">
         <v>4898</v>
@@ -15738,21 +16332,27 @@
         <v>0.717</v>
       </c>
       <c r="AT105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU105" t="n">
         <v>34.42013201320133</v>
       </c>
-      <c r="AU105" t="n">
+      <c r="AV105" t="n">
+        <v>29.05276480684226</v>
+      </c>
+      <c r="AW105" t="n">
         <v>0.5026672137874436</v>
       </c>
-      <c r="AV105" t="n">
+      <c r="AX105" t="n">
         <v>51.94526295590641</v>
       </c>
-      <c r="AW105" t="n">
+      <c r="AY105" t="n">
         <v>-0.7809629835791817</v>
       </c>
-      <c r="AX105" t="n">
+      <c r="AZ105" t="n">
         <v>0.2627407067212578</v>
       </c>
-      <c r="AY105" t="n">
+      <c r="BA105" t="n">
         <v>13.64813509985642</v>
       </c>
     </row>
@@ -15760,10 +16360,8 @@
       <c r="A106" s="1" t="n">
         <v>104</v>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="B106" t="n">
+        <v>8</v>
       </c>
       <c r="C106" t="n">
         <v>8381</v>
@@ -15903,21 +16501,27 @@
         <v>0.717</v>
       </c>
       <c r="AT106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU106" t="n">
         <v>37.13388601036269</v>
       </c>
-      <c r="AU106" t="n">
+      <c r="AV106" t="n">
+        <v>26.92958123803518</v>
+      </c>
+      <c r="AW106" t="n">
         <v>0.5488546049555867</v>
       </c>
-      <c r="AV106" t="n">
+      <c r="AX106" t="n">
         <v>55.62393534386633</v>
       </c>
-      <c r="AW106" t="n">
+      <c r="AY106" t="n">
         <v>-0.9106683804627249</v>
       </c>
-      <c r="AX106" t="n">
+      <c r="AZ106" t="n">
         <v>0.2253565398386968</v>
       </c>
-      <c r="AY106" t="n">
+      <c r="BA106" t="n">
         <v>12.53521760130511</v>
       </c>
     </row>
@@ -15925,10 +16529,8 @@
       <c r="A107" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="B107" t="n">
+        <v>11</v>
       </c>
       <c r="C107" t="n">
         <v>9090</v>
@@ -16068,21 +16670,27 @@
         <v>0.717</v>
       </c>
       <c r="AT107" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU107" t="n">
         <v>34.93205417607223</v>
       </c>
-      <c r="AU107" t="n">
+      <c r="AV107" t="n">
+        <v>28.62700243620314</v>
+      </c>
+      <c r="AW107" t="n">
         <v>0.4978747520544063</v>
       </c>
-      <c r="AV107" t="n">
+      <c r="AX107" t="n">
         <v>58.95157666997726</v>
       </c>
-      <c r="AW107" t="n">
+      <c r="AY107" t="n">
         <v>-0.840602950609365</v>
       </c>
-      <c r="AX107" t="n">
+      <c r="AZ107" t="n">
         <v>0.2310070069738794</v>
       </c>
-      <c r="AY107" t="n">
+      <c r="BA107" t="n">
         <v>13.61822728292262</v>
       </c>
     </row>
@@ -16090,10 +16698,8 @@
       <c r="A108" s="1" t="n">
         <v>106</v>
       </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="B108" t="n">
+        <v>8</v>
       </c>
       <c r="C108" t="n">
         <v>9080</v>
@@ -16233,21 +16839,27 @@
         <v>0.717</v>
       </c>
       <c r="AT108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU108" t="n">
         <v>38.12042253521127</v>
       </c>
-      <c r="AU108" t="n">
+      <c r="AV108" t="n">
+        <v>26.23265781160518</v>
+      </c>
+      <c r="AW108" t="n">
         <v>0.5200386286817963</v>
       </c>
-      <c r="AV108" t="n">
+      <c r="AX108" t="n">
         <v>61.68991897543837</v>
       </c>
-      <c r="AW108" t="n">
+      <c r="AY108" t="n">
         <v>-0.9048231511254019</v>
       </c>
-      <c r="AX108" t="n">
+      <c r="AZ108" t="n">
         <v>0.2004180823301927</v>
       </c>
-      <c r="AY108" t="n">
+      <c r="BA108" t="n">
         <v>12.36377526016233</v>
       </c>
     </row>
@@ -16255,10 +16867,8 @@
       <c r="A109" s="1" t="n">
         <v>107</v>
       </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="B109" t="n">
+        <v>14</v>
       </c>
       <c r="C109" t="n">
         <v>580</v>
@@ -16398,21 +17008,27 @@
         <v>0.717</v>
       </c>
       <c r="AT109" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU109" t="n">
         <v>34.02602230483271</v>
       </c>
-      <c r="AU109" t="n">
+      <c r="AV109" t="n">
+        <v>29.38927127717688</v>
+      </c>
+      <c r="AW109" t="n">
         <v>0.5066483264557542</v>
       </c>
-      <c r="AV109" t="n">
+      <c r="AX109" t="n">
         <v>42.51564615776595</v>
       </c>
-      <c r="AW109" t="n">
+      <c r="AY109" t="n">
         <v>-0.8401015228426396</v>
       </c>
-      <c r="AX109" t="n">
+      <c r="AZ109" t="n">
         <v>0.3164054433208752</v>
       </c>
-      <c r="AY109" t="n">
+      <c r="BA109" t="n">
         <v>13.4521818706214</v>
       </c>
     </row>
@@ -16420,10 +17036,8 @@
       <c r="A110" s="1" t="n">
         <v>108</v>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="B110" t="n">
+        <v>7</v>
       </c>
       <c r="C110" t="n">
         <v>378</v>
@@ -16563,21 +17177,27 @@
         <v>0.523</v>
       </c>
       <c r="AT110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU110" t="n">
         <v>36.02815442561206</v>
       </c>
-      <c r="AU110" t="n">
+      <c r="AV110" t="n">
+        <v>27.75607066036971</v>
+      </c>
+      <c r="AW110" t="n">
         <v>0.5085608514576585</v>
       </c>
-      <c r="AV110" t="n">
+      <c r="AX110" t="n">
         <v>43.63977691743113</v>
       </c>
-      <c r="AW110" t="n">
+      <c r="AY110" t="n">
         <v>-0.9122807017543859</v>
       </c>
-      <c r="AX110" t="n">
+      <c r="AZ110" t="n">
         <v>0.3143298872640892</v>
       </c>
-      <c r="AY110" t="n">
+      <c r="BA110" t="n">
         <v>13.71728615868613</v>
       </c>
     </row>
@@ -16585,10 +17205,8 @@
       <c r="A111" s="1" t="n">
         <v>109</v>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="B111" t="n">
+        <v>3</v>
       </c>
       <c r="C111" t="n">
         <v>9738</v>
@@ -16728,21 +17346,27 @@
         <v>0.717</v>
       </c>
       <c r="AT111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU111" t="n">
         <v>35.10835322195704</v>
       </c>
-      <c r="AU111" t="n">
+      <c r="AV111" t="n">
+        <v>28.48324994561671</v>
+      </c>
+      <c r="AW111" t="n">
         <v>0.5398132894014278</v>
       </c>
-      <c r="AV111" t="n">
+      <c r="AX111" t="n">
         <v>48.27107341587141</v>
       </c>
-      <c r="AW111" t="n">
+      <c r="AY111" t="n">
         <v>-0.9649181423321083</v>
       </c>
-      <c r="AX111" t="n">
+      <c r="AZ111" t="n">
         <v>0.2727743536270423</v>
       </c>
-      <c r="AY111" t="n">
+      <c r="BA111" t="n">
         <v>13.16711084989783</v>
       </c>
     </row>
@@ -16750,10 +17374,8 @@
       <c r="A112" s="1" t="n">
         <v>110</v>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="B112" t="n">
+        <v>2</v>
       </c>
       <c r="C112" t="n">
         <v>356</v>
@@ -16893,21 +17515,27 @@
         <v>0.717</v>
       </c>
       <c r="AT112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU112" t="n">
         <v>32.21244286439817</v>
       </c>
-      <c r="AU112" t="n">
+      <c r="AV112" t="n">
+        <v>31.04390450018368</v>
+      </c>
+      <c r="AW112" t="n">
         <v>0.5466267556988257</v>
       </c>
-      <c r="AV112" t="n">
+      <c r="AX112" t="n">
         <v>55.68533253151493</v>
       </c>
-      <c r="AW112" t="n">
+      <c r="AY112" t="n">
         <v>-0.9372869802317655</v>
       </c>
-      <c r="AX112" t="n">
+      <c r="AZ112" t="n">
         <v>0.2677287744794695</v>
       </c>
-      <c r="AY112" t="n">
+      <c r="BA112" t="n">
         <v>14.90856583514423</v>
       </c>
     </row>
@@ -16915,10 +17543,8 @@
       <c r="A113" s="1" t="n">
         <v>111</v>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="B113" t="n">
+        <v>2</v>
       </c>
       <c r="C113" t="n">
         <v>172</v>
@@ -17058,21 +17684,27 @@
         <v>0.523</v>
       </c>
       <c r="AT113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU113" t="n">
         <v>38.78301343570058</v>
       </c>
-      <c r="AU113" t="n">
+      <c r="AV113" t="n">
+        <v>25.78448427319675</v>
+      </c>
+      <c r="AW113" t="n">
         <v>0.5035731300619343</v>
       </c>
-      <c r="AV113" t="n">
+      <c r="AX113" t="n">
         <v>46.55285938373989</v>
       </c>
-      <c r="AW113" t="n">
+      <c r="AY113" t="n">
         <v>-0.8688741721854304</v>
       </c>
-      <c r="AX113" t="n">
+      <c r="AZ113" t="n">
         <v>0.2699350840327465</v>
       </c>
-      <c r="AY113" t="n">
+      <c r="BA113" t="n">
         <v>12.56625000971446</v>
       </c>
     </row>
@@ -17080,10 +17712,8 @@
       <c r="A114" s="1" t="n">
         <v>112</v>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="B114" t="n">
+        <v>3</v>
       </c>
       <c r="C114" t="n">
         <v>9084</v>
@@ -17223,21 +17853,27 @@
         <v>0.523</v>
       </c>
       <c r="AT114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU114" t="n">
         <v>35.49061855670104</v>
       </c>
-      <c r="AU114" t="n">
+      <c r="AV114" t="n">
+        <v>28.17646016516634</v>
+      </c>
+      <c r="AW114" t="n">
         <v>0.4870438921205711</v>
       </c>
-      <c r="AV114" t="n">
+      <c r="AX114" t="n">
         <v>28.78285344011537</v>
       </c>
-      <c r="AW114" t="n">
+      <c r="AY114" t="n">
         <v>-0.821639344262295</v>
       </c>
-      <c r="AX114" t="n">
+      <c r="AZ114" t="n">
         <v>0.4709552277566549</v>
       </c>
-      <c r="AY114" t="n">
+      <c r="BA114" t="n">
         <v>13.55543529737596</v>
       </c>
     </row>
@@ -17245,10 +17881,8 @@
       <c r="A115" s="1" t="n">
         <v>113</v>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="B115" t="n">
+        <v>2</v>
       </c>
       <c r="C115" t="n">
         <v>254</v>
@@ -17388,21 +18022,27 @@
         <v>0.523</v>
       </c>
       <c r="AT115" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU115" t="n">
         <v>34.75611814345991</v>
       </c>
-      <c r="AU115" t="n">
+      <c r="AV115" t="n">
+        <v>28.77191278589812</v>
+      </c>
+      <c r="AW115" t="n">
         <v>0.5466524973432518</v>
       </c>
-      <c r="AV115" t="n">
+      <c r="AX115" t="n">
         <v>40.26096003557048</v>
       </c>
-      <c r="AW115" t="n">
+      <c r="AY115" t="n">
         <v>-1.043353636689359</v>
       </c>
-      <c r="AX115" t="n">
+      <c r="AZ115" t="n">
         <v>0.3439129986152255</v>
       </c>
-      <c r="AY115" t="n">
+      <c r="BA115" t="n">
         <v>13.8462674929608</v>
       </c>
     </row>
@@ -17410,10 +18050,8 @@
       <c r="A116" s="1" t="n">
         <v>114</v>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="B116" t="n">
+        <v>2</v>
       </c>
       <c r="C116" t="n">
         <v>8396</v>
@@ -17553,21 +18191,27 @@
         <v>0.523</v>
       </c>
       <c r="AT116" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU116" t="n">
         <v>34.20469107551487</v>
       </c>
-      <c r="AU116" t="n">
+      <c r="AV116" t="n">
+        <v>29.23575593161375</v>
+      </c>
+      <c r="AW116" t="n">
         <v>0.5594758064516129</v>
       </c>
-      <c r="AV116" t="n">
+      <c r="AX116" t="n">
         <v>40.26096003557048</v>
       </c>
-      <c r="AW116" t="n">
+      <c r="AY116" t="n">
         <v>-1.023550087873462</v>
       </c>
-      <c r="AX116" t="n">
+      <c r="AZ116" t="n">
         <v>0.3494573532195661</v>
       </c>
-      <c r="AY116" t="n">
+      <c r="BA116" t="n">
         <v>14.06948853210919</v>
       </c>
     </row>
@@ -17575,10 +18219,8 @@
       <c r="A117" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B117" t="n">
+        <v>1</v>
       </c>
       <c r="C117" t="n">
         <v>7924</v>
@@ -17718,21 +18360,27 @@
         <v>0.523</v>
       </c>
       <c r="AT117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU117" t="n">
         <v>43.41372646184341</v>
       </c>
-      <c r="AU117" t="n">
+      <c r="AV117" t="n">
+        <v>23.03418944878888</v>
+      </c>
+      <c r="AW117" t="n">
         <v>0.5943718592964824</v>
       </c>
-      <c r="AV117" t="n">
+      <c r="AX117" t="n">
         <v>38.62830546324884</v>
       </c>
-      <c r="AW117" t="n">
+      <c r="AY117" t="n">
         <v>-0.9992862241256246</v>
       </c>
-      <c r="AX117" t="n">
+      <c r="AZ117" t="n">
         <v>0.2941786834792475</v>
       </c>
-      <c r="AY117" t="n">
+      <c r="BA117" t="n">
         <v>11.36362404621276</v>
       </c>
     </row>
@@ -17740,10 +18388,8 @@
       <c r="A118" s="1" t="n">
         <v>116</v>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="B118" t="n">
+        <v>2</v>
       </c>
       <c r="C118" t="n">
         <v>7924</v>
@@ -17883,21 +18529,27 @@
         <v>0.523</v>
       </c>
       <c r="AT118" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU118" t="n">
         <v>43.41372646184341</v>
       </c>
-      <c r="AU118" t="n">
+      <c r="AV118" t="n">
+        <v>23.03418944878888</v>
+      </c>
+      <c r="AW118" t="n">
         <v>0.5943718592964824</v>
       </c>
-      <c r="AV118" t="n">
+      <c r="AX118" t="n">
         <v>47.60443554531614</v>
       </c>
-      <c r="AW118" t="n">
+      <c r="AY118" t="n">
         <v>-0.9220733427362482</v>
       </c>
-      <c r="AX118" t="n">
+      <c r="AZ118" t="n">
         <v>0.2356234081045346</v>
       </c>
-      <c r="AY118" t="n">
+      <c r="BA118" t="n">
         <v>11.21671934408004</v>
       </c>
     </row>
@@ -17905,10 +18557,8 @@
       <c r="A119" s="1" t="n">
         <v>117</v>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="B119" t="n">
+        <v>2</v>
       </c>
       <c r="C119" t="n">
         <v>69</v>
@@ -18048,21 +18698,27 @@
         <v>0.523</v>
       </c>
       <c r="AT119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU119" t="n">
         <v>38.38884093711468</v>
       </c>
-      <c r="AU119" t="n">
+      <c r="AV119" t="n">
+        <v>26.04923659034443</v>
+      </c>
+      <c r="AW119" t="n">
         <v>0.5616216216216217</v>
       </c>
-      <c r="AV119" t="n">
+      <c r="AX119" t="n">
         <v>47.60443554531614</v>
       </c>
-      <c r="AW119" t="n">
+      <c r="AY119" t="n">
         <v>-0.9540313754104341</v>
       </c>
-      <c r="AX119" t="n">
+      <c r="AZ119" t="n">
         <v>0.2664652002443708</v>
       </c>
-      <c r="AY119" t="n">
+      <c r="BA119" t="n">
         <v>12.68492545010291</v>
       </c>
     </row>
@@ -18070,10 +18726,8 @@
       <c r="A120" s="1" t="n">
         <v>118</v>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="B120" t="n">
+        <v>3</v>
       </c>
       <c r="C120" t="n">
         <v>7922</v>
@@ -18213,21 +18867,27 @@
         <v>0.523</v>
       </c>
       <c r="AT120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU120" t="n">
         <v>28.00729765590447</v>
       </c>
-      <c r="AU120" t="n">
+      <c r="AV120" t="n">
+        <v>35.70497990509202</v>
+      </c>
+      <c r="AW120" t="n">
         <v>0.5872581234027018</v>
       </c>
-      <c r="AV120" t="n">
+      <c r="AX120" t="n">
         <v>38.09610849251812</v>
       </c>
-      <c r="AW120" t="n">
+      <c r="AY120" t="n">
         <v>-0.8568159529257928</v>
       </c>
-      <c r="AX120" t="n">
+      <c r="AZ120" t="n">
         <v>0.4458705469717965</v>
       </c>
-      <c r="AY120" t="n">
+      <c r="BA120" t="n">
         <v>16.98593273105596</v>
       </c>
     </row>
@@ -18235,10 +18895,8 @@
       <c r="A121" s="1" t="n">
         <v>119</v>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="B121" t="n">
+        <v>11</v>
       </c>
       <c r="C121" t="n">
         <v>7922</v>
@@ -18378,21 +19036,27 @@
         <v>0.523</v>
       </c>
       <c r="AT121" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU121" t="n">
         <v>28.00729765590447</v>
       </c>
-      <c r="AU121" t="n">
+      <c r="AV121" t="n">
+        <v>35.70497990509202</v>
+      </c>
+      <c r="AW121" t="n">
         <v>0.5872581234027018</v>
       </c>
-      <c r="AV121" t="n">
+      <c r="AX121" t="n">
         <v>35.84967061566433</v>
       </c>
-      <c r="AW121" t="n">
+      <c r="AY121" t="n">
         <v>-0.8646491519787163</v>
       </c>
-      <c r="AX121" t="n">
+      <c r="AZ121" t="n">
         <v>0.4809162989997219</v>
       </c>
-      <c r="AY121" t="n">
+      <c r="BA121" t="n">
         <v>17.24069091284437</v>
       </c>
     </row>
@@ -18400,10 +19064,8 @@
       <c r="A122" s="1" t="n">
         <v>120</v>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="B122" t="n">
+        <v>11</v>
       </c>
       <c r="C122" t="n">
         <v>141</v>
@@ -18543,21 +19205,27 @@
         <v>0.523</v>
       </c>
       <c r="AT122" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU122" t="n">
         <v>37.72970873786407</v>
       </c>
-      <c r="AU122" t="n">
+      <c r="AV122" t="n">
+        <v>26.50431274059741</v>
+      </c>
+      <c r="AW122" t="n">
         <v>0.5840064620355412</v>
       </c>
-      <c r="AV122" t="n">
+      <c r="AX122" t="n">
         <v>46.88581586268426</v>
       </c>
-      <c r="AW122" t="n">
+      <c r="AY122" t="n">
         <v>-0.8040981061782054</v>
       </c>
-      <c r="AX122" t="n">
+      <c r="AZ122" t="n">
         <v>0.2754411937467637</v>
       </c>
-      <c r="AY122" t="n">
+      <c r="BA122" t="n">
         <v>12.9142850910087</v>
       </c>
     </row>
@@ -18565,10 +19233,8 @@
       <c r="A123" s="1" t="n">
         <v>121</v>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="B123" t="n">
+        <v>11</v>
       </c>
       <c r="C123" t="n">
         <v>587</v>
@@ -18708,21 +19374,27 @@
         <v>0.523</v>
       </c>
       <c r="AT123" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU123" t="n">
         <v>34.93055141579732</v>
       </c>
-      <c r="AU123" t="n">
+      <c r="AV123" t="n">
+        <v>28.62823400914738</v>
+      </c>
+      <c r="AW123" t="n">
         <v>0.5502680965147453</v>
       </c>
-      <c r="AV123" t="n">
+      <c r="AX123" t="n">
         <v>51.2080861390158</v>
       </c>
-      <c r="AW123" t="n">
+      <c r="AY123" t="n">
         <v>-0.9652323580034423</v>
       </c>
-      <c r="AX123" t="n">
+      <c r="AZ123" t="n">
         <v>0.2712645733328085</v>
       </c>
-      <c r="AY123" t="n">
+      <c r="BA123" t="n">
         <v>13.89093963768983</v>
       </c>
     </row>
@@ -18730,10 +19402,8 @@
       <c r="A124" s="1" t="n">
         <v>122</v>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="B124" t="n">
+        <v>13</v>
       </c>
       <c r="C124" t="n">
         <v>575</v>
@@ -18873,21 +19543,27 @@
         <v>0.523</v>
       </c>
       <c r="AT124" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU124" t="n">
         <v>31.18076158940397</v>
       </c>
-      <c r="AU124" t="n">
+      <c r="AV124" t="n">
+        <v>32.07105756967225</v>
+      </c>
+      <c r="AW124" t="n">
         <v>0.5213187509906483</v>
       </c>
-      <c r="AV124" t="n">
+      <c r="AX124" t="n">
         <v>44.75623909743305</v>
       </c>
-      <c r="AW124" t="n">
+      <c r="AY124" t="n">
         <v>-0.9461077844311376</v>
       </c>
-      <c r="AX124" t="n">
+      <c r="AZ124" t="n">
         <v>0.3551411071187895</v>
       </c>
-      <c r="AY124" t="n">
+      <c r="BA124" t="n">
         <v>15.89478030353562</v>
       </c>
     </row>
@@ -18895,10 +19571,8 @@
       <c r="A125" s="1" t="n">
         <v>123</v>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="B125" t="n">
+        <v>13</v>
       </c>
       <c r="C125" t="n">
         <v>596</v>
@@ -19038,21 +19712,27 @@
         <v>0.523</v>
       </c>
       <c r="AT125" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU125" t="n">
         <v>41.06741071428572</v>
       </c>
-      <c r="AU125" t="n">
+      <c r="AV125" t="n">
+        <v>24.35020817253862</v>
+      </c>
+      <c r="AW125" t="n">
         <v>0.5998809169395655</v>
       </c>
-      <c r="AV125" t="n">
+      <c r="AX125" t="n">
         <v>38.4857211629195</v>
       </c>
-      <c r="AW125" t="n">
+      <c r="AY125" t="n">
         <v>-0.9985683607730851</v>
       </c>
-      <c r="AX125" t="n">
+      <c r="AZ125" t="n">
         <v>0.307205325190028</v>
       </c>
-      <c r="AY125" t="n">
+      <c r="BA125" t="n">
         <v>11.82301848502743</v>
       </c>
     </row>
@@ -19060,10 +19740,8 @@
       <c r="A126" s="1" t="n">
         <v>124</v>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="B126" t="n">
+        <v>14</v>
       </c>
       <c r="C126" t="n">
         <v>631</v>
@@ -19203,21 +19881,27 @@
         <v>0.523</v>
       </c>
       <c r="AT126" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU126" t="n">
         <v>37.32312049433573</v>
       </c>
-      <c r="AU126" t="n">
+      <c r="AV126" t="n">
+        <v>26.79304374219629</v>
+      </c>
+      <c r="AW126" t="n">
         <v>0.5242528172464478</v>
       </c>
-      <c r="AV126" t="n">
+      <c r="AX126" t="n">
         <v>38.02881287743782</v>
       </c>
-      <c r="AW126" t="n">
+      <c r="AY126" t="n">
         <v>-0.8554932365555923</v>
       </c>
-      <c r="AX126" t="n">
+      <c r="AZ126" t="n">
         <v>0.3403595277379776</v>
       </c>
-      <c r="AY126" t="n">
+      <c r="BA126" t="n">
         <v>12.94346879140066</v>
       </c>
     </row>
@@ -19225,10 +19909,8 @@
       <c r="A127" s="1" t="n">
         <v>125</v>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B127" t="n">
+        <v>4</v>
       </c>
       <c r="C127" t="n">
         <v>4445</v>
@@ -19368,21 +20050,27 @@
         <v>0.523</v>
       </c>
       <c r="AT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU127" t="n">
         <v>36.17970168612192</v>
       </c>
-      <c r="AU127" t="n">
+      <c r="AV127" t="n">
+        <v>27.63980777607096</v>
+      </c>
+      <c r="AW127" t="n">
         <v>0.5462036492054149</v>
       </c>
-      <c r="AV127" t="n">
+      <c r="AX127" t="n">
         <v>42.69161633319679</v>
       </c>
-      <c r="AW127" t="n">
+      <c r="AY127" t="n">
         <v>-0.8341742347796839</v>
       </c>
-      <c r="AX127" t="n">
+      <c r="AZ127" t="n">
         <v>0.3160063990834164</v>
       </c>
-      <c r="AY127" t="n">
+      <c r="BA127" t="n">
         <v>13.49082394850428</v>
       </c>
     </row>
@@ -19390,10 +20078,8 @@
       <c r="A128" s="1" t="n">
         <v>126</v>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="B128" t="n">
+        <v>11</v>
       </c>
       <c r="C128" t="n">
         <v>6976</v>
@@ -19533,21 +20219,27 @@
         <v>0.523</v>
       </c>
       <c r="AT128" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU128" t="n">
         <v>32.91402805611222</v>
       </c>
-      <c r="AU128" t="n">
+      <c r="AV128" t="n">
+        <v>30.38218228091646</v>
+      </c>
+      <c r="AW128" t="n">
         <v>0.5709372312983663</v>
       </c>
-      <c r="AV128" t="n">
+      <c r="AX128" t="n">
         <v>42.92451945516472</v>
       </c>
-      <c r="AW128" t="n">
+      <c r="AY128" t="n">
         <v>-0.8899897505978819</v>
       </c>
-      <c r="AX128" t="n">
+      <c r="AZ128" t="n">
         <v>0.3483273407058165</v>
       </c>
-      <c r="AY128" t="n">
+      <c r="BA128" t="n">
         <v>14.95178371289261</v>
       </c>
     </row>
@@ -19555,10 +20247,8 @@
       <c r="A129" s="1" t="n">
         <v>127</v>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="B129" t="n">
+        <v>9</v>
       </c>
       <c r="C129" t="n">
         <v>213</v>
@@ -19698,21 +20388,27 @@
         <v>0.523</v>
       </c>
       <c r="AT129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU129" t="n">
         <v>31.10285451197053</v>
       </c>
-      <c r="AU129" t="n">
+      <c r="AV129" t="n">
+        <v>32.1513898222792</v>
+      </c>
+      <c r="AW129" t="n">
         <v>0.5543701272055807</v>
       </c>
-      <c r="AV129" t="n">
+      <c r="AX129" t="n">
         <v>40.16479905872414</v>
       </c>
-      <c r="AW129" t="n">
+      <c r="AY129" t="n">
         <v>-0.9594183293878932</v>
       </c>
-      <c r="AX129" t="n">
+      <c r="AZ129" t="n">
         <v>0.3335399262952408</v>
       </c>
-      <c r="AY129" t="n">
+      <c r="BA129" t="n">
         <v>13.39656411771</v>
       </c>
     </row>
@@ -19720,10 +20416,8 @@
       <c r="A130" s="1" t="n">
         <v>128</v>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B130" t="n">
+        <v>4</v>
       </c>
       <c r="C130" t="n">
         <v>569</v>
@@ -19863,21 +20557,27 @@
         <v>0.717</v>
       </c>
       <c r="AT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU130" t="n">
         <v>30.39869888475836</v>
       </c>
-      <c r="AU130" t="n">
+      <c r="AV130" t="n">
+        <v>32.89614479195329</v>
+      </c>
+      <c r="AW130" t="n">
         <v>0.5485314685314685</v>
       </c>
-      <c r="AV130" t="n">
+      <c r="AX130" t="n">
         <v>54.14554217891045</v>
       </c>
-      <c r="AW130" t="n">
+      <c r="AY130" t="n">
         <v>-0.8095535435529191</v>
       </c>
-      <c r="AX130" t="n">
+      <c r="AZ130" t="n">
         <v>0.2816077793273518</v>
       </c>
-      <c r="AY130" t="n">
+      <c r="BA130" t="n">
         <v>15.24780589347843</v>
       </c>
     </row>
@@ -19885,10 +20585,8 @@
       <c r="A131" s="1" t="n">
         <v>129</v>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B131" t="n">
+        <v>4</v>
       </c>
       <c r="C131" t="n">
         <v>8361</v>
@@ -20028,21 +20726,27 @@
         <v>0.717</v>
       </c>
       <c r="AT131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU131" t="n">
         <v>37.48323197219809</v>
       </c>
-      <c r="AU131" t="n">
+      <c r="AV131" t="n">
+        <v>26.67859593168796</v>
+      </c>
+      <c r="AW131" t="n">
         <v>0.5674558436677941</v>
       </c>
-      <c r="AV131" t="n">
+      <c r="AX131" t="n">
         <v>54.14554217891045</v>
       </c>
-      <c r="AW131" t="n">
+      <c r="AY131" t="n">
         <v>-0.8061192631907587</v>
       </c>
-      <c r="AX131" t="n">
+      <c r="AZ131" t="n">
         <v>0.2283823895902871</v>
       </c>
-      <c r="AY131" t="n">
+      <c r="BA131" t="n">
         <v>12.36588830848125</v>
       </c>
     </row>
@@ -20050,10 +20754,8 @@
       <c r="A132" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="B132" t="n">
+        <v>9</v>
       </c>
       <c r="C132" t="n">
         <v>191</v>
@@ -20193,21 +20895,27 @@
         <v>0.523</v>
       </c>
       <c r="AT132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU132" t="n">
         <v>32.09768</v>
       </c>
-      <c r="AU132" t="n">
+      <c r="AV132" t="n">
+        <v>31.1548996687611</v>
+      </c>
+      <c r="AW132" t="n">
         <v>0.491869918699187</v>
       </c>
-      <c r="AV132" t="n">
+      <c r="AX132" t="n">
         <v>34.63030631687734</v>
       </c>
-      <c r="AW132" t="n">
+      <c r="AY132" t="n">
         <v>-0.9432647644326476</v>
       </c>
-      <c r="AX132" t="n">
+      <c r="AZ132" t="n">
         <v>0.4425021074703185</v>
       </c>
-      <c r="AY132" t="n">
+      <c r="BA132" t="n">
         <v>15.32398352756091</v>
       </c>
     </row>
@@ -20215,10 +20923,8 @@
       <c r="A133" s="1" t="n">
         <v>131</v>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="B133" t="n">
+        <v>12</v>
       </c>
       <c r="C133" t="n">
         <v>191</v>
@@ -20358,21 +21064,27 @@
         <v>0.523</v>
       </c>
       <c r="AT133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU133" t="n">
         <v>32.09768</v>
       </c>
-      <c r="AU133" t="n">
+      <c r="AV133" t="n">
+        <v>31.1548996687611</v>
+      </c>
+      <c r="AW133" t="n">
         <v>0.491869918699187</v>
       </c>
-      <c r="AV133" t="n">
+      <c r="AX133" t="n">
         <v>44.89996935838486</v>
       </c>
-      <c r="AW133" t="n">
+      <c r="AY133" t="n">
         <v>-0.9047947568126941</v>
       </c>
-      <c r="AX133" t="n">
+      <c r="AZ133" t="n">
         <v>0.3424239972728017</v>
       </c>
-      <c r="AY133" t="n">
+      <c r="BA133" t="n">
         <v>15.37482698512445</v>
       </c>
     </row>
@@ -20380,10 +21092,8 @@
       <c r="A134" s="1" t="n">
         <v>132</v>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="B134" t="n">
+        <v>8</v>
       </c>
       <c r="C134" t="n">
         <v>4469</v>
@@ -20523,21 +21233,27 @@
         <v>0.523</v>
       </c>
       <c r="AT134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU134" t="n">
         <v>39.16065382370111</v>
       </c>
-      <c r="AU134" t="n">
+      <c r="AV134" t="n">
+        <v>25.53583513957503</v>
+      </c>
+      <c r="AW134" t="n">
         <v>0.5946521533364885</v>
       </c>
-      <c r="AV134" t="n">
+      <c r="AX134" t="n">
         <v>43.93419906095097</v>
       </c>
-      <c r="AW134" t="n">
+      <c r="AY134" t="n">
         <v>-0.925575101488498</v>
       </c>
-      <c r="AX134" t="n">
+      <c r="AZ134" t="n">
         <v>0.2877727947098655</v>
       </c>
-      <c r="AY134" t="n">
+      <c r="BA134" t="n">
         <v>12.64306724710941</v>
       </c>
     </row>
@@ -20545,10 +21261,8 @@
       <c r="A135" s="1" t="n">
         <v>133</v>
       </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="B135" t="n">
+        <v>16</v>
       </c>
       <c r="C135" t="n">
         <v>4894</v>
@@ -20688,21 +21402,27 @@
         <v>0.717</v>
       </c>
       <c r="AT135" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU135" t="n">
         <v>32.11846846846846</v>
       </c>
-      <c r="AU135" t="n">
+      <c r="AV135" t="n">
+        <v>31.13473486389072</v>
+      </c>
+      <c r="AW135" t="n">
         <v>0.5555555555555556</v>
       </c>
-      <c r="AV135" t="n">
+      <c r="AX135" t="n">
         <v>62.73974732172039</v>
       </c>
-      <c r="AW135" t="n">
+      <c r="AY135" t="n">
         <v>-0.8729547641963427</v>
       </c>
-      <c r="AX135" t="n">
+      <c r="AZ135" t="n">
         <v>0.2286543990281047</v>
       </c>
-      <c r="AY135" t="n">
+      <c r="BA135" t="n">
         <v>14.34571921902312</v>
       </c>
     </row>
@@ -20710,10 +21430,8 @@
       <c r="A136" s="1" t="n">
         <v>134</v>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="B136" t="n">
+        <v>16</v>
       </c>
       <c r="C136" t="n">
         <v>389</v>
@@ -20853,21 +21571,27 @@
         <v>0.523</v>
       </c>
       <c r="AT136" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU136" t="n">
         <v>38.09801840056618</v>
       </c>
-      <c r="AU136" t="n">
+      <c r="AV136" t="n">
+        <v>26.24808433567083</v>
+      </c>
+      <c r="AW136" t="n">
         <v>0.5716883904213398</v>
       </c>
-      <c r="AV136" t="n">
+      <c r="AX136" t="n">
         <v>56.82593529734338</v>
       </c>
-      <c r="AW136" t="n">
+      <c r="AY136" t="n">
         <v>-0.8111718275652702</v>
       </c>
-      <c r="AX136" t="n">
+      <c r="AZ136" t="n">
         <v>0.212522899192218</v>
       </c>
-      <c r="AY136" t="n">
+      <c r="BA136" t="n">
         <v>12.07681251870081</v>
       </c>
     </row>
@@ -20875,10 +21599,8 @@
       <c r="A137" s="1" t="n">
         <v>135</v>
       </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="B137" t="n">
+        <v>16</v>
       </c>
       <c r="C137" t="n">
         <v>746</v>
@@ -21018,21 +21740,27 @@
         <v>0.717</v>
       </c>
       <c r="AT137" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU137" t="n">
         <v>37.71034928848641</v>
       </c>
-      <c r="AU137" t="n">
+      <c r="AV137" t="n">
+        <v>26.5179193210315</v>
+      </c>
+      <c r="AW137" t="n">
         <v>0.5222496909765142</v>
       </c>
-      <c r="AV137" t="n">
+      <c r="AX137" t="n">
         <v>51.97156457320585</v>
       </c>
-      <c r="AW137" t="n">
+      <c r="AY137" t="n">
         <v>-0.9191253037139883</v>
       </c>
-      <c r="AX137" t="n">
+      <c r="AZ137" t="n">
         <v>0.2487492359828174</v>
       </c>
-      <c r="AY137" t="n">
+      <c r="BA137" t="n">
         <v>12.92788698041661</v>
       </c>
     </row>
@@ -21040,10 +21768,8 @@
       <c r="A138" s="1" t="n">
         <v>136</v>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="B138" t="n">
+        <v>18</v>
       </c>
       <c r="C138" t="n">
         <v>763</v>
@@ -21183,21 +21909,27 @@
         <v>0.523</v>
       </c>
       <c r="AT138" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU138" t="n">
         <v>39.72764811490126</v>
       </c>
-      <c r="AU138" t="n">
+      <c r="AV138" t="n">
+        <v>25.17138686659165</v>
+      </c>
+      <c r="AW138" t="n">
         <v>0.5884236453201971</v>
       </c>
-      <c r="AV138" t="n">
+      <c r="AX138" t="n">
         <v>34.71279366258031</v>
       </c>
-      <c r="AW138" t="n">
+      <c r="AY138" t="n">
         <v>-0.983991462113127</v>
       </c>
-      <c r="AX138" t="n">
+      <c r="AZ138" t="n">
         <v>0.3634267201648407</v>
       </c>
-      <c r="AY138" t="n">
+      <c r="BA138" t="n">
         <v>12.61555674855043</v>
       </c>
     </row>
@@ -21205,10 +21937,8 @@
       <c r="A139" s="1" t="n">
         <v>137</v>
       </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="B139" t="n">
+        <v>17</v>
       </c>
       <c r="C139" t="n">
         <v>768</v>
@@ -21348,21 +22078,27 @@
         <v>0.717</v>
       </c>
       <c r="AT139" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU139" t="n">
         <v>33.31036454610436</v>
       </c>
-      <c r="AU139" t="n">
+      <c r="AV139" t="n">
+        <v>30.02068616258809</v>
+      </c>
+      <c r="AW139" t="n">
         <v>0.5165860400829302</v>
       </c>
-      <c r="AV139" t="n">
+      <c r="AX139" t="n">
         <v>16.82978356315537</v>
       </c>
-      <c r="AW139" t="n">
+      <c r="AY139" t="n">
         <v>-0.8676616915422886</v>
       </c>
-      <c r="AX139" t="n">
+      <c r="AZ139" t="n">
         <v>0.887896060770315</v>
       </c>
-      <c r="AY139" t="n">
+      <c r="BA139" t="n">
         <v>14.94309852934265</v>
       </c>
     </row>
@@ -21370,10 +22106,8 @@
       <c r="A140" s="1" t="n">
         <v>138</v>
       </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="B140" t="n">
+        <v>18</v>
       </c>
       <c r="C140" t="n">
         <v>4940</v>
@@ -21513,21 +22247,27 @@
         <v>0.717</v>
       </c>
       <c r="AT140" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU140" t="n">
         <v>34.7460815047022</v>
       </c>
-      <c r="AU140" t="n">
+      <c r="AV140" t="n">
+        <v>28.78022374594009</v>
+      </c>
+      <c r="AW140" t="n">
         <v>0.5231689088191331</v>
       </c>
-      <c r="AV140" t="n">
+      <c r="AX140" t="n">
         <v>48.86662529556703</v>
       </c>
-      <c r="AW140" t="n">
+      <c r="AY140" t="n">
         <v>-0.9794520547945206</v>
       </c>
-      <c r="AX140" t="n">
+      <c r="AZ140" t="n">
         <v>0.2763025421902743</v>
       </c>
-      <c r="AY140" t="n">
+      <c r="BA140" t="n">
         <v>13.50197279742473</v>
       </c>
     </row>
@@ -21535,10 +22275,8 @@
       <c r="A141" s="1" t="n">
         <v>139</v>
       </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="B141" t="n">
+        <v>12</v>
       </c>
       <c r="C141" t="n">
         <v>902</v>
@@ -21678,21 +22416,27 @@
         <v>0.717</v>
       </c>
       <c r="AT141" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU141" t="n">
         <v>31.98261633011413</v>
       </c>
-      <c r="AU141" t="n">
+      <c r="AV141" t="n">
+        <v>31.26698546730281</v>
+      </c>
+      <c r="AW141" t="n">
         <v>0.4660103141115798</v>
       </c>
-      <c r="AV141" t="n">
+      <c r="AX141" t="n">
         <v>48.48989580379418</v>
       </c>
-      <c r="AW141" t="n">
+      <c r="AY141" t="n">
         <v>-0.8755935422602089</v>
       </c>
-      <c r="AX141" t="n">
+      <c r="AZ141" t="n">
         <v>0.3071371534917146</v>
       </c>
-      <c r="AY141" t="n">
+      <c r="BA141" t="n">
         <v>14.89304857028718</v>
       </c>
     </row>
@@ -21700,10 +22444,8 @@
       <c r="A142" s="1" t="n">
         <v>140</v>
       </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B142" t="n">
+        <v>1</v>
       </c>
       <c r="C142" t="n">
         <v>5880</v>
@@ -21843,21 +22585,27 @@
         <v>0.717</v>
       </c>
       <c r="AT142" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU142" t="n">
         <v>38.49102196752626</v>
       </c>
-      <c r="AU142" t="n">
+      <c r="AV142" t="n">
+        <v>25.98008441666398</v>
+      </c>
+      <c r="AW142" t="n">
         <v>0.526886579304112</v>
       </c>
-      <c r="AV142" t="n">
+      <c r="AX142" t="n">
         <v>52.45513538310598</v>
       </c>
-      <c r="AW142" t="n">
+      <c r="AY142" t="n">
         <v>-0.8558154437680231</v>
       </c>
-      <c r="AX142" t="n">
+      <c r="AZ142" t="n">
         <v>0.2351665444744986</v>
       </c>
-      <c r="AY142" t="n">
+      <c r="BA142" t="n">
         <v>12.33569292798704</v>
       </c>
     </row>
@@ -21865,10 +22613,8 @@
       <c r="A143" s="1" t="n">
         <v>141</v>
       </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="B143" t="n">
+        <v>7</v>
       </c>
       <c r="C143" t="n">
         <v>708</v>
@@ -22008,21 +22754,27 @@
         <v>0.717</v>
       </c>
       <c r="AT143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU143" t="n">
         <v>35.47107516650809</v>
       </c>
-      <c r="AU143" t="n">
+      <c r="AV143" t="n">
+        <v>28.19198446356099</v>
+      </c>
+      <c r="AW143" t="n">
         <v>0.5007125890736343</v>
       </c>
-      <c r="AV143" t="n">
+      <c r="AX143" t="n">
         <v>50.12173210626537</v>
       </c>
-      <c r="AW143" t="n">
+      <c r="AY143" t="n">
         <v>-0.910299003322259</v>
       </c>
-      <c r="AX143" t="n">
+      <c r="AZ143" t="n">
         <v>0.2634069568539765</v>
       </c>
-      <c r="AY143" t="n">
+      <c r="BA143" t="n">
         <v>13.20241292636161</v>
       </c>
     </row>
@@ -22030,10 +22782,8 @@
       <c r="A144" s="1" t="n">
         <v>142</v>
       </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="B144" t="n">
+        <v>18</v>
       </c>
       <c r="C144" t="n">
         <v>5812</v>
@@ -22173,21 +22923,27 @@
         <v>0.717</v>
       </c>
       <c r="AT144" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU144" t="n">
         <v>32.22464912280702</v>
       </c>
-      <c r="AU144" t="n">
+      <c r="AV144" t="n">
+        <v>31.03214549176423</v>
+      </c>
+      <c r="AW144" t="n">
         <v>0.474896361123906</v>
       </c>
-      <c r="AV144" t="n">
+      <c r="AX144" t="n">
         <v>51.64905585832408</v>
       </c>
-      <c r="AW144" t="n">
+      <c r="AY144" t="n">
         <v>-0.8479307025986524</v>
       </c>
-      <c r="AX144" t="n">
+      <c r="AZ144" t="n">
         <v>0.2850083474322018</v>
       </c>
-      <c r="AY144" t="n">
+      <c r="BA144" t="n">
         <v>14.72041205661443</v>
       </c>
     </row>
@@ -22195,10 +22951,8 @@
       <c r="A145" s="1" t="n">
         <v>143</v>
       </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="B145" t="n">
+        <v>3</v>
       </c>
       <c r="C145" t="n">
         <v>333</v>
@@ -22338,21 +23092,27 @@
         <v>0.717</v>
       </c>
       <c r="AT145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU145" t="n">
         <v>33.99637952559301</v>
       </c>
-      <c r="AU145" t="n">
+      <c r="AV145" t="n">
+        <v>29.41489693769256</v>
+      </c>
+      <c r="AW145" t="n">
         <v>0.5288235294117647</v>
       </c>
-      <c r="AV145" t="n">
+      <c r="AX145" t="n">
         <v>40.84573233660999</v>
       </c>
-      <c r="AW145" t="n">
+      <c r="AY145" t="n">
         <v>-0.9031939413895291</v>
       </c>
-      <c r="AX145" t="n">
+      <c r="AZ145" t="n">
         <v>0.3306302943724049</v>
       </c>
-      <c r="AY145" t="n">
+      <c r="BA145" t="n">
         <v>13.50483650630982</v>
       </c>
     </row>
@@ -22360,10 +23120,8 @@
       <c r="A146" s="1" t="n">
         <v>144</v>
       </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="B146" t="n">
+        <v>17</v>
       </c>
       <c r="C146" t="n">
         <v>816</v>
@@ -22503,21 +23261,27 @@
         <v>0.523</v>
       </c>
       <c r="AT146" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU146" t="n">
         <v>33.4044665012407</v>
       </c>
-      <c r="AU146" t="n">
+      <c r="AV146" t="n">
+        <v>29.93611647600654</v>
+      </c>
+      <c r="AW146" t="n">
         <v>0.4903035413153457</v>
       </c>
-      <c r="AV146" t="n">
+      <c r="AX146" t="n">
         <v>37.41961875184389</v>
       </c>
-      <c r="AW146" t="n">
+      <c r="AY146" t="n">
         <v>-0.8867924528301887</v>
       </c>
-      <c r="AX146" t="n">
+      <c r="AZ146" t="n">
         <v>0.3753925003975221</v>
       </c>
-      <c r="AY146" t="n">
+      <c r="BA146" t="n">
         <v>14.04704424717668</v>
       </c>
     </row>
@@ -22525,10 +23289,8 @@
       <c r="A147" s="1" t="n">
         <v>145</v>
       </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B147" t="n">
+        <v>1</v>
       </c>
       <c r="C147" t="n">
         <v>143</v>
@@ -22668,21 +23430,27 @@
         <v>0.717</v>
       </c>
       <c r="AT147" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU147" t="n">
         <v>37.73743016759776</v>
       </c>
-      <c r="AU147" t="n">
+      <c r="AV147" t="n">
+        <v>26.49888971132494</v>
+      </c>
+      <c r="AW147" t="n">
         <v>0.4713526284701713</v>
       </c>
-      <c r="AV147" t="n">
+      <c r="AX147" t="n">
         <v>44.98594091218243</v>
       </c>
-      <c r="AW147" t="n">
+      <c r="AY147" t="n">
         <v>-0.9927797833935018</v>
       </c>
-      <c r="AX147" t="n">
+      <c r="AZ147" t="n">
         <v>0.275498874631122</v>
       </c>
-      <c r="AY147" t="n">
+      <c r="BA147" t="n">
         <v>12.39357609552841</v>
       </c>
     </row>
@@ -22690,10 +23458,8 @@
       <c r="A148" s="1" t="n">
         <v>146</v>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="B148" t="n">
+        <v>12</v>
       </c>
       <c r="C148" t="n">
         <v>4932</v>
@@ -22833,21 +23599,27 @@
         <v>0.717</v>
       </c>
       <c r="AT148" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU148" t="n">
         <v>37.00026553372279</v>
       </c>
-      <c r="AU148" t="n">
+      <c r="AV148" t="n">
+        <v>27.02683306660542</v>
+      </c>
+      <c r="AW148" t="n">
         <v>0.5766636690647482</v>
       </c>
-      <c r="AV148" t="n">
+      <c r="AX148" t="n">
         <v>62.3287590104805</v>
       </c>
-      <c r="AW148" t="n">
+      <c r="AY148" t="n">
         <v>-0.8752424046541692</v>
       </c>
-      <c r="AX148" t="n">
+      <c r="AZ148" t="n">
         <v>0.204352754630459</v>
       </c>
-      <c r="AY148" t="n">
+      <c r="BA148" t="n">
         <v>12.73705359648974</v>
       </c>
     </row>
@@ -22855,10 +23627,8 @@
       <c r="A149" s="1" t="n">
         <v>147</v>
       </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="B149" t="n">
+        <v>7</v>
       </c>
       <c r="C149" t="n">
         <v>96</v>
@@ -22998,21 +23768,27 @@
         <v>0.717</v>
       </c>
       <c r="AT149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU149" t="n">
         <v>45.65359911406424</v>
       </c>
-      <c r="AU149" t="n">
+      <c r="AV149" t="n">
+        <v>21.90407808815967</v>
+      </c>
+      <c r="AW149" t="n">
         <v>0.5908473040326235</v>
       </c>
-      <c r="AV149" t="n">
+      <c r="AX149" t="n">
         <v>63.04106431069755</v>
       </c>
-      <c r="AW149" t="n">
+      <c r="AY149" t="n">
         <v>-0.9457209457209457</v>
       </c>
-      <c r="AX149" t="n">
+      <c r="AZ149" t="n">
         <v>0.1613708822578354</v>
       </c>
-      <c r="AY149" t="n">
+      <c r="BA149" t="n">
         <v>10.17299216629021</v>
       </c>
     </row>
@@ -23020,10 +23796,8 @@
       <c r="A150" s="1" t="n">
         <v>148</v>
       </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B150" t="n">
+        <v>1</v>
       </c>
       <c r="C150" t="n">
         <v>729</v>
@@ -23163,21 +23937,27 @@
         <v>0.717</v>
       </c>
       <c r="AT150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU150" t="n">
         <v>31.62051282051283</v>
       </c>
-      <c r="AU150" t="n">
+      <c r="AV150" t="n">
+        <v>31.62504054492377</v>
+      </c>
+      <c r="AW150" t="n">
         <v>0.4886769964243147</v>
       </c>
-      <c r="AV150" t="n">
+      <c r="AX150" t="n">
         <v>55.56667726163774</v>
       </c>
-      <c r="AW150" t="n">
+      <c r="AY150" t="n">
         <v>-0.8900032351989647</v>
       </c>
-      <c r="AX150" t="n">
+      <c r="AZ150" t="n">
         <v>0.2776338886342699</v>
       </c>
-      <c r="AY150" t="n">
+      <c r="BA150" t="n">
         <v>15.42719268663395</v>
       </c>
     </row>
@@ -23185,10 +23965,8 @@
       <c r="A151" s="1" t="n">
         <v>149</v>
       </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="B151" t="n">
+        <v>7</v>
       </c>
       <c r="C151" t="n">
         <v>6992</v>
@@ -23328,21 +24106,27 @@
         <v>0.717</v>
       </c>
       <c r="AT151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU151" t="n">
         <v>38.07644376899696</v>
       </c>
-      <c r="AU151" t="n">
+      <c r="AV151" t="n">
+        <v>26.26295685770506</v>
+      </c>
+      <c r="AW151" t="n">
         <v>0.5359661495063469</v>
       </c>
-      <c r="AV151" t="n">
+      <c r="AX151" t="n">
         <v>61.70799806962501</v>
       </c>
-      <c r="AW151" t="n">
+      <c r="AY151" t="n">
         <v>-0.9144542772861356</v>
       </c>
-      <c r="AX151" t="n">
+      <c r="AZ151" t="n">
         <v>0.1992943083149607</v>
       </c>
-      <c r="AY151" t="n">
+      <c r="BA151" t="n">
         <v>12.29805279278685</v>
       </c>
     </row>
@@ -23350,10 +24134,8 @@
       <c r="A152" s="1" t="n">
         <v>150</v>
       </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="B152" t="n">
+        <v>19</v>
       </c>
       <c r="C152" t="n">
         <v>90</v>
@@ -23493,21 +24275,27 @@
         <v>0.717</v>
       </c>
       <c r="AT152" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU152" t="n">
         <v>34.4926213592233</v>
       </c>
-      <c r="AU152" t="n">
+      <c r="AV152" t="n">
+        <v>28.99170780862095</v>
+      </c>
+      <c r="AW152" t="n">
         <v>0.4950980392156862</v>
       </c>
-      <c r="AV152" t="n">
+      <c r="AX152" t="n">
         <v>47.27323855607655</v>
       </c>
-      <c r="AW152" t="n">
+      <c r="AY152" t="n">
         <v>-0.870988867059594</v>
       </c>
-      <c r="AX152" t="n">
+      <c r="AZ152" t="n">
         <v>0.2929222953305048</v>
       </c>
-      <c r="AY152" t="n">
+      <c r="BA152" t="n">
         <v>13.84738554555246</v>
       </c>
     </row>
@@ -23515,10 +24303,8 @@
       <c r="A153" s="1" t="n">
         <v>151</v>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="B153" t="n">
+        <v>18</v>
       </c>
       <c r="C153" t="n">
         <v>341</v>
@@ -23658,21 +24444,27 @@
         <v>0.717</v>
       </c>
       <c r="AT153" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU153" t="n">
         <v>36.54322709163347</v>
       </c>
-      <c r="AU153" t="n">
+      <c r="AV153" t="n">
+        <v>27.36485197359455</v>
+      </c>
+      <c r="AW153" t="n">
         <v>0.5332403533240354</v>
       </c>
-      <c r="AV153" t="n">
+      <c r="AX153" t="n">
         <v>46.60021045219221</v>
       </c>
-      <c r="AW153" t="n">
+      <c r="AY153" t="n">
         <v>-0.9734422880490295</v>
       </c>
-      <c r="AX153" t="n">
+      <c r="AZ153" t="n">
         <v>0.278928268195533</v>
       </c>
-      <c r="AY153" t="n">
+      <c r="BA153" t="n">
         <v>12.99811599897735</v>
       </c>
     </row>
@@ -23680,10 +24472,8 @@
       <c r="A154" s="1" t="n">
         <v>152</v>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="B154" t="n">
+        <v>16</v>
       </c>
       <c r="C154" t="n">
         <v>4952</v>
@@ -23823,21 +24613,27 @@
         <v>0.523</v>
       </c>
       <c r="AT154" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU154" t="n">
         <v>36.84074074074074</v>
       </c>
-      <c r="AU154" t="n">
+      <c r="AV154" t="n">
+        <v>27.14386247109681</v>
+      </c>
+      <c r="AW154" t="n">
         <v>0.5225263157894737</v>
       </c>
-      <c r="AV154" t="n">
+      <c r="AX154" t="n">
         <v>36.4008599384631</v>
       </c>
-      <c r="AW154" t="n">
+      <c r="AY154" t="n">
         <v>-0.8216748768472907</v>
       </c>
-      <c r="AX154" t="n">
+      <c r="AZ154" t="n">
         <v>0.3594130595075935</v>
       </c>
-      <c r="AY154" t="n">
+      <c r="BA154" t="n">
         <v>13.08294443919041</v>
       </c>
     </row>
@@ -23845,10 +24641,8 @@
       <c r="A155" s="1" t="n">
         <v>153</v>
       </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="B155" t="n">
+        <v>17</v>
       </c>
       <c r="C155" t="n">
         <v>7578</v>
@@ -23988,21 +24782,27 @@
         <v>0.717</v>
       </c>
       <c r="AT155" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU155" t="n">
         <v>36.31700201207244</v>
       </c>
-      <c r="AU155" t="n">
+      <c r="AV155" t="n">
+        <v>27.53531251471643</v>
+      </c>
+      <c r="AW155" t="n">
         <v>0.5096201282683769</v>
       </c>
-      <c r="AV155" t="n">
+      <c r="AX155" t="n">
         <v>55.60819532627404</v>
       </c>
-      <c r="AW155" t="n">
+      <c r="AY155" t="n">
         <v>-0.8612735542560104</v>
       </c>
-      <c r="AX155" t="n">
+      <c r="AZ155" t="n">
         <v>0.2320891755316213</v>
       </c>
-      <c r="AY155" t="n">
+      <c r="BA155" t="n">
         <v>12.9060602060763</v>
       </c>
     </row>
@@ -24010,10 +24810,8 @@
       <c r="A156" s="1" t="n">
         <v>154</v>
       </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="B156" t="n">
+        <v>8</v>
       </c>
       <c r="C156" t="n">
         <v>755</v>
@@ -24153,21 +24951,27 @@
         <v>0.523</v>
       </c>
       <c r="AT156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU156" t="n">
         <v>33.07568366592757</v>
       </c>
-      <c r="AU156" t="n">
+      <c r="AV156" t="n">
+        <v>30.23369101301859</v>
+      </c>
+      <c r="AW156" t="n">
         <v>0.5494505494505494</v>
       </c>
-      <c r="AV156" t="n">
+      <c r="AX156" t="n">
         <v>43.12164298019695</v>
       </c>
-      <c r="AW156" t="n">
+      <c r="AY156" t="n">
         <v>-1.018099547511312</v>
       </c>
-      <c r="AX156" t="n">
+      <c r="AZ156" t="n">
         <v>0.3462797777914783</v>
       </c>
-      <c r="AY156" t="n">
+      <c r="BA156" t="n">
         <v>14.93215294918606</v>
       </c>
     </row>
@@ -24175,10 +24979,8 @@
       <c r="A157" s="1" t="n">
         <v>155</v>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="B157" t="n">
+        <v>8</v>
       </c>
       <c r="C157" t="n">
         <v>4933</v>
@@ -24318,21 +25120,27 @@
         <v>0.523</v>
       </c>
       <c r="AT157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU157" t="n">
         <v>32.22326111744584</v>
       </c>
-      <c r="AU157" t="n">
+      <c r="AV157" t="n">
+        <v>31.03348219024904</v>
+      </c>
+      <c r="AW157" t="n">
         <v>0.4868344060854301</v>
       </c>
-      <c r="AV157" t="n">
+      <c r="AX157" t="n">
         <v>43.12164298019695</v>
       </c>
-      <c r="AW157" t="n">
+      <c r="AY157" t="n">
         <v>-1.04876299749014</v>
       </c>
-      <c r="AX157" t="n">
+      <c r="AZ157" t="n">
         <v>0.3554401383644461</v>
       </c>
-      <c r="AY157" t="n">
+      <c r="BA157" t="n">
         <v>15.32716274738345</v>
       </c>
     </row>
@@ -24340,10 +25148,8 @@
       <c r="A158" s="1" t="n">
         <v>156</v>
       </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="B158" t="n">
+        <v>6</v>
       </c>
       <c r="C158" t="n">
         <v>410</v>
@@ -24483,21 +25289,27 @@
         <v>0.523</v>
       </c>
       <c r="AT158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU158" t="n">
         <v>36.82448866777225</v>
       </c>
-      <c r="AU158" t="n">
+      <c r="AV158" t="n">
+        <v>27.15584210881852</v>
+      </c>
+      <c r="AW158" t="n">
         <v>0.5639913232104121</v>
       </c>
-      <c r="AV158" t="n">
+      <c r="AX158" t="n">
         <v>40.64145553340282</v>
       </c>
-      <c r="AW158" t="n">
+      <c r="AY158" t="n">
         <v>-0.8695652173913042</v>
       </c>
-      <c r="AX158" t="n">
+      <c r="AZ158" t="n">
         <v>0.3274162961093018</v>
       </c>
-      <c r="AY158" t="n">
+      <c r="BA158" t="n">
         <v>13.30667483923764</v>
       </c>
     </row>
@@ -24505,10 +25317,8 @@
       <c r="A159" s="1" t="n">
         <v>157</v>
       </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="B159" t="n">
+        <v>6</v>
       </c>
       <c r="C159" t="n">
         <v>410</v>
@@ -24646,19 +25456,25 @@
         <v>0.523</v>
       </c>
       <c r="AT159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU159" t="n">
         <v>36.82448866777225</v>
       </c>
-      <c r="AU159" t="n">
+      <c r="AV159" t="n">
+        <v>27.15584210881852</v>
+      </c>
+      <c r="AW159" t="n">
         <v>0.5639913232104121</v>
       </c>
-      <c r="AV159" t="n">
+      <c r="AX159" t="n">
         <v>39.86388713858987</v>
       </c>
-      <c r="AW159" t="inlineStr"/>
-      <c r="AX159" t="n">
+      <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="n">
         <v>0.3352256061133059</v>
       </c>
-      <c r="AY159" t="n">
+      <c r="BA159" t="n">
         <v>13.36339572806621</v>
       </c>
     </row>
@@ -24666,10 +25482,8 @@
       <c r="A160" s="1" t="n">
         <v>158</v>
       </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B160" t="n">
+        <v>4</v>
       </c>
       <c r="C160" t="n">
         <v>310</v>
@@ -24807,19 +25621,25 @@
         <v>0.717</v>
       </c>
       <c r="AT160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU160" t="n">
         <v>37.93288288288289</v>
       </c>
-      <c r="AU160" t="n">
+      <c r="AV160" t="n">
+        <v>26.36235171177162</v>
+      </c>
+      <c r="AW160" t="n">
         <v>0.5806799784133837</v>
       </c>
-      <c r="AV160" t="n">
+      <c r="AX160" t="n">
         <v>50.48954256485062</v>
       </c>
-      <c r="AW160" t="inlineStr"/>
-      <c r="AX160" t="n">
+      <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="n">
         <v>0.2434472726667247</v>
       </c>
-      <c r="AY160" t="n">
+      <c r="BA160" t="n">
         <v>12.29154143560339</v>
       </c>
     </row>
@@ -24827,10 +25647,8 @@
       <c r="A161" s="1" t="n">
         <v>159</v>
       </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="B161" t="n">
+        <v>11</v>
       </c>
       <c r="C161" t="n">
         <v>290</v>
@@ -24970,21 +25788,27 @@
         <v>0.717</v>
       </c>
       <c r="AT161" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU161" t="n">
         <v>39.81607142857143</v>
       </c>
-      <c r="AU161" t="n">
+      <c r="AV161" t="n">
+        <v>25.11548638830336</v>
+      </c>
+      <c r="AW161" t="n">
         <v>0.5831663326653306</v>
       </c>
-      <c r="AV161" t="n">
+      <c r="AX161" t="n">
         <v>53.08725031617568</v>
       </c>
-      <c r="AW161" t="n">
+      <c r="AY161" t="n">
         <v>-0.9148648648648647</v>
       </c>
-      <c r="AX161" t="n">
+      <c r="AZ161" t="n">
         <v>0.2193729066609965</v>
       </c>
-      <c r="AY161" t="n">
+      <c r="BA161" t="n">
         <v>11.64590440849937</v>
       </c>
     </row>
@@ -24992,10 +25816,8 @@
       <c r="A162" s="1" t="n">
         <v>160</v>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="B162" t="n">
+        <v>6</v>
       </c>
       <c r="C162" t="n">
         <v>200</v>
@@ -25135,21 +25957,27 @@
         <v>0.717</v>
       </c>
       <c r="AT162" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU162" t="n">
         <v>38.9956570155902</v>
       </c>
-      <c r="AU162" t="n">
+      <c r="AV162" t="n">
+        <v>25.64388130709547</v>
+      </c>
+      <c r="AW162" t="n">
         <v>0.5505505505505506</v>
       </c>
-      <c r="AV162" t="n">
+      <c r="AX162" t="n">
         <v>45.2001414226272</v>
       </c>
-      <c r="AW162" t="n">
+      <c r="AY162" t="n">
         <v>-0.875</v>
       </c>
-      <c r="AX162" t="n">
+      <c r="AZ162" t="n">
         <v>0.2693134402703707</v>
       </c>
-      <c r="AY162" t="n">
+      <c r="BA162" t="n">
         <v>12.17300558723502</v>
       </c>
     </row>
@@ -25157,10 +25985,8 @@
       <c r="A163" s="1" t="n">
         <v>161</v>
       </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B163" t="n">
+        <v>4</v>
       </c>
       <c r="C163" t="n">
         <v>915</v>
@@ -25300,21 +26126,27 @@
         <v>0.717</v>
       </c>
       <c r="AT163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU163" t="n">
         <v>35.01108280254777</v>
       </c>
-      <c r="AU163" t="n">
+      <c r="AV163" t="n">
+        <v>28.56238424957338</v>
+      </c>
+      <c r="AW163" t="n">
         <v>0.5213414634146342</v>
       </c>
-      <c r="AV163" t="n">
+      <c r="AX163" t="n">
         <v>48.16685335643782</v>
       </c>
-      <c r="AW163" t="n">
+      <c r="AY163" t="n">
         <v>-0.9019350606756315</v>
       </c>
-      <c r="AX163" t="n">
+      <c r="AZ163" t="n">
         <v>0.2786500146224659</v>
       </c>
-      <c r="AY163" t="n">
+      <c r="BA163" t="n">
         <v>13.42169439208957</v>
       </c>
     </row>
@@ -25322,10 +26154,8 @@
       <c r="A164" s="1" t="n">
         <v>162</v>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B164" t="n">
+        <v>4</v>
       </c>
       <c r="C164" t="n">
         <v>4905</v>
@@ -25465,21 +26295,27 @@
         <v>0.523</v>
       </c>
       <c r="AT164" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU164" t="n">
         <v>35.7625352112676</v>
       </c>
-      <c r="AU164" t="n">
+      <c r="AV164" t="n">
+        <v>27.96222342998023</v>
+      </c>
+      <c r="AW164" t="n">
         <v>0.5279255319148936</v>
       </c>
-      <c r="AV164" t="n">
+      <c r="AX164" t="n">
         <v>42.61425540516829</v>
       </c>
-      <c r="AW164" t="n">
+      <c r="AY164" t="n">
         <v>-0.8602257636122178</v>
       </c>
-      <c r="AX164" t="n">
+      <c r="AZ164" t="n">
         <v>0.3302696303234725</v>
       </c>
-      <c r="AY164" t="n">
+      <c r="BA164" t="n">
         <v>14.07419437917497</v>
       </c>
     </row>
@@ -25487,10 +26323,8 @@
       <c r="A165" s="1" t="n">
         <v>163</v>
       </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="B165" t="n">
+        <v>2</v>
       </c>
       <c r="C165" t="n">
         <v>5807</v>
@@ -25630,21 +26464,27 @@
         <v>0.523</v>
       </c>
       <c r="AT165" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU165" t="n">
         <v>36.05222437137331</v>
       </c>
-      <c r="AU165" t="n">
+      <c r="AV165" t="n">
+        <v>27.73753956757337</v>
+      </c>
+      <c r="AW165" t="n">
         <v>0.5409884581237053</v>
       </c>
-      <c r="AV165" t="n">
+      <c r="AX165" t="n">
         <v>42.46993249100026</v>
       </c>
-      <c r="AW165" t="n">
+      <c r="AY165" t="n">
         <v>-0.8340425531914893</v>
       </c>
-      <c r="AX165" t="n">
+      <c r="AZ165" t="n">
         <v>0.3140509103601919</v>
       </c>
-      <c r="AY165" t="n">
+      <c r="BA165" t="n">
         <v>13.33772096173453</v>
       </c>
     </row>
@@ -25652,10 +26492,8 @@
       <c r="A166" s="1" t="n">
         <v>164</v>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="B166" t="n">
+        <v>13</v>
       </c>
       <c r="C166" t="n">
         <v>219</v>
@@ -25795,21 +26633,27 @@
         <v>0.523</v>
       </c>
       <c r="AT166" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU166" t="n">
         <v>29.2687074829932</v>
       </c>
-      <c r="AU166" t="n">
+      <c r="AV166" t="n">
+        <v>34.16618245206275</v>
+      </c>
+      <c r="AW166" t="n">
         <v>0.5394736842105263</v>
       </c>
-      <c r="AV166" t="n">
+      <c r="AX166" t="n">
         <v>38.40701417106357</v>
       </c>
-      <c r="AW166" t="n">
+      <c r="AY166" t="n">
         <v>-0.9123961218836566</v>
       </c>
-      <c r="AX166" t="n">
+      <c r="AZ166" t="n">
         <v>0.4419867263324095</v>
       </c>
-      <c r="AY166" t="n">
+      <c r="BA166" t="n">
         <v>16.97539046167085</v>
       </c>
     </row>
@@ -25817,10 +26661,8 @@
       <c r="A167" s="1" t="n">
         <v>165</v>
       </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="B167" t="n">
+        <v>6</v>
       </c>
       <c r="C167" t="n">
         <v>267</v>
@@ -25960,21 +26802,27 @@
         <v>0.523</v>
       </c>
       <c r="AT167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU167" t="n">
         <v>40.31574858757062</v>
       </c>
-      <c r="AU167" t="n">
+      <c r="AV167" t="n">
+        <v>24.80420270078529</v>
+      </c>
+      <c r="AW167" t="n">
         <v>0.6319209773849753</v>
       </c>
-      <c r="AV167" t="n">
+      <c r="AX167" t="n">
         <v>41.27967137504851</v>
       </c>
-      <c r="AW167" t="n">
+      <c r="AY167" t="n">
         <v>-0.9287135278514589</v>
       </c>
-      <c r="AX167" t="n">
+      <c r="AZ167" t="n">
         <v>0.2822534280040117</v>
       </c>
-      <c r="AY167" t="n">
+      <c r="BA167" t="n">
         <v>11.65132875248652</v>
       </c>
     </row>
@@ -25982,10 +26830,8 @@
       <c r="A168" s="1" t="n">
         <v>166</v>
       </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="B168" t="n">
+        <v>12</v>
       </c>
       <c r="C168" t="n">
         <v>642</v>
@@ -26125,21 +26971,27 @@
         <v>0.523</v>
       </c>
       <c r="AT168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU168" t="n">
         <v>32.95561719833564</v>
       </c>
-      <c r="AU168" t="n">
+      <c r="AV168" t="n">
+        <v>30.34384074744329</v>
+      </c>
+      <c r="AW168" t="n">
         <v>0.4881079162229322</v>
       </c>
-      <c r="AV168" t="n">
+      <c r="AX168" t="n">
         <v>40.6374878617617</v>
       </c>
-      <c r="AW168" t="n">
+      <c r="AY168" t="n">
         <v>-0.794580970384373</v>
       </c>
-      <c r="AX168" t="n">
+      <c r="AZ168" t="n">
         <v>0.3720589980627997</v>
       </c>
-      <c r="AY168" t="n">
+      <c r="BA168" t="n">
         <v>15.11954301763624</v>
       </c>
     </row>
@@ -26147,10 +26999,8 @@
       <c r="A169" s="1" t="n">
         <v>167</v>
       </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="B169" t="n">
+        <v>7</v>
       </c>
       <c r="C169" t="n">
         <v>286</v>
@@ -26290,21 +27140,27 @@
         <v>0.523</v>
       </c>
       <c r="AT169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU169" t="n">
         <v>37.79894273127753</v>
       </c>
-      <c r="AU169" t="n">
+      <c r="AV169" t="n">
+        <v>26.45576642471877</v>
+      </c>
+      <c r="AW169" t="n">
         <v>0.554552590266876</v>
       </c>
-      <c r="AV169" t="n">
+      <c r="AX169" t="n">
         <v>38.08684472600527</v>
       </c>
-      <c r="AW169" t="n">
+      <c r="AY169" t="n">
         <v>-0.8666886109282422</v>
       </c>
-      <c r="AX169" t="n">
+      <c r="AZ169" t="n">
         <v>0.3370510290002701</v>
       </c>
-      <c r="AY169" t="n">
+      <c r="BA169" t="n">
         <v>12.83721020627359</v>
       </c>
     </row>
@@ -26312,10 +27168,8 @@
       <c r="A170" s="1" t="n">
         <v>168</v>
       </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B170" t="n">
+        <v>1</v>
       </c>
       <c r="C170" t="n">
         <v>7594</v>
@@ -26455,21 +27309,27 @@
         <v>0.523</v>
       </c>
       <c r="AT170" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU170" t="n">
         <v>31.78387096774194</v>
       </c>
-      <c r="AU170" t="n">
+      <c r="AV170" t="n">
+        <v>31.46249873135085</v>
+      </c>
+      <c r="AW170" t="n">
         <v>0.5653791130185981</v>
       </c>
-      <c r="AV170" t="n">
+      <c r="AX170" t="n">
         <v>43.33108356621307</v>
       </c>
-      <c r="AW170" t="n">
+      <c r="AY170" t="n">
         <v>-0.8734652114597544</v>
       </c>
-      <c r="AX170" t="n">
+      <c r="AZ170" t="n">
         <v>0.3618600999053327</v>
       </c>
-      <c r="AY170" t="n">
+      <c r="BA170" t="n">
         <v>15.67979022827618</v>
       </c>
     </row>
@@ -26477,10 +27337,8 @@
       <c r="A171" s="1" t="n">
         <v>169</v>
       </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="B171" t="n">
+        <v>7</v>
       </c>
       <c r="C171" t="n">
         <v>6994</v>
@@ -26620,21 +27478,27 @@
         <v>0.523</v>
       </c>
       <c r="AT171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU171" t="n">
         <v>41.63273092369477</v>
       </c>
-      <c r="AU171" t="n">
+      <c r="AV171" t="n">
+        <v>24.01956292112612</v>
+      </c>
+      <c r="AW171" t="n">
         <v>0.6081825334382376</v>
       </c>
-      <c r="AV171" t="n">
+      <c r="AX171" t="n">
         <v>45.59782712484886</v>
       </c>
-      <c r="AW171" t="n">
+      <c r="AY171" t="n">
         <v>-0.9163306451612903</v>
       </c>
-      <c r="AX171" t="n">
+      <c r="AZ171" t="n">
         <v>0.254785183807967</v>
       </c>
-      <c r="AY171" t="n">
+      <c r="BA171" t="n">
         <v>11.61765076524852</v>
       </c>
     </row>
@@ -26642,10 +27506,8 @@
       <c r="A172" s="1" t="n">
         <v>170</v>
       </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="B172" t="n">
+        <v>13</v>
       </c>
       <c r="C172" t="n">
         <v>92</v>
@@ -26785,21 +27647,27 @@
         <v>0.717</v>
       </c>
       <c r="AT172" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU172" t="n">
         <v>32.12362911266202</v>
       </c>
-      <c r="AU172" t="n">
+      <c r="AV172" t="n">
+        <v>31.12973308504035</v>
+      </c>
+      <c r="AW172" t="n">
         <v>0.5760777683854608</v>
       </c>
-      <c r="AV172" t="n">
+      <c r="AX172" t="n">
         <v>46.08862851636469</v>
       </c>
-      <c r="AW172" t="n">
+      <c r="AY172" t="n">
         <v>-0.8450749123366273</v>
       </c>
-      <c r="AX172" t="n">
+      <c r="AZ172" t="n">
         <v>0.3188696860136649</v>
       </c>
-      <c r="AY172" t="n">
+      <c r="BA172" t="n">
         <v>14.69626650381366</v>
       </c>
     </row>
@@ -26807,10 +27675,8 @@
       <c r="A173" s="1" t="n">
         <v>171</v>
       </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="B173" t="n">
+        <v>3</v>
       </c>
       <c r="C173" t="n">
         <v>335</v>
@@ -26950,21 +27816,27 @@
         <v>0.523</v>
       </c>
       <c r="AT173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU173" t="n">
         <v>39.07777777777778</v>
       </c>
-      <c r="AU173" t="n">
+      <c r="AV173" t="n">
+        <v>25.58999147000285</v>
+      </c>
+      <c r="AW173" t="n">
         <v>0.5766246362754607</v>
       </c>
-      <c r="AV173" t="n">
+      <c r="AX173" t="n">
         <v>31.20218338168698</v>
       </c>
-      <c r="AW173" t="n">
+      <c r="AY173" t="n">
         <v>-0.8522613065326633</v>
       </c>
-      <c r="AX173" t="n">
+      <c r="AZ173" t="n">
         <v>0.399707243754127</v>
       </c>
-      <c r="AY173" t="n">
+      <c r="BA173" t="n">
         <v>12.47173871860493</v>
       </c>
     </row>
@@ -26972,10 +27844,8 @@
       <c r="A174" s="1" t="n">
         <v>172</v>
       </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B174" t="n">
+        <v>1</v>
       </c>
       <c r="C174" t="n">
         <v>9742</v>
@@ -27115,21 +27985,27 @@
         <v>0.523</v>
       </c>
       <c r="AT174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU174" t="n">
         <v>34.49588744588745</v>
       </c>
-      <c r="AU174" t="n">
+      <c r="AV174" t="n">
+        <v>28.98896286024434</v>
+      </c>
+      <c r="AW174" t="n">
         <v>0.5402985074626866</v>
       </c>
-      <c r="AV174" t="n">
+      <c r="AX174" t="n">
         <v>37.47652040214079</v>
       </c>
-      <c r="AW174" t="n">
+      <c r="AY174" t="n">
         <v>-0.9190476190476191</v>
       </c>
-      <c r="AX174" t="n">
+      <c r="AZ174" t="n">
         <v>0.3801718619146223</v>
       </c>
-      <c r="AY174" t="n">
+      <c r="BA174" t="n">
         <v>14.2475185393632</v>
       </c>
     </row>
@@ -27137,10 +28013,8 @@
       <c r="A175" s="1" t="n">
         <v>173</v>
       </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B175" t="n">
+        <v>4</v>
       </c>
       <c r="C175" t="n">
         <v>155</v>
@@ -27280,21 +28154,27 @@
         <v>0.523</v>
       </c>
       <c r="AT175" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU175" t="n">
         <v>43.50616113744076</v>
       </c>
-      <c r="AU175" t="n">
+      <c r="AV175" t="n">
+        <v>22.98525022331641</v>
+      </c>
+      <c r="AW175" t="n">
         <v>0.6444219750589821</v>
       </c>
-      <c r="AV175" t="n">
+      <c r="AX175" t="n">
         <v>45.90057484261069</v>
       </c>
-      <c r="AW175" t="n">
+      <c r="AY175" t="n">
         <v>-0.8253346392425727</v>
       </c>
-      <c r="AX175" t="n">
+      <c r="AZ175" t="n">
         <v>0.2470312536106503</v>
       </c>
-      <c r="AY175" t="n">
+      <c r="BA175" t="n">
         <v>11.3388765448196</v>
       </c>
     </row>
@@ -27302,10 +28182,8 @@
       <c r="A176" s="1" t="n">
         <v>174</v>
       </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="B176" t="n">
+        <v>14</v>
       </c>
       <c r="C176" t="n">
         <v>101</v>
@@ -27445,21 +28323,27 @@
         <v>0.717</v>
       </c>
       <c r="AT176" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU176" t="n">
         <v>41.68621562952244</v>
       </c>
-      <c r="AU176" t="n">
+      <c r="AV176" t="n">
+        <v>23.98874507792436</v>
+      </c>
+      <c r="AW176" t="n">
         <v>0.5922100914724108</v>
       </c>
-      <c r="AV176" t="n">
+      <c r="AX176" t="n">
         <v>47.40155652187085</v>
       </c>
-      <c r="AW176" t="n">
+      <c r="AY176" t="n">
         <v>-0.8593242365172189</v>
       </c>
-      <c r="AX176" t="n">
+      <c r="AZ176" t="n">
         <v>0.2303895675632164</v>
       </c>
-      <c r="AY176" t="n">
+      <c r="BA176" t="n">
         <v>10.92082410889718</v>
       </c>
     </row>
@@ -27467,10 +28351,8 @@
       <c r="A177" s="1" t="n">
         <v>175</v>
       </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B177" t="n">
+        <v>4</v>
       </c>
       <c r="C177" t="n">
         <v>209</v>
@@ -27610,21 +28492,27 @@
         <v>0.523</v>
       </c>
       <c r="AT177" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU177" t="n">
         <v>35.96792650918635</v>
       </c>
-      <c r="AU177" t="n">
+      <c r="AV177" t="n">
+        <v>27.80254791013867</v>
+      </c>
+      <c r="AW177" t="n">
         <v>0.5765725716825961</v>
       </c>
-      <c r="AV177" t="n">
+      <c r="AX177" t="n">
         <v>44.74207179927146</v>
       </c>
-      <c r="AW177" t="n">
+      <c r="AY177" t="n">
         <v>-1.011280931586608</v>
       </c>
-      <c r="AX177" t="n">
+      <c r="AZ177" t="n">
         <v>0.2939442645614514</v>
       </c>
-      <c r="AY177" t="n">
+      <c r="BA177" t="n">
         <v>13.1516753899925</v>
       </c>
     </row>
@@ -27632,10 +28520,8 @@
       <c r="A178" s="1" t="n">
         <v>176</v>
       </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="B178" t="n">
+        <v>14</v>
       </c>
       <c r="C178" t="n">
         <v>666</v>
@@ -27775,21 +28661,27 @@
         <v>0.717</v>
       </c>
       <c r="AT178" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU178" t="n">
         <v>34.36061538461539</v>
       </c>
-      <c r="AU178" t="n">
+      <c r="AV178" t="n">
+        <v>29.10308761372591</v>
+      </c>
+      <c r="AW178" t="n">
         <v>0.5083207261724659</v>
       </c>
-      <c r="AV178" t="n">
+      <c r="AX178" t="n">
         <v>44.0343228797727</v>
       </c>
-      <c r="AW178" t="n">
+      <c r="AY178" t="n">
         <v>-0.8638230647709321</v>
       </c>
-      <c r="AX178" t="n">
+      <c r="AZ178" t="n">
         <v>0.3054467120359153</v>
       </c>
-      <c r="AY178" t="n">
+      <c r="BA178" t="n">
         <v>13.45013914035445</v>
       </c>
     </row>
@@ -27797,10 +28689,8 @@
       <c r="A179" s="1" t="n">
         <v>177</v>
       </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="B179" t="n">
+        <v>13</v>
       </c>
       <c r="C179" t="n">
         <v>188</v>
@@ -27940,21 +28830,27 @@
         <v>0.717</v>
       </c>
       <c r="AT179" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU179" t="n">
         <v>35.34196357878068</v>
       </c>
-      <c r="AU179" t="n">
+      <c r="AV179" t="n">
+        <v>28.29497568155495</v>
+      </c>
+      <c r="AW179" t="n">
         <v>0.5822031094938803</v>
       </c>
-      <c r="AV179" t="n">
+      <c r="AX179" t="n">
         <v>54.20072825178515</v>
       </c>
-      <c r="AW179" t="n">
+      <c r="AY179" t="n">
         <v>-0.8194444444444445</v>
       </c>
-      <c r="AX179" t="n">
+      <c r="AZ179" t="n">
         <v>0.2464363334952325</v>
       </c>
-      <c r="AY179" t="n">
+      <c r="BA179" t="n">
         <v>13.35702874314139</v>
       </c>
     </row>
@@ -27962,10 +28858,8 @@
       <c r="A180" s="1" t="n">
         <v>178</v>
       </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B180" t="n">
+        <v>1</v>
       </c>
       <c r="C180" t="n">
         <v>685</v>
@@ -28105,21 +28999,27 @@
         <v>0.523</v>
       </c>
       <c r="AT180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU180" t="n">
         <v>38.64987714987715</v>
       </c>
-      <c r="AU180" t="n">
+      <c r="AV180" t="n">
+        <v>25.87330345507136</v>
+      </c>
+      <c r="AW180" t="n">
         <v>0.5340583858042358</v>
       </c>
-      <c r="AV180" t="n">
+      <c r="AX180" t="n">
         <v>39.38800376216415</v>
       </c>
-      <c r="AW180" t="n">
+      <c r="AY180" t="n">
         <v>-0.8907371167645139</v>
       </c>
-      <c r="AX180" t="n">
+      <c r="AZ180" t="n">
         <v>0.3280651598232026</v>
       </c>
-      <c r="AY180" t="n">
+      <c r="BA180" t="n">
         <v>12.92183174935129</v>
       </c>
     </row>
@@ -28127,10 +29027,8 @@
       <c r="A181" s="1" t="n">
         <v>179</v>
       </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="B181" t="n">
+        <v>14</v>
       </c>
       <c r="C181" t="n">
         <v>627</v>
@@ -28270,21 +29168,27 @@
         <v>0.717</v>
       </c>
       <c r="AT181" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU181" t="n">
         <v>30.17824074074074</v>
       </c>
-      <c r="AU181" t="n">
+      <c r="AV181" t="n">
+        <v>33.13645777402777</v>
+      </c>
+      <c r="AW181" t="n">
         <v>0.4705882352941176</v>
       </c>
-      <c r="AV181" t="n">
+      <c r="AX181" t="n">
         <v>42.7829066706362</v>
       </c>
-      <c r="AW181" t="n">
+      <c r="AY181" t="n">
         <v>-0.9359058207979072</v>
       </c>
-      <c r="AX181" t="n">
+      <c r="AZ181" t="n">
         <v>0.3562090494563998</v>
       </c>
-      <c r="AY181" t="n">
+      <c r="BA181" t="n">
         <v>15.23965851812918</v>
       </c>
     </row>

--- a/Results_isofys/Numex_preliminar_base.xlsx
+++ b/Results_isofys/Numex_preliminar_base.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA181"/>
+  <dimension ref="A1:AZ181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,11 +686,6 @@
       <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>Narea</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>Carea</t>
         </is>
       </c>
     </row>
@@ -835,10 +830,7 @@
         <v>-1.069204566063425</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.1583411527786951</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>6.267862957094129</v>
+        <v>1.583411527786951</v>
       </c>
     </row>
     <row r="3">
@@ -982,10 +974,7 @@
         <v>-1.162714378482783</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.1927929018543231</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.931398966307422</v>
+        <v>1.927929018543231</v>
       </c>
     </row>
     <row r="4">
@@ -1129,10 +1118,7 @@
         <v>-1.083217188451016</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.1459443363957555</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>6.201410491775166</v>
+        <v>1.459443363957554</v>
       </c>
     </row>
     <row r="5">
@@ -1276,10 +1262,7 @@
         <v>-1.173469655199274</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.2308390026071944</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>6.803966990152447</v>
+        <v>2.308390026071943</v>
       </c>
     </row>
     <row r="6">
@@ -1423,10 +1406,7 @@
         <v>-1.152717050430573</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.1972952651382424</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>5.814010355624786</v>
+        <v>1.972952651382424</v>
       </c>
     </row>
     <row r="7">
@@ -1570,10 +1550,7 @@
         <v>-0.9757692279498354</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.2411024955423218</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6.393667365779264</v>
+        <v>2.411024955423218</v>
       </c>
     </row>
     <row r="8">
@@ -1717,10 +1694,7 @@
         <v>-1.066817746219274</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.2212734935521185</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>6.582919875238116</v>
+        <v>2.212734935521185</v>
       </c>
     </row>
     <row r="9">
@@ -1864,10 +1838,7 @@
         <v>-1.120257664680253</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.2491330280495736</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>7.04653963916366</v>
+        <v>2.491330280495736</v>
       </c>
     </row>
     <row r="10">
@@ -2011,10 +1982,7 @@
         <v>-1.176763154946914</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.1922442143630735</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5.385976820401974</v>
+        <v>1.922442143630735</v>
       </c>
     </row>
     <row r="11">
@@ -2158,10 +2126,7 @@
         <v>-1.083133704760353</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.1541538771183675</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>6.156964889603419</v>
+        <v>1.541538771183675</v>
       </c>
     </row>
     <row r="12">
@@ -2305,10 +2270,7 @@
         <v>-0.9693632665794485</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.1704503359635594</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>7.04539122144526</v>
+        <v>1.704503359635594</v>
       </c>
     </row>
     <row r="13">
@@ -2452,10 +2414,7 @@
         <v>-1.01178671221848</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.1893086604314295</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>6.298227944361334</v>
+        <v>1.893086604314296</v>
       </c>
     </row>
     <row r="14">
@@ -2599,10 +2558,7 @@
         <v>-0.9086318732906992</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.2420263723581012</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>5.933547349313596</v>
+        <v>2.420263723581012</v>
       </c>
     </row>
     <row r="15">
@@ -2746,10 +2702,7 @@
         <v>-0.9710658232898745</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.2262696828216982</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>6.737742901484933</v>
+        <v>2.262696828216981</v>
       </c>
     </row>
     <row r="16">
@@ -2809,7 +2762,7 @@
         <v>42.28</v>
       </c>
       <c r="P16" t="n">
-        <v>-28.2</v>
+        <v>-31.00109077040427</v>
       </c>
       <c r="Q16" t="n">
         <v>15.5</v>
@@ -2851,16 +2804,16 @@
       <c r="AJ16" t="inlineStr"/>
       <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="n">
-        <v>19.32430148930667</v>
+        <v>22.27086816317477</v>
       </c>
       <c r="AM16" t="n">
-        <v>324.3159602666282</v>
+        <v>384.1537123992449</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.7066443400185419</v>
+        <v>0.8370233963843873</v>
       </c>
       <c r="AO16" t="n">
-        <v>84.14763727184936</v>
+        <v>46.74904218896397</v>
       </c>
       <c r="AP16" t="n">
         <v>2000</v>
@@ -2890,13 +2843,10 @@
         <v>32.32547486872957</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.9202190103021481</v>
+        <v>-1.011623867625123</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.2346594974817987</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>7.585479688556592</v>
+        <v>2.346594974817986</v>
       </c>
     </row>
     <row r="17">
@@ -3040,10 +2990,7 @@
         <v>-1.137930339273472</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.2040293659175826</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>5.793309073325802</v>
+        <v>2.040293659175827</v>
       </c>
     </row>
     <row r="18">
@@ -3187,10 +3134,7 @@
         <v>-0.9983195512068304</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.2199748552043699</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>6.418104834646514</v>
+        <v>2.199748552043698</v>
       </c>
     </row>
     <row r="19">
@@ -3334,10 +3278,7 @@
         <v>-1.159881181147376</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.1804095984933663</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>4.811120672929789</v>
+        <v>1.804095984933663</v>
       </c>
     </row>
     <row r="20">
@@ -3397,7 +3338,7 @@
         <v>47.75</v>
       </c>
       <c r="P20" t="n">
-        <v>-26.37</v>
+        <v>-32.60541078255443</v>
       </c>
       <c r="Q20" t="n">
         <v>15.9</v>
@@ -3439,16 +3380,16 @@
       <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="inlineStr"/>
       <c r="AL20" t="n">
-        <v>17.40841612040325</v>
+        <v>23.9661945893428</v>
       </c>
       <c r="AM20" t="n">
-        <v>285.4088909524788</v>
+        <v>418.5817548299786</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.6218706511290104</v>
+        <v>0.9120378400201408</v>
       </c>
       <c r="AO20" t="n">
-        <v>108.4645555931928</v>
+        <v>25.23151566975534</v>
       </c>
       <c r="AP20" t="n">
         <v>2000</v>
@@ -3478,13 +3419,10 @@
         <v>30.75436275117814</v>
       </c>
       <c r="AY20" t="n">
-        <v>-0.9251081452731393</v>
+        <v>-1.14385783446787</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.2216436966512492</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>6.816510648324604</v>
+        <v>2.216436966512492</v>
       </c>
     </row>
     <row r="21">
@@ -3628,10 +3566,7 @@
         <v>-0.8250529055541557</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.2731252805030631</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>6.269341168086865</v>
+        <v>2.731252805030631</v>
       </c>
     </row>
     <row r="22">
@@ -3775,10 +3710,7 @@
         <v>-0.9307778716019919</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.1359691165823957</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>7.209869586996444</v>
+        <v>1.359691165823957</v>
       </c>
     </row>
     <row r="23">
@@ -3922,10 +3854,7 @@
         <v>-1.076624094600751</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.1532285064088778</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>5.8814772925756</v>
+        <v>1.532285064088778</v>
       </c>
     </row>
     <row r="24">
@@ -4069,10 +3998,7 @@
         <v>-0.9531215121310557</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.2083919474390169</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>6.450269324889292</v>
+        <v>2.083919474390169</v>
       </c>
     </row>
     <row r="25">
@@ -4216,10 +4142,7 @@
         <v>-1.127672428671739</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.1924962019984864</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>5.922628309595306</v>
+        <v>1.924962019984864</v>
       </c>
     </row>
     <row r="26">
@@ -4363,10 +4286,7 @@
         <v>-1.093730835683608</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.1993680458705612</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>5.819873982352418</v>
+        <v>1.993680458705612</v>
       </c>
     </row>
     <row r="27">
@@ -4510,10 +4430,7 @@
         <v>-0.9251981278059437</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.2247906864753312</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>4.353630630525455</v>
+        <v>2.247906864753312</v>
       </c>
     </row>
     <row r="28">
@@ -4657,10 +4574,7 @@
         <v>-1.110646754176239</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.1941969337398241</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>6.180318961158282</v>
+        <v>1.941969337398241</v>
       </c>
     </row>
     <row r="29">
@@ -4804,10 +4718,7 @@
         <v>-0.8721981465115956</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.2299853817964811</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>4.77039521233669</v>
+        <v>2.299853817964811</v>
       </c>
     </row>
     <row r="30">
@@ -4951,10 +4862,7 @@
         <v>-1.026018023099852</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.2056480718564838</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>6.003256549989229</v>
+        <v>2.056480718564837</v>
       </c>
     </row>
     <row r="31">
@@ -5098,10 +5006,7 @@
         <v>-1.081725628636109</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.136631885562437</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>5.871422404388254</v>
+        <v>1.36631885562437</v>
       </c>
     </row>
     <row r="32">
@@ -5245,10 +5150,7 @@
         <v>-0.9757257325131097</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.2060536274187499</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>4.248872527334292</v>
+        <v>2.060536274187499</v>
       </c>
     </row>
     <row r="33">
@@ -5392,10 +5294,7 @@
         <v>-1.108000186694067</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.2140487849336566</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>4.707179999838402</v>
+        <v>2.140487849336566</v>
       </c>
     </row>
     <row r="34">
@@ -5539,10 +5438,7 @@
         <v>-1.1317622997201</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.1262484116656832</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>5.538752547725021</v>
+        <v>1.262484116656831</v>
       </c>
     </row>
     <row r="35">
@@ -5686,10 +5582,7 @@
         <v>-1.097985206987246</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.236853606683806</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>5.72708070874746</v>
+        <v>2.36853606683806</v>
       </c>
     </row>
     <row r="36">
@@ -5833,10 +5726,7 @@
         <v>-1.041003254864917</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.1404492354378129</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>6.421580057406096</v>
+        <v>1.404492354378129</v>
       </c>
     </row>
     <row r="37">
@@ -5980,10 +5870,7 @@
         <v>-1.128326182974303</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.165736668134432</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>5.382476778431748</v>
+        <v>1.65736668134432</v>
       </c>
     </row>
     <row r="38">
@@ -6127,10 +6014,7 @@
         <v>-1.052221717593601</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.25370946862891</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>7.926449640071605</v>
+        <v>2.5370946862891</v>
       </c>
     </row>
     <row r="39">
@@ -6274,10 +6158,7 @@
         <v>-1.018263130425242</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0.1790085898974969</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>3.990234824028318</v>
+        <v>1.790085898974969</v>
       </c>
     </row>
     <row r="40">
@@ -6421,10 +6302,7 @@
         <v>-1.134852638614013</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0.1636334848571583</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>6.701960533465813</v>
+        <v>1.636334848571583</v>
       </c>
     </row>
     <row r="41">
@@ -6568,10 +6446,7 @@
         <v>-1.046794083447492</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.1962293560349081</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>6.406993482654983</v>
+        <v>1.962293560349081</v>
       </c>
     </row>
     <row r="42">
@@ -6715,10 +6590,7 @@
         <v>-1.055363556422817</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0.1962293560349081</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>6.406993482654983</v>
+        <v>1.962293560349081</v>
       </c>
     </row>
     <row r="43">
@@ -6862,10 +6734,7 @@
         <v>-1.027478472194354</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0.1962293560349081</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>6.406993482654983</v>
+        <v>1.962293560349081</v>
       </c>
     </row>
     <row r="44">
@@ -7009,10 +6878,7 @@
         <v>-1.035889819888641</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.1962293560349081</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>6.406993482654983</v>
+        <v>1.962293560349081</v>
       </c>
     </row>
     <row r="45">
@@ -7156,10 +7022,7 @@
         <v>-1.016944806660762</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0.2080347916779913</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>7.270477607848516</v>
+        <v>2.080347916779913</v>
       </c>
     </row>
     <row r="46">
@@ -7303,10 +7166,7 @@
         <v>-1.168428613749502</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0.1803572361821152</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>4.981358951370535</v>
+        <v>1.803572361821152</v>
       </c>
     </row>
     <row r="47">
@@ -7450,10 +7310,7 @@
         <v>-1.006406074511895</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0.1563233988308393</v>
-      </c>
-      <c r="BA47" t="n">
-        <v>4.941560931653564</v>
+        <v>1.563233988308393</v>
       </c>
     </row>
     <row r="48">
@@ -7597,10 +7454,7 @@
         <v>-1.002974473340656</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0.1727182447385554</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>5.627608137299266</v>
+        <v>1.727182447385554</v>
       </c>
     </row>
     <row r="49">
@@ -7744,10 +7598,7 @@
         <v>-1.033343565098957</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0.2118768969038876</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>7.860992204916545</v>
+        <v>2.118768969038876</v>
       </c>
     </row>
     <row r="50">
@@ -7891,10 +7742,7 @@
         <v>-1.094831536193773</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0.1305405133948935</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>6.085878779925097</v>
+        <v>1.305405133948935</v>
       </c>
     </row>
     <row r="51">
@@ -8038,10 +7886,7 @@
         <v>-1.034130614924995</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0.2749705279828398</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>7.600880368696366</v>
+        <v>2.749705279828397</v>
       </c>
     </row>
     <row r="52">
@@ -8185,10 +8030,7 @@
         <v>-0.9330413776996519</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0.2554237568151246</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>8.029662939995131</v>
+        <v>2.554237568151246</v>
       </c>
     </row>
     <row r="53">
@@ -8232,9 +8074,7 @@
       <c r="J53" t="n">
         <v>-32.30627681984863</v>
       </c>
-      <c r="K53" t="n">
-        <v>0.0253654953216571</v>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="n">
         <v>2.212395175186674</v>
       </c>
@@ -8325,18 +8165,11 @@
       <c r="AW53" t="n">
         <v>0.5561426684280054</v>
       </c>
-      <c r="AX53" t="n">
-        <v>16.47515809594595</v>
-      </c>
+      <c r="AX53" t="inlineStr"/>
       <c r="AY53" t="n">
         <v>-1.059704205037399</v>
       </c>
-      <c r="AZ53" t="n">
-        <v>0.2105696461538427</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>3.469168210591955</v>
-      </c>
+      <c r="AZ53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -8479,10 +8312,7 @@
         <v>-1.09799079624996</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0.2230482700063978</v>
-      </c>
-      <c r="BA54" t="n">
-        <v>3.834114387266885</v>
+        <v>2.230482700063977</v>
       </c>
     </row>
     <row r="55">
@@ -8626,10 +8456,7 @@
         <v>-1.013558134662488</v>
       </c>
       <c r="AZ55" t="n">
-        <v>0.2700331914670088</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>9.226808188432537</v>
+        <v>2.700331914670088</v>
       </c>
     </row>
     <row r="56">
@@ -8773,10 +8600,7 @@
         <v>-1.029758709416929</v>
       </c>
       <c r="AZ56" t="n">
-        <v>0.1811914954031918</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>5.640759522824799</v>
+        <v>1.811914954031917</v>
       </c>
     </row>
     <row r="57">
@@ -8920,10 +8744,7 @@
         <v>-1.071407723597514</v>
       </c>
       <c r="AZ57" t="n">
-        <v>0.1485071659290358</v>
-      </c>
-      <c r="BA57" t="n">
-        <v>6.279270830799232</v>
+        <v>1.485071659290358</v>
       </c>
     </row>
     <row r="58">
@@ -9067,10 +8888,7 @@
         <v>-1.076020463092165</v>
       </c>
       <c r="AZ58" t="n">
-        <v>0.181805467668072</v>
-      </c>
-      <c r="BA58" t="n">
-        <v>5.528408572483942</v>
+        <v>1.818054676680719</v>
       </c>
     </row>
     <row r="59">
@@ -9214,10 +9032,7 @@
         <v>-1.131721301339614</v>
       </c>
       <c r="AZ59" t="n">
-        <v>0.1468960643433882</v>
-      </c>
-      <c r="BA59" t="n">
-        <v>6.080598725084783</v>
+        <v>1.468960643433882</v>
       </c>
     </row>
     <row r="60">
@@ -9361,10 +9176,7 @@
         <v>-1.148906986345209</v>
       </c>
       <c r="AZ60" t="n">
-        <v>0.1640718941643498</v>
-      </c>
-      <c r="BA60" t="n">
-        <v>4.620440023861259</v>
+        <v>1.640718941643499</v>
       </c>
     </row>
     <row r="61">
@@ -9508,10 +9320,7 @@
         <v>-0.9802187884414533</v>
       </c>
       <c r="AZ61" t="n">
-        <v>0.2324436326842925</v>
-      </c>
-      <c r="BA61" t="n">
-        <v>6.589693642640406</v>
+        <v>2.324436326842925</v>
       </c>
     </row>
     <row r="62">
@@ -9655,10 +9464,7 @@
         <v>-1.059967417806882</v>
       </c>
       <c r="AZ62" t="n">
-        <v>0.2271852849396293</v>
-      </c>
-      <c r="BA62" t="n">
-        <v>8.1219991100984</v>
+        <v>2.271852849396293</v>
       </c>
     </row>
     <row r="63">
@@ -9802,10 +9608,7 @@
         <v>-1.07072599241777</v>
       </c>
       <c r="AZ63" t="n">
-        <v>0.2097736888129386</v>
-      </c>
-      <c r="BA63" t="n">
-        <v>6.659317142649229</v>
+        <v>2.097736888129386</v>
       </c>
     </row>
     <row r="64">
@@ -9949,10 +9752,7 @@
         <v>-1.07072599241777</v>
       </c>
       <c r="AZ64" t="n">
-        <v>0.2051731480905204</v>
-      </c>
-      <c r="BA64" t="n">
-        <v>6.720409857723063</v>
+        <v>2.051731480905203</v>
       </c>
     </row>
     <row r="65">
@@ -10096,10 +9896,7 @@
         <v>-1.072717162486702</v>
       </c>
       <c r="AZ65" t="n">
-        <v>0.1711270057226029</v>
-      </c>
-      <c r="BA65" t="n">
-        <v>6.465141386759904</v>
+        <v>1.71127005722603</v>
       </c>
     </row>
     <row r="66">
@@ -10243,10 +10040,7 @@
         <v>-1.186907968195777</v>
       </c>
       <c r="AZ66" t="n">
-        <v>0.1264668813853405</v>
-      </c>
-      <c r="BA66" t="n">
-        <v>5.917373389442116</v>
+        <v>1.264668813853404</v>
       </c>
     </row>
     <row r="67">
@@ -10390,10 +10184,7 @@
         <v>-1.05716724908219</v>
       </c>
       <c r="AZ67" t="n">
-        <v>0.1735620252135451</v>
-      </c>
-      <c r="BA67" t="n">
-        <v>5.130229695978934</v>
+        <v>1.735620252135451</v>
       </c>
     </row>
     <row r="68">
@@ -10537,10 +10328,7 @@
         <v>-1.062612342442872</v>
       </c>
       <c r="AZ68" t="n">
-        <v>0.1651892043876882</v>
-      </c>
-      <c r="BA68" t="n">
-        <v>4.61721716535054</v>
+        <v>1.651892043876882</v>
       </c>
     </row>
     <row r="69">
@@ -10684,10 +10472,7 @@
         <v>-1.162202419950019</v>
       </c>
       <c r="AZ69" t="n">
-        <v>0.1729739026459769</v>
-      </c>
-      <c r="BA69" t="n">
-        <v>4.169261023831525</v>
+        <v>1.72973902645977</v>
       </c>
     </row>
     <row r="70">
@@ -10831,10 +10616,7 @@
         <v>-0.9735100220183867</v>
       </c>
       <c r="AZ70" t="n">
-        <v>0.1653302877966243</v>
-      </c>
-      <c r="BA70" t="n">
-        <v>5.468910140257988</v>
+        <v>1.653302877966243</v>
       </c>
     </row>
     <row r="71">
@@ -10978,10 +10760,7 @@
         <v>-1.151540486656524</v>
       </c>
       <c r="AZ71" t="n">
-        <v>0.224534879706159</v>
-      </c>
-      <c r="BA71" t="n">
-        <v>6.385261085941602</v>
+        <v>2.24534879706159</v>
       </c>
     </row>
     <row r="72">
@@ -11125,10 +10904,7 @@
         <v>-1.081507885923864</v>
       </c>
       <c r="AZ72" t="n">
-        <v>0.1704181532420173</v>
-      </c>
-      <c r="BA72" t="n">
-        <v>4.64552151410903</v>
+        <v>1.704181532420173</v>
       </c>
     </row>
     <row r="73">
@@ -11272,10 +11048,7 @@
         <v>-1.008164398010397</v>
       </c>
       <c r="AZ73" t="n">
-        <v>0.1771344004138958</v>
-      </c>
-      <c r="BA73" t="n">
-        <v>5.317720031155273</v>
+        <v>1.771344004138958</v>
       </c>
     </row>
     <row r="74">
@@ -11419,10 +11192,7 @@
         <v>-0.9019527661726316</v>
       </c>
       <c r="AZ74" t="n">
-        <v>0.2890653446677475</v>
-      </c>
-      <c r="BA74" t="n">
-        <v>7.650714677495467</v>
+        <v>2.890653446677475</v>
       </c>
     </row>
     <row r="75">
@@ -11566,10 +11336,7 @@
         <v>-1.064321440481539</v>
       </c>
       <c r="AZ75" t="n">
-        <v>0.2678379030470969</v>
-      </c>
-      <c r="BA75" t="n">
-        <v>8.094394089102797</v>
+        <v>2.678379030470969</v>
       </c>
     </row>
     <row r="76">
@@ -11713,10 +11480,7 @@
         <v>-1.036430349351861</v>
       </c>
       <c r="AZ76" t="n">
-        <v>0.2020516390549202</v>
-      </c>
-      <c r="BA76" t="n">
-        <v>6.613829372688381</v>
+        <v>2.020516390549202</v>
       </c>
     </row>
     <row r="77">
@@ -11860,10 +11624,7 @@
         <v>-0.9447135609596995</v>
       </c>
       <c r="AZ77" t="n">
-        <v>0.2290004233178914</v>
-      </c>
-      <c r="BA77" t="n">
-        <v>6.379856596163442</v>
+        <v>2.290004233178915</v>
       </c>
     </row>
     <row r="78">
@@ -12007,10 +11768,7 @@
         <v>-1.136069687512091</v>
       </c>
       <c r="AZ78" t="n">
-        <v>0.2143935207599353</v>
-      </c>
-      <c r="BA78" t="n">
-        <v>4.677253989798563</v>
+        <v>2.143935207599353</v>
       </c>
     </row>
     <row r="79">
@@ -12154,10 +11912,7 @@
         <v>-0.7957323640055816</v>
       </c>
       <c r="AZ79" t="n">
-        <v>0.3250436485054538</v>
-      </c>
-      <c r="BA79" t="n">
-        <v>5.943353709831833</v>
+        <v>3.250436485054538</v>
       </c>
     </row>
     <row r="80">
@@ -12301,10 +12056,7 @@
         <v>-1.083830924468203</v>
       </c>
       <c r="AZ80" t="n">
-        <v>0.2998648154876037</v>
-      </c>
-      <c r="BA80" t="n">
-        <v>6.635735356277657</v>
+        <v>2.998648154876038</v>
       </c>
     </row>
     <row r="81">
@@ -12448,10 +12200,7 @@
         <v>-0.852490835998494</v>
       </c>
       <c r="AZ81" t="n">
-        <v>0.2994186256562353</v>
-      </c>
-      <c r="BA81" t="n">
-        <v>7.152431113667959</v>
+        <v>2.994186256562354</v>
       </c>
     </row>
     <row r="82">
@@ -12595,10 +12344,7 @@
         <v>-1.073512489772441</v>
       </c>
       <c r="AZ82" t="n">
-        <v>0.1986099449474032</v>
-      </c>
-      <c r="BA82" t="n">
-        <v>5.80366638296212</v>
+        <v>1.986099449474032</v>
       </c>
     </row>
     <row r="83">
@@ -12742,10 +12488,7 @@
         <v>-1.045162407612312</v>
       </c>
       <c r="AZ83" t="n">
-        <v>0.1574768288150041</v>
-      </c>
-      <c r="BA83" t="n">
-        <v>4.144199615258708</v>
+        <v>1.574768288150041</v>
       </c>
     </row>
     <row r="84">
@@ -12889,10 +12632,7 @@
         <v>-1.011763599487811</v>
       </c>
       <c r="AZ84" t="n">
-        <v>0.1625698637855855</v>
-      </c>
-      <c r="BA84" t="n">
-        <v>4.910286937521602</v>
+        <v>1.625698637855855</v>
       </c>
     </row>
     <row r="85">
@@ -13036,10 +12776,7 @@
         <v>-1.056436243301099</v>
       </c>
       <c r="AZ85" t="n">
-        <v>0.2261410104794487</v>
-      </c>
-      <c r="BA85" t="n">
-        <v>6.328175428570905</v>
+        <v>2.261410104794487</v>
       </c>
     </row>
     <row r="86">
@@ -13183,10 +12920,7 @@
         <v>-1.139184969499528</v>
       </c>
       <c r="AZ86" t="n">
-        <v>0.2131678007547578</v>
-      </c>
-      <c r="BA86" t="n">
-        <v>6.522638295327906</v>
+        <v>2.131678007547578</v>
       </c>
     </row>
     <row r="87">
@@ -13330,10 +13064,7 @@
         <v>-0.9994064701242487</v>
       </c>
       <c r="AZ87" t="n">
-        <v>0.2723142473493239</v>
-      </c>
-      <c r="BA87" t="n">
-        <v>7.354363492686352</v>
+        <v>2.723142473493239</v>
       </c>
     </row>
     <row r="88">
@@ -13477,10 +13208,7 @@
         <v>-0.9530514877786842</v>
       </c>
       <c r="AZ88" t="n">
-        <v>0.2165437559626953</v>
-      </c>
-      <c r="BA88" t="n">
-        <v>4.352489670002637</v>
+        <v>2.165437559626953</v>
       </c>
     </row>
     <row r="89">
@@ -13646,10 +13374,7 @@
         <v>-0.921325744894543</v>
       </c>
       <c r="AZ89" t="n">
-        <v>0.2273110803333757</v>
-      </c>
-      <c r="BA89" t="n">
-        <v>13.49936057389324</v>
+        <v>2.273110803333757</v>
       </c>
     </row>
     <row r="90">
@@ -13815,10 +13540,7 @@
         <v>-0.9396264176117411</v>
       </c>
       <c r="AZ90" t="n">
-        <v>0.2562349769016561</v>
-      </c>
-      <c r="BA90" t="n">
-        <v>14.11226797838226</v>
+        <v>2.562349769016562</v>
       </c>
     </row>
     <row r="91">
@@ -13984,10 +13706,7 @@
         <v>-0.9000000000000001</v>
       </c>
       <c r="AZ91" t="n">
-        <v>0.2747689268163115</v>
-      </c>
-      <c r="BA91" t="n">
-        <v>12.41339472150039</v>
+        <v>2.747689268163116</v>
       </c>
     </row>
     <row r="92">
@@ -14153,10 +13872,7 @@
         <v>-0.9772876892692561</v>
       </c>
       <c r="AZ92" t="n">
-        <v>0.2638257036105743</v>
-      </c>
-      <c r="BA92" t="n">
-        <v>11.44644073918296</v>
+        <v>2.638257036105744</v>
       </c>
     </row>
     <row r="93">
@@ -14322,10 +14038,7 @@
         <v>-0.8726919339164237</v>
       </c>
       <c r="AZ93" t="n">
-        <v>0.2205905999210828</v>
-      </c>
-      <c r="BA93" t="n">
-        <v>13.46108772447198</v>
+        <v>2.205905999210828</v>
       </c>
     </row>
     <row r="94">
@@ -14491,10 +14204,7 @@
         <v>-0.8030209617755858</v>
       </c>
       <c r="AZ94" t="n">
-        <v>0.2899244513121407</v>
-      </c>
-      <c r="BA94" t="n">
-        <v>14.55098595795598</v>
+        <v>2.899244513121407</v>
       </c>
     </row>
     <row r="95">
@@ -14660,10 +14370,7 @@
         <v>-0.9410150891632374</v>
       </c>
       <c r="AZ95" t="n">
-        <v>0.3639814907180162</v>
-      </c>
-      <c r="BA95" t="n">
-        <v>16.21005166131244</v>
+        <v>3.639814907180162</v>
       </c>
     </row>
     <row r="96">
@@ -14829,10 +14536,7 @@
         <v>-0.8697027197975964</v>
       </c>
       <c r="AZ96" t="n">
-        <v>0.2754165199655664</v>
-      </c>
-      <c r="BA96" t="n">
-        <v>11.5432612977339</v>
+        <v>2.754165199655663</v>
       </c>
     </row>
     <row r="97">
@@ -14998,10 +14702,7 @@
         <v>-0.8926196808510639</v>
       </c>
       <c r="AZ97" t="n">
-        <v>0.2635851161810385</v>
-      </c>
-      <c r="BA97" t="n">
-        <v>18.63708247181081</v>
+        <v>2.635851161810386</v>
       </c>
     </row>
     <row r="98">
@@ -15167,10 +14868,7 @@
         <v>-0.9120214909335124</v>
       </c>
       <c r="AZ98" t="n">
-        <v>0.2379812101557392</v>
-      </c>
-      <c r="BA98" t="n">
-        <v>13.36431271950471</v>
+        <v>2.379812101557392</v>
       </c>
     </row>
     <row r="99">
@@ -15336,10 +15034,7 @@
         <v>-0.9579330904272938</v>
       </c>
       <c r="AZ99" t="n">
-        <v>0.1937192235493845</v>
-      </c>
-      <c r="BA99" t="n">
-        <v>10.8080729022015</v>
+        <v>1.937192235493844</v>
       </c>
     </row>
     <row r="100">
@@ -15505,10 +15200,7 @@
         <v>-0.8845169545745361</v>
       </c>
       <c r="AZ100" t="n">
-        <v>0.1937567807703534</v>
-      </c>
-      <c r="BA100" t="n">
-        <v>12.77530493515518</v>
+        <v>1.937567807703533</v>
       </c>
     </row>
     <row r="101">
@@ -15674,10 +15366,7 @@
         <v>-0.8345370978332239</v>
       </c>
       <c r="AZ101" t="n">
-        <v>0.2390186769233919</v>
-      </c>
-      <c r="BA101" t="n">
-        <v>14.95225993840202</v>
+        <v>2.390186769233919</v>
       </c>
     </row>
     <row r="102">
@@ -15843,10 +15532,7 @@
         <v>-0.8655913978494624</v>
       </c>
       <c r="AZ102" t="n">
-        <v>0.3022826134073608</v>
-      </c>
-      <c r="BA102" t="n">
-        <v>14.56543934132861</v>
+        <v>3.022826134073608</v>
       </c>
     </row>
     <row r="103">
@@ -16012,10 +15698,7 @@
         <v>-0.8713188220230473</v>
       </c>
       <c r="AZ103" t="n">
-        <v>0.2697981424651091</v>
-      </c>
-      <c r="BA103" t="n">
-        <v>13.085308400592</v>
+        <v>2.697981424651091</v>
       </c>
     </row>
     <row r="104">
@@ -16181,10 +15864,7 @@
         <v>-0.873405299313052</v>
       </c>
       <c r="AZ104" t="n">
-        <v>0.3273385634947573</v>
-      </c>
-      <c r="BA104" t="n">
-        <v>13.77626263997392</v>
+        <v>3.273385634947574</v>
       </c>
     </row>
     <row r="105">
@@ -16350,10 +16030,7 @@
         <v>-0.7809629835791817</v>
       </c>
       <c r="AZ105" t="n">
-        <v>0.2627407067212578</v>
-      </c>
-      <c r="BA105" t="n">
-        <v>13.64813509985642</v>
+        <v>2.627407067212578</v>
       </c>
     </row>
     <row r="106">
@@ -16519,10 +16196,7 @@
         <v>-0.9106683804627249</v>
       </c>
       <c r="AZ106" t="n">
-        <v>0.2253565398386968</v>
-      </c>
-      <c r="BA106" t="n">
-        <v>12.53521760130511</v>
+        <v>2.253565398386967</v>
       </c>
     </row>
     <row r="107">
@@ -16688,10 +16362,7 @@
         <v>-0.840602950609365</v>
       </c>
       <c r="AZ107" t="n">
-        <v>0.2310070069738794</v>
-      </c>
-      <c r="BA107" t="n">
-        <v>13.61822728292262</v>
+        <v>2.310070069738794</v>
       </c>
     </row>
     <row r="108">
@@ -16857,10 +16528,7 @@
         <v>-0.9048231511254019</v>
       </c>
       <c r="AZ108" t="n">
-        <v>0.2004180823301927</v>
-      </c>
-      <c r="BA108" t="n">
-        <v>12.36377526016233</v>
+        <v>2.004180823301927</v>
       </c>
     </row>
     <row r="109">
@@ -17026,10 +16694,7 @@
         <v>-0.8401015228426396</v>
       </c>
       <c r="AZ109" t="n">
-        <v>0.3164054433208752</v>
-      </c>
-      <c r="BA109" t="n">
-        <v>13.4521818706214</v>
+        <v>3.164054433208753</v>
       </c>
     </row>
     <row r="110">
@@ -17195,10 +16860,7 @@
         <v>-0.9122807017543859</v>
       </c>
       <c r="AZ110" t="n">
-        <v>0.3143298872640892</v>
-      </c>
-      <c r="BA110" t="n">
-        <v>13.71728615868613</v>
+        <v>3.143298872640891</v>
       </c>
     </row>
     <row r="111">
@@ -17364,10 +17026,7 @@
         <v>-0.9649181423321083</v>
       </c>
       <c r="AZ111" t="n">
-        <v>0.2727743536270423</v>
-      </c>
-      <c r="BA111" t="n">
-        <v>13.16711084989783</v>
+        <v>2.727743536270423</v>
       </c>
     </row>
     <row r="112">
@@ -17533,10 +17192,7 @@
         <v>-0.9372869802317655</v>
       </c>
       <c r="AZ112" t="n">
-        <v>0.2677287744794695</v>
-      </c>
-      <c r="BA112" t="n">
-        <v>14.90856583514423</v>
+        <v>2.677287744794695</v>
       </c>
     </row>
     <row r="113">
@@ -17702,10 +17358,7 @@
         <v>-0.8688741721854304</v>
       </c>
       <c r="AZ113" t="n">
-        <v>0.2699350840327465</v>
-      </c>
-      <c r="BA113" t="n">
-        <v>12.56625000971446</v>
+        <v>2.699350840327465</v>
       </c>
     </row>
     <row r="114">
@@ -17871,10 +17524,7 @@
         <v>-0.821639344262295</v>
       </c>
       <c r="AZ114" t="n">
-        <v>0.4709552277566549</v>
-      </c>
-      <c r="BA114" t="n">
-        <v>13.55543529737596</v>
+        <v>4.70955227756655</v>
       </c>
     </row>
     <row r="115">
@@ -18040,10 +17690,7 @@
         <v>-1.043353636689359</v>
       </c>
       <c r="AZ115" t="n">
-        <v>0.3439129986152255</v>
-      </c>
-      <c r="BA115" t="n">
-        <v>13.8462674929608</v>
+        <v>3.439129986152254</v>
       </c>
     </row>
     <row r="116">
@@ -18209,10 +17856,7 @@
         <v>-1.023550087873462</v>
       </c>
       <c r="AZ116" t="n">
-        <v>0.3494573532195661</v>
-      </c>
-      <c r="BA116" t="n">
-        <v>14.06948853210919</v>
+        <v>3.494573532195661</v>
       </c>
     </row>
     <row r="117">
@@ -18378,10 +18022,7 @@
         <v>-0.9992862241256246</v>
       </c>
       <c r="AZ117" t="n">
-        <v>0.2941786834792475</v>
-      </c>
-      <c r="BA117" t="n">
-        <v>11.36362404621276</v>
+        <v>2.941786834792475</v>
       </c>
     </row>
     <row r="118">
@@ -18547,10 +18188,7 @@
         <v>-0.9220733427362482</v>
       </c>
       <c r="AZ118" t="n">
-        <v>0.2356234081045346</v>
-      </c>
-      <c r="BA118" t="n">
-        <v>11.21671934408004</v>
+        <v>2.356234081045346</v>
       </c>
     </row>
     <row r="119">
@@ -18716,10 +18354,7 @@
         <v>-0.9540313754104341</v>
       </c>
       <c r="AZ119" t="n">
-        <v>0.2664652002443708</v>
-      </c>
-      <c r="BA119" t="n">
-        <v>12.68492545010291</v>
+        <v>2.664652002443708</v>
       </c>
     </row>
     <row r="120">
@@ -18885,10 +18520,7 @@
         <v>-0.8568159529257928</v>
       </c>
       <c r="AZ120" t="n">
-        <v>0.4458705469717965</v>
-      </c>
-      <c r="BA120" t="n">
-        <v>16.98593273105596</v>
+        <v>4.458705469717965</v>
       </c>
     </row>
     <row r="121">
@@ -19054,10 +18686,7 @@
         <v>-0.8646491519787163</v>
       </c>
       <c r="AZ121" t="n">
-        <v>0.4809162989997219</v>
-      </c>
-      <c r="BA121" t="n">
-        <v>17.24069091284437</v>
+        <v>4.809162989997219</v>
       </c>
     </row>
     <row r="122">
@@ -19223,10 +18852,7 @@
         <v>-0.8040981061782054</v>
       </c>
       <c r="AZ122" t="n">
-        <v>0.2754411937467637</v>
-      </c>
-      <c r="BA122" t="n">
-        <v>12.9142850910087</v>
+        <v>2.754411937467637</v>
       </c>
     </row>
     <row r="123">
@@ -19392,10 +19018,7 @@
         <v>-0.9652323580034423</v>
       </c>
       <c r="AZ123" t="n">
-        <v>0.2712645733328085</v>
-      </c>
-      <c r="BA123" t="n">
-        <v>13.89093963768983</v>
+        <v>2.712645733328085</v>
       </c>
     </row>
     <row r="124">
@@ -19561,10 +19184,7 @@
         <v>-0.9461077844311376</v>
       </c>
       <c r="AZ124" t="n">
-        <v>0.3551411071187895</v>
-      </c>
-      <c r="BA124" t="n">
-        <v>15.89478030353562</v>
+        <v>3.551411071187895</v>
       </c>
     </row>
     <row r="125">
@@ -19730,10 +19350,7 @@
         <v>-0.9985683607730851</v>
       </c>
       <c r="AZ125" t="n">
-        <v>0.307205325190028</v>
-      </c>
-      <c r="BA125" t="n">
-        <v>11.82301848502743</v>
+        <v>3.07205325190028</v>
       </c>
     </row>
     <row r="126">
@@ -19899,10 +19516,7 @@
         <v>-0.8554932365555923</v>
       </c>
       <c r="AZ126" t="n">
-        <v>0.3403595277379776</v>
-      </c>
-      <c r="BA126" t="n">
-        <v>12.94346879140066</v>
+        <v>3.403595277379776</v>
       </c>
     </row>
     <row r="127">
@@ -20068,10 +19682,7 @@
         <v>-0.8341742347796839</v>
       </c>
       <c r="AZ127" t="n">
-        <v>0.3160063990834164</v>
-      </c>
-      <c r="BA127" t="n">
-        <v>13.49082394850428</v>
+        <v>3.160063990834163</v>
       </c>
     </row>
     <row r="128">
@@ -20237,10 +19848,7 @@
         <v>-0.8899897505978819</v>
       </c>
       <c r="AZ128" t="n">
-        <v>0.3483273407058165</v>
-      </c>
-      <c r="BA128" t="n">
-        <v>14.95178371289261</v>
+        <v>3.483273407058165</v>
       </c>
     </row>
     <row r="129">
@@ -20406,10 +20014,7 @@
         <v>-0.9594183293878932</v>
       </c>
       <c r="AZ129" t="n">
-        <v>0.3335399262952408</v>
-      </c>
-      <c r="BA129" t="n">
-        <v>13.39656411771</v>
+        <v>3.335399262952408</v>
       </c>
     </row>
     <row r="130">
@@ -20575,10 +20180,7 @@
         <v>-0.8095535435529191</v>
       </c>
       <c r="AZ130" t="n">
-        <v>0.2816077793273518</v>
-      </c>
-      <c r="BA130" t="n">
-        <v>15.24780589347843</v>
+        <v>2.816077793273518</v>
       </c>
     </row>
     <row r="131">
@@ -20744,10 +20346,7 @@
         <v>-0.8061192631907587</v>
       </c>
       <c r="AZ131" t="n">
-        <v>0.2283823895902871</v>
-      </c>
-      <c r="BA131" t="n">
-        <v>12.36588830848125</v>
+        <v>2.283823895902871</v>
       </c>
     </row>
     <row r="132">
@@ -20913,10 +20512,7 @@
         <v>-0.9432647644326476</v>
       </c>
       <c r="AZ132" t="n">
-        <v>0.4425021074703185</v>
-      </c>
-      <c r="BA132" t="n">
-        <v>15.32398352756091</v>
+        <v>4.425021074703185</v>
       </c>
     </row>
     <row r="133">
@@ -21082,10 +20678,7 @@
         <v>-0.9047947568126941</v>
       </c>
       <c r="AZ133" t="n">
-        <v>0.3424239972728017</v>
-      </c>
-      <c r="BA133" t="n">
-        <v>15.37482698512445</v>
+        <v>3.424239972728016</v>
       </c>
     </row>
     <row r="134">
@@ -21251,10 +20844,7 @@
         <v>-0.925575101488498</v>
       </c>
       <c r="AZ134" t="n">
-        <v>0.2877727947098655</v>
-      </c>
-      <c r="BA134" t="n">
-        <v>12.64306724710941</v>
+        <v>2.877727947098654</v>
       </c>
     </row>
     <row r="135">
@@ -21420,10 +21010,7 @@
         <v>-0.8729547641963427</v>
       </c>
       <c r="AZ135" t="n">
-        <v>0.2286543990281047</v>
-      </c>
-      <c r="BA135" t="n">
-        <v>14.34571921902312</v>
+        <v>2.286543990281047</v>
       </c>
     </row>
     <row r="136">
@@ -21589,10 +21176,7 @@
         <v>-0.8111718275652702</v>
       </c>
       <c r="AZ136" t="n">
-        <v>0.212522899192218</v>
-      </c>
-      <c r="BA136" t="n">
-        <v>12.07681251870081</v>
+        <v>2.12522899192218</v>
       </c>
     </row>
     <row r="137">
@@ -21758,10 +21342,7 @@
         <v>-0.9191253037139883</v>
       </c>
       <c r="AZ137" t="n">
-        <v>0.2487492359828174</v>
-      </c>
-      <c r="BA137" t="n">
-        <v>12.92788698041661</v>
+        <v>2.487492359828174</v>
       </c>
     </row>
     <row r="138">
@@ -21927,10 +21508,7 @@
         <v>-0.983991462113127</v>
       </c>
       <c r="AZ138" t="n">
-        <v>0.3634267201648407</v>
-      </c>
-      <c r="BA138" t="n">
-        <v>12.61555674855043</v>
+        <v>3.634267201648408</v>
       </c>
     </row>
     <row r="139">
@@ -21975,7 +21553,7 @@
         <v>-30.32987330795573</v>
       </c>
       <c r="K139" t="n">
-        <v>0.02957614146330922</v>
+        <v>0.0117556</v>
       </c>
       <c r="L139" t="n">
         <v>2.373333643299183</v>
@@ -22090,16 +21668,13 @@
         <v>0.5165860400829302</v>
       </c>
       <c r="AX139" t="n">
-        <v>16.82978356315537</v>
+        <v>42.34237805477897</v>
       </c>
       <c r="AY139" t="n">
         <v>-0.8676616915422886</v>
       </c>
       <c r="AZ139" t="n">
-        <v>0.887896060770315</v>
-      </c>
-      <c r="BA139" t="n">
-        <v>14.94309852934265</v>
+        <v>3.529111782529205</v>
       </c>
     </row>
     <row r="140">
@@ -22265,10 +21840,7 @@
         <v>-0.9794520547945206</v>
       </c>
       <c r="AZ140" t="n">
-        <v>0.2763025421902743</v>
-      </c>
-      <c r="BA140" t="n">
-        <v>13.50197279742473</v>
+        <v>2.763025421902743</v>
       </c>
     </row>
     <row r="141">
@@ -22434,10 +22006,7 @@
         <v>-0.8755935422602089</v>
       </c>
       <c r="AZ141" t="n">
-        <v>0.3071371534917146</v>
-      </c>
-      <c r="BA141" t="n">
-        <v>14.89304857028718</v>
+        <v>3.071371534917147</v>
       </c>
     </row>
     <row r="142">
@@ -22603,10 +22172,7 @@
         <v>-0.8558154437680231</v>
       </c>
       <c r="AZ142" t="n">
-        <v>0.2351665444744986</v>
-      </c>
-      <c r="BA142" t="n">
-        <v>12.33569292798704</v>
+        <v>2.351665444744986</v>
       </c>
     </row>
     <row r="143">
@@ -22772,10 +22338,7 @@
         <v>-0.910299003322259</v>
       </c>
       <c r="AZ143" t="n">
-        <v>0.2634069568539765</v>
-      </c>
-      <c r="BA143" t="n">
-        <v>13.20241292636161</v>
+        <v>2.634069568539765</v>
       </c>
     </row>
     <row r="144">
@@ -22941,10 +22504,7 @@
         <v>-0.8479307025986524</v>
       </c>
       <c r="AZ144" t="n">
-        <v>0.2850083474322018</v>
-      </c>
-      <c r="BA144" t="n">
-        <v>14.72041205661443</v>
+        <v>2.850083474322018</v>
       </c>
     </row>
     <row r="145">
@@ -23110,10 +22670,7 @@
         <v>-0.9031939413895291</v>
       </c>
       <c r="AZ145" t="n">
-        <v>0.3306302943724049</v>
-      </c>
-      <c r="BA145" t="n">
-        <v>13.50483650630982</v>
+        <v>3.306302943724048</v>
       </c>
     </row>
     <row r="146">
@@ -23279,10 +22836,7 @@
         <v>-0.8867924528301887</v>
       </c>
       <c r="AZ146" t="n">
-        <v>0.3753925003975221</v>
-      </c>
-      <c r="BA146" t="n">
-        <v>14.04704424717668</v>
+        <v>3.753925003975221</v>
       </c>
     </row>
     <row r="147">
@@ -23448,10 +23002,7 @@
         <v>-0.9927797833935018</v>
       </c>
       <c r="AZ147" t="n">
-        <v>0.275498874631122</v>
-      </c>
-      <c r="BA147" t="n">
-        <v>12.39357609552841</v>
+        <v>2.754988746311219</v>
       </c>
     </row>
     <row r="148">
@@ -23617,10 +23168,7 @@
         <v>-0.8752424046541692</v>
       </c>
       <c r="AZ148" t="n">
-        <v>0.204352754630459</v>
-      </c>
-      <c r="BA148" t="n">
-        <v>12.73705359648974</v>
+        <v>2.043527546304591</v>
       </c>
     </row>
     <row r="149">
@@ -23786,10 +23334,7 @@
         <v>-0.9457209457209457</v>
       </c>
       <c r="AZ149" t="n">
-        <v>0.1613708822578354</v>
-      </c>
-      <c r="BA149" t="n">
-        <v>10.17299216629021</v>
+        <v>1.613708822578354</v>
       </c>
     </row>
     <row r="150">
@@ -23955,10 +23500,7 @@
         <v>-0.8900032351989647</v>
       </c>
       <c r="AZ150" t="n">
-        <v>0.2776338886342699</v>
-      </c>
-      <c r="BA150" t="n">
-        <v>15.42719268663395</v>
+        <v>2.776338886342698</v>
       </c>
     </row>
     <row r="151">
@@ -24124,10 +23666,7 @@
         <v>-0.9144542772861356</v>
       </c>
       <c r="AZ151" t="n">
-        <v>0.1992943083149607</v>
-      </c>
-      <c r="BA151" t="n">
-        <v>12.29805279278685</v>
+        <v>1.992943083149608</v>
       </c>
     </row>
     <row r="152">
@@ -24293,10 +23832,7 @@
         <v>-0.870988867059594</v>
       </c>
       <c r="AZ152" t="n">
-        <v>0.2929222953305048</v>
-      </c>
-      <c r="BA152" t="n">
-        <v>13.84738554555246</v>
+        <v>2.929222953305048</v>
       </c>
     </row>
     <row r="153">
@@ -24462,10 +23998,7 @@
         <v>-0.9734422880490295</v>
       </c>
       <c r="AZ153" t="n">
-        <v>0.278928268195533</v>
-      </c>
-      <c r="BA153" t="n">
-        <v>12.99811599897735</v>
+        <v>2.78928268195533</v>
       </c>
     </row>
     <row r="154">
@@ -24631,10 +24164,7 @@
         <v>-0.8216748768472907</v>
       </c>
       <c r="AZ154" t="n">
-        <v>0.3594130595075935</v>
-      </c>
-      <c r="BA154" t="n">
-        <v>13.08294443919041</v>
+        <v>3.594130595075935</v>
       </c>
     </row>
     <row r="155">
@@ -24800,10 +24330,7 @@
         <v>-0.8612735542560104</v>
       </c>
       <c r="AZ155" t="n">
-        <v>0.2320891755316213</v>
-      </c>
-      <c r="BA155" t="n">
-        <v>12.9060602060763</v>
+        <v>2.320891755316213</v>
       </c>
     </row>
     <row r="156">
@@ -24969,10 +24496,7 @@
         <v>-1.018099547511312</v>
       </c>
       <c r="AZ156" t="n">
-        <v>0.3462797777914783</v>
-      </c>
-      <c r="BA156" t="n">
-        <v>14.93215294918606</v>
+        <v>3.462797777914784</v>
       </c>
     </row>
     <row r="157">
@@ -25138,10 +24662,7 @@
         <v>-1.04876299749014</v>
       </c>
       <c r="AZ157" t="n">
-        <v>0.3554401383644461</v>
-      </c>
-      <c r="BA157" t="n">
-        <v>15.32716274738345</v>
+        <v>3.554401383644462</v>
       </c>
     </row>
     <row r="158">
@@ -25307,10 +24828,7 @@
         <v>-0.8695652173913042</v>
       </c>
       <c r="AZ158" t="n">
-        <v>0.3274162961093018</v>
-      </c>
-      <c r="BA158" t="n">
-        <v>13.30667483923764</v>
+        <v>3.274162961093018</v>
       </c>
     </row>
     <row r="159">
@@ -25472,10 +24990,7 @@
       </c>
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="n">
-        <v>0.3352256061133059</v>
-      </c>
-      <c r="BA159" t="n">
-        <v>13.36339572806621</v>
+        <v>3.352256061133059</v>
       </c>
     </row>
     <row r="160">
@@ -25637,10 +25152,7 @@
       </c>
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="n">
-        <v>0.2434472726667247</v>
-      </c>
-      <c r="BA160" t="n">
-        <v>12.29154143560339</v>
+        <v>2.434472726667246</v>
       </c>
     </row>
     <row r="161">
@@ -25806,10 +25318,7 @@
         <v>-0.9148648648648647</v>
       </c>
       <c r="AZ161" t="n">
-        <v>0.2193729066609965</v>
-      </c>
-      <c r="BA161" t="n">
-        <v>11.64590440849937</v>
+        <v>2.193729066609965</v>
       </c>
     </row>
     <row r="162">
@@ -25975,10 +25484,7 @@
         <v>-0.875</v>
       </c>
       <c r="AZ162" t="n">
-        <v>0.2693134402703707</v>
-      </c>
-      <c r="BA162" t="n">
-        <v>12.17300558723502</v>
+        <v>2.693134402703707</v>
       </c>
     </row>
     <row r="163">
@@ -26144,10 +25650,7 @@
         <v>-0.9019350606756315</v>
       </c>
       <c r="AZ163" t="n">
-        <v>0.2786500146224659</v>
-      </c>
-      <c r="BA163" t="n">
-        <v>13.42169439208957</v>
+        <v>2.786500146224659</v>
       </c>
     </row>
     <row r="164">
@@ -26313,10 +25816,7 @@
         <v>-0.8602257636122178</v>
       </c>
       <c r="AZ164" t="n">
-        <v>0.3302696303234725</v>
-      </c>
-      <c r="BA164" t="n">
-        <v>14.07419437917497</v>
+        <v>3.302696303234725</v>
       </c>
     </row>
     <row r="165">
@@ -26482,10 +25982,7 @@
         <v>-0.8340425531914893</v>
       </c>
       <c r="AZ165" t="n">
-        <v>0.3140509103601919</v>
-      </c>
-      <c r="BA165" t="n">
-        <v>13.33772096173453</v>
+        <v>3.140509103601919</v>
       </c>
     </row>
     <row r="166">
@@ -26651,10 +26148,7 @@
         <v>-0.9123961218836566</v>
       </c>
       <c r="AZ166" t="n">
-        <v>0.4419867263324095</v>
-      </c>
-      <c r="BA166" t="n">
-        <v>16.97539046167085</v>
+        <v>4.419867263324095</v>
       </c>
     </row>
     <row r="167">
@@ -26820,10 +26314,7 @@
         <v>-0.9287135278514589</v>
       </c>
       <c r="AZ167" t="n">
-        <v>0.2822534280040117</v>
-      </c>
-      <c r="BA167" t="n">
-        <v>11.65132875248652</v>
+        <v>2.822534280040117</v>
       </c>
     </row>
     <row r="168">
@@ -26989,10 +26480,7 @@
         <v>-0.794580970384373</v>
       </c>
       <c r="AZ168" t="n">
-        <v>0.3720589980627997</v>
-      </c>
-      <c r="BA168" t="n">
-        <v>15.11954301763624</v>
+        <v>3.720589980627997</v>
       </c>
     </row>
     <row r="169">
@@ -27158,10 +26646,7 @@
         <v>-0.8666886109282422</v>
       </c>
       <c r="AZ169" t="n">
-        <v>0.3370510290002701</v>
-      </c>
-      <c r="BA169" t="n">
-        <v>12.83721020627359</v>
+        <v>3.370510290002701</v>
       </c>
     </row>
     <row r="170">
@@ -27327,10 +26812,7 @@
         <v>-0.8734652114597544</v>
       </c>
       <c r="AZ170" t="n">
-        <v>0.3618600999053327</v>
-      </c>
-      <c r="BA170" t="n">
-        <v>15.67979022827618</v>
+        <v>3.618600999053328</v>
       </c>
     </row>
     <row r="171">
@@ -27496,10 +26978,7 @@
         <v>-0.9163306451612903</v>
       </c>
       <c r="AZ171" t="n">
-        <v>0.254785183807967</v>
-      </c>
-      <c r="BA171" t="n">
-        <v>11.61765076524852</v>
+        <v>2.547851838079669</v>
       </c>
     </row>
     <row r="172">
@@ -27665,10 +27144,7 @@
         <v>-0.8450749123366273</v>
       </c>
       <c r="AZ172" t="n">
-        <v>0.3188696860136649</v>
-      </c>
-      <c r="BA172" t="n">
-        <v>14.69626650381366</v>
+        <v>3.18869686013665</v>
       </c>
     </row>
     <row r="173">
@@ -27834,10 +27310,7 @@
         <v>-0.8522613065326633</v>
       </c>
       <c r="AZ173" t="n">
-        <v>0.399707243754127</v>
-      </c>
-      <c r="BA173" t="n">
-        <v>12.47173871860493</v>
+        <v>3.99707243754127</v>
       </c>
     </row>
     <row r="174">
@@ -28003,10 +27476,7 @@
         <v>-0.9190476190476191</v>
       </c>
       <c r="AZ174" t="n">
-        <v>0.3801718619146223</v>
-      </c>
-      <c r="BA174" t="n">
-        <v>14.2475185393632</v>
+        <v>3.801718619146223</v>
       </c>
     </row>
     <row r="175">
@@ -28172,10 +27642,7 @@
         <v>-0.8253346392425727</v>
       </c>
       <c r="AZ175" t="n">
-        <v>0.2470312536106503</v>
-      </c>
-      <c r="BA175" t="n">
-        <v>11.3388765448196</v>
+        <v>2.470312536106503</v>
       </c>
     </row>
     <row r="176">
@@ -28341,10 +27808,7 @@
         <v>-0.8593242365172189</v>
       </c>
       <c r="AZ176" t="n">
-        <v>0.2303895675632164</v>
-      </c>
-      <c r="BA176" t="n">
-        <v>10.92082410889718</v>
+        <v>2.303895675632163</v>
       </c>
     </row>
     <row r="177">
@@ -28510,10 +27974,7 @@
         <v>-1.011280931586608</v>
       </c>
       <c r="AZ177" t="n">
-        <v>0.2939442645614514</v>
-      </c>
-      <c r="BA177" t="n">
-        <v>13.1516753899925</v>
+        <v>2.939442645614514</v>
       </c>
     </row>
     <row r="178">
@@ -28679,10 +28140,7 @@
         <v>-0.8638230647709321</v>
       </c>
       <c r="AZ178" t="n">
-        <v>0.3054467120359153</v>
-      </c>
-      <c r="BA178" t="n">
-        <v>13.45013914035445</v>
+        <v>3.054467120359153</v>
       </c>
     </row>
     <row r="179">
@@ -28848,10 +28306,7 @@
         <v>-0.8194444444444445</v>
       </c>
       <c r="AZ179" t="n">
-        <v>0.2464363334952325</v>
-      </c>
-      <c r="BA179" t="n">
-        <v>13.35702874314139</v>
+        <v>2.464363334952325</v>
       </c>
     </row>
     <row r="180">
@@ -29017,10 +28472,7 @@
         <v>-0.8907371167645139</v>
       </c>
       <c r="AZ180" t="n">
-        <v>0.3280651598232026</v>
-      </c>
-      <c r="BA180" t="n">
-        <v>12.92183174935129</v>
+        <v>3.280651598232026</v>
       </c>
     </row>
     <row r="181">
@@ -29186,10 +28638,7 @@
         <v>-0.9359058207979072</v>
       </c>
       <c r="AZ181" t="n">
-        <v>0.3562090494563998</v>
-      </c>
-      <c r="BA181" t="n">
-        <v>15.23965851812918</v>
+        <v>3.562090494563997</v>
       </c>
     </row>
   </sheetData>

--- a/Results_isofys/Numex_preliminar_base.xlsx
+++ b/Results_isofys/Numex_preliminar_base.xlsx
@@ -904,13 +904,13 @@
         <v>0.586048687666667</v>
       </c>
       <c r="BE2" t="n">
-        <v>1583.411527786951</v>
+        <v>1.583411527786951</v>
       </c>
       <c r="BF2" t="n">
-        <v>62678.6295709413</v>
+        <v>62.6786295709413</v>
       </c>
       <c r="BG2" t="n">
-        <v>81.98919152048342</v>
+        <v>0.08198919152048342</v>
       </c>
       <c r="BH2" t="n">
         <v>764.4742972649296</v>
@@ -1089,13 +1089,13 @@
         <v>0.827745731739708</v>
       </c>
       <c r="BE3" t="n">
-        <v>1927.929018543231</v>
+        <v>1.927929018543231</v>
       </c>
       <c r="BF3" t="n">
-        <v>49313.98966307422</v>
+        <v>49.31398966307422</v>
       </c>
       <c r="BG3" t="n">
-        <v>85.97204781478952</v>
+        <v>0.08597204781478951</v>
       </c>
       <c r="BH3" t="n">
         <v>573.6049206285264</v>
@@ -1274,13 +1274,13 @@
         <v>0.586801039508632</v>
       </c>
       <c r="BE4" t="n">
-        <v>1459.443363957555</v>
+        <v>1.459443363957555</v>
       </c>
       <c r="BF4" t="n">
-        <v>62014.10491775165</v>
+        <v>62.01410491775165</v>
       </c>
       <c r="BG4" t="n">
-        <v>80.23105743376664</v>
+        <v>0.08023105743376663</v>
       </c>
       <c r="BH4" t="n">
         <v>772.9438811017334</v>
@@ -1459,13 +1459,13 @@
         <v>0.7090190245683931</v>
       </c>
       <c r="BE5" t="n">
-        <v>2308.390026071944</v>
+        <v>2.308390026071944</v>
       </c>
       <c r="BF5" t="n">
-        <v>68039.66990152447</v>
+        <v>68.03966990152448</v>
       </c>
       <c r="BG5" t="n">
-        <v>102.5630023455334</v>
+        <v>0.1025630023455334</v>
       </c>
       <c r="BH5" t="n">
         <v>663.3938978531428</v>
@@ -1644,13 +1644,13 @@
         <v>0.629324291421087</v>
       </c>
       <c r="BE6" t="n">
-        <v>1972.952651382424</v>
+        <v>1.972952651382424</v>
       </c>
       <c r="BF6" t="n">
-        <v>58140.10355624786</v>
+        <v>58.14010355624787</v>
       </c>
       <c r="BG6" t="n">
-        <v>76.36880331298339</v>
+        <v>0.07636880331298337</v>
       </c>
       <c r="BH6" t="n">
         <v>761.3069870686782</v>
@@ -1829,13 +1829,13 @@
         <v>0.85184102744709</v>
       </c>
       <c r="BE7" t="n">
-        <v>2411.024955423218</v>
+        <v>2.411024955423218</v>
       </c>
       <c r="BF7" t="n">
-        <v>63936.67365779264</v>
+        <v>63.93667365779265</v>
       </c>
       <c r="BG7" t="n">
-        <v>125.6379244892002</v>
+        <v>0.1256379244892002</v>
       </c>
       <c r="BH7" t="n">
         <v>508.8962900154292</v>
@@ -2014,13 +2014,13 @@
         <v>0.666581855706874</v>
       </c>
       <c r="BE8" t="n">
-        <v>2212.734935521185</v>
+        <v>2.212734935521185</v>
       </c>
       <c r="BF8" t="n">
-        <v>65829.19875238115</v>
+        <v>65.82919875238116</v>
       </c>
       <c r="BG8" t="n">
-        <v>92.64851857109888</v>
+        <v>0.09264851857109888</v>
       </c>
       <c r="BH8" t="n">
         <v>710.5261883044957</v>
@@ -2199,13 +2199,13 @@
         <v>0.525173295666667</v>
       </c>
       <c r="BE9" t="n">
-        <v>2491.330280495736</v>
+        <v>2.491330280495736</v>
       </c>
       <c r="BF9" t="n">
-        <v>70465.3963916366</v>
+        <v>70.4653963916366</v>
       </c>
       <c r="BG9" t="n">
-        <v>75.68407956598034</v>
+        <v>0.07568407956598033</v>
       </c>
       <c r="BH9" t="n">
         <v>931.0464868665787</v>
@@ -2384,13 +2384,13 @@
         <v>0.907511655978624</v>
       </c>
       <c r="BE10" t="n">
-        <v>1922.442143630735</v>
+        <v>1.922442143630735</v>
       </c>
       <c r="BF10" t="n">
-        <v>53859.76820401974</v>
+        <v>53.85976820401974</v>
       </c>
       <c r="BG10" t="n">
-        <v>101.7744649299599</v>
+        <v>0.1017744649299599</v>
       </c>
       <c r="BH10" t="n">
         <v>529.2070878592726</v>
@@ -2569,13 +2569,13 @@
         <v>0.578893611326861</v>
       </c>
       <c r="BE11" t="n">
-        <v>1541.538771183675</v>
+        <v>1.541538771183675</v>
       </c>
       <c r="BF11" t="n">
-        <v>61569.64889603419</v>
+        <v>61.56964889603419</v>
       </c>
       <c r="BG11" t="n">
-        <v>80.19603864765268</v>
+        <v>0.08019603864765268</v>
       </c>
       <c r="BH11" t="n">
         <v>767.7392790751805</v>
@@ -2754,13 +2754,13 @@
         <v>0.627050194054776</v>
       </c>
       <c r="BE12" t="n">
-        <v>1704.503359635594</v>
+        <v>1.704503359635594</v>
       </c>
       <c r="BF12" t="n">
-        <v>70453.9122144526</v>
+        <v>70.4539122144526</v>
       </c>
       <c r="BG12" t="n">
-        <v>96.68356330223143</v>
+        <v>0.09668356330223143</v>
       </c>
       <c r="BH12" t="n">
         <v>728.7062020481669</v>
@@ -2939,13 +2939,13 @@
         <v>1.21053150264026</v>
       </c>
       <c r="BE13" t="n">
-        <v>1893.086604314296</v>
+        <v>1.893086604314296</v>
       </c>
       <c r="BF13" t="n">
-        <v>62982.27944361334</v>
+        <v>62.98227944361334</v>
       </c>
       <c r="BG13" t="n">
-        <v>169.6420166821183</v>
+        <v>0.1696420166821183</v>
       </c>
       <c r="BH13" t="n">
         <v>371.265802396301</v>
@@ -3124,13 +3124,13 @@
         <v>2.15640457208089</v>
       </c>
       <c r="BE14" t="n">
-        <v>2420.263723581012</v>
+        <v>2.420263723581012</v>
       </c>
       <c r="BF14" t="n">
-        <v>59335.47349313596</v>
+        <v>59.33547349313596</v>
       </c>
       <c r="BG14" t="n">
-        <v>290.6871507126771</v>
+        <v>0.2906871507126771</v>
       </c>
       <c r="BH14" t="n">
         <v>204.1214183277908</v>
@@ -3309,13 +3309,13 @@
         <v>0.8031287501650169</v>
       </c>
       <c r="BE15" t="n">
-        <v>2262.696828216982</v>
+        <v>2.262696828216982</v>
       </c>
       <c r="BF15" t="n">
-        <v>67377.42901484933</v>
+        <v>67.37742901484933</v>
       </c>
       <c r="BG15" t="n">
-        <v>113.1241952885253</v>
+        <v>0.1131241952885253</v>
       </c>
       <c r="BH15" t="n">
         <v>595.6058192767865</v>
@@ -3494,13 +3494,13 @@
         <v>0.543376352145214</v>
       </c>
       <c r="BE16" t="n">
-        <v>2346.594974817986</v>
+        <v>2.346594974817986</v>
       </c>
       <c r="BF16" t="n">
-        <v>75854.79688556591</v>
+        <v>75.85479688556592</v>
       </c>
       <c r="BG16" t="n">
-        <v>86.60033209198477</v>
+        <v>0.08660033209198477</v>
       </c>
       <c r="BH16" t="n">
         <v>875.9180831430851</v>
@@ -3679,13 +3679,13 @@
         <v>0.614479672666667</v>
       </c>
       <c r="BE17" t="n">
-        <v>2040.293659175826</v>
+        <v>2.040293659175827</v>
       </c>
       <c r="BF17" t="n">
-        <v>57933.09073325802</v>
+        <v>57.93309073325802</v>
       </c>
       <c r="BG17" t="n">
-        <v>73.8952274288045</v>
+        <v>0.0738952274288045</v>
       </c>
       <c r="BH17" t="n">
         <v>783.9896127131425</v>
@@ -3864,13 +3864,13 @@
         <v>0.733080008530184</v>
       </c>
       <c r="BE18" t="n">
-        <v>2199.748552043699</v>
+        <v>2.199748552043698</v>
       </c>
       <c r="BF18" t="n">
-        <v>64181.04834646514</v>
+        <v>64.18104834646515</v>
       </c>
       <c r="BG18" t="n">
-        <v>97.23724315459992</v>
+        <v>0.09723724315459993</v>
       </c>
       <c r="BH18" t="n">
         <v>660.0459480779612</v>
@@ -4049,13 +4049,13 @@
         <v>0.692635240264026</v>
       </c>
       <c r="BE19" t="n">
-        <v>1804.095984933663</v>
+        <v>1.804095984933663</v>
       </c>
       <c r="BF19" t="n">
-        <v>48111.20672929789</v>
+        <v>48.11120672929789</v>
       </c>
       <c r="BG19" t="n">
-        <v>71.36813755565903</v>
+        <v>0.07136813755565903</v>
       </c>
       <c r="BH19" t="n">
         <v>674.1272559029107</v>
@@ -4234,13 +4234,13 @@
         <v>0.549719054790026</v>
       </c>
       <c r="BE20" t="n">
-        <v>2216.436966512492</v>
+        <v>2.216436966512492</v>
       </c>
       <c r="BF20" t="n">
-        <v>68165.10648324604</v>
+        <v>68.16510648324603</v>
       </c>
       <c r="BG20" t="n">
-        <v>76.53916563813738</v>
+        <v>0.07653916563813738</v>
       </c>
       <c r="BH20" t="n">
         <v>890.5911883795245</v>
@@ -4419,13 +4419,13 @@
         <v>1.16688620768229</v>
       </c>
       <c r="BE21" t="n">
-        <v>2731.252805030631</v>
+        <v>2.731252805030631</v>
       </c>
       <c r="BF21" t="n">
-        <v>62693.41168086865</v>
+        <v>62.69341168086865</v>
       </c>
       <c r="BG21" t="n">
-        <v>167.791336712078</v>
+        <v>0.1677913367120781</v>
       </c>
       <c r="BH21" t="n">
         <v>373.6391455564095</v>
@@ -4604,13 +4604,13 @@
         <v>0.472759833658854</v>
       </c>
       <c r="BE22" t="n">
-        <v>1359.691165823957</v>
+        <v>1.359691165823957</v>
       </c>
       <c r="BF22" t="n">
-        <v>72098.69586996443</v>
+        <v>72.09869586996444</v>
       </c>
       <c r="BG22" t="n">
-        <v>78.81098756214665</v>
+        <v>0.07881098756214665</v>
       </c>
       <c r="BH22" t="n">
         <v>914.8305090468607</v>
@@ -4789,13 +4789,13 @@
         <v>0.541857143239625</v>
       </c>
       <c r="BE23" t="n">
-        <v>1532.285064088778</v>
+        <v>1.532285064088778</v>
       </c>
       <c r="BF23" t="n">
-        <v>58814.77292575601</v>
+        <v>58.814772925756</v>
       </c>
       <c r="BG23" t="n">
-        <v>72.14665247249056</v>
+        <v>0.07214665247249055</v>
       </c>
       <c r="BH23" t="n">
         <v>815.2113911062197</v>
@@ -4974,13 +4974,13 @@
         <v>0.907596492739274</v>
       </c>
       <c r="BE24" t="n">
-        <v>2083.919474390169</v>
+        <v>2.083919474390169</v>
       </c>
       <c r="BF24" t="n">
-        <v>64502.69324889292</v>
+        <v>64.50269324889292</v>
       </c>
       <c r="BG24" t="n">
-        <v>133.6534991978402</v>
+        <v>0.1336534991978402</v>
       </c>
       <c r="BH24" t="n">
         <v>482.6113318096744</v>
@@ -5159,13 +5159,13 @@
         <v>0.689000921175685</v>
       </c>
       <c r="BE25" t="n">
-        <v>1924.962019984864</v>
+        <v>1.924962019984864</v>
       </c>
       <c r="BF25" t="n">
-        <v>59226.28309595306</v>
+        <v>59.22628309595306</v>
       </c>
       <c r="BG25" t="n">
-        <v>84.04879803272316</v>
+        <v>0.08404879803272315</v>
       </c>
       <c r="BH25" t="n">
         <v>704.6654382004866</v>
@@ -5344,13 +5344,13 @@
         <v>0.702029613176778</v>
       </c>
       <c r="BE26" t="n">
-        <v>1993.680458705612</v>
+        <v>1.993680458705612</v>
       </c>
       <c r="BF26" t="n">
-        <v>58198.73982352419</v>
+        <v>58.19873982352419</v>
       </c>
       <c r="BG26" t="n">
-        <v>86.06477042797445</v>
+        <v>0.08606477042797446</v>
       </c>
       <c r="BH26" t="n">
         <v>676.2202412685143</v>
@@ -5529,13 +5529,13 @@
         <v>1.17576645368558</v>
       </c>
       <c r="BE27" t="n">
-        <v>2247.906864753312</v>
+        <v>2.247906864753312</v>
       </c>
       <c r="BF27" t="n">
-        <v>43536.30630525455</v>
+        <v>43.53630630525455</v>
       </c>
       <c r="BG27" t="n">
-        <v>115.5297984473839</v>
+        <v>0.1155297984473839</v>
       </c>
       <c r="BH27" t="n">
         <v>376.8404938842028</v>
@@ -5714,13 +5714,13 @@
         <v>2.73427812416332</v>
       </c>
       <c r="BE28" t="n">
-        <v>1941.969337398241</v>
+        <v>1.941969337398241</v>
       </c>
       <c r="BF28" t="n">
-        <v>61803.18961158281</v>
+        <v>61.80318961158282</v>
       </c>
       <c r="BG28" t="n">
-        <v>392.4651391362423</v>
+        <v>0.3924651391362423</v>
       </c>
       <c r="BH28" t="n">
         <v>157.4743421736833</v>
@@ -5899,13 +5899,13 @@
         <v>1.40558051353135</v>
       </c>
       <c r="BE29" t="n">
-        <v>2299.853817964811</v>
+        <v>2.299853817964811</v>
       </c>
       <c r="BF29" t="n">
-        <v>47703.9521233669</v>
+        <v>47.7039521233669</v>
       </c>
       <c r="BG29" t="n">
-        <v>148.4202958654755</v>
+        <v>0.1484202958654755</v>
       </c>
       <c r="BH29" t="n">
         <v>321.4112453097694</v>
@@ -6084,13 +6084,13 @@
         <v>0.840966547043011</v>
       </c>
       <c r="BE30" t="n">
-        <v>2056.480718564838</v>
+        <v>2.056480718564838</v>
       </c>
       <c r="BF30" t="n">
-        <v>60032.56549989229</v>
+        <v>60.03256549989229</v>
       </c>
       <c r="BG30" t="n">
-        <v>106.5298553812398</v>
+        <v>0.1065298553812398</v>
       </c>
       <c r="BH30" t="n">
         <v>563.528085953491</v>
@@ -6269,13 +6269,13 @@
         <v>1.68222301339869</v>
       </c>
       <c r="BE31" t="n">
-        <v>1366.31885562437</v>
+        <v>1.36631885562437</v>
       </c>
       <c r="BF31" t="n">
-        <v>58714.22404388255</v>
+        <v>58.71422404388255</v>
       </c>
       <c r="BG31" t="n">
-        <v>230.0974793772151</v>
+        <v>0.2300974793772151</v>
       </c>
       <c r="BH31" t="n">
         <v>255.1710875008246</v>
@@ -6454,13 +6454,13 @@
         <v>1.12802003685584</v>
       </c>
       <c r="BE32" t="n">
-        <v>2060.536274187499</v>
+        <v>2.060536274187499</v>
       </c>
       <c r="BF32" t="n">
-        <v>42488.72527334292</v>
+        <v>42.48872527334292</v>
       </c>
       <c r="BG32" t="n">
-        <v>107.993509188816</v>
+        <v>0.107993509188816</v>
       </c>
       <c r="BH32" t="n">
         <v>393.437768551956</v>
@@ -6639,13 +6639,13 @@
         <v>1.00512667963684</v>
       </c>
       <c r="BE33" t="n">
-        <v>2140.487849336566</v>
+        <v>2.140487849336566</v>
       </c>
       <c r="BF33" t="n">
-        <v>47071.79999838402</v>
+        <v>47.07179999838402</v>
       </c>
       <c r="BG33" t="n">
-        <v>112.1486530696386</v>
+        <v>0.1121486530696386</v>
       </c>
       <c r="BH33" t="n">
         <v>419.7268420972906</v>
@@ -6824,13 +6824,13 @@
         <v>2.08665858366667</v>
       </c>
       <c r="BE34" t="n">
-        <v>1262.484116656831</v>
+        <v>1.262484116656831</v>
       </c>
       <c r="BF34" t="n">
-        <v>55387.52547725021</v>
+        <v>55.38752547725021</v>
       </c>
       <c r="BG34" t="n">
-        <v>261.6555036990323</v>
+        <v>0.2616555036990323</v>
       </c>
       <c r="BH34" t="n">
         <v>211.6811024199185</v>
@@ -7009,13 +7009,13 @@
         <v>0.774807667332003</v>
       </c>
       <c r="BE35" t="n">
-        <v>2368.53606683806</v>
+        <v>2.36853606683806</v>
       </c>
       <c r="BF35" t="n">
-        <v>57270.8070874746</v>
+        <v>57.27080708747459</v>
       </c>
       <c r="BG35" t="n">
-        <v>91.57430319646703</v>
+        <v>0.09157430319646703</v>
       </c>
       <c r="BH35" t="n">
         <v>625.4025975453355</v>
@@ -7194,13 +7194,13 @@
         <v>1.94216136813922</v>
       </c>
       <c r="BE36" t="n">
-        <v>1404.492354378129</v>
+        <v>1.404492354378129</v>
       </c>
       <c r="BF36" t="n">
-        <v>64215.80057406097</v>
+        <v>64.21580057406096</v>
       </c>
       <c r="BG36" t="n">
-        <v>287.9610376304444</v>
+        <v>0.2879610376304444</v>
       </c>
       <c r="BH36" t="n">
         <v>223.0016987800707</v>
@@ -7379,13 +7379,13 @@
         <v>0.628281845285525</v>
       </c>
       <c r="BE37" t="n">
-        <v>1657.36668134432</v>
+        <v>1.65736668134432</v>
       </c>
       <c r="BF37" t="n">
-        <v>53824.76778431748</v>
+        <v>53.82476778431748</v>
       </c>
       <c r="BG37" t="n">
-        <v>75.01750757791727</v>
+        <v>0.07501750757791728</v>
       </c>
       <c r="BH37" t="n">
         <v>717.496082210038</v>
@@ -7564,13 +7564,13 @@
         <v>0.750170432291667</v>
       </c>
       <c r="BE38" t="n">
-        <v>2537.0946862891</v>
+        <v>2.5370946862891</v>
       </c>
       <c r="BF38" t="n">
-        <v>79264.49640071606</v>
+        <v>79.26449640071606</v>
       </c>
       <c r="BG38" t="n">
-        <v>132.9760039281311</v>
+        <v>0.1329760039281311</v>
       </c>
       <c r="BH38" t="n">
         <v>596.0812030684556</v>
@@ -7749,13 +7749,13 @@
         <v>0.961635565666667</v>
       </c>
       <c r="BE39" t="n">
-        <v>1790.085898974969</v>
+        <v>1.790085898974969</v>
       </c>
       <c r="BF39" t="n">
-        <v>39902.34824028318</v>
+        <v>39.90234824028317</v>
       </c>
       <c r="BG39" t="n">
-        <v>85.81442940428201</v>
+        <v>0.08581442940428201</v>
       </c>
       <c r="BH39" t="n">
         <v>464.9841351539898</v>
@@ -7934,13 +7934,13 @@
         <v>0.672914162127108</v>
       </c>
       <c r="BE40" t="n">
-        <v>1636.334848571583</v>
+        <v>1.636334848571583</v>
       </c>
       <c r="BF40" t="n">
-        <v>67019.60533465813</v>
+        <v>67.01960533465812</v>
       </c>
       <c r="BG40" t="n">
-        <v>99.41332983713632</v>
+        <v>0.09941332983713633</v>
       </c>
       <c r="BH40" t="n">
         <v>674.1510966834412</v>
@@ -8119,13 +8119,13 @@
         <v>0.631807111000663</v>
       </c>
       <c r="BE41" t="n">
-        <v>1962.293560349081</v>
+        <v>1.962293560349081</v>
       </c>
       <c r="BF41" t="n">
-        <v>64069.93482654983</v>
+        <v>64.06993482654983</v>
       </c>
       <c r="BG41" t="n">
-        <v>84.18811911277291</v>
+        <v>0.08418811911277291</v>
       </c>
       <c r="BH41" t="n">
         <v>761.0329759324582</v>
@@ -8304,13 +8304,13 @@
         <v>0.631807111000663</v>
       </c>
       <c r="BE42" t="n">
-        <v>1962.293560349081</v>
+        <v>1.962293560349081</v>
       </c>
       <c r="BF42" t="n">
-        <v>64069.93482654983</v>
+        <v>64.06993482654983</v>
       </c>
       <c r="BG42" t="n">
-        <v>84.18811911277291</v>
+        <v>0.08418811911277291</v>
       </c>
       <c r="BH42" t="n">
         <v>761.0329759324582</v>
@@ -8489,13 +8489,13 @@
         <v>0.631807111000663</v>
       </c>
       <c r="BE43" t="n">
-        <v>1962.293560349081</v>
+        <v>1.962293560349081</v>
       </c>
       <c r="BF43" t="n">
-        <v>64069.93482654983</v>
+        <v>64.06993482654983</v>
       </c>
       <c r="BG43" t="n">
-        <v>84.18811911277291</v>
+        <v>0.08418811911277291</v>
       </c>
       <c r="BH43" t="n">
         <v>761.0329759324582</v>
@@ -8674,13 +8674,13 @@
         <v>0.631807111000663</v>
       </c>
       <c r="BE44" t="n">
-        <v>1962.293560349081</v>
+        <v>1.962293560349081</v>
       </c>
       <c r="BF44" t="n">
-        <v>64069.93482654983</v>
+        <v>64.06993482654983</v>
       </c>
       <c r="BG44" t="n">
-        <v>84.18811911277291</v>
+        <v>0.08418811911277291</v>
       </c>
       <c r="BH44" t="n">
         <v>761.0329759324582</v>
@@ -8859,13 +8859,13 @@
         <v>0.519642683828383</v>
       </c>
       <c r="BE45" t="n">
-        <v>2080.347916779913</v>
+        <v>2.080347916779913</v>
       </c>
       <c r="BF45" t="n">
-        <v>72704.77607848516</v>
+        <v>72.70477607848517</v>
       </c>
       <c r="BG45" t="n">
-        <v>68.322993604077</v>
+        <v>0.06832299360407701</v>
       </c>
       <c r="BH45" t="n">
         <v>1064.133350183688</v>
@@ -9044,13 +9044,13 @@
         <v>0.739226720261438</v>
       </c>
       <c r="BE46" t="n">
-        <v>1803.572361821152</v>
+        <v>1.803572361821152</v>
       </c>
       <c r="BF46" t="n">
-        <v>49813.58951370534</v>
+        <v>49.81358951370535</v>
       </c>
       <c r="BG46" t="n">
-        <v>90.96646912462749</v>
+        <v>0.0909664691246275</v>
       </c>
       <c r="BH46" t="n">
         <v>547.6038587961334</v>
@@ -9229,13 +9229,13 @@
         <v>0.891906181936322</v>
       </c>
       <c r="BE47" t="n">
-        <v>1563.233988308393</v>
+        <v>1.563233988308393</v>
       </c>
       <c r="BF47" t="n">
-        <v>49415.60931653564</v>
+        <v>49.41560931653564</v>
       </c>
       <c r="BG47" t="n">
-        <v>91.86950982567778</v>
+        <v>0.09186950982567778</v>
       </c>
       <c r="BH47" t="n">
         <v>537.8891147922924</v>
@@ -9414,13 +9414,13 @@
         <v>0.736298419596354</v>
       </c>
       <c r="BE48" t="n">
-        <v>1727.182447385554</v>
+        <v>1.727182447385554</v>
       </c>
       <c r="BF48" t="n">
-        <v>56276.08137299266</v>
+        <v>56.27608137299266</v>
       </c>
       <c r="BG48" t="n">
-        <v>87.61808220891884</v>
+        <v>0.08761808220891884</v>
       </c>
       <c r="BH48" t="n">
         <v>642.2884404021363</v>
@@ -9599,13 +9599,13 @@
         <v>0.659533250666667</v>
       </c>
       <c r="BE49" t="n">
-        <v>2118.768969038877</v>
+        <v>2.118768969038876</v>
       </c>
       <c r="BF49" t="n">
-        <v>78609.92204916544</v>
+        <v>78.60992204916545</v>
       </c>
       <c r="BG49" t="n">
-        <v>114.2772903664339</v>
+        <v>0.1142772903664339</v>
       </c>
       <c r="BH49" t="n">
         <v>687.8875216335649</v>
@@ -9784,13 +9784,13 @@
         <v>0.533526070957096</v>
       </c>
       <c r="BE50" t="n">
-        <v>1305.405133948935</v>
+        <v>1.305405133948935</v>
       </c>
       <c r="BF50" t="n">
-        <v>60858.78779925097</v>
+        <v>60.85878779925097</v>
       </c>
       <c r="BG50" t="n">
-        <v>77.04597268100757</v>
+        <v>0.07704597268100756</v>
       </c>
       <c r="BH50" t="n">
         <v>789.9022581131373</v>
@@ -9969,13 +9969,13 @@
         <v>0.745449478580991</v>
       </c>
       <c r="BE51" t="n">
-        <v>2749.705279828398</v>
+        <v>2.749705279828398</v>
       </c>
       <c r="BF51" t="n">
-        <v>76008.80368696366</v>
+        <v>76.00880368696366</v>
       </c>
       <c r="BG51" t="n">
-        <v>131.1078270933511</v>
+        <v>0.1311078270933511</v>
       </c>
       <c r="BH51" t="n">
         <v>579.7426848729941</v>
@@ -10154,13 +10154,13 @@
         <v>0.844184348484848</v>
       </c>
       <c r="BE52" t="n">
-        <v>2554.237568151246</v>
+        <v>2.554237568151246</v>
       </c>
       <c r="BF52" t="n">
-        <v>80296.6293999513</v>
+        <v>80.29662939995131</v>
       </c>
       <c r="BG52" t="n">
-        <v>152.4967523895981</v>
+        <v>0.1524967523895981</v>
       </c>
       <c r="BH52" t="n">
         <v>526.5464879855921</v>
@@ -10334,10 +10334,10 @@
       </c>
       <c r="BE53" t="inlineStr"/>
       <c r="BF53" t="n">
-        <v>34691.68210591955</v>
+        <v>34.69168210591955</v>
       </c>
       <c r="BG53" t="n">
-        <v>92.71228920458452</v>
+        <v>0.09271228920458452</v>
       </c>
       <c r="BH53" t="n">
         <v>374.1864471641596</v>
@@ -10514,13 +10514,13 @@
         <v>0.994744053177691</v>
       </c>
       <c r="BE54" t="n">
-        <v>2230.482700063978</v>
+        <v>2.230482700063978</v>
       </c>
       <c r="BF54" t="n">
-        <v>38341.14387266885</v>
+        <v>38.34114387266885</v>
       </c>
       <c r="BG54" t="n">
-        <v>91.07493274206992</v>
+        <v>0.09107493274206992</v>
       </c>
       <c r="BH54" t="n">
         <v>420.9845971696014</v>
@@ -10699,13 +10699,13 @@
         <v>0.737201217191601</v>
       </c>
       <c r="BE55" t="n">
-        <v>2700.331914670088</v>
+        <v>2.700331914670088</v>
       </c>
       <c r="BF55" t="n">
-        <v>92268.08188432537</v>
+        <v>92.26808188432537</v>
       </c>
       <c r="BG55" t="n">
-        <v>153.3735609526217</v>
+        <v>0.1533735609526217</v>
       </c>
       <c r="BH55" t="n">
         <v>601.5905304097862</v>
@@ -10884,13 +10884,13 @@
         <v>0.780848745701058</v>
       </c>
       <c r="BE56" t="n">
-        <v>1811.914954031918</v>
+        <v>1.811914954031918</v>
       </c>
       <c r="BF56" t="n">
-        <v>56407.59522824798</v>
+        <v>56.40759522824798</v>
       </c>
       <c r="BG56" t="n">
-        <v>92.6429867997474</v>
+        <v>0.0926429867997474</v>
       </c>
       <c r="BH56" t="n">
         <v>608.8706460876085</v>
@@ -11069,13 +11069,13 @@
         <v>0.608936419471947</v>
       </c>
       <c r="BE57" t="n">
-        <v>1485.071659290358</v>
+        <v>1.485071659290358</v>
       </c>
       <c r="BF57" t="n">
-        <v>62792.70830799232</v>
+        <v>62.79270830799231</v>
       </c>
       <c r="BG57" t="n">
-        <v>86.00555541924115</v>
+        <v>0.08600555541924114</v>
       </c>
       <c r="BH57" t="n">
         <v>730.1006080584458</v>
@@ -11254,13 +11254,13 @@
         <v>0.9247194051332031</v>
       </c>
       <c r="BE58" t="n">
-        <v>1818.05467668072</v>
+        <v>1.81805467668072</v>
       </c>
       <c r="BF58" t="n">
-        <v>55284.08572483942</v>
+        <v>55.28408572483941</v>
       </c>
       <c r="BG58" t="n">
-        <v>106.2801065910518</v>
+        <v>0.1062801065910518</v>
       </c>
       <c r="BH58" t="n">
         <v>520.1734124859641</v>
@@ -11439,13 +11439,13 @@
         <v>0.767365057856673</v>
       </c>
       <c r="BE59" t="n">
-        <v>1468.960643433882</v>
+        <v>1.468960643433882</v>
       </c>
       <c r="BF59" t="n">
-        <v>60805.98725084784</v>
+        <v>60.80598725084783</v>
       </c>
       <c r="BG59" t="n">
-        <v>100.0115293640498</v>
+        <v>0.1000115293640498</v>
       </c>
       <c r="BH59" t="n">
         <v>607.9897751539154</v>
@@ -11624,13 +11624,13 @@
         <v>0.905815394205729</v>
       </c>
       <c r="BE60" t="n">
-        <v>1640.718941643498</v>
+        <v>1.640718941643498</v>
       </c>
       <c r="BF60" t="n">
-        <v>46204.40023861259</v>
+        <v>46.20440023861259</v>
       </c>
       <c r="BG60" t="n">
-        <v>96.820681841672</v>
+        <v>0.09682068184167199</v>
       </c>
       <c r="BH60" t="n">
         <v>477.2162244650299</v>
@@ -11809,13 +11809,13 @@
         <v>1.0241003369709</v>
       </c>
       <c r="BE61" t="n">
-        <v>2324.436326842925</v>
+        <v>2.324436326842925</v>
       </c>
       <c r="BF61" t="n">
-        <v>65896.93642640406</v>
+        <v>65.89693642640407</v>
       </c>
       <c r="BG61" t="n">
-        <v>150.2198334650496</v>
+        <v>0.1502198334650496</v>
       </c>
       <c r="BH61" t="n">
         <v>438.6700138483095</v>
@@ -11994,13 +11994,13 @@
         <v>0.5485383858085811</v>
       </c>
       <c r="BE62" t="n">
-        <v>2271.852849396293</v>
+        <v>2.271852849396293</v>
       </c>
       <c r="BF62" t="n">
-        <v>81219.991100984</v>
+        <v>81.219991100984</v>
       </c>
       <c r="BG62" t="n">
-        <v>90.75866832792745</v>
+        <v>0.09075866832792745</v>
       </c>
       <c r="BH62" t="n">
         <v>894.9006480298004</v>
@@ -12179,13 +12179,13 @@
         <v>0.475137969907407</v>
       </c>
       <c r="BE63" t="n">
-        <v>2097.736888129386</v>
+        <v>2.097736888129386</v>
       </c>
       <c r="BF63" t="n">
-        <v>66593.17142649229</v>
+        <v>66.59317142649229</v>
       </c>
       <c r="BG63" t="n">
-        <v>66.70897453309414</v>
+        <v>0.06670897453309414</v>
       </c>
       <c r="BH63" t="n">
         <v>998.2640550628702</v>
@@ -12364,13 +12364,13 @@
         <v>0.475137969907407</v>
       </c>
       <c r="BE64" t="n">
-        <v>2051.731480905204</v>
+        <v>2.051731480905204</v>
       </c>
       <c r="BF64" t="n">
-        <v>67204.09857723063</v>
+        <v>67.20409857723064</v>
       </c>
       <c r="BG64" t="n">
-        <v>66.70897453309414</v>
+        <v>0.06670897453309414</v>
       </c>
       <c r="BH64" t="n">
         <v>1007.422150431811</v>
@@ -12549,13 +12549,13 @@
         <v>0.993249184926959</v>
       </c>
       <c r="BE65" t="n">
-        <v>1711.270057226029</v>
+        <v>1.71127005722603</v>
       </c>
       <c r="BF65" t="n">
-        <v>64651.41386759904</v>
+        <v>64.65141386759905</v>
       </c>
       <c r="BG65" t="n">
-        <v>140.3287181341011</v>
+        <v>0.1403287181341011</v>
       </c>
       <c r="BH65" t="n">
         <v>460.7140628607237</v>
@@ -12734,13 +12734,13 @@
         <v>1.90429296090126</v>
       </c>
       <c r="BE66" t="n">
-        <v>1264.668813853405</v>
+        <v>1.264668813853405</v>
       </c>
       <c r="BF66" t="n">
-        <v>59173.73389442117</v>
+        <v>59.17373389442116</v>
       </c>
       <c r="BG66" t="n">
-        <v>260.7374490835797</v>
+        <v>0.2607374490835797</v>
       </c>
       <c r="BH66" t="n">
         <v>226.9475831047689</v>
@@ -12919,13 +12919,13 @@
         <v>1.16583652948973</v>
       </c>
       <c r="BE67" t="n">
-        <v>1735.620252135451</v>
+        <v>1.735620252135451</v>
       </c>
       <c r="BF67" t="n">
-        <v>51302.29695978934</v>
+        <v>51.30229695978934</v>
       </c>
       <c r="BG67" t="n">
-        <v>137.0709413665789</v>
+        <v>0.1370709413665789</v>
       </c>
       <c r="BH67" t="n">
         <v>374.2755134553855</v>
@@ -13104,13 +13104,13 @@
         <v>1.36348950458415</v>
       </c>
       <c r="BE68" t="n">
-        <v>1651.892043876882</v>
+        <v>1.651892043876882</v>
       </c>
       <c r="BF68" t="n">
-        <v>46172.17165350541</v>
+        <v>46.1721716535054</v>
       </c>
       <c r="BG68" t="n">
-        <v>142.319283016586</v>
+        <v>0.1423192830165859</v>
       </c>
       <c r="BH68" t="n">
         <v>324.4266741290741</v>
@@ -13289,13 +13289,13 @@
         <v>0.82408405687048</v>
       </c>
       <c r="BE69" t="n">
-        <v>1729.739026459769</v>
+        <v>1.729739026459769</v>
       </c>
       <c r="BF69" t="n">
-        <v>41692.61023831525</v>
+        <v>41.69261023831525</v>
       </c>
       <c r="BG69" t="n">
-        <v>80.06093000193269</v>
+        <v>0.08006093000193269</v>
       </c>
       <c r="BH69" t="n">
         <v>520.7610033671701</v>
@@ -13474,13 +13474,13 @@
         <v>0.535751518300654</v>
       </c>
       <c r="BE70" t="n">
-        <v>1653.302877966243</v>
+        <v>1.653302877966243</v>
       </c>
       <c r="BF70" t="n">
-        <v>54689.10140257988</v>
+        <v>54.68910140257988</v>
       </c>
       <c r="BG70" t="n">
-        <v>68.09229172210588</v>
+        <v>0.06809229172210589</v>
       </c>
       <c r="BH70" t="n">
         <v>803.1614154767136</v>
@@ -13659,13 +13659,13 @@
         <v>0.459120420727745</v>
       </c>
       <c r="BE71" t="n">
-        <v>2245.34879706159</v>
+        <v>2.24534879706159</v>
       </c>
       <c r="BF71" t="n">
-        <v>63852.61085941602</v>
+        <v>63.85261085941602</v>
       </c>
       <c r="BG71" t="n">
-        <v>61.6838561941078</v>
+        <v>0.06168385619410779</v>
       </c>
       <c r="BH71" t="n">
         <v>1035.159193979111</v>
@@ -13844,13 +13844,13 @@
         <v>1.15668780924479</v>
       </c>
       <c r="BE72" t="n">
-        <v>1704.181532420173</v>
+        <v>1.704181532420173</v>
       </c>
       <c r="BF72" t="n">
-        <v>46455.2151410903</v>
+        <v>46.45521514109029</v>
       </c>
       <c r="BG72" t="n">
-        <v>123.2649263881841</v>
+        <v>0.1232649263881841</v>
       </c>
       <c r="BH72" t="n">
         <v>376.872939466935</v>
@@ -14029,13 +14029,13 @@
         <v>1.54303913845144</v>
       </c>
       <c r="BE73" t="n">
-        <v>1771.344004138958</v>
+        <v>1.771344004138958</v>
       </c>
       <c r="BF73" t="n">
-        <v>53177.20031155273</v>
+        <v>53.17720031155272</v>
       </c>
       <c r="BG73" t="n">
-        <v>191.2114171631317</v>
+        <v>0.1912114171631317</v>
       </c>
       <c r="BH73" t="n">
         <v>278.1068259443143</v>
@@ -14214,13 +14214,13 @@
         <v>1.41513398290598</v>
       </c>
       <c r="BE74" t="n">
-        <v>2890.653446677475</v>
+        <v>2.890653446677475</v>
       </c>
       <c r="BF74" t="n">
-        <v>76507.14677495467</v>
+        <v>76.50714677495466</v>
       </c>
       <c r="BG74" t="n">
-        <v>243.3980165400989</v>
+        <v>0.2433980165400989</v>
       </c>
       <c r="BH74" t="n">
         <v>314.3293764776855</v>
@@ -14399,13 +14399,13 @@
         <v>0.708585888888889</v>
       </c>
       <c r="BE75" t="n">
-        <v>2678.379030470969</v>
+        <v>2.678379030470969</v>
       </c>
       <c r="BF75" t="n">
-        <v>80943.94089102797</v>
+        <v>80.94394089102798</v>
       </c>
       <c r="BG75" t="n">
-        <v>120.5138510574179</v>
+        <v>0.1205138510574179</v>
       </c>
       <c r="BH75" t="n">
         <v>671.6567446879022</v>
@@ -14584,13 +14584,13 @@
         <v>0.781730154808959</v>
       </c>
       <c r="BE76" t="n">
-        <v>2020.516390549202</v>
+        <v>2.020516390549202</v>
       </c>
       <c r="BF76" t="n">
-        <v>66138.2937268838</v>
+        <v>66.1382937268838</v>
       </c>
       <c r="BG76" t="n">
-        <v>116.2431558041077</v>
+        <v>0.1162431558041077</v>
       </c>
       <c r="BH76" t="n">
         <v>568.9650566467731</v>
@@ -14769,13 +14769,13 @@
         <v>0.84443941309987</v>
       </c>
       <c r="BE77" t="n">
-        <v>2290.004233178915</v>
+        <v>2.290004233178915</v>
       </c>
       <c r="BF77" t="n">
-        <v>63798.56596163442</v>
+        <v>63.79856596163442</v>
       </c>
       <c r="BG77" t="n">
-        <v>124.8451324330222</v>
+        <v>0.1248451324330223</v>
       </c>
       <c r="BH77" t="n">
         <v>511.0216531338256</v>
@@ -14954,13 +14954,13 @@
         <v>0.8158367908299869</v>
       </c>
       <c r="BE78" t="n">
-        <v>2143.935207599353</v>
+        <v>2.143935207599353</v>
       </c>
       <c r="BF78" t="n">
-        <v>46772.53989798563</v>
+        <v>46.77253989798564</v>
       </c>
       <c r="BG78" t="n">
-        <v>88.70798703209563</v>
+        <v>0.08870798703209562</v>
       </c>
       <c r="BH78" t="n">
         <v>527.2641332855717</v>
@@ -15139,13 +15139,13 @@
         <v>0.830341156785244</v>
       </c>
       <c r="BE79" t="n">
-        <v>3250.436485054538</v>
+        <v>3.250436485054538</v>
       </c>
       <c r="BF79" t="n">
-        <v>59433.53709831833</v>
+        <v>59.43353709831833</v>
       </c>
       <c r="BG79" t="n">
-        <v>113.7751793388308</v>
+        <v>0.1137751793388307</v>
       </c>
       <c r="BH79" t="n">
         <v>522.377002116788</v>
@@ -15324,13 +15324,13 @@
         <v>0.778980451155116</v>
       </c>
       <c r="BE80" t="n">
-        <v>2998.648154876038</v>
+        <v>2.998648154876038</v>
       </c>
       <c r="BF80" t="n">
-        <v>66357.35356277657</v>
+        <v>66.35735356277657</v>
       </c>
       <c r="BG80" t="n">
-        <v>123.3753247448174</v>
+        <v>0.1233753247448174</v>
       </c>
       <c r="BH80" t="n">
         <v>537.8494743582348</v>
@@ -15509,13 +15509,13 @@
         <v>0.860931369189907</v>
       </c>
       <c r="BE81" t="n">
-        <v>2994.186256562353</v>
+        <v>2.994186256562354</v>
       </c>
       <c r="BF81" t="n">
-        <v>71524.31113667959</v>
+        <v>71.5243111366796</v>
       </c>
       <c r="BG81" t="n">
-        <v>142.3646390213997</v>
+        <v>0.1423646390213997</v>
       </c>
       <c r="BH81" t="n">
         <v>502.4022231105318</v>
@@ -15694,13 +15694,13 @@
         <v>0.56359897356091</v>
       </c>
       <c r="BE82" t="n">
-        <v>1986.099449474032</v>
+        <v>1.986099449474032</v>
       </c>
       <c r="BF82" t="n">
-        <v>58036.6638296212</v>
+        <v>58.0366638296212</v>
       </c>
       <c r="BG82" t="n">
-        <v>68.16167495226779</v>
+        <v>0.06816167495226778</v>
       </c>
       <c r="BH82" t="n">
         <v>851.4559519005818</v>
@@ -15879,13 +15879,13 @@
         <v>1.05432551060305</v>
       </c>
       <c r="BE83" t="n">
-        <v>1574.768288150041</v>
+        <v>1.574768288150041</v>
       </c>
       <c r="BF83" t="n">
-        <v>41441.99615258708</v>
+        <v>41.44199615258708</v>
       </c>
       <c r="BG83" t="n">
-        <v>99.14099335271644</v>
+        <v>0.09914099335271642</v>
       </c>
       <c r="BH83" t="n">
         <v>418.0107012358434</v>
@@ -16064,13 +16064,13 @@
         <v>0.939988653135314</v>
       </c>
       <c r="BE84" t="n">
-        <v>1625.698637855855</v>
+        <v>1.625698637855855</v>
       </c>
       <c r="BF84" t="n">
-        <v>49102.86937521602</v>
+        <v>49.10286937521602</v>
       </c>
       <c r="BG84" t="n">
-        <v>97.56221518246466</v>
+        <v>0.09756221518246466</v>
       </c>
       <c r="BH84" t="n">
         <v>503.298016382489</v>
@@ -16249,13 +16249,13 @@
         <v>0.638802563523248</v>
       </c>
       <c r="BE85" t="n">
-        <v>2261.410104794486</v>
+        <v>2.261410104794487</v>
       </c>
       <c r="BF85" t="n">
-        <v>63281.75428570905</v>
+        <v>63.28175428570905</v>
       </c>
       <c r="BG85" t="n">
-        <v>84.14982775568258</v>
+        <v>0.08414982775568258</v>
       </c>
       <c r="BH85" t="n">
         <v>752.0128795680829</v>
@@ -16434,13 +16434,13 @@
         <v>0.744430595751634</v>
       </c>
       <c r="BE86" t="n">
-        <v>2131.678007547578</v>
+        <v>2.131678007547578</v>
       </c>
       <c r="BF86" t="n">
-        <v>65226.38295327906</v>
+        <v>65.22638295327906</v>
       </c>
       <c r="BG86" t="n">
-        <v>100.5776032211469</v>
+        <v>0.1005776032211469</v>
       </c>
       <c r="BH86" t="n">
         <v>648.5179688549674</v>
@@ -16619,13 +16619,13 @@
         <v>1.02055795016502</v>
       </c>
       <c r="BE87" t="n">
-        <v>2723.142473493238</v>
+        <v>2.723142473493239</v>
       </c>
       <c r="BF87" t="n">
-        <v>73543.63492686352</v>
+        <v>73.54363492686352</v>
       </c>
       <c r="BG87" t="n">
-        <v>169.4962030644245</v>
+        <v>0.1694962030644245</v>
       </c>
       <c r="BH87" t="n">
         <v>433.8954713865184</v>
@@ -16804,13 +16804,13 @@
         <v>1.32171089713542</v>
       </c>
       <c r="BE88" t="n">
-        <v>2165.437559626952</v>
+        <v>2.165437559626953</v>
       </c>
       <c r="BF88" t="n">
-        <v>43524.89670002637</v>
+        <v>43.52489670002637</v>
       </c>
       <c r="BG88" t="n">
-        <v>130.0815175398405</v>
+        <v>0.1300815175398405</v>
       </c>
       <c r="BH88" t="n">
         <v>334.5970859134222</v>
@@ -16995,13 +16995,13 @@
         <v>0.3022689226426593</v>
       </c>
       <c r="BE89" t="n">
-        <v>2273.110803333757</v>
+        <v>2.273110803333757</v>
       </c>
       <c r="BF89" t="n">
-        <v>134993.6057389324</v>
+        <v>134.9936057389324</v>
       </c>
       <c r="BG89" t="n">
-        <v>88.48636680398482</v>
+        <v>0.08848636680398482</v>
       </c>
       <c r="BH89" t="n">
         <v>1525.586489927545</v>
@@ -17186,13 +17186,13 @@
         <v>1.663948688200762</v>
       </c>
       <c r="BE90" t="n">
-        <v>2562.349769016561</v>
+        <v>2.562349769016561</v>
       </c>
       <c r="BF90" t="n">
-        <v>141122.6797838226</v>
+        <v>141.1226797838225</v>
       </c>
       <c r="BG90" t="n">
-        <v>501.4469628804882</v>
+        <v>0.5014469628804882</v>
       </c>
       <c r="BH90" t="n">
         <v>281.4309193801157</v>
@@ -17377,13 +17377,13 @@
         <v>0.3625060659950419</v>
       </c>
       <c r="BE91" t="n">
-        <v>2747.689268163115</v>
+        <v>2.747689268163116</v>
       </c>
       <c r="BF91" t="n">
-        <v>124133.9472150039</v>
+        <v>124.1339472150039</v>
       </c>
       <c r="BG91" t="n">
-        <v>95.55605740821525</v>
+        <v>0.09555605740821525</v>
       </c>
       <c r="BH91" t="n">
         <v>1299.069369142178</v>
@@ -17568,13 +17568,13 @@
         <v>0.4849510454859731</v>
       </c>
       <c r="BE92" t="n">
-        <v>2638.257036105743</v>
+        <v>2.638257036105744</v>
       </c>
       <c r="BF92" t="n">
-        <v>114464.4073918296</v>
+        <v>114.4644073918296</v>
       </c>
       <c r="BG92" t="n">
-        <v>119.5499967120293</v>
+        <v>0.1195499967120293</v>
       </c>
       <c r="BH92" t="n">
         <v>957.4605649513329</v>
@@ -17759,13 +17759,13 @@
         <v>0.3547881208221685</v>
       </c>
       <c r="BE93" t="n">
-        <v>2205.905999210828</v>
+        <v>2.205905999210827</v>
       </c>
       <c r="BF93" t="n">
-        <v>134610.8772447198</v>
+        <v>134.6108772447198</v>
       </c>
       <c r="BG93" t="n">
-        <v>100.621858720207</v>
+        <v>0.100621858720207</v>
       </c>
       <c r="BH93" t="n">
         <v>1337.789611092595</v>
@@ -17950,13 +17950,13 @@
         <v>0.3949439937897002</v>
       </c>
       <c r="BE94" t="n">
-        <v>2899.244513121407</v>
+        <v>2.899244513121407</v>
       </c>
       <c r="BF94" t="n">
-        <v>145509.8595795598</v>
+        <v>145.5098595795598</v>
       </c>
       <c r="BG94" t="n">
-        <v>119.1322287326202</v>
+        <v>0.1191322287326202</v>
       </c>
       <c r="BH94" t="n">
         <v>1221.414734934082</v>
@@ -18141,13 +18141,13 @@
         <v>0.7511820368610592</v>
       </c>
       <c r="BE95" t="n">
-        <v>3639.814907180162</v>
+        <v>3.639814907180162</v>
       </c>
       <c r="BF95" t="n">
-        <v>162100.5166131244</v>
+        <v>162.1005166131244</v>
       </c>
       <c r="BG95" t="n">
-        <v>246.2501351629302</v>
+        <v>0.2462501351629302</v>
       </c>
       <c r="BH95" t="n">
         <v>658.2758482787081</v>
@@ -18332,13 +18332,13 @@
         <v>1.381135177865805</v>
       </c>
       <c r="BE96" t="n">
-        <v>2754.165199655664</v>
+        <v>2.754165199655664</v>
       </c>
       <c r="BF96" t="n">
-        <v>115432.612977339</v>
+        <v>115.432612977339</v>
       </c>
       <c r="BG96" t="n">
-        <v>344.6635811046561</v>
+        <v>0.3446635811046561</v>
       </c>
       <c r="BH96" t="n">
         <v>334.9138676252779</v>
@@ -18523,13 +18523,13 @@
         <v>2.442251007971658</v>
       </c>
       <c r="BE97" t="n">
-        <v>2635.851161810385</v>
+        <v>2.635851161810385</v>
       </c>
       <c r="BF97" t="n">
-        <v>186370.8247181081</v>
+        <v>186.3708247181081</v>
       </c>
       <c r="BG97" t="n">
-        <v>971.3779599734123</v>
+        <v>0.9713779599734124</v>
       </c>
       <c r="BH97" t="n">
         <v>191.862315594652</v>
@@ -18714,13 +18714,13 @@
         <v>2.513685244069834</v>
       </c>
       <c r="BE98" t="n">
-        <v>2379.812101557392</v>
+        <v>2.379812101557392</v>
       </c>
       <c r="BF98" t="n">
-        <v>133643.1271950471</v>
+        <v>133.6431271950471</v>
       </c>
       <c r="BG98" t="n">
-        <v>736.9732006727197</v>
+        <v>0.7369732006727198</v>
       </c>
       <c r="BH98" t="n">
         <v>181.3405522386102</v>
@@ -18905,13 +18905,13 @@
         <v>0.435002842237245</v>
       </c>
       <c r="BE99" t="n">
-        <v>1937.192235493844</v>
+        <v>1.937192235493844</v>
       </c>
       <c r="BF99" t="n">
-        <v>108080.729022015</v>
+        <v>108.080729022015</v>
       </c>
       <c r="BG99" t="n">
-        <v>100.2304190887461</v>
+        <v>0.1002304190887461</v>
       </c>
       <c r="BH99" t="n">
         <v>1078.322629044563</v>
@@ -19096,13 +19096,13 @@
         <v>1.128182611778521</v>
       </c>
       <c r="BE100" t="n">
-        <v>1937.567807703534</v>
+        <v>1.937567807703533</v>
       </c>
       <c r="BF100" t="n">
-        <v>127753.0493515518</v>
+        <v>127.7530493515518</v>
       </c>
       <c r="BG100" t="n">
-        <v>314.468218366653</v>
+        <v>0.314468218366653</v>
       </c>
       <c r="BH100" t="n">
         <v>406.251067325979</v>
@@ -19287,13 +19287,13 @@
         <v>0.7365982038830503</v>
       </c>
       <c r="BE101" t="n">
-        <v>4431.249649472029</v>
+        <v>4.431249649472029</v>
       </c>
       <c r="BF101" t="n">
-        <v>157281.7308080371</v>
+        <v>157.2817308080371</v>
       </c>
       <c r="BG101" t="n">
-        <v>230.407831176971</v>
+        <v>0.230407831176971</v>
       </c>
       <c r="BH101" t="n">
         <v>682.6231990666696</v>
@@ -19478,13 +19478,13 @@
         <v>0.6125897805332587</v>
       </c>
       <c r="BE102" t="n">
-        <v>2369.266782339464</v>
+        <v>2.369266782339464</v>
       </c>
       <c r="BF102" t="n">
-        <v>148213.9105150992</v>
+        <v>148.2139105150992</v>
       </c>
       <c r="BG102" t="n">
-        <v>189.9408842031573</v>
+        <v>0.1899408842031573</v>
       </c>
       <c r="BH102" t="n">
         <v>780.3159974583056</v>
@@ -19669,13 +19669,13 @@
         <v>0.4058516935832551</v>
       </c>
       <c r="BE103" t="n">
-        <v>2767.201366776576</v>
+        <v>2.767201366776576</v>
       </c>
       <c r="BF103" t="n">
-        <v>133337.1549183661</v>
+        <v>133.3371549183661</v>
       </c>
       <c r="BG103" t="n">
-        <v>115.1976622107068</v>
+        <v>0.1151976622107068</v>
       </c>
       <c r="BH103" t="n">
         <v>1157.464069665586</v>
@@ -19860,13 +19860,13 @@
         <v>0.8893053640303116</v>
       </c>
       <c r="BE104" t="n">
-        <v>2793.068603846922</v>
+        <v>2.793068603846922</v>
       </c>
       <c r="BF104" t="n">
-        <v>135464.8469089234</v>
+        <v>135.4648469089233</v>
       </c>
       <c r="BG104" t="n">
-        <v>261.3183231977535</v>
+        <v>0.2613183231977535</v>
       </c>
       <c r="BH104" t="n">
         <v>518.3901582225059</v>
@@ -20051,13 +20051,13 @@
         <v>1.433819373048095</v>
       </c>
       <c r="BE105" t="n">
-        <v>2872.854831093412</v>
+        <v>2.872854831093412</v>
       </c>
       <c r="BF105" t="n">
-        <v>140264.4284387566</v>
+        <v>140.2644284387566</v>
       </c>
       <c r="BG105" t="n">
-        <v>416.5641702066033</v>
+        <v>0.4165641702066033</v>
       </c>
       <c r="BH105" t="n">
         <v>336.7174578869558</v>
@@ -20242,13 +20242,13 @@
         <v>0.4225314752105393</v>
       </c>
       <c r="BE106" t="n">
-        <v>2999.907207031169</v>
+        <v>2.999907207031169</v>
       </c>
       <c r="BF106" t="n">
-        <v>126253.1036318729</v>
+        <v>126.2531036318729</v>
       </c>
       <c r="BG106" t="n">
-        <v>113.7859568730906</v>
+        <v>0.1137859568730906</v>
       </c>
       <c r="BH106" t="n">
         <v>1109.566655687461</v>
@@ -20433,13 +20433,13 @@
         <v>0.4239581226118181</v>
       </c>
       <c r="BE107" t="n">
-        <v>2588.902949996616</v>
+        <v>2.588902949996617</v>
       </c>
       <c r="BF107" t="n">
-        <v>134481.2445048961</v>
+        <v>134.4812445048961</v>
       </c>
       <c r="BG107" t="n">
-        <v>121.3665020885663</v>
+        <v>0.1213665020885663</v>
       </c>
       <c r="BH107" t="n">
         <v>1108.058996433459</v>
@@ -20624,13 +20624,13 @@
         <v>2.296553217814438</v>
       </c>
       <c r="BE108" t="n">
-        <v>2195.244308829524</v>
+        <v>2.195244308829523</v>
       </c>
       <c r="BF108" t="n">
-        <v>122108.1274983239</v>
+        <v>122.1081274983239</v>
       </c>
       <c r="BG108" t="n">
-        <v>602.4469470906693</v>
+        <v>0.6024469470906693</v>
       </c>
       <c r="BH108" t="n">
         <v>202.6869388051633</v>
@@ -20815,13 +20815,13 @@
         <v>2.206920483298215</v>
       </c>
       <c r="BE109" t="n">
-        <v>2371.581729527561</v>
+        <v>2.371581729527561</v>
       </c>
       <c r="BF109" t="n">
-        <v>139808.4821573612</v>
+        <v>139.8084821573613</v>
       </c>
       <c r="BG109" t="n">
-        <v>648.5978477080954</v>
+        <v>0.6485978477080955</v>
       </c>
       <c r="BH109" t="n">
         <v>215.5549585176587</v>
@@ -21006,13 +21006,13 @@
         <v>2.0718698133459</v>
       </c>
       <c r="BE110" t="n">
-        <v>2120.569899826035</v>
+        <v>2.120569899826035</v>
       </c>
       <c r="BF110" t="n">
-        <v>130817.7853020215</v>
+        <v>130.8177853020215</v>
       </c>
       <c r="BG110" t="n">
-        <v>575.069649383158</v>
+        <v>0.575069649383158</v>
       </c>
       <c r="BH110" t="n">
         <v>227.4816371240279</v>
@@ -21197,13 +21197,13 @@
         <v>1.718324936833187</v>
       </c>
       <c r="BE111" t="n">
-        <v>3066.512007482434</v>
+        <v>3.066512007482434</v>
       </c>
       <c r="BF111" t="n">
-        <v>130374.7394486637</v>
+        <v>130.3747394486637</v>
       </c>
       <c r="BG111" t="n">
-        <v>489.434786636057</v>
+        <v>0.4894347866360571</v>
       </c>
       <c r="BH111" t="n">
         <v>266.3781631557998</v>
@@ -21388,13 +21388,13 @@
         <v>0.7330294163502471</v>
       </c>
       <c r="BE112" t="n">
-        <v>3515.637037094179</v>
+        <v>3.515637037094179</v>
       </c>
       <c r="BF112" t="n">
-        <v>153421.6160214485</v>
+        <v>153.4216160214486</v>
       </c>
       <c r="BG112" t="n">
-        <v>227.5609519700245</v>
+        <v>0.2275609519700245</v>
       </c>
       <c r="BH112" t="n">
         <v>674.2000975705974</v>
@@ -21579,13 +21579,13 @@
         <v>0.3719852691735669</v>
       </c>
       <c r="BE113" t="n">
-        <v>2469.291967965981</v>
+        <v>2.469291967965981</v>
       </c>
       <c r="BF113" t="n">
-        <v>119195.3738709075</v>
+        <v>119.1953738709075</v>
       </c>
       <c r="BG113" t="n">
-        <v>95.91448322866695</v>
+        <v>0.09591448322866696</v>
       </c>
       <c r="BH113" t="n">
         <v>1242.725497323873</v>
@@ -21770,13 +21770,13 @@
         <v>1.116051620086352</v>
       </c>
       <c r="BE114" t="n">
-        <v>2429.99367207335</v>
+        <v>2.42999367207335</v>
       </c>
       <c r="BF114" t="n">
-        <v>135315.0056788815</v>
+        <v>135.3150056788816</v>
       </c>
       <c r="BG114" t="n">
-        <v>314.4638401563245</v>
+        <v>0.3144638401563246</v>
       </c>
       <c r="BH114" t="n">
         <v>430.3038645448536</v>
@@ -21961,13 +21961,13 @@
         <v>1.032273647779503</v>
       </c>
       <c r="BE115" t="n">
-        <v>3012.101624121943</v>
+        <v>3.012101624121943</v>
       </c>
       <c r="BF115" t="n">
-        <v>140221.9433572833</v>
+        <v>140.2219433572834</v>
       </c>
       <c r="BG115" t="n">
-        <v>297.0048736509277</v>
+        <v>0.2970048736509278</v>
       </c>
       <c r="BH115" t="n">
         <v>472.1200081116762</v>
@@ -22152,13 +22152,13 @@
         <v>0.9959949821321988</v>
       </c>
       <c r="BE116" t="n">
-        <v>4886.608187366623</v>
+        <v>4.886608187366623</v>
       </c>
       <c r="BF116" t="n">
-        <v>140650.5272762413</v>
+        <v>140.6505272762413</v>
       </c>
       <c r="BG116" t="n">
-        <v>291.1866620672897</v>
+        <v>0.2911866620672897</v>
       </c>
       <c r="BH116" t="n">
         <v>483.0253085003554</v>
@@ -22343,13 +22343,13 @@
         <v>1.294556897594681</v>
       </c>
       <c r="BE117" t="n">
-        <v>2753.295278959289</v>
+        <v>2.753295278959289</v>
       </c>
       <c r="BF117" t="n">
-        <v>110850.3111923048</v>
+        <v>110.8503111923048</v>
       </c>
       <c r="BG117" t="n">
-        <v>298.1906883143227</v>
+        <v>0.2981906883143227</v>
       </c>
       <c r="BH117" t="n">
         <v>371.7430340261248</v>
@@ -22534,13 +22534,13 @@
         <v>1.294556897594681</v>
       </c>
       <c r="BE118" t="n">
-        <v>2753.295278959289</v>
+        <v>2.753295278959289</v>
       </c>
       <c r="BF118" t="n">
-        <v>110850.3111923048</v>
+        <v>110.8503111923048</v>
       </c>
       <c r="BG118" t="n">
-        <v>298.1906883143227</v>
+        <v>0.2981906883143227</v>
       </c>
       <c r="BH118" t="n">
         <v>371.7430340261248</v>
@@ -22725,13 +22725,13 @@
         <v>0.7330305807834134</v>
       </c>
       <c r="BE119" t="n">
-        <v>3326.850351224271</v>
+        <v>3.32685035122427</v>
       </c>
       <c r="BF119" t="n">
-        <v>128510.5915976078</v>
+        <v>128.5105915976078</v>
       </c>
       <c r="BG119" t="n">
-        <v>190.9488702678472</v>
+        <v>0.1909488702678472</v>
       </c>
       <c r="BH119" t="n">
         <v>673.0104839968092</v>
@@ -22916,13 +22916,13 @@
         <v>1.190130963299714</v>
       </c>
       <c r="BE120" t="n">
-        <v>3652.366005865274</v>
+        <v>3.652366005865273</v>
       </c>
       <c r="BF120" t="n">
-        <v>173868.8221141171</v>
+        <v>173.8688221141171</v>
       </c>
       <c r="BG120" t="n">
-        <v>424.936021290441</v>
+        <v>0.424936021290441</v>
       </c>
       <c r="BH120" t="n">
         <v>409.1647057505604</v>
@@ -23107,13 +23107,13 @@
         <v>1.190130963299714</v>
       </c>
       <c r="BE121" t="n">
-        <v>3652.366005865274</v>
+        <v>3.652366005865273</v>
       </c>
       <c r="BF121" t="n">
-        <v>173868.8221141171</v>
+        <v>173.8688221141171</v>
       </c>
       <c r="BG121" t="n">
-        <v>424.936021290441</v>
+        <v>0.424936021290441</v>
       </c>
       <c r="BH121" t="n">
         <v>409.1647057505604</v>
@@ -23298,13 +23298,13 @@
         <v>0.70388853315343</v>
       </c>
       <c r="BE122" t="n">
-        <v>3309.760277186539</v>
+        <v>3.309760277186538</v>
       </c>
       <c r="BF122" t="n">
-        <v>126088.9866039253</v>
+        <v>126.0889866039252</v>
       </c>
       <c r="BG122" t="n">
-        <v>186.5608181721887</v>
+        <v>0.1865608181721887</v>
       </c>
       <c r="BH122" t="n">
         <v>675.8599573011616</v>
@@ -23489,13 +23489,13 @@
         <v>1.706487181309719</v>
       </c>
       <c r="BE123" t="n">
-        <v>3855.984342568878</v>
+        <v>3.855984342568878</v>
       </c>
       <c r="BF123" t="n">
-        <v>138235.7685802533</v>
+        <v>138.2357685802533</v>
       </c>
       <c r="BG123" t="n">
-        <v>488.5371436014495</v>
+        <v>0.4885371436014496</v>
       </c>
       <c r="BH123" t="n">
         <v>282.958563930661</v>
@@ -23680,13 +23680,13 @@
         <v>1.24432515516913</v>
       </c>
       <c r="BE124" t="n">
-        <v>3332.925651824539</v>
+        <v>3.332925651824539</v>
       </c>
       <c r="BF124" t="n">
-        <v>156266.9383954623</v>
+        <v>156.2669383954623</v>
       </c>
       <c r="BG124" t="n">
-        <v>399.0682368682052</v>
+        <v>0.3990682368682052</v>
       </c>
       <c r="BH124" t="n">
         <v>391.5794943286114</v>
@@ -23871,13 +23871,13 @@
         <v>1.528358225791803</v>
       </c>
       <c r="BE125" t="n">
-        <v>2307.284769426641</v>
+        <v>2.307284769426641</v>
       </c>
       <c r="BF125" t="n">
-        <v>118151.6372200387</v>
+        <v>118.1516372200387</v>
       </c>
       <c r="BG125" t="n">
-        <v>372.1584096024218</v>
+        <v>0.3721584096024217</v>
       </c>
       <c r="BH125" t="n">
         <v>317.4767361733422</v>
@@ -24062,13 +24062,13 @@
         <v>0.6059605665087811</v>
       </c>
       <c r="BE126" t="n">
-        <v>2966.946505276404</v>
+        <v>2.966946505276404</v>
       </c>
       <c r="BF126" t="n">
-        <v>132789.3671794441</v>
+        <v>132.7893671794441</v>
       </c>
       <c r="BG126" t="n">
-        <v>162.3552796451581</v>
+        <v>0.1623552796451581</v>
       </c>
       <c r="BH126" t="n">
         <v>817.8937418583928</v>
@@ -24253,13 +24253,13 @@
         <v>0.67413284412384</v>
       </c>
       <c r="BE127" t="n">
-        <v>3487.073324331464</v>
+        <v>3.487073324331464</v>
       </c>
       <c r="BF127" t="n">
-        <v>134202.5316348755</v>
+        <v>134.2025316348755</v>
       </c>
       <c r="BG127" t="n">
-        <v>186.3290222711894</v>
+        <v>0.1863290222711894</v>
       </c>
       <c r="BH127" t="n">
         <v>720.2449194390807</v>
@@ -24444,13 +24444,13 @@
         <v>1.445586054889317</v>
       </c>
       <c r="BE128" t="n">
-        <v>3859.533583523428</v>
+        <v>3.859533583523428</v>
       </c>
       <c r="BF128" t="n">
-        <v>146773.4804419995</v>
+        <v>146.7734804419995</v>
       </c>
       <c r="BG128" t="n">
-        <v>439.2005902239814</v>
+        <v>0.4392005902239814</v>
       </c>
       <c r="BH128" t="n">
         <v>334.1832495424213</v>
@@ -24635,13 +24635,13 @@
         <v>1.818650572788979</v>
       </c>
       <c r="BE129" t="n">
-        <v>3675.873944413487</v>
+        <v>3.675873944413487</v>
       </c>
       <c r="BF129" t="n">
-        <v>156929.0001240953</v>
+        <v>156.9290001240953</v>
       </c>
       <c r="BG129" t="n">
-        <v>584.7214351624981</v>
+        <v>0.5847214351624981</v>
       </c>
       <c r="BH129" t="n">
         <v>268.3824992331325</v>
@@ -24826,13 +24826,13 @@
         <v>1.236769225312605</v>
       </c>
       <c r="BE130" t="n">
-        <v>3771.495585441185</v>
+        <v>3.771495585441185</v>
       </c>
       <c r="BF130" t="n">
-        <v>161889.635632338</v>
+        <v>161.889635632338</v>
       </c>
       <c r="BG130" t="n">
-        <v>406.8493951011535</v>
+        <v>0.4068493951011535</v>
       </c>
       <c r="BH130" t="n">
         <v>397.9104739533605</v>
@@ -25017,13 +25017,13 @@
         <v>1.264200753020895</v>
       </c>
       <c r="BE131" t="n">
-        <v>2767.649227576971</v>
+        <v>2.767649227576972</v>
       </c>
       <c r="BF131" t="n">
-        <v>111162.0750906621</v>
+        <v>111.1620750906621</v>
       </c>
       <c r="BG131" t="n">
-        <v>337.2710106638011</v>
+        <v>0.3372710106638011</v>
       </c>
       <c r="BH131" t="n">
         <v>329.5927357405492</v>
@@ -25208,13 +25208,13 @@
         <v>0.6203181408041061</v>
       </c>
       <c r="BE132" t="n">
-        <v>2667.01832885668</v>
+        <v>2.667018328856681</v>
       </c>
       <c r="BF132" t="n">
-        <v>144407.1534170367</v>
+        <v>144.4071534170367</v>
       </c>
       <c r="BG132" t="n">
-        <v>193.2594943946435</v>
+        <v>0.1932594943946435</v>
       </c>
       <c r="BH132" t="n">
         <v>747.2189341557086</v>
@@ -25399,13 +25399,13 @@
         <v>0.6203181408041061</v>
       </c>
       <c r="BE133" t="n">
-        <v>2667.01832885668</v>
+        <v>2.667018328856681</v>
       </c>
       <c r="BF133" t="n">
-        <v>144407.1534170367</v>
+        <v>144.4071534170367</v>
       </c>
       <c r="BG133" t="n">
-        <v>193.2594943946435</v>
+        <v>0.1932594943946435</v>
       </c>
       <c r="BH133" t="n">
         <v>747.2189341557086</v>
@@ -25590,13 +25590,13 @@
         <v>1.549984801394928</v>
       </c>
       <c r="BE134" t="n">
-        <v>3626.928985621702</v>
+        <v>3.626928985621702</v>
       </c>
       <c r="BF134" t="n">
-        <v>125601.6617616408</v>
+        <v>125.6016617616408</v>
       </c>
       <c r="BG134" t="n">
-        <v>395.8015635726782</v>
+        <v>0.3958015635726783</v>
       </c>
       <c r="BH134" t="n">
         <v>317.3349307362639</v>
@@ -25781,13 +25781,13 @@
         <v>0.8285671225617766</v>
       </c>
       <c r="BE135" t="n">
-        <v>3422.023655820771</v>
+        <v>3.42202365582077</v>
       </c>
       <c r="BF135" t="n">
-        <v>153648.7572900207</v>
+        <v>153.6487572900207</v>
       </c>
       <c r="BG135" t="n">
-        <v>257.9721767789777</v>
+        <v>0.2579721767789777</v>
       </c>
       <c r="BH135" t="n">
         <v>595.6020498352506</v>
@@ -25972,13 +25972,13 @@
         <v>3.752305574824123</v>
       </c>
       <c r="BE136" t="n">
-        <v>2957.9939499805</v>
+        <v>2.9579939499805</v>
       </c>
       <c r="BF136" t="n">
-        <v>129957.0950195319</v>
+        <v>129.9570950195319</v>
       </c>
       <c r="BG136" t="n">
-        <v>984.908331811914</v>
+        <v>0.984908331811914</v>
       </c>
       <c r="BH136" t="n">
         <v>131.9484167429599</v>
@@ -26163,13 +26163,13 @@
         <v>2.003502733491316</v>
       </c>
       <c r="BE137" t="n">
-        <v>1947.483713072644</v>
+        <v>1.947483713072644</v>
       </c>
       <c r="BF137" t="n">
-        <v>122184.6360713435</v>
+        <v>122.1846360713435</v>
       </c>
       <c r="BG137" t="n">
-        <v>531.2872384618877</v>
+        <v>0.5312872384618876</v>
       </c>
       <c r="BH137" t="n">
         <v>229.9784885198377</v>
@@ -26354,13 +26354,13 @@
         <v>0.4976190619757426</v>
       </c>
       <c r="BE138" t="n">
-        <v>2038.052013688129</v>
+        <v>2.038052013688129</v>
       </c>
       <c r="BF138" t="n">
-        <v>115814.211862462</v>
+        <v>115.814211862462</v>
       </c>
       <c r="BG138" t="n">
-        <v>125.2576192118186</v>
+        <v>0.1252576192118186</v>
       </c>
       <c r="BH138" t="n">
         <v>924.6081203779931</v>
@@ -26545,13 +26545,13 @@
         <v>0.442454971215987</v>
       </c>
       <c r="BE139" t="n">
-        <v>2816.066621298269</v>
+        <v>2.816066621298269</v>
       </c>
       <c r="BF139" t="n">
-        <v>146355.3882512526</v>
+        <v>146.3553882512526</v>
       </c>
       <c r="BG139" t="n">
-        <v>132.8280183195209</v>
+        <v>0.1328280183195209</v>
       </c>
       <c r="BH139" t="n">
         <v>1101.841238790383</v>
@@ -26736,13 +26736,13 @@
         <v>1.170421599484877</v>
       </c>
       <c r="BE140" t="n">
-        <v>4155.314276894092</v>
+        <v>4.155314276894092</v>
       </c>
       <c r="BF140" t="n">
-        <v>144242.5670969987</v>
+        <v>144.2425670969987</v>
       </c>
       <c r="BG140" t="n">
-        <v>336.8499551025584</v>
+        <v>0.3368499551025584</v>
       </c>
       <c r="BH140" t="n">
         <v>428.210141969834</v>
@@ -26927,13 +26927,13 @@
         <v>1.034293220205778</v>
       </c>
       <c r="BE141" t="n">
-        <v>9247.567853121815</v>
+        <v>9.247567853121815</v>
       </c>
       <c r="BF141" t="n">
-        <v>155634.5654536335</v>
+        <v>155.6345654536335</v>
       </c>
       <c r="BG141" t="n">
-        <v>323.3923108510388</v>
+        <v>0.3233923108510388</v>
       </c>
       <c r="BH141" t="n">
         <v>481.2562334709375</v>
@@ -27118,13 +27118,13 @@
         <v>0.9413367540650814</v>
       </c>
       <c r="BE142" t="n">
-        <v>2494.199987467023</v>
+        <v>2.494199987467023</v>
       </c>
       <c r="BF142" t="n">
-        <v>121883.136199759</v>
+        <v>121.883136199759</v>
       </c>
       <c r="BG142" t="n">
-        <v>244.5600833511928</v>
+        <v>0.2445600833511928</v>
       </c>
       <c r="BH142" t="n">
         <v>498.3770635403839</v>
@@ -27309,13 +27309,13 @@
         <v>0.4332464644027982</v>
       </c>
       <c r="BE143" t="n">
-        <v>2769.312656787985</v>
+        <v>2.769312656787986</v>
       </c>
       <c r="BF143" t="n">
-        <v>134283.6821757779</v>
+        <v>134.2836821757778</v>
       </c>
       <c r="BG143" t="n">
-        <v>122.1407759333642</v>
+        <v>0.1221407759333641</v>
       </c>
       <c r="BH143" t="n">
         <v>1099.417300648544</v>
@@ -27500,13 +27500,13 @@
         <v>0.3301460673610775</v>
       </c>
       <c r="BE144" t="n">
-        <v>2808.967940938339</v>
+        <v>2.808967940938339</v>
       </c>
       <c r="BF144" t="n">
-        <v>147344.793628725</v>
+        <v>147.344793628725</v>
       </c>
       <c r="BG144" t="n">
-        <v>102.4514079588275</v>
+        <v>0.1024514079588275</v>
       </c>
       <c r="BH144" t="n">
         <v>1438.191983539542</v>
@@ -27691,13 +27691,13 @@
         <v>0.4090062180236554</v>
       </c>
       <c r="BE145" t="n">
-        <v>2748.330291734374</v>
+        <v>2.748330291734374</v>
       </c>
       <c r="BF145" t="n">
-        <v>137751.0746218444</v>
+        <v>137.7510746218445</v>
       </c>
       <c r="BG145" t="n">
-        <v>120.3087575004124</v>
+        <v>0.1203087575004124</v>
       </c>
       <c r="BH145" t="n">
         <v>1144.979613153866</v>
@@ -27882,13 +27882,13 @@
         <v>0.5453809105310884</v>
       </c>
       <c r="BE146" t="n">
-        <v>2749.420947265438</v>
+        <v>2.749420947265438</v>
       </c>
       <c r="BF146" t="n">
-        <v>142004.9960833589</v>
+        <v>142.0049960833589</v>
       </c>
       <c r="BG146" t="n">
-        <v>163.2658646144916</v>
+        <v>0.1632658646144916</v>
       </c>
       <c r="BH146" t="n">
         <v>869.777625706791</v>
@@ -28073,13 +28073,13 @@
         <v>0.421627376985528</v>
       </c>
       <c r="BE147" t="n">
-        <v>2978.536938054128</v>
+        <v>2.978536938054128</v>
       </c>
       <c r="BF147" t="n">
-        <v>121660.5225264648</v>
+        <v>121.6605225264648</v>
       </c>
       <c r="BG147" t="n">
-        <v>111.7265736201473</v>
+        <v>0.1117265736201473</v>
       </c>
       <c r="BH147" t="n">
         <v>1088.913036392679</v>
@@ -28264,13 +28264,13 @@
         <v>0.6299664353692545</v>
       </c>
       <c r="BE148" t="n">
-        <v>3389.107084357813</v>
+        <v>3.389107084357813</v>
       </c>
       <c r="BF148" t="n">
-        <v>126819.0950058426</v>
+        <v>126.8190950058426</v>
       </c>
       <c r="BG148" t="n">
-        <v>170.2599768628932</v>
+        <v>0.1702599768628932</v>
       </c>
       <c r="BH148" t="n">
         <v>744.855586982532</v>
@@ -28455,13 +28455,13 @@
         <v>0.3602235709573822</v>
       </c>
       <c r="BE149" t="n">
-        <v>2277.283663149553</v>
+        <v>2.277283663149553</v>
       </c>
       <c r="BF149" t="n">
-        <v>102445.7483107241</v>
+        <v>102.4457483107241</v>
       </c>
       <c r="BG149" t="n">
-        <v>78.90365227446225</v>
+        <v>0.07890365227446225</v>
       </c>
       <c r="BH149" t="n">
         <v>1298.365099176549</v>
@@ -28646,13 +28646,13 @@
         <v>0.3894930957229775</v>
       </c>
       <c r="BE150" t="n">
-        <v>2391.202896295107</v>
+        <v>2.391202896295107</v>
       </c>
       <c r="BF150" t="n">
-        <v>149040.7090683407</v>
+        <v>149.0407090683408</v>
       </c>
       <c r="BG150" t="n">
-        <v>123.1773494420704</v>
+        <v>0.1231773494420704</v>
       </c>
       <c r="BH150" t="n">
         <v>1209.968470205098</v>
@@ -28837,13 +28837,13 @@
         <v>0.4436594649764164</v>
       </c>
       <c r="BE151" t="n">
-        <v>1934.834464052721</v>
+        <v>1.934834464052721</v>
       </c>
       <c r="BF151" t="n">
-        <v>121974.0238789016</v>
+        <v>121.9740238789016</v>
       </c>
       <c r="BG151" t="n">
-        <v>116.5180938818814</v>
+        <v>0.1165180938818813</v>
       </c>
       <c r="BH151" t="n">
         <v>1046.82474468344</v>
@@ -29028,13 +29028,13 @@
         <v>0.324984654635016</v>
       </c>
       <c r="BE152" t="n">
-        <v>2545.160555801388</v>
+        <v>2.545160555801389</v>
       </c>
       <c r="BF152" t="n">
-        <v>141426.1151832663</v>
+        <v>141.4261151832662</v>
       </c>
       <c r="BG152" t="n">
-        <v>94.21860149463978</v>
+        <v>0.09421860149463979</v>
       </c>
       <c r="BH152" t="n">
         <v>1501.04239438655</v>
@@ -29219,13 +29219,13 @@
         <v>0.4191162035677621</v>
       </c>
       <c r="BE153" t="n">
-        <v>2076.55949623921</v>
+        <v>2.07655949623921</v>
       </c>
       <c r="BF153" t="n">
-        <v>128140.3293853907</v>
+        <v>128.1403293853907</v>
       </c>
       <c r="BG153" t="n">
-        <v>114.6905287036673</v>
+        <v>0.1146905287036673</v>
       </c>
       <c r="BH153" t="n">
         <v>1117.270369521745</v>
@@ -29410,13 +29410,13 @@
         <v>0.4538509821073275</v>
       </c>
       <c r="BE154" t="n">
-        <v>2742.522983349366</v>
+        <v>2.742522983349367</v>
       </c>
       <c r="BF154" t="n">
-        <v>129647.9432373974</v>
+        <v>129.6479432373974</v>
       </c>
       <c r="BG154" t="n">
-        <v>123.1926864069352</v>
+        <v>0.1231926864069352</v>
       </c>
       <c r="BH154" t="n">
         <v>1052.399675814674</v>
@@ -29601,13 +29601,13 @@
         <v>0.7535500201908957</v>
       </c>
       <c r="BE155" t="n">
-        <v>2806.657621010977</v>
+        <v>2.806657621010977</v>
       </c>
       <c r="BF155" t="n">
-        <v>130790.8358063607</v>
+        <v>130.7908358063607</v>
       </c>
       <c r="BG155" t="n">
-        <v>207.4923530142719</v>
+        <v>0.2074923530142719</v>
       </c>
       <c r="BH155" t="n">
         <v>630.3405108975969</v>
@@ -29792,13 +29792,13 @@
         <v>1.172287562238779</v>
       </c>
       <c r="BE156" t="n">
-        <v>4003.25613157189</v>
+        <v>4.00325613157189</v>
       </c>
       <c r="BF156" t="n">
-        <v>145721.965743142</v>
+        <v>145.721965743142</v>
       </c>
       <c r="BG156" t="n">
-        <v>354.4257993513203</v>
+        <v>0.3544257993513203</v>
       </c>
       <c r="BH156" t="n">
         <v>411.1494310229285</v>
@@ -29983,13 +29983,13 @@
         <v>0.4231620695175342</v>
       </c>
       <c r="BE157" t="n">
-        <v>2615.744888154333</v>
+        <v>2.615744888154333</v>
       </c>
       <c r="BF157" t="n">
-        <v>145456.8526641889</v>
+        <v>145.4568526641889</v>
       </c>
       <c r="BG157" t="n">
-        <v>131.3219254796132</v>
+        <v>0.1313219254796132</v>
       </c>
       <c r="BH157" t="n">
         <v>1107.635698554923</v>
@@ -30174,13 +30174,13 @@
         <v>1.447062020901036</v>
       </c>
       <c r="BE158" t="n">
-        <v>3110.278188373693</v>
+        <v>3.110278188373694</v>
       </c>
       <c r="BF158" t="n">
-        <v>134120.3056081442</v>
+        <v>134.1203056081442</v>
       </c>
       <c r="BG158" t="n">
-        <v>392.9618776125638</v>
+        <v>0.3929618776125638</v>
       </c>
       <c r="BH158" t="n">
         <v>341.3061501614122</v>
@@ -30365,13 +30365,13 @@
         <v>1.447062020901036</v>
       </c>
       <c r="BE159" t="n">
-        <v>3110.278188373693</v>
+        <v>3.110278188373694</v>
       </c>
       <c r="BF159" t="n">
-        <v>134120.3056081442</v>
+        <v>134.1203056081442</v>
       </c>
       <c r="BG159" t="n">
-        <v>392.9618776125638</v>
+        <v>0.3929618776125638</v>
       </c>
       <c r="BH159" t="n">
         <v>341.3061501614122</v>
@@ -30556,13 +30556,13 @@
         <v>0.8361223093456559</v>
       </c>
       <c r="BE160" t="n">
-        <v>3178.492318378893</v>
+        <v>3.178492318378893</v>
       </c>
       <c r="BF160" t="n">
-        <v>129178.5542206582</v>
+        <v>129.1785542206582</v>
       </c>
       <c r="BG160" t="n">
-        <v>220.4215039302889</v>
+        <v>0.2204215039302889</v>
       </c>
       <c r="BH160" t="n">
         <v>586.052412842227</v>
@@ -30743,13 +30743,13 @@
         <v>0.8117757739071965</v>
       </c>
       <c r="BE161" t="n">
-        <v>3100.384113890322</v>
+        <v>3.100384113890322</v>
       </c>
       <c r="BF161" t="n">
-        <v>123593.3624024007</v>
+        <v>123.5933624024007</v>
       </c>
       <c r="BG161" t="n">
-        <v>203.8814339992062</v>
+        <v>0.2038814339992062</v>
       </c>
       <c r="BH161" t="n">
         <v>606.2021439523618</v>
@@ -30930,13 +30930,13 @@
         <v>0.5765357094251896</v>
       </c>
       <c r="BE162" t="n">
-        <v>2368.124449995078</v>
+        <v>2.368124449995078</v>
       </c>
       <c r="BF162" t="n">
-        <v>119565.5202168899</v>
+        <v>119.5655202168899</v>
       </c>
       <c r="BG162" t="n">
-        <v>147.8461330180165</v>
+        <v>0.1478461330180165</v>
       </c>
       <c r="BH162" t="n">
         <v>808.7159114423353</v>
@@ -31121,13 +31121,13 @@
         <v>1.046102945540786</v>
       </c>
       <c r="BE163" t="n">
-        <v>2494.800680792413</v>
+        <v>2.494800680792413</v>
       </c>
       <c r="BF163" t="n">
-        <v>132442.1082301923</v>
+        <v>132.4421082301923</v>
       </c>
       <c r="BG163" t="n">
-        <v>298.7919429514647</v>
+        <v>0.2987919429514647</v>
       </c>
       <c r="BH163" t="n">
         <v>443.2586331543284</v>
@@ -31312,13 +31312,13 @@
         <v>0.4695082726749009</v>
       </c>
       <c r="BE164" t="n">
-        <v>2936.607957022901</v>
+        <v>2.936607957022901</v>
       </c>
       <c r="BF164" t="n">
-        <v>132735.0949602475</v>
+        <v>132.7350949602475</v>
       </c>
       <c r="BG164" t="n">
-        <v>131.2849522275966</v>
+        <v>0.1312849522275966</v>
       </c>
       <c r="BH164" t="n">
         <v>1011.045765017585</v>
@@ -31503,13 +31503,13 @@
         <v>1.240984290338432</v>
       </c>
       <c r="BE165" t="n">
-        <v>2706.029629235518</v>
+        <v>2.706029629235518</v>
       </c>
       <c r="BF165" t="n">
-        <v>130340.932329563</v>
+        <v>130.340932329563</v>
       </c>
       <c r="BG165" t="n">
-        <v>344.2185085599922</v>
+        <v>0.3442185085599922</v>
       </c>
       <c r="BH165" t="n">
         <v>378.6575360948277</v>
@@ -31694,13 +31694,13 @@
         <v>1.507902613849702</v>
       </c>
       <c r="BE166" t="n">
-        <v>4035.463229976435</v>
+        <v>4.035463229976434</v>
       </c>
       <c r="BF166" t="n">
-        <v>171968.2607603812</v>
+        <v>171.9682607603812</v>
       </c>
       <c r="BG166" t="n">
-        <v>515.1927582473124</v>
+        <v>0.5151927582473125</v>
       </c>
       <c r="BH166" t="n">
         <v>333.794017884525</v>
@@ -31885,13 +31885,13 @@
         <v>1.110726579043297</v>
       </c>
       <c r="BE167" t="n">
-        <v>2808.389842928612</v>
+        <v>2.808389842928612</v>
       </c>
       <c r="BF167" t="n">
-        <v>119272.127037589</v>
+        <v>119.272127037589</v>
       </c>
       <c r="BG167" t="n">
-        <v>275.5068721173976</v>
+        <v>0.2755068721173976</v>
       </c>
       <c r="BH167" t="n">
         <v>432.9188819172734</v>
@@ -32076,13 +32076,13 @@
         <v>0.7129588548014306</v>
       </c>
       <c r="BE168" t="n">
-        <v>3925.394607703596</v>
+        <v>3.925394607703596</v>
       </c>
       <c r="BF168" t="n">
-        <v>150762.6863250885</v>
+        <v>150.7626863250885</v>
       </c>
       <c r="BG168" t="n">
-        <v>216.3390994957416</v>
+        <v>0.2163390994957415</v>
       </c>
       <c r="BH168" t="n">
         <v>696.8813620676838</v>
@@ -32267,13 +32267,13 @@
         <v>0.7458032085161251</v>
       </c>
       <c r="BE169" t="n">
-        <v>3010.46998120762</v>
+        <v>3.01046998120762</v>
       </c>
       <c r="BF169" t="n">
-        <v>124271.211508699</v>
+        <v>124.271211508699</v>
       </c>
       <c r="BG169" t="n">
-        <v>197.3079548330844</v>
+        <v>0.1973079548330844</v>
       </c>
       <c r="BH169" t="n">
         <v>629.8337622212349</v>
@@ -32458,13 +32458,13 @@
         <v>1.060681081061475</v>
       </c>
       <c r="BE170" t="n">
-        <v>3857.753490063654</v>
+        <v>3.857753490063654</v>
       </c>
       <c r="BF170" t="n">
-        <v>156769.4106261306</v>
+        <v>156.7694106261306</v>
       </c>
       <c r="BG170" t="n">
-        <v>333.7167716726452</v>
+        <v>0.3337167716726452</v>
       </c>
       <c r="BH170" t="n">
         <v>469.7678508645989</v>
@@ -32649,13 +32649,13 @@
         <v>0.876007634737751</v>
       </c>
       <c r="BE171" t="n">
-        <v>3060.13376015371</v>
+        <v>3.06013376015371</v>
       </c>
       <c r="BF171" t="n">
-        <v>116550.839363781</v>
+        <v>116.550839363781</v>
       </c>
       <c r="BG171" t="n">
-        <v>210.4132050197028</v>
+        <v>0.2104132050197028</v>
       </c>
       <c r="BH171" t="n">
         <v>553.914091812191</v>
@@ -32840,13 +32840,13 @@
         <v>0.7321314863248521</v>
       </c>
       <c r="BE172" t="n">
-        <v>3580.328574778584</v>
+        <v>3.580328574778584</v>
       </c>
       <c r="BF172" t="n">
-        <v>155139.5166682314</v>
+        <v>155.1395166682314</v>
       </c>
       <c r="BG172" t="n">
-        <v>227.9105775244651</v>
+        <v>0.2279105775244651</v>
       </c>
       <c r="BH172" t="n">
         <v>680.7034511225257</v>
@@ -33031,13 +33031,13 @@
         <v>0.7135182431806696</v>
       </c>
       <c r="BE173" t="n">
-        <v>2714.433523098972</v>
+        <v>2.714433523098972</v>
       </c>
       <c r="BF173" t="n">
-        <v>123772.2705281614</v>
+        <v>123.7722705281614</v>
       </c>
       <c r="BG173" t="n">
-        <v>182.5892575668475</v>
+        <v>0.1825892575668475</v>
       </c>
       <c r="BH173" t="n">
         <v>677.8726863646251</v>
@@ -33222,13 +33222,13 @@
         <v>0.4657407982928221</v>
       </c>
       <c r="BE174" t="n">
-        <v>2969.412381357694</v>
+        <v>2.969412381357694</v>
       </c>
       <c r="BF174" t="n">
-        <v>136856.1441562886</v>
+        <v>136.8561441562886</v>
       </c>
       <c r="BG174" t="n">
-        <v>135.0134270421117</v>
+        <v>0.1350134270421117</v>
       </c>
       <c r="BH174" t="n">
         <v>1013.648398937405</v>
@@ -33413,13 +33413,13 @@
         <v>1.076097980645826</v>
       </c>
       <c r="BE175" t="n">
-        <v>3590.220428377389</v>
+        <v>3.590220428377389</v>
       </c>
       <c r="BF175" t="n">
-        <v>112022.7161869101</v>
+        <v>112.0227161869101</v>
       </c>
       <c r="BG175" t="n">
-        <v>247.3438134994981</v>
+        <v>0.2473438134994981</v>
       </c>
       <c r="BH175" t="n">
         <v>452.9028424118535</v>
@@ -33604,13 +33604,13 @@
         <v>0.7889988860287893</v>
       </c>
       <c r="BE176" t="n">
-        <v>3145.971770441211</v>
+        <v>3.145971770441211</v>
       </c>
       <c r="BF176" t="n">
-        <v>117900.075239499</v>
+        <v>117.900075239499</v>
       </c>
       <c r="BG176" t="n">
-        <v>189.2709314371093</v>
+        <v>0.1892709314371092</v>
       </c>
       <c r="BH176" t="n">
         <v>622.9169706319891</v>
@@ -33795,13 +33795,13 @@
         <v>0.8998972351497689</v>
       </c>
       <c r="BE177" t="n">
-        <v>2988.045897731698</v>
+        <v>2.988045897731697</v>
       </c>
       <c r="BF177" t="n">
-        <v>137153.0243619897</v>
+        <v>137.1530243619897</v>
       </c>
       <c r="BG177" t="n">
-        <v>250.1943599445277</v>
+        <v>0.2501943599445277</v>
       </c>
       <c r="BH177" t="n">
         <v>548.1859159111293</v>
@@ -33986,13 +33986,13 @@
         <v>0.760049464742248</v>
       </c>
       <c r="BE178" t="n">
-        <v>2795.080671498331</v>
+        <v>2.795080671498331</v>
       </c>
       <c r="BF178" t="n">
-        <v>132491.1744332169</v>
+        <v>132.4911744332169</v>
       </c>
       <c r="BG178" t="n">
-        <v>221.1978616315913</v>
+        <v>0.2211978616315912</v>
       </c>
       <c r="BH178" t="n">
         <v>598.971316702343</v>
@@ -34177,13 +34177,13 @@
         <v>0.8704905427894011</v>
       </c>
       <c r="BE179" t="n">
-        <v>2991.504895299842</v>
+        <v>2.991504895299842</v>
       </c>
       <c r="BF179" t="n">
-        <v>133846.1268133776</v>
+        <v>133.8461268133776</v>
       </c>
       <c r="BG179" t="n">
-        <v>246.3050873924967</v>
+        <v>0.2463050873924967</v>
       </c>
       <c r="BH179" t="n">
         <v>543.4160058581681</v>
@@ -34368,13 +34368,13 @@
         <v>0.7904204876191047</v>
       </c>
       <c r="BE180" t="n">
-        <v>2715.490388769533</v>
+        <v>2.715490388769533</v>
       </c>
       <c r="BF180" t="n">
-        <v>119574.7805559971</v>
+        <v>119.5747805559971</v>
       </c>
       <c r="BG180" t="n">
-        <v>204.5078913327457</v>
+        <v>0.2045078913327457</v>
       </c>
       <c r="BH180" t="n">
         <v>584.6951908640156</v>
@@ -34559,13 +34559,13 @@
         <v>0.4290615053355752</v>
       </c>
       <c r="BE181" t="n">
-        <v>2886.034344314457</v>
+        <v>2.886034344314457</v>
       </c>
       <c r="BF181" t="n">
-        <v>156425.1632215068</v>
+        <v>156.4251632215068</v>
       </c>
       <c r="BG181" t="n">
-        <v>142.1757845401308</v>
+        <v>0.1421757845401308</v>
       </c>
       <c r="BH181" t="n">
         <v>1100.223668379716</v>
@@ -34750,13 +34750,13 @@
         <v>0.8868190945788528</v>
       </c>
       <c r="BE182" t="n">
-        <v>3227.764288178313</v>
+        <v>3.227764288178313</v>
       </c>
       <c r="BF182" t="n">
-        <v>127135.1919261465</v>
+        <v>127.1351919261465</v>
       </c>
       <c r="BG182" t="n">
-        <v>225.7504469348979</v>
+        <v>0.2257504469348978</v>
       </c>
       <c r="BH182" t="n">
         <v>563.1669556021295</v>
@@ -34941,13 +34941,13 @@
         <v>0.579333851742069</v>
       </c>
       <c r="BE183" t="n">
-        <v>2924.394554936031</v>
+        <v>2.924394554936031</v>
       </c>
       <c r="BF183" t="n">
-        <v>125114.0993119449</v>
+        <v>125.1140993119449</v>
       </c>
       <c r="BG183" t="n">
-        <v>157.6035535331282</v>
+        <v>0.1576035535331282</v>
       </c>
       <c r="BH183" t="n">
         <v>793.8532888831468</v>
